--- a/Resources/Admin/Crosswalks and Schemas.xlsx
+++ b/Resources/Admin/Crosswalks and Schemas.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SHDTJB\Documents\LocalSave\Code\R\GitHub\WA-DOH-CHS-Death-Files-ETL\Resources\Admin\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1C29C4D-539E-44C0-8834-F9B729F1CAA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DA9971D-67F4-49C8-965B-6ED0067B6BFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20520" yWindow="-16365" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="3" r:id="rId1"/>
@@ -21,7 +21,7 @@
     <sheet name="harmonized_data_schema" sheetId="7" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">harmonized_data_schema!$A$1:$G$295</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">harmonized_data_schema!$A$1:$G$372</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">recode_variables_statistical!$A$1:$H$432</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5391" uniqueCount="673">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5692" uniqueCount="731">
   <si>
     <t>to_name</t>
   </si>
@@ -3042,12 +3042,186 @@
   <si>
     <t>Enforce desired data types</t>
   </si>
+  <si>
+    <t>race_code</t>
+  </si>
+  <si>
+    <t>race_asian</t>
+  </si>
+  <si>
+    <t>race_nhpi</t>
+  </si>
+  <si>
+    <t>age_6g</t>
+  </si>
+  <si>
+    <t>15-24</t>
+  </si>
+  <si>
+    <t>25-44</t>
+  </si>
+  <si>
+    <t>45-64</t>
+  </si>
+  <si>
+    <t>1-14</t>
+  </si>
+  <si>
+    <t>65+</t>
+  </si>
+  <si>
+    <t>age_11g</t>
+  </si>
+  <si>
+    <t>1-4</t>
+  </si>
+  <si>
+    <t>5-14</t>
+  </si>
+  <si>
+    <t>25-34</t>
+  </si>
+  <si>
+    <t>35-44</t>
+  </si>
+  <si>
+    <t>45-54</t>
+  </si>
+  <si>
+    <t>55-64</t>
+  </si>
+  <si>
+    <t>65-74</t>
+  </si>
+  <si>
+    <t>75-84</t>
+  </si>
+  <si>
+    <t>85+</t>
+  </si>
+  <si>
+    <t>age_20g</t>
+  </si>
+  <si>
+    <t>5-9</t>
+  </si>
+  <si>
+    <t>10-14</t>
+  </si>
+  <si>
+    <t>15-17</t>
+  </si>
+  <si>
+    <t>18-19</t>
+  </si>
+  <si>
+    <t>20-24</t>
+  </si>
+  <si>
+    <t>25-29</t>
+  </si>
+  <si>
+    <t>30-34</t>
+  </si>
+  <si>
+    <t>35-39</t>
+  </si>
+  <si>
+    <t>40-44</t>
+  </si>
+  <si>
+    <t>45-49</t>
+  </si>
+  <si>
+    <t>50-54</t>
+  </si>
+  <si>
+    <t>55-59</t>
+  </si>
+  <si>
+    <t>60-64</t>
+  </si>
+  <si>
+    <t>65-69</t>
+  </si>
+  <si>
+    <t>70-74</t>
+  </si>
+  <si>
+    <t>75-79</t>
+  </si>
+  <si>
+    <t>80-84</t>
+  </si>
+  <si>
+    <t>age_5yr</t>
+  </si>
+  <si>
+    <t>0-4</t>
+  </si>
+  <si>
+    <t>15-19</t>
+  </si>
+  <si>
+    <t>hispanic</t>
+  </si>
+  <si>
+    <t>race_ethnicity2</t>
+  </si>
+  <si>
+    <t>Not Hispanic</t>
+  </si>
+  <si>
+    <t>race6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">American Indian/Alaska Native Only </t>
+  </si>
+  <si>
+    <t>Asian Only</t>
+  </si>
+  <si>
+    <t>Black Only</t>
+  </si>
+  <si>
+    <t>Multi Race</t>
+  </si>
+  <si>
+    <t>Native Hawaiian and Pacific Islander Only</t>
+  </si>
+  <si>
+    <t>race_ethnicity7</t>
+  </si>
+  <si>
+    <t>American Indian/Alaska Native Only-NH</t>
+  </si>
+  <si>
+    <t>Asian Only-NH</t>
+  </si>
+  <si>
+    <t>Black Only-NH</t>
+  </si>
+  <si>
+    <t>Hispanic as Race</t>
+  </si>
+  <si>
+    <t>Multi-Race-NH</t>
+  </si>
+  <si>
+    <t>Native Hawaiian and Pacific Islander Only-NH</t>
+  </si>
+  <si>
+    <t>White Only-NH</t>
+  </si>
+  <si>
+    <t>White Only</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3073,6 +3247,12 @@
       <i/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -3152,7 +3332,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3261,6 +3441,22 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -20088,14 +20284,14 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51D60DD1-DC0B-4658-A996-7DC0B41964ED}">
-  <dimension ref="A1:H295"/>
+  <dimension ref="A1:H372"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30.140625" style="12" customWidth="1"/>
     <col min="2" max="2" width="22.5703125" style="12" customWidth="1"/>
     <col min="3" max="3" width="18.42578125" style="24" customWidth="1"/>
-    <col min="4" max="4" width="18" style="12" customWidth="1"/>
-    <col min="5" max="5" width="72.5703125" style="12" customWidth="1"/>
+    <col min="4" max="4" width="18" style="40" customWidth="1"/>
+    <col min="5" max="5" width="68" style="12" customWidth="1"/>
     <col min="6" max="6" width="18.42578125" style="15" customWidth="1"/>
     <col min="7" max="7" width="43" style="9" customWidth="1"/>
   </cols>
@@ -20110,7 +20306,7 @@
       <c r="C1" s="13" t="s">
         <v>609</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="D1" s="38" t="s">
         <v>611</v>
       </c>
       <c r="E1" s="11" t="s">
@@ -20131,1520 +20327,1667 @@
         <v>521</v>
       </c>
       <c r="C2" s="23"/>
-      <c r="D2" s="17"/>
+      <c r="D2" s="39"/>
       <c r="E2" s="17"/>
       <c r="F2" s="20"/>
       <c r="G2" s="18"/>
     </row>
     <row r="3" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="17" t="s">
-        <v>6</v>
+        <v>676</v>
       </c>
       <c r="B3" s="17" t="s">
         <v>522</v>
       </c>
       <c r="C3" s="23" t="b">
-        <v>0</v>
-      </c>
-      <c r="D3" s="17">
         <v>1</v>
       </c>
-      <c r="E3" s="17" t="s">
-        <v>401</v>
-      </c>
-      <c r="F3" s="20"/>
+      <c r="D3" s="39">
+        <v>0</v>
+      </c>
+      <c r="E3" s="39" t="s">
+        <v>398</v>
+      </c>
+      <c r="F3" s="20">
+        <v>1</v>
+      </c>
       <c r="G3" s="18"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
-        <v>6</v>
+        <v>676</v>
       </c>
       <c r="B4" s="12" t="s">
         <v>522</v>
       </c>
       <c r="C4" s="24" t="b">
-        <v>0</v>
-      </c>
-      <c r="D4" s="12">
+        <v>1</v>
+      </c>
+      <c r="D4" s="40" t="s">
+        <v>680</v>
+      </c>
+      <c r="E4" s="40" t="s">
+        <v>680</v>
+      </c>
+      <c r="F4" s="15">
         <v>2</v>
-      </c>
-      <c r="E4" s="12" t="s">
-        <v>474</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
-        <v>6</v>
+        <v>676</v>
       </c>
       <c r="B5" s="12" t="s">
         <v>522</v>
       </c>
       <c r="C5" s="24" t="b">
-        <v>0</v>
-      </c>
-      <c r="D5" s="12">
+        <v>1</v>
+      </c>
+      <c r="D5" s="40" t="s">
+        <v>677</v>
+      </c>
+      <c r="E5" s="40" t="s">
+        <v>677</v>
+      </c>
+      <c r="F5" s="15">
         <v>3</v>
-      </c>
-      <c r="E5" s="12" t="s">
-        <v>475</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="12" t="s">
-        <v>6</v>
+        <v>676</v>
       </c>
       <c r="B6" s="12" t="s">
         <v>522</v>
       </c>
       <c r="C6" s="24" t="b">
-        <v>0</v>
-      </c>
-      <c r="D6" s="12">
+        <v>1</v>
+      </c>
+      <c r="D6" s="40" t="s">
+        <v>678</v>
+      </c>
+      <c r="E6" s="40" t="s">
+        <v>678</v>
+      </c>
+      <c r="F6" s="15">
         <v>4</v>
-      </c>
-      <c r="E6" s="12" t="s">
-        <v>476</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
-        <v>6</v>
+        <v>676</v>
       </c>
       <c r="B7" s="12" t="s">
         <v>522</v>
       </c>
       <c r="C7" s="24" t="b">
-        <v>0</v>
-      </c>
-      <c r="D7" s="12">
+        <v>1</v>
+      </c>
+      <c r="D7" s="40" t="s">
+        <v>679</v>
+      </c>
+      <c r="E7" s="40" t="s">
+        <v>679</v>
+      </c>
+      <c r="F7" s="15">
         <v>5</v>
-      </c>
-      <c r="E7" s="12" t="s">
-        <v>477</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
+        <v>676</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="C8" s="24" t="b">
+        <v>1</v>
+      </c>
+      <c r="D8" s="40" t="s">
+        <v>681</v>
+      </c>
+      <c r="E8" s="40" t="s">
+        <v>681</v>
+      </c>
+      <c r="F8" s="15">
         <v>6</v>
-      </c>
-      <c r="B8" s="12" t="s">
-        <v>522</v>
-      </c>
-      <c r="C8" s="24" t="b">
-        <v>0</v>
-      </c>
-      <c r="D8" s="12">
-        <v>9</v>
-      </c>
-      <c r="E8" s="12" t="s">
-        <v>404</v>
       </c>
     </row>
     <row r="9" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
-        <v>7</v>
+        <v>682</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>521</v>
-      </c>
-      <c r="C9" s="23"/>
-      <c r="D9" s="17"/>
-      <c r="E9" s="17"/>
-      <c r="F9" s="20"/>
+        <v>522</v>
+      </c>
+      <c r="C9" s="23" t="b">
+        <v>1</v>
+      </c>
+      <c r="D9" s="39" t="s">
+        <v>398</v>
+      </c>
+      <c r="E9" s="39" t="s">
+        <v>398</v>
+      </c>
+      <c r="F9" s="20">
+        <v>1</v>
+      </c>
       <c r="G9" s="18"/>
     </row>
-    <row r="10" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="17" t="s">
-        <v>523</v>
-      </c>
-      <c r="B10" s="17" t="s">
-        <v>524</v>
-      </c>
-      <c r="C10" s="23"/>
-      <c r="D10" s="17"/>
-      <c r="E10" s="17"/>
-      <c r="F10" s="20"/>
-      <c r="G10" s="18"/>
-    </row>
-    <row r="11" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="B11" s="17" t="s">
-        <v>522</v>
-      </c>
-      <c r="C11" s="23" t="b">
-        <v>0</v>
-      </c>
-      <c r="D11" s="19" t="s">
-        <v>407</v>
-      </c>
-      <c r="E11" s="17" t="s">
-        <v>406</v>
-      </c>
-      <c r="F11" s="20"/>
-      <c r="G11" s="18"/>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="12" t="s">
+        <v>682</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="C10" s="24" t="b">
+        <v>1</v>
+      </c>
+      <c r="D10" s="40" t="s">
+        <v>683</v>
+      </c>
+      <c r="E10" s="40" t="s">
+        <v>683</v>
+      </c>
+      <c r="F10" s="15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="12" t="s">
+        <v>682</v>
+      </c>
+      <c r="B11" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="C11" s="24" t="b">
+        <v>1</v>
+      </c>
+      <c r="D11" s="40" t="s">
+        <v>684</v>
+      </c>
+      <c r="E11" s="40" t="s">
+        <v>684</v>
+      </c>
+      <c r="F11" s="15">
+        <v>3</v>
+      </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="12" t="s">
-        <v>9</v>
+        <v>682</v>
       </c>
       <c r="B12" s="12" t="s">
         <v>522</v>
       </c>
       <c r="C12" s="24" t="b">
-        <v>0</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>410</v>
-      </c>
-      <c r="E12" s="12" t="s">
-        <v>409</v>
+        <v>1</v>
+      </c>
+      <c r="D12" s="40" t="s">
+        <v>677</v>
+      </c>
+      <c r="E12" s="40" t="s">
+        <v>677</v>
+      </c>
+      <c r="F12" s="15">
+        <v>4</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
-        <v>9</v>
+        <v>682</v>
       </c>
       <c r="B13" s="12" t="s">
         <v>522</v>
       </c>
       <c r="C13" s="24" t="b">
-        <v>0</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>412</v>
-      </c>
-      <c r="E13" s="12" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="B14" s="17" t="s">
-        <v>522</v>
-      </c>
-      <c r="C14" s="23" t="b">
-        <v>0</v>
-      </c>
-      <c r="D14" s="19" t="s">
-        <v>407</v>
-      </c>
-      <c r="E14" s="17" t="s">
-        <v>406</v>
-      </c>
-      <c r="F14" s="20"/>
-      <c r="G14" s="18"/>
+        <v>1</v>
+      </c>
+      <c r="D13" s="40" t="s">
+        <v>685</v>
+      </c>
+      <c r="E13" s="40" t="s">
+        <v>685</v>
+      </c>
+      <c r="F13" s="15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="12" t="s">
+        <v>682</v>
+      </c>
+      <c r="B14" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="C14" s="24" t="b">
+        <v>1</v>
+      </c>
+      <c r="D14" s="40" t="s">
+        <v>686</v>
+      </c>
+      <c r="E14" s="40" t="s">
+        <v>686</v>
+      </c>
+      <c r="F14" s="15">
+        <v>6</v>
+      </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="12" t="s">
-        <v>10</v>
+        <v>682</v>
       </c>
       <c r="B15" s="12" t="s">
         <v>522</v>
       </c>
       <c r="C15" s="24" t="b">
-        <v>0</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>410</v>
-      </c>
-      <c r="E15" s="12" t="s">
-        <v>409</v>
+        <v>1</v>
+      </c>
+      <c r="D15" s="40" t="s">
+        <v>687</v>
+      </c>
+      <c r="E15" s="40" t="s">
+        <v>687</v>
+      </c>
+      <c r="F15" s="15">
+        <v>7</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="12" t="s">
+        <v>682</v>
+      </c>
+      <c r="B16" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="C16" s="24" t="b">
+        <v>1</v>
+      </c>
+      <c r="D16" s="40" t="s">
+        <v>688</v>
+      </c>
+      <c r="E16" s="40" t="s">
+        <v>688</v>
+      </c>
+      <c r="F16" s="15">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="12" t="s">
+        <v>682</v>
+      </c>
+      <c r="B17" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="C17" s="24" t="b">
+        <v>1</v>
+      </c>
+      <c r="D17" s="40" t="s">
+        <v>689</v>
+      </c>
+      <c r="E17" s="40" t="s">
+        <v>689</v>
+      </c>
+      <c r="F17" s="15">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="12" t="s">
+        <v>682</v>
+      </c>
+      <c r="B18" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="C18" s="24" t="b">
+        <v>1</v>
+      </c>
+      <c r="D18" s="40" t="s">
+        <v>690</v>
+      </c>
+      <c r="E18" s="40" t="s">
+        <v>690</v>
+      </c>
+      <c r="F18" s="15">
         <v>10</v>
       </c>
-      <c r="B16" s="12" t="s">
-        <v>522</v>
-      </c>
-      <c r="C16" s="24" t="b">
-        <v>0</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>412</v>
-      </c>
-      <c r="E16" s="12" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="17" t="s">
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="12" t="s">
+        <v>682</v>
+      </c>
+      <c r="B19" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="C19" s="24" t="b">
+        <v>1</v>
+      </c>
+      <c r="D19" s="40" t="s">
+        <v>691</v>
+      </c>
+      <c r="E19" s="40" t="s">
+        <v>691</v>
+      </c>
+      <c r="F19" s="15">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="17" t="s">
+        <v>692</v>
+      </c>
+      <c r="B20" s="17" t="s">
+        <v>522</v>
+      </c>
+      <c r="C20" s="23" t="b">
+        <v>1</v>
+      </c>
+      <c r="D20" s="39" t="s">
+        <v>398</v>
+      </c>
+      <c r="E20" s="39" t="s">
+        <v>398</v>
+      </c>
+      <c r="F20" s="20">
+        <v>1</v>
+      </c>
+      <c r="G20" s="18"/>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="12" t="s">
+        <v>692</v>
+      </c>
+      <c r="B21" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="C21" s="24" t="b">
+        <v>1</v>
+      </c>
+      <c r="D21" s="40" t="s">
+        <v>683</v>
+      </c>
+      <c r="E21" s="40" t="s">
+        <v>683</v>
+      </c>
+      <c r="F21" s="15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" s="12" t="s">
+        <v>692</v>
+      </c>
+      <c r="B22" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="C22" s="24" t="b">
+        <v>1</v>
+      </c>
+      <c r="D22" s="40" t="s">
+        <v>693</v>
+      </c>
+      <c r="E22" s="40" t="s">
+        <v>693</v>
+      </c>
+      <c r="F22" s="15">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="12" t="s">
+        <v>692</v>
+      </c>
+      <c r="B23" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="C23" s="24" t="b">
+        <v>1</v>
+      </c>
+      <c r="D23" s="40" t="s">
+        <v>694</v>
+      </c>
+      <c r="E23" s="40" t="s">
+        <v>694</v>
+      </c>
+      <c r="F23" s="15">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="12" t="s">
+        <v>692</v>
+      </c>
+      <c r="B24" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="C24" s="24" t="b">
+        <v>1</v>
+      </c>
+      <c r="D24" s="40" t="s">
+        <v>695</v>
+      </c>
+      <c r="E24" s="40" t="s">
+        <v>695</v>
+      </c>
+      <c r="F24" s="15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="12" t="s">
+        <v>692</v>
+      </c>
+      <c r="B25" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="C25" s="24" t="b">
+        <v>1</v>
+      </c>
+      <c r="D25" s="40" t="s">
+        <v>696</v>
+      </c>
+      <c r="E25" s="40" t="s">
+        <v>696</v>
+      </c>
+      <c r="F25" s="15">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="12" t="s">
+        <v>692</v>
+      </c>
+      <c r="B26" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="C26" s="24" t="b">
+        <v>1</v>
+      </c>
+      <c r="D26" s="40" t="s">
+        <v>697</v>
+      </c>
+      <c r="E26" s="40" t="s">
+        <v>697</v>
+      </c>
+      <c r="F26" s="15">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" s="12" t="s">
+        <v>692</v>
+      </c>
+      <c r="B27" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="C27" s="24" t="b">
+        <v>1</v>
+      </c>
+      <c r="D27" s="40" t="s">
+        <v>698</v>
+      </c>
+      <c r="E27" s="40" t="s">
+        <v>698</v>
+      </c>
+      <c r="F27" s="15">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" s="12" t="s">
+        <v>692</v>
+      </c>
+      <c r="B28" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="C28" s="24" t="b">
+        <v>1</v>
+      </c>
+      <c r="D28" s="40" t="s">
+        <v>699</v>
+      </c>
+      <c r="E28" s="40" t="s">
+        <v>699</v>
+      </c>
+      <c r="F28" s="15">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" s="12" t="s">
+        <v>692</v>
+      </c>
+      <c r="B29" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="C29" s="24" t="b">
+        <v>1</v>
+      </c>
+      <c r="D29" s="40" t="s">
+        <v>700</v>
+      </c>
+      <c r="E29" s="40" t="s">
+        <v>700</v>
+      </c>
+      <c r="F29" s="15">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" s="12" t="s">
+        <v>692</v>
+      </c>
+      <c r="B30" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="C30" s="24" t="b">
+        <v>1</v>
+      </c>
+      <c r="D30" s="40" t="s">
+        <v>701</v>
+      </c>
+      <c r="E30" s="40" t="s">
+        <v>701</v>
+      </c>
+      <c r="F30" s="15">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31" s="12" t="s">
+        <v>692</v>
+      </c>
+      <c r="B31" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="C31" s="24" t="b">
+        <v>1</v>
+      </c>
+      <c r="D31" s="40" t="s">
+        <v>702</v>
+      </c>
+      <c r="E31" s="40" t="s">
+        <v>702</v>
+      </c>
+      <c r="F31" s="15">
         <v>12</v>
       </c>
-      <c r="B17" s="17" t="s">
-        <v>524</v>
-      </c>
-      <c r="C17" s="23"/>
-      <c r="D17" s="19">
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32" s="12" t="s">
+        <v>692</v>
+      </c>
+      <c r="B32" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="C32" s="24" t="b">
         <v>1</v>
       </c>
-      <c r="E17" s="17" t="s">
-        <v>417</v>
-      </c>
-      <c r="F17" s="20"/>
-      <c r="G17" s="18"/>
-    </row>
-    <row r="18" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="17" t="s">
+      <c r="D32" s="40" t="s">
+        <v>703</v>
+      </c>
+      <c r="E32" s="40" t="s">
+        <v>703</v>
+      </c>
+      <c r="F32" s="15">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33" s="12" t="s">
+        <v>692</v>
+      </c>
+      <c r="B33" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="C33" s="24" t="b">
+        <v>1</v>
+      </c>
+      <c r="D33" s="40" t="s">
+        <v>704</v>
+      </c>
+      <c r="E33" s="40" t="s">
+        <v>704</v>
+      </c>
+      <c r="F33" s="15">
         <v>14</v>
       </c>
-      <c r="B18" s="17" t="s">
-        <v>524</v>
-      </c>
-      <c r="C18" s="23"/>
-      <c r="D18" s="19">
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A34" s="12" t="s">
+        <v>692</v>
+      </c>
+      <c r="B34" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="C34" s="24" t="b">
+        <v>1</v>
+      </c>
+      <c r="D34" s="40" t="s">
+        <v>705</v>
+      </c>
+      <c r="E34" s="40" t="s">
+        <v>705</v>
+      </c>
+      <c r="F34" s="15">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A35" s="12" t="s">
+        <v>692</v>
+      </c>
+      <c r="B35" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="C35" s="24" t="b">
+        <v>1</v>
+      </c>
+      <c r="D35" s="40" t="s">
+        <v>706</v>
+      </c>
+      <c r="E35" s="40" t="s">
+        <v>706</v>
+      </c>
+      <c r="F35" s="15">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A36" s="12" t="s">
+        <v>692</v>
+      </c>
+      <c r="B36" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="C36" s="24" t="b">
+        <v>1</v>
+      </c>
+      <c r="D36" s="40" t="s">
+        <v>707</v>
+      </c>
+      <c r="E36" s="40" t="s">
+        <v>707</v>
+      </c>
+      <c r="F36" s="15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A37" s="12" t="s">
+        <v>692</v>
+      </c>
+      <c r="B37" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="C37" s="24" t="b">
+        <v>1</v>
+      </c>
+      <c r="D37" s="40" t="s">
+        <v>708</v>
+      </c>
+      <c r="E37" s="40" t="s">
+        <v>708</v>
+      </c>
+      <c r="F37" s="15">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A38" s="12" t="s">
+        <v>692</v>
+      </c>
+      <c r="B38" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="C38" s="24" t="b">
+        <v>1</v>
+      </c>
+      <c r="D38" s="40" t="s">
+        <v>709</v>
+      </c>
+      <c r="E38" s="40" t="s">
+        <v>709</v>
+      </c>
+      <c r="F38" s="15">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A39" s="12" t="s">
+        <v>692</v>
+      </c>
+      <c r="B39" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="C39" s="24" t="b">
+        <v>1</v>
+      </c>
+      <c r="D39" s="40" t="s">
+        <v>691</v>
+      </c>
+      <c r="E39" s="40" t="s">
+        <v>691</v>
+      </c>
+      <c r="F39" s="15">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="17" t="s">
+        <v>710</v>
+      </c>
+      <c r="B40" s="17" t="s">
+        <v>522</v>
+      </c>
+      <c r="C40" s="23" t="b">
+        <v>1</v>
+      </c>
+      <c r="D40" s="39" t="s">
+        <v>711</v>
+      </c>
+      <c r="E40" s="39" t="s">
+        <v>711</v>
+      </c>
+      <c r="F40" s="20">
+        <v>1</v>
+      </c>
+      <c r="G40" s="18"/>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A41" s="12" t="s">
+        <v>710</v>
+      </c>
+      <c r="B41" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="C41" s="24" t="b">
+        <v>1</v>
+      </c>
+      <c r="D41" s="40" t="s">
+        <v>693</v>
+      </c>
+      <c r="E41" s="40" t="s">
+        <v>693</v>
+      </c>
+      <c r="F41" s="15">
         <v>2</v>
       </c>
-      <c r="E18" s="17" t="s">
-        <v>420</v>
-      </c>
-      <c r="F18" s="20"/>
-      <c r="G18" s="18"/>
-    </row>
-    <row r="19" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="19" t="s">
-        <v>16</v>
-      </c>
-      <c r="B19" s="17" t="s">
-        <v>522</v>
-      </c>
-      <c r="C19" s="23" t="b">
-        <v>0</v>
-      </c>
-      <c r="D19" s="19">
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A42" s="12" t="s">
+        <v>710</v>
+      </c>
+      <c r="B42" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="C42" s="24" t="b">
         <v>1</v>
       </c>
-      <c r="E19" s="19" t="s">
-        <v>417</v>
-      </c>
-      <c r="F19" s="20"/>
-      <c r="G19" s="18"/>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B20" s="12" t="s">
-        <v>522</v>
-      </c>
-      <c r="C20" s="24" t="b">
-        <v>0</v>
-      </c>
-      <c r="D20" s="4">
-        <v>2</v>
-      </c>
-      <c r="E20" s="4" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B21" s="12" t="s">
-        <v>522</v>
-      </c>
-      <c r="C21" s="24" t="b">
-        <v>0</v>
-      </c>
-      <c r="D21" s="4">
+      <c r="D42" s="40" t="s">
+        <v>694</v>
+      </c>
+      <c r="E42" s="40" t="s">
+        <v>694</v>
+      </c>
+      <c r="F42" s="15">
         <v>3</v>
       </c>
-      <c r="E21" s="12" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B22" s="12" t="s">
-        <v>522</v>
-      </c>
-      <c r="C22" s="24" t="b">
-        <v>0</v>
-      </c>
-      <c r="D22" s="4">
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A43" s="12" t="s">
+        <v>710</v>
+      </c>
+      <c r="B43" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="C43" s="24" t="b">
+        <v>1</v>
+      </c>
+      <c r="D43" s="40" t="s">
+        <v>712</v>
+      </c>
+      <c r="E43" s="40" t="s">
+        <v>712</v>
+      </c>
+      <c r="F43" s="15">
         <v>4</v>
       </c>
-      <c r="E22" s="12" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B23" s="12" t="s">
-        <v>522</v>
-      </c>
-      <c r="C23" s="24" t="b">
-        <v>0</v>
-      </c>
-      <c r="D23" s="4">
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A44" s="12" t="s">
+        <v>710</v>
+      </c>
+      <c r="B44" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="C44" s="24" t="b">
+        <v>1</v>
+      </c>
+      <c r="D44" s="40" t="s">
+        <v>697</v>
+      </c>
+      <c r="E44" s="40" t="s">
+        <v>697</v>
+      </c>
+      <c r="F44" s="15">
         <v>5</v>
       </c>
-      <c r="E23" s="12" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B24" s="12" t="s">
-        <v>522</v>
-      </c>
-      <c r="C24" s="24" t="b">
-        <v>0</v>
-      </c>
-      <c r="D24" s="4">
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A45" s="12" t="s">
+        <v>710</v>
+      </c>
+      <c r="B45" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="C45" s="24" t="b">
+        <v>1</v>
+      </c>
+      <c r="D45" s="40" t="s">
+        <v>698</v>
+      </c>
+      <c r="E45" s="40" t="s">
+        <v>698</v>
+      </c>
+      <c r="F45" s="15">
         <v>6</v>
       </c>
-      <c r="E24" s="12" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B25" s="12" t="s">
-        <v>522</v>
-      </c>
-      <c r="C25" s="24" t="b">
-        <v>0</v>
-      </c>
-      <c r="D25" s="4">
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A46" s="12" t="s">
+        <v>710</v>
+      </c>
+      <c r="B46" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="C46" s="24" t="b">
+        <v>1</v>
+      </c>
+      <c r="D46" s="40" t="s">
+        <v>699</v>
+      </c>
+      <c r="E46" s="40" t="s">
+        <v>699</v>
+      </c>
+      <c r="F46" s="15">
         <v>7</v>
       </c>
-      <c r="E25" s="12" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B26" s="12" t="s">
-        <v>522</v>
-      </c>
-      <c r="C26" s="24" t="b">
-        <v>0</v>
-      </c>
-      <c r="D26" s="4">
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A47" s="12" t="s">
+        <v>710</v>
+      </c>
+      <c r="B47" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="C47" s="24" t="b">
+        <v>1</v>
+      </c>
+      <c r="D47" s="40" t="s">
+        <v>700</v>
+      </c>
+      <c r="E47" s="40" t="s">
+        <v>700</v>
+      </c>
+      <c r="F47" s="15">
         <v>8</v>
       </c>
-      <c r="E26" s="12" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B27" s="12" t="s">
-        <v>522</v>
-      </c>
-      <c r="C27" s="24" t="b">
-        <v>0</v>
-      </c>
-      <c r="D27" s="4">
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A48" s="12" t="s">
+        <v>710</v>
+      </c>
+      <c r="B48" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="C48" s="24" t="b">
+        <v>1</v>
+      </c>
+      <c r="D48" s="40" t="s">
+        <v>701</v>
+      </c>
+      <c r="E48" s="40" t="s">
+        <v>701</v>
+      </c>
+      <c r="F48" s="15">
         <v>9</v>
       </c>
-      <c r="E27" s="12" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="34" t="s">
-        <v>629</v>
-      </c>
-      <c r="B28" s="17" t="s">
-        <v>524</v>
-      </c>
-      <c r="C28" s="23"/>
-      <c r="E28" s="17"/>
-      <c r="F28" s="35"/>
-      <c r="G28" s="17"/>
-    </row>
-    <row r="29" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="34" t="s">
-        <v>630</v>
-      </c>
-      <c r="B29" s="17" t="s">
-        <v>524</v>
-      </c>
-      <c r="C29" s="23"/>
-      <c r="D29" s="19"/>
-      <c r="E29" s="17"/>
-      <c r="F29" s="20"/>
-      <c r="G29" s="18"/>
-    </row>
-    <row r="30" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="34" t="s">
-        <v>631</v>
-      </c>
-      <c r="B30" s="17" t="s">
-        <v>524</v>
-      </c>
-      <c r="C30" s="23"/>
-      <c r="D30" s="19"/>
-      <c r="E30" s="17"/>
-      <c r="F30" s="20"/>
-      <c r="G30" s="18"/>
-    </row>
-    <row r="31" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="34" t="s">
-        <v>632</v>
-      </c>
-      <c r="B31" s="17" t="s">
-        <v>524</v>
-      </c>
-      <c r="C31" s="23"/>
-      <c r="D31" s="19"/>
-      <c r="E31" s="17"/>
-      <c r="F31" s="20"/>
-      <c r="G31" s="18"/>
-    </row>
-    <row r="32" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="34" t="s">
-        <v>633</v>
-      </c>
-      <c r="B32" s="17" t="s">
-        <v>524</v>
-      </c>
-      <c r="C32" s="23"/>
-      <c r="D32" s="19"/>
-      <c r="E32" s="17"/>
-      <c r="F32" s="20"/>
-      <c r="G32" s="18"/>
-    </row>
-    <row r="33" spans="1:8" s="21" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="17" t="s">
-        <v>525</v>
-      </c>
-      <c r="B33" s="17" t="s">
-        <v>526</v>
-      </c>
-      <c r="C33" s="23"/>
-      <c r="D33" s="17"/>
-      <c r="E33" s="17"/>
-      <c r="F33" s="20"/>
-      <c r="G33" s="18"/>
-      <c r="H33" s="18"/>
-    </row>
-    <row r="34" spans="1:8" s="21" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="B34" s="17" t="s">
-        <v>526</v>
-      </c>
-      <c r="C34" s="23"/>
-      <c r="D34" s="17"/>
-      <c r="E34" s="17"/>
-      <c r="F34" s="20"/>
-      <c r="G34" s="18"/>
-    </row>
-    <row r="35" spans="1:8" s="21" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="B35" s="17" t="s">
-        <v>526</v>
-      </c>
-      <c r="C35" s="23"/>
-      <c r="D35" s="17"/>
-      <c r="E35" s="17"/>
-      <c r="F35" s="20"/>
-      <c r="G35" s="18"/>
-    </row>
-    <row r="36" spans="1:8" s="21" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="B36" s="17" t="s">
-        <v>522</v>
-      </c>
-      <c r="C36" s="23" t="b">
-        <v>0</v>
-      </c>
-      <c r="D36" s="19" t="s">
-        <v>458</v>
-      </c>
-      <c r="E36" s="17" t="s">
-        <v>530</v>
-      </c>
-      <c r="F36" s="20"/>
-      <c r="G36" s="18"/>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A37" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="B37" s="12" t="s">
-        <v>522</v>
-      </c>
-      <c r="C37" s="24" t="b">
-        <v>0</v>
-      </c>
-      <c r="D37" s="4" t="s">
-        <v>512</v>
-      </c>
-      <c r="E37" s="12" t="s">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A38" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="B38" s="12" t="s">
-        <v>522</v>
-      </c>
-      <c r="C38" s="24" t="b">
-        <v>0</v>
-      </c>
-      <c r="D38" s="4" t="s">
-        <v>443</v>
-      </c>
-      <c r="E38" s="12" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A39" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="B39" s="12" t="s">
-        <v>522</v>
-      </c>
-      <c r="C39" s="24" t="b">
-        <v>0</v>
-      </c>
-      <c r="D39" s="4" t="s">
-        <v>451</v>
-      </c>
-      <c r="E39" s="12" t="s">
-        <v>533</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A40" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="B40" s="12" t="s">
-        <v>522</v>
-      </c>
-      <c r="C40" s="24" t="b">
-        <v>0</v>
-      </c>
-      <c r="D40" s="4" t="s">
-        <v>519</v>
-      </c>
-      <c r="E40" s="12" t="s">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A41" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="B41" s="12" t="s">
-        <v>522</v>
-      </c>
-      <c r="C41" s="24" t="b">
-        <v>0</v>
-      </c>
-      <c r="D41" s="4" t="s">
-        <v>465</v>
-      </c>
-      <c r="E41" s="12" t="s">
-        <v>535</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A42" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="B42" s="12" t="s">
-        <v>522</v>
-      </c>
-      <c r="C42" s="24" t="b">
-        <v>0</v>
-      </c>
-      <c r="D42" s="4" t="s">
-        <v>412</v>
-      </c>
-      <c r="E42" s="12" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" s="21" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="17" t="s">
-        <v>24</v>
-      </c>
-      <c r="B43" s="17" t="s">
-        <v>526</v>
-      </c>
-      <c r="C43" s="23"/>
-      <c r="D43" s="17"/>
-      <c r="E43" s="17"/>
-      <c r="F43" s="20"/>
-      <c r="G43" s="18"/>
-    </row>
-    <row r="44" spans="1:8" s="21" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="B44" s="17" t="s">
-        <v>526</v>
-      </c>
-      <c r="C44" s="23"/>
-      <c r="D44" s="17"/>
-      <c r="E44" s="17"/>
-      <c r="F44" s="20"/>
-      <c r="G44" s="18"/>
-    </row>
-    <row r="45" spans="1:8" s="21" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="B45" s="19" t="s">
-        <v>524</v>
-      </c>
-      <c r="C45" s="23"/>
-      <c r="D45" s="17"/>
-      <c r="E45" s="17"/>
-      <c r="F45" s="20"/>
-      <c r="G45" s="18"/>
-    </row>
-    <row r="46" spans="1:8" s="21" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="17" t="s">
-        <v>28</v>
-      </c>
-      <c r="B46" s="19" t="s">
-        <v>524</v>
-      </c>
-      <c r="C46" s="23"/>
-      <c r="D46" s="17"/>
-      <c r="E46" s="17"/>
-      <c r="F46" s="20"/>
-      <c r="G46" s="18"/>
-    </row>
-    <row r="47" spans="1:8" s="21" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="B47" s="19" t="s">
-        <v>524</v>
-      </c>
-      <c r="C47" s="23"/>
-      <c r="D47" s="17"/>
-      <c r="E47" s="17"/>
-      <c r="F47" s="20"/>
-      <c r="G47" s="18"/>
-    </row>
-    <row r="48" spans="1:8" s="21" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="17" t="s">
-        <v>32</v>
-      </c>
-      <c r="B48" s="19" t="s">
-        <v>524</v>
-      </c>
-      <c r="C48" s="23"/>
-      <c r="D48" s="17"/>
-      <c r="E48" s="17"/>
-      <c r="F48" s="20"/>
-      <c r="G48" s="18"/>
-    </row>
-    <row r="49" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="B49" s="19" t="s">
-        <v>524</v>
-      </c>
-      <c r="C49" s="23"/>
-      <c r="D49" s="17"/>
-      <c r="E49" s="17"/>
-      <c r="F49" s="20"/>
-      <c r="G49" s="18"/>
-    </row>
-    <row r="50" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="B50" s="19" t="s">
-        <v>524</v>
-      </c>
-      <c r="C50" s="23"/>
-      <c r="D50" s="17"/>
-      <c r="E50" s="17"/>
-      <c r="F50" s="20"/>
-      <c r="G50" s="18"/>
-    </row>
-    <row r="51" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="17" t="s">
-        <v>38</v>
-      </c>
-      <c r="B51" s="19" t="s">
-        <v>524</v>
-      </c>
-      <c r="C51" s="23"/>
-      <c r="D51" s="17"/>
-      <c r="E51" s="17"/>
-      <c r="F51" s="20"/>
-      <c r="G51" s="18"/>
-    </row>
-    <row r="52" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="17" t="s">
-        <v>40</v>
-      </c>
-      <c r="B52" s="19" t="s">
-        <v>522</v>
-      </c>
-      <c r="C52" s="23" t="b">
-        <v>0</v>
-      </c>
-      <c r="D52" s="19" t="s">
-        <v>441</v>
-      </c>
-      <c r="E52" s="17" t="s">
-        <v>440</v>
-      </c>
-      <c r="F52" s="20"/>
-      <c r="G52" s="18"/>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A49" s="12" t="s">
+        <v>710</v>
+      </c>
+      <c r="B49" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="C49" s="24" t="b">
+        <v>1</v>
+      </c>
+      <c r="D49" s="40" t="s">
+        <v>702</v>
+      </c>
+      <c r="E49" s="40" t="s">
+        <v>702</v>
+      </c>
+      <c r="F49" s="15">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A50" s="12" t="s">
+        <v>710</v>
+      </c>
+      <c r="B50" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="C50" s="24" t="b">
+        <v>1</v>
+      </c>
+      <c r="D50" s="40" t="s">
+        <v>703</v>
+      </c>
+      <c r="E50" s="40" t="s">
+        <v>703</v>
+      </c>
+      <c r="F50" s="15">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A51" s="12" t="s">
+        <v>710</v>
+      </c>
+      <c r="B51" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="C51" s="24" t="b">
+        <v>1</v>
+      </c>
+      <c r="D51" s="40" t="s">
+        <v>704</v>
+      </c>
+      <c r="E51" s="40" t="s">
+        <v>704</v>
+      </c>
+      <c r="F51" s="15">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A52" s="12" t="s">
+        <v>710</v>
+      </c>
+      <c r="B52" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="C52" s="24" t="b">
+        <v>1</v>
+      </c>
+      <c r="D52" s="40" t="s">
+        <v>705</v>
+      </c>
+      <c r="E52" s="40" t="s">
+        <v>705</v>
+      </c>
+      <c r="F52" s="15">
+        <v>13</v>
+      </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="B53" s="4" t="s">
+        <v>710</v>
+      </c>
+      <c r="B53" s="12" t="s">
         <v>522</v>
       </c>
       <c r="C53" s="24" t="b">
-        <v>0</v>
-      </c>
-      <c r="D53" s="4" t="s">
-        <v>443</v>
-      </c>
-      <c r="E53" s="12" t="s">
-        <v>442</v>
+        <v>1</v>
+      </c>
+      <c r="D53" s="40" t="s">
+        <v>706</v>
+      </c>
+      <c r="E53" s="40" t="s">
+        <v>706</v>
+      </c>
+      <c r="F53" s="15">
+        <v>14</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="B54" s="4" t="s">
+        <v>710</v>
+      </c>
+      <c r="B54" s="12" t="s">
         <v>522</v>
       </c>
       <c r="C54" s="24" t="b">
-        <v>0</v>
-      </c>
-      <c r="D54" s="4" t="s">
-        <v>445</v>
-      </c>
-      <c r="E54" s="12" t="s">
-        <v>444</v>
+        <v>1</v>
+      </c>
+      <c r="D54" s="40" t="s">
+        <v>707</v>
+      </c>
+      <c r="E54" s="40" t="s">
+        <v>707</v>
+      </c>
+      <c r="F54" s="15">
+        <v>15</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="B55" s="4" t="s">
+        <v>710</v>
+      </c>
+      <c r="B55" s="12" t="s">
         <v>522</v>
       </c>
       <c r="C55" s="24" t="b">
-        <v>0</v>
-      </c>
-      <c r="D55" s="4" t="s">
-        <v>447</v>
-      </c>
-      <c r="E55" s="12" t="s">
-        <v>448</v>
+        <v>1</v>
+      </c>
+      <c r="D55" s="40" t="s">
+        <v>708</v>
+      </c>
+      <c r="E55" s="40" t="s">
+        <v>708</v>
+      </c>
+      <c r="F55" s="15">
+        <v>16</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="B56" s="4" t="s">
+        <v>710</v>
+      </c>
+      <c r="B56" s="12" t="s">
         <v>522</v>
       </c>
       <c r="C56" s="24" t="b">
-        <v>0</v>
-      </c>
-      <c r="D56" s="4" t="s">
-        <v>410</v>
-      </c>
-      <c r="E56" s="12" t="s">
-        <v>449</v>
+        <v>1</v>
+      </c>
+      <c r="D56" s="40" t="s">
+        <v>709</v>
+      </c>
+      <c r="E56" s="40" t="s">
+        <v>709</v>
+      </c>
+      <c r="F56" s="15">
+        <v>17</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="B57" s="4" t="s">
+        <v>710</v>
+      </c>
+      <c r="B57" s="12" t="s">
         <v>522</v>
       </c>
       <c r="C57" s="24" t="b">
-        <v>0</v>
-      </c>
-      <c r="D57" s="4" t="s">
-        <v>451</v>
-      </c>
-      <c r="E57" s="12" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A58" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="B58" s="4" t="s">
-        <v>522</v>
-      </c>
-      <c r="C58" s="24" t="b">
-        <v>0</v>
-      </c>
-      <c r="D58" s="4" t="s">
-        <v>452</v>
-      </c>
-      <c r="E58" s="12" t="s">
-        <v>439</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="D57" s="40" t="s">
+        <v>691</v>
+      </c>
+      <c r="E57" s="40" t="s">
+        <v>691</v>
+      </c>
+      <c r="F57" s="15">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="B58" s="17" t="s">
+        <v>522</v>
+      </c>
+      <c r="C58" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="D58" s="39">
+        <v>1</v>
+      </c>
+      <c r="E58" s="17" t="s">
+        <v>401</v>
+      </c>
+      <c r="F58" s="20"/>
+      <c r="G58" s="18"/>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="B59" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B59" s="12" t="s">
         <v>522</v>
       </c>
       <c r="C59" s="24" t="b">
         <v>0</v>
       </c>
-      <c r="D59" s="4" t="s">
-        <v>412</v>
+      <c r="D59" s="40">
+        <v>2</v>
       </c>
       <c r="E59" s="12" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="17" t="s">
-        <v>42</v>
-      </c>
-      <c r="B60" s="17" t="s">
-        <v>526</v>
-      </c>
-      <c r="C60" s="23"/>
-      <c r="D60" s="17"/>
-      <c r="E60" s="17"/>
-      <c r="F60" s="20"/>
-      <c r="G60" s="18"/>
-    </row>
-    <row r="61" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="17" t="s">
-        <v>44</v>
-      </c>
-      <c r="B61" s="17" t="s">
-        <v>522</v>
-      </c>
-      <c r="C61" s="23" t="b">
-        <v>1</v>
-      </c>
-      <c r="D61" s="19">
-        <v>1</v>
-      </c>
-      <c r="E61" s="17" t="s">
-        <v>483</v>
-      </c>
-      <c r="F61" s="22">
-        <v>1</v>
-      </c>
-      <c r="G61" s="18"/>
+        <v>474</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A60" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="B60" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="C60" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="D60" s="40">
+        <v>3</v>
+      </c>
+      <c r="E60" s="12" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A61" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="B61" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="C61" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="D61" s="40">
+        <v>4</v>
+      </c>
+      <c r="E61" s="12" t="s">
+        <v>476</v>
+      </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" s="12" t="s">
-        <v>44</v>
+        <v>6</v>
       </c>
       <c r="B62" s="12" t="s">
         <v>522</v>
       </c>
       <c r="C62" s="24" t="b">
-        <v>1</v>
-      </c>
-      <c r="D62" s="4">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="D62" s="40">
+        <v>5</v>
       </c>
       <c r="E62" s="12" t="s">
-        <v>487</v>
-      </c>
-      <c r="F62" s="16">
-        <v>2</v>
+        <v>477</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" s="12" t="s">
-        <v>44</v>
+        <v>6</v>
       </c>
       <c r="B63" s="12" t="s">
         <v>522</v>
       </c>
       <c r="C63" s="24" t="b">
-        <v>1</v>
-      </c>
-      <c r="D63" s="4">
-        <v>3</v>
+        <v>0</v>
+      </c>
+      <c r="D63" s="40">
+        <v>9</v>
       </c>
       <c r="E63" s="12" t="s">
-        <v>490</v>
-      </c>
-      <c r="F63" s="16">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A64" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="B64" s="12" t="s">
-        <v>522</v>
-      </c>
-      <c r="C64" s="24" t="b">
-        <v>1</v>
-      </c>
-      <c r="D64" s="4">
-        <v>4</v>
-      </c>
-      <c r="E64" s="12" t="s">
-        <v>493</v>
-      </c>
-      <c r="F64" s="16">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A65" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="B65" s="12" t="s">
-        <v>522</v>
-      </c>
-      <c r="C65" s="24" t="b">
-        <v>1</v>
-      </c>
-      <c r="D65" s="4">
-        <v>5</v>
-      </c>
-      <c r="E65" s="12" t="s">
-        <v>495</v>
-      </c>
-      <c r="F65" s="16">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A66" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="B66" s="12" t="s">
-        <v>522</v>
-      </c>
-      <c r="C66" s="24" t="b">
-        <v>1</v>
-      </c>
-      <c r="D66" s="4">
-        <v>6</v>
-      </c>
-      <c r="E66" s="12" t="s">
-        <v>498</v>
-      </c>
-      <c r="F66" s="16">
-        <v>6</v>
-      </c>
+        <v>404</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="B64" s="17" t="s">
+        <v>521</v>
+      </c>
+      <c r="C64" s="23"/>
+      <c r="D64" s="39"/>
+      <c r="E64" s="17"/>
+      <c r="F64" s="20"/>
+      <c r="G64" s="18"/>
+    </row>
+    <row r="65" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="17" t="s">
+        <v>523</v>
+      </c>
+      <c r="B65" s="17" t="s">
+        <v>524</v>
+      </c>
+      <c r="C65" s="23"/>
+      <c r="D65" s="39"/>
+      <c r="E65" s="17"/>
+      <c r="F65" s="20"/>
+      <c r="G65" s="18"/>
+    </row>
+    <row r="66" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="B66" s="17" t="s">
+        <v>522</v>
+      </c>
+      <c r="C66" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="D66" s="41" t="s">
+        <v>407</v>
+      </c>
+      <c r="E66" s="17" t="s">
+        <v>406</v>
+      </c>
+      <c r="F66" s="20"/>
+      <c r="G66" s="18"/>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" s="12" t="s">
-        <v>44</v>
+        <v>9</v>
       </c>
       <c r="B67" s="12" t="s">
         <v>522</v>
       </c>
       <c r="C67" s="24" t="b">
-        <v>1</v>
-      </c>
-      <c r="D67" s="4">
-        <v>7</v>
+        <v>0</v>
+      </c>
+      <c r="D67" s="42" t="s">
+        <v>410</v>
       </c>
       <c r="E67" s="12" t="s">
-        <v>501</v>
-      </c>
-      <c r="F67" s="16">
-        <v>7</v>
+        <v>409</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" s="12" t="s">
-        <v>44</v>
+        <v>9</v>
       </c>
       <c r="B68" s="12" t="s">
         <v>522</v>
       </c>
       <c r="C68" s="24" t="b">
-        <v>1</v>
-      </c>
-      <c r="D68" s="4">
-        <v>8</v>
+        <v>0</v>
+      </c>
+      <c r="D68" s="42" t="s">
+        <v>412</v>
       </c>
       <c r="E68" s="12" t="s">
-        <v>503</v>
-      </c>
-      <c r="F68" s="16">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A69" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="B69" s="12" t="s">
-        <v>522</v>
-      </c>
-      <c r="C69" s="24" t="b">
-        <v>1</v>
-      </c>
-      <c r="D69" s="4">
-        <v>9</v>
-      </c>
-      <c r="E69" s="12" t="s">
         <v>404</v>
       </c>
-      <c r="F69" s="16">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="70" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="17" t="s">
-        <v>46</v>
-      </c>
-      <c r="B70" s="17" t="s">
-        <v>522</v>
-      </c>
-      <c r="C70" s="23" t="b">
-        <v>1</v>
-      </c>
-      <c r="D70" s="19">
-        <v>0</v>
-      </c>
-      <c r="E70" s="17" t="s">
-        <v>536</v>
-      </c>
-      <c r="F70" s="22">
-        <v>1</v>
-      </c>
-      <c r="G70" s="18"/>
+    </row>
+    <row r="69" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="B69" s="17" t="s">
+        <v>522</v>
+      </c>
+      <c r="C69" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="D69" s="41" t="s">
+        <v>407</v>
+      </c>
+      <c r="E69" s="17" t="s">
+        <v>406</v>
+      </c>
+      <c r="F69" s="20"/>
+      <c r="G69" s="18"/>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A70" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="B70" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="C70" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="D70" s="42" t="s">
+        <v>410</v>
+      </c>
+      <c r="E70" s="12" t="s">
+        <v>409</v>
+      </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" s="12" t="s">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="B71" s="12" t="s">
         <v>522</v>
       </c>
       <c r="C71" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="D71" s="42" t="s">
+        <v>412</v>
+      </c>
+      <c r="E71" s="12" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="B72" s="17" t="s">
+        <v>524</v>
+      </c>
+      <c r="C72" s="23"/>
+      <c r="D72" s="41">
         <v>1</v>
       </c>
-      <c r="D71" s="4">
+      <c r="E72" s="17" t="s">
+        <v>417</v>
+      </c>
+      <c r="F72" s="20"/>
+      <c r="G72" s="18"/>
+    </row>
+    <row r="73" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="B73" s="17" t="s">
+        <v>524</v>
+      </c>
+      <c r="C73" s="23"/>
+      <c r="D73" s="41">
+        <v>2</v>
+      </c>
+      <c r="E73" s="17" t="s">
+        <v>420</v>
+      </c>
+      <c r="F73" s="20"/>
+      <c r="G73" s="18"/>
+    </row>
+    <row r="74" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="B74" s="17" t="s">
+        <v>522</v>
+      </c>
+      <c r="C74" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="D74" s="41">
         <v>1</v>
       </c>
-      <c r="E71" s="12" t="s">
-        <v>537</v>
-      </c>
-      <c r="F71" s="16">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A72" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="B72" s="12" t="s">
-        <v>522</v>
-      </c>
-      <c r="C72" s="24" t="b">
-        <v>1</v>
-      </c>
-      <c r="D72" s="4">
-        <v>2</v>
-      </c>
-      <c r="E72" s="12" t="s">
-        <v>538</v>
-      </c>
-      <c r="F72" s="16">
+      <c r="E74" s="19" t="s">
+        <v>417</v>
+      </c>
+      <c r="F74" s="20"/>
+      <c r="G74" s="18"/>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A75" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B75" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="C75" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="D75" s="42" t="s">
+        <v>408</v>
+      </c>
+      <c r="E75" s="4" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A76" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B76" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="C76" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="D76" s="42">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A73" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="B73" s="12" t="s">
-        <v>522</v>
-      </c>
-      <c r="C73" s="24" t="b">
-        <v>1</v>
-      </c>
-      <c r="D73" s="4">
-        <v>3</v>
-      </c>
-      <c r="E73" s="12" t="s">
-        <v>539</v>
-      </c>
-      <c r="F73" s="16">
+      <c r="E76" s="12" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A77" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B77" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="C77" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="D77" s="42">
         <v>4</v>
       </c>
-    </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A74" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="B74" s="12" t="s">
-        <v>522</v>
-      </c>
-      <c r="C74" s="24" t="b">
-        <v>1</v>
-      </c>
-      <c r="D74" s="4">
-        <v>4</v>
-      </c>
-      <c r="E74" s="12" t="s">
-        <v>540</v>
-      </c>
-      <c r="F74" s="16">
+      <c r="E77" s="12" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A78" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B78" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="C78" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="D78" s="42">
         <v>5</v>
       </c>
-    </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A75" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="B75" s="12" t="s">
-        <v>522</v>
-      </c>
-      <c r="C75" s="24" t="b">
-        <v>1</v>
-      </c>
-      <c r="D75" s="4">
-        <v>5</v>
-      </c>
-      <c r="E75" s="12" t="s">
-        <v>541</v>
-      </c>
-      <c r="F75" s="16">
+      <c r="E78" s="12" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A79" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B79" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="C79" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="D79" s="42">
         <v>6</v>
       </c>
-    </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A76" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="B76" s="12" t="s">
-        <v>522</v>
-      </c>
-      <c r="C76" s="24" t="b">
-        <v>1</v>
-      </c>
-      <c r="D76" s="4">
-        <v>6</v>
-      </c>
-      <c r="E76" s="12" t="s">
-        <v>542</v>
-      </c>
-      <c r="F76" s="16">
+      <c r="E79" s="12" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A80" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B80" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="C80" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="D80" s="42">
         <v>7</v>
       </c>
-    </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A77" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="B77" s="12" t="s">
-        <v>522</v>
-      </c>
-      <c r="C77" s="24" t="b">
-        <v>1</v>
-      </c>
-      <c r="D77" s="4">
-        <v>7</v>
-      </c>
-      <c r="E77" s="12" t="s">
-        <v>543</v>
-      </c>
-      <c r="F77" s="16">
+      <c r="E80" s="12" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A81" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B81" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="C81" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="D81" s="42">
         <v>8</v>
       </c>
-    </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A78" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="B78" s="12" t="s">
-        <v>522</v>
-      </c>
-      <c r="C78" s="24" t="b">
-        <v>1</v>
-      </c>
-      <c r="D78" s="4">
-        <v>8</v>
-      </c>
-      <c r="E78" s="12" t="s">
-        <v>544</v>
-      </c>
-      <c r="F78" s="16">
+      <c r="E81" s="12" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A82" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B82" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="C82" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="D82" s="42">
         <v>9</v>
       </c>
-    </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A79" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="B79" s="12" t="s">
-        <v>522</v>
-      </c>
-      <c r="C79" s="24" t="b">
-        <v>1</v>
-      </c>
-      <c r="D79" s="4">
-        <v>9</v>
-      </c>
-      <c r="E79" s="12" t="s">
+      <c r="E82" s="12" t="s">
         <v>404</v>
       </c>
-      <c r="F79" s="16">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="80" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="19" t="s">
-        <v>391</v>
-      </c>
-      <c r="B80" s="17" t="s">
-        <v>521</v>
-      </c>
-      <c r="C80" s="23"/>
-      <c r="D80" s="17"/>
-      <c r="E80" s="17"/>
-      <c r="F80" s="20"/>
-      <c r="G80" s="18"/>
-    </row>
-    <row r="81" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="17" t="s">
-        <v>48</v>
-      </c>
-      <c r="B81" s="17" t="s">
-        <v>522</v>
-      </c>
-      <c r="C81" s="23" t="b">
-        <v>0</v>
-      </c>
-      <c r="D81" s="17" t="s">
-        <v>407</v>
-      </c>
-      <c r="E81" s="17" t="s">
-        <v>406</v>
-      </c>
-      <c r="F81" s="20"/>
-      <c r="G81" s="18"/>
-    </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A82" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="B82" s="12" t="s">
-        <v>522</v>
-      </c>
-      <c r="C82" s="24" t="b">
-        <v>0</v>
-      </c>
-      <c r="D82" s="12" t="s">
-        <v>410</v>
-      </c>
-      <c r="E82" s="12" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A83" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="B83" s="12" t="s">
-        <v>522</v>
-      </c>
-      <c r="C83" s="24" t="b">
-        <v>0</v>
-      </c>
-      <c r="D83" s="12" t="s">
-        <v>412</v>
-      </c>
-      <c r="E83" s="12" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="84" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="17" t="s">
-        <v>50</v>
+    </row>
+    <row r="83" spans="1:8" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A83" s="34" t="s">
+        <v>629</v>
+      </c>
+      <c r="B83" s="17" t="s">
+        <v>524</v>
+      </c>
+      <c r="C83" s="23"/>
+      <c r="D83" s="41"/>
+      <c r="E83" s="17"/>
+      <c r="F83" s="35"/>
+      <c r="G83" s="17"/>
+    </row>
+    <row r="84" spans="1:8" s="21" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A84" s="34" t="s">
+        <v>630</v>
       </c>
       <c r="B84" s="17" t="s">
-        <v>522</v>
-      </c>
-      <c r="C84" s="23" t="b">
-        <v>0</v>
-      </c>
-      <c r="D84" s="17" t="s">
-        <v>407</v>
-      </c>
-      <c r="E84" s="17" t="s">
-        <v>406</v>
-      </c>
+        <v>524</v>
+      </c>
+      <c r="C84" s="23"/>
+      <c r="D84" s="41"/>
+      <c r="E84" s="17"/>
       <c r="F84" s="20"/>
       <c r="G84" s="18"/>
     </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A85" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="B85" s="12" t="s">
-        <v>522</v>
-      </c>
-      <c r="C85" s="24" t="b">
-        <v>0</v>
-      </c>
-      <c r="D85" s="12" t="s">
-        <v>410</v>
-      </c>
-      <c r="E85" s="12" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A86" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="B86" s="12" t="s">
-        <v>522</v>
-      </c>
-      <c r="C86" s="24" t="b">
-        <v>0</v>
-      </c>
-      <c r="D86" s="12" t="s">
-        <v>412</v>
-      </c>
-      <c r="E86" s="12" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="87" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="17" t="s">
-        <v>52</v>
+    <row r="85" spans="1:8" s="21" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A85" s="34" t="s">
+        <v>631</v>
+      </c>
+      <c r="B85" s="17" t="s">
+        <v>524</v>
+      </c>
+      <c r="C85" s="23"/>
+      <c r="D85" s="41"/>
+      <c r="E85" s="17"/>
+      <c r="F85" s="20"/>
+      <c r="G85" s="18"/>
+    </row>
+    <row r="86" spans="1:8" s="21" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A86" s="34" t="s">
+        <v>632</v>
+      </c>
+      <c r="B86" s="17" t="s">
+        <v>524</v>
+      </c>
+      <c r="C86" s="23"/>
+      <c r="D86" s="41"/>
+      <c r="E86" s="17"/>
+      <c r="F86" s="20"/>
+      <c r="G86" s="18"/>
+    </row>
+    <row r="87" spans="1:8" s="21" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A87" s="34" t="s">
+        <v>633</v>
       </c>
       <c r="B87" s="17" t="s">
-        <v>522</v>
-      </c>
-      <c r="C87" s="23" t="b">
-        <v>0</v>
-      </c>
-      <c r="D87" s="19">
-        <v>0</v>
-      </c>
-      <c r="E87" s="17" t="s">
-        <v>545</v>
-      </c>
+        <v>524</v>
+      </c>
+      <c r="C87" s="23"/>
+      <c r="D87" s="41"/>
+      <c r="E87" s="17"/>
       <c r="F87" s="20"/>
       <c r="G87" s="18"/>
     </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A88" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="B88" s="12" t="s">
-        <v>522</v>
-      </c>
-      <c r="C88" s="24" t="b">
-        <v>0</v>
-      </c>
-      <c r="D88" s="4">
-        <v>1</v>
-      </c>
-      <c r="E88" s="12" t="s">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A89" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="B89" s="12" t="s">
-        <v>522</v>
-      </c>
-      <c r="C89" s="24" t="b">
-        <v>0</v>
-      </c>
-      <c r="D89" s="4">
-        <v>2</v>
-      </c>
-      <c r="E89" s="12" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A90" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="B90" s="12" t="s">
-        <v>522</v>
-      </c>
-      <c r="C90" s="24" t="b">
-        <v>0</v>
-      </c>
-      <c r="D90" s="4">
-        <v>3</v>
-      </c>
-      <c r="E90" s="12" t="s">
-        <v>548</v>
-      </c>
-    </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A91" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="B91" s="12" t="s">
-        <v>522</v>
-      </c>
-      <c r="C91" s="24" t="b">
-        <v>0</v>
-      </c>
-      <c r="D91" s="4">
-        <v>4</v>
-      </c>
-      <c r="E91" s="12" t="s">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:8" s="21" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A88" s="17" t="s">
+        <v>525</v>
+      </c>
+      <c r="B88" s="17" t="s">
+        <v>526</v>
+      </c>
+      <c r="C88" s="23"/>
+      <c r="D88" s="39"/>
+      <c r="E88" s="17"/>
+      <c r="F88" s="20"/>
+      <c r="G88" s="18"/>
+      <c r="H88" s="18"/>
+    </row>
+    <row r="89" spans="1:8" s="21" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A89" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="B89" s="17" t="s">
+        <v>526</v>
+      </c>
+      <c r="C89" s="23"/>
+      <c r="D89" s="39"/>
+      <c r="E89" s="17"/>
+      <c r="F89" s="20"/>
+      <c r="G89" s="18"/>
+    </row>
+    <row r="90" spans="1:8" s="21" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A90" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="B90" s="17" t="s">
+        <v>526</v>
+      </c>
+      <c r="C90" s="23"/>
+      <c r="D90" s="39"/>
+      <c r="E90" s="17"/>
+      <c r="F90" s="20"/>
+      <c r="G90" s="18"/>
+    </row>
+    <row r="91" spans="1:8" s="21" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A91" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="B91" s="17" t="s">
+        <v>522</v>
+      </c>
+      <c r="C91" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="D91" s="41" t="s">
+        <v>458</v>
+      </c>
+      <c r="E91" s="17" t="s">
+        <v>530</v>
+      </c>
+      <c r="F91" s="20"/>
+      <c r="G91" s="18"/>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" s="12" t="s">
-        <v>52</v>
+        <v>22</v>
       </c>
       <c r="B92" s="12" t="s">
         <v>522</v>
@@ -21652,16 +21995,16 @@
       <c r="C92" s="24" t="b">
         <v>0</v>
       </c>
-      <c r="D92" s="4">
-        <v>5</v>
+      <c r="D92" s="42" t="s">
+        <v>512</v>
       </c>
       <c r="E92" s="12" t="s">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" s="12" t="s">
-        <v>52</v>
+        <v>22</v>
       </c>
       <c r="B93" s="12" t="s">
         <v>522</v>
@@ -21669,35 +22012,33 @@
       <c r="C93" s="24" t="b">
         <v>0</v>
       </c>
-      <c r="D93" s="4">
-        <v>9</v>
+      <c r="D93" s="42" t="s">
+        <v>443</v>
       </c>
       <c r="E93" s="12" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="94" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="B94" s="17" t="s">
-        <v>522</v>
-      </c>
-      <c r="C94" s="23" t="b">
-        <v>0</v>
-      </c>
-      <c r="D94" s="19" t="s">
-        <v>407</v>
-      </c>
-      <c r="E94" s="17" t="s">
-        <v>406</v>
-      </c>
-      <c r="F94" s="20"/>
-      <c r="G94" s="18"/>
-    </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A94" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="B94" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="C94" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="D94" s="42" t="s">
+        <v>451</v>
+      </c>
+      <c r="E94" s="12" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" s="12" t="s">
-        <v>54</v>
+        <v>22</v>
       </c>
       <c r="B95" s="12" t="s">
         <v>522</v>
@@ -21705,16 +22046,16 @@
       <c r="C95" s="24" t="b">
         <v>0</v>
       </c>
-      <c r="D95" s="4" t="s">
-        <v>410</v>
+      <c r="D95" s="42" t="s">
+        <v>519</v>
       </c>
       <c r="E95" s="12" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96" s="12" t="s">
-        <v>54</v>
+        <v>22</v>
       </c>
       <c r="B96" s="12" t="s">
         <v>522</v>
@@ -21722,690 +22063,736 @@
       <c r="C96" s="24" t="b">
         <v>0</v>
       </c>
-      <c r="D96" s="4" t="s">
+      <c r="D96" s="42" t="s">
+        <v>465</v>
+      </c>
+      <c r="E96" s="12" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A97" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="B97" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="C97" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="D97" s="42" t="s">
         <v>412</v>
       </c>
-      <c r="E96" s="12" t="s">
+      <c r="E97" s="12" t="s">
         <v>404</v>
       </c>
     </row>
-    <row r="97" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A97" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="B97" s="17" t="s">
-        <v>522</v>
-      </c>
-      <c r="C97" s="23" t="b">
-        <v>0</v>
-      </c>
-      <c r="D97" s="19" t="s">
-        <v>407</v>
-      </c>
-      <c r="E97" s="17" t="s">
-        <v>406</v>
-      </c>
-      <c r="F97" s="20"/>
-      <c r="G97" s="18"/>
-    </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A98" s="12" t="s">
-        <v>56</v>
-      </c>
-      <c r="B98" s="12" t="s">
-        <v>522</v>
-      </c>
-      <c r="C98" s="24" t="b">
-        <v>0</v>
-      </c>
-      <c r="D98" s="4" t="s">
-        <v>410</v>
-      </c>
-      <c r="E98" s="12" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A99" s="12" t="s">
-        <v>56</v>
-      </c>
-      <c r="B99" s="12" t="s">
-        <v>522</v>
-      </c>
-      <c r="C99" s="24" t="b">
-        <v>0</v>
-      </c>
-      <c r="D99" s="4" t="s">
-        <v>412</v>
-      </c>
-      <c r="E99" s="12" t="s">
-        <v>404</v>
-      </c>
+    <row r="98" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A98" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="B98" s="17" t="s">
+        <v>526</v>
+      </c>
+      <c r="C98" s="23"/>
+      <c r="D98" s="39"/>
+      <c r="E98" s="17"/>
+      <c r="F98" s="20"/>
+      <c r="G98" s="18"/>
+    </row>
+    <row r="99" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A99" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="B99" s="17" t="s">
+        <v>526</v>
+      </c>
+      <c r="C99" s="23"/>
+      <c r="D99" s="39"/>
+      <c r="E99" s="17"/>
+      <c r="F99" s="20"/>
+      <c r="G99" s="18"/>
     </row>
     <row r="100" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A100" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="B100" s="17" t="s">
-        <v>522</v>
-      </c>
-      <c r="C100" s="23" t="b">
-        <v>0</v>
-      </c>
-      <c r="D100" s="17" t="s">
-        <v>407</v>
-      </c>
-      <c r="E100" s="17" t="s">
-        <v>406</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="B100" s="19" t="s">
+        <v>524</v>
+      </c>
+      <c r="C100" s="23"/>
+      <c r="D100" s="39"/>
+      <c r="E100" s="17"/>
       <c r="F100" s="20"/>
       <c r="G100" s="18"/>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A101" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="B101" s="12" t="s">
-        <v>522</v>
-      </c>
-      <c r="C101" s="24" t="b">
-        <v>0</v>
-      </c>
-      <c r="D101" s="12" t="s">
-        <v>410</v>
-      </c>
-      <c r="E101" s="12" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A102" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="B102" s="12" t="s">
-        <v>522</v>
-      </c>
-      <c r="C102" s="24" t="b">
-        <v>0</v>
-      </c>
-      <c r="D102" s="12" t="s">
-        <v>412</v>
-      </c>
-      <c r="E102" s="12" t="s">
-        <v>404</v>
-      </c>
+    <row r="101" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A101" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="B101" s="19" t="s">
+        <v>524</v>
+      </c>
+      <c r="C101" s="23"/>
+      <c r="D101" s="39"/>
+      <c r="E101" s="17"/>
+      <c r="F101" s="20"/>
+      <c r="G101" s="18"/>
+    </row>
+    <row r="102" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A102" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="B102" s="19" t="s">
+        <v>524</v>
+      </c>
+      <c r="C102" s="23"/>
+      <c r="D102" s="39"/>
+      <c r="E102" s="17"/>
+      <c r="F102" s="20"/>
+      <c r="G102" s="18"/>
     </row>
     <row r="103" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A103" s="17" t="s">
-        <v>60</v>
-      </c>
-      <c r="B103" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="B103" s="19" t="s">
         <v>524</v>
       </c>
       <c r="C103" s="23"/>
-      <c r="D103" s="17"/>
+      <c r="D103" s="39"/>
       <c r="E103" s="17"/>
       <c r="F103" s="20"/>
       <c r="G103" s="18"/>
     </row>
     <row r="104" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A104" s="17" t="s">
-        <v>62</v>
-      </c>
-      <c r="B104" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="B104" s="19" t="s">
         <v>524</v>
       </c>
       <c r="C104" s="23"/>
-      <c r="D104" s="17"/>
+      <c r="D104" s="39"/>
       <c r="E104" s="17"/>
       <c r="F104" s="20"/>
       <c r="G104" s="18"/>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A105" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="B105" s="12" t="s">
-        <v>522</v>
-      </c>
-      <c r="C105" s="24" t="b">
-        <v>0</v>
-      </c>
-      <c r="D105" s="4">
-        <v>0</v>
-      </c>
-      <c r="E105" s="12" t="s">
-        <v>551</v>
-      </c>
-    </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A106" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="B106" s="12" t="s">
-        <v>522</v>
-      </c>
-      <c r="C106" s="24" t="b">
-        <v>0</v>
-      </c>
-      <c r="D106" s="4">
-        <v>1</v>
-      </c>
-      <c r="E106" s="12" t="s">
-        <v>552</v>
-      </c>
-    </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A107" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="B107" s="12" t="s">
-        <v>522</v>
-      </c>
-      <c r="C107" s="24" t="b">
-        <v>0</v>
-      </c>
-      <c r="D107" s="4">
-        <v>2</v>
-      </c>
-      <c r="E107" s="12" t="s">
-        <v>553</v>
-      </c>
+    <row r="105" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A105" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="B105" s="19" t="s">
+        <v>524</v>
+      </c>
+      <c r="C105" s="23"/>
+      <c r="D105" s="39"/>
+      <c r="E105" s="17"/>
+      <c r="F105" s="20"/>
+      <c r="G105" s="18"/>
+    </row>
+    <row r="106" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A106" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="B106" s="19" t="s">
+        <v>524</v>
+      </c>
+      <c r="C106" s="23"/>
+      <c r="D106" s="39"/>
+      <c r="E106" s="17"/>
+      <c r="F106" s="20"/>
+      <c r="G106" s="18"/>
+    </row>
+    <row r="107" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A107" s="17" t="s">
+        <v>40</v>
+      </c>
+      <c r="B107" s="19" t="s">
+        <v>522</v>
+      </c>
+      <c r="C107" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="D107" s="41" t="s">
+        <v>441</v>
+      </c>
+      <c r="E107" s="17" t="s">
+        <v>440</v>
+      </c>
+      <c r="F107" s="20"/>
+      <c r="G107" s="18"/>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A108" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="B108" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="B108" s="4" t="s">
         <v>522</v>
       </c>
       <c r="C108" s="24" t="b">
         <v>0</v>
       </c>
-      <c r="D108" s="4">
-        <v>3</v>
+      <c r="D108" s="42" t="s">
+        <v>443</v>
       </c>
       <c r="E108" s="12" t="s">
-        <v>554</v>
+        <v>442</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A109" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="B109" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="B109" s="4" t="s">
         <v>522</v>
       </c>
       <c r="C109" s="24" t="b">
         <v>0</v>
       </c>
-      <c r="D109" s="4">
-        <v>4</v>
+      <c r="D109" s="42" t="s">
+        <v>445</v>
       </c>
       <c r="E109" s="12" t="s">
-        <v>555</v>
+        <v>444</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="B110" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="B110" s="4" t="s">
         <v>522</v>
       </c>
       <c r="C110" s="24" t="b">
         <v>0</v>
       </c>
-      <c r="D110" s="4">
-        <v>5</v>
+      <c r="D110" s="42" t="s">
+        <v>447</v>
       </c>
       <c r="E110" s="12" t="s">
-        <v>556</v>
+        <v>448</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="B111" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="B111" s="4" t="s">
         <v>522</v>
       </c>
       <c r="C111" s="24" t="b">
         <v>0</v>
       </c>
-      <c r="D111" s="4">
-        <v>6</v>
+      <c r="D111" s="42" t="s">
+        <v>410</v>
       </c>
       <c r="E111" s="12" t="s">
-        <v>557</v>
+        <v>449</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="B112" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="B112" s="4" t="s">
         <v>522</v>
       </c>
       <c r="C112" s="24" t="b">
         <v>0</v>
       </c>
-      <c r="D112" s="4">
-        <v>7</v>
+      <c r="D112" s="42" t="s">
+        <v>451</v>
       </c>
       <c r="E112" s="12" t="s">
-        <v>558</v>
+        <v>450</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="B113" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="B113" s="4" t="s">
         <v>522</v>
       </c>
       <c r="C113" s="24" t="b">
         <v>0</v>
       </c>
-      <c r="D113" s="4">
-        <v>8</v>
+      <c r="D113" s="42" t="s">
+        <v>452</v>
       </c>
       <c r="E113" s="12" t="s">
-        <v>559</v>
+        <v>439</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A114" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="B114" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="B114" s="4" t="s">
         <v>522</v>
       </c>
       <c r="C114" s="24" t="b">
         <v>0</v>
       </c>
-      <c r="D114" s="4">
-        <v>9</v>
+      <c r="D114" s="42" t="s">
+        <v>412</v>
       </c>
       <c r="E114" s="12" t="s">
-        <v>514</v>
+        <v>404</v>
       </c>
     </row>
     <row r="115" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A115" s="17" t="s">
-        <v>66</v>
+        <v>42</v>
       </c>
       <c r="B115" s="17" t="s">
-        <v>522</v>
-      </c>
-      <c r="C115" s="23" t="b">
-        <v>0</v>
-      </c>
-      <c r="D115" s="19" t="s">
-        <v>407</v>
-      </c>
-      <c r="E115" s="17" t="s">
-        <v>406</v>
-      </c>
+        <v>526</v>
+      </c>
+      <c r="C115" s="23"/>
+      <c r="D115" s="39"/>
+      <c r="E115" s="17"/>
       <c r="F115" s="20"/>
       <c r="G115" s="18"/>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A116" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="B116" s="12" t="s">
-        <v>522</v>
-      </c>
-      <c r="C116" s="24" t="b">
-        <v>0</v>
-      </c>
-      <c r="D116" s="4" t="s">
-        <v>410</v>
-      </c>
-      <c r="E116" s="12" t="s">
-        <v>409</v>
-      </c>
+    <row r="116" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A116" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="B116" s="17" t="s">
+        <v>522</v>
+      </c>
+      <c r="C116" s="23" t="b">
+        <v>1</v>
+      </c>
+      <c r="D116" s="41">
+        <v>1</v>
+      </c>
+      <c r="E116" s="17" t="s">
+        <v>483</v>
+      </c>
+      <c r="F116" s="22">
+        <v>1</v>
+      </c>
+      <c r="G116" s="18"/>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A117" s="12" t="s">
-        <v>66</v>
+        <v>44</v>
       </c>
       <c r="B117" s="12" t="s">
         <v>522</v>
       </c>
       <c r="C117" s="24" t="b">
-        <v>0</v>
-      </c>
-      <c r="D117" s="4" t="s">
-        <v>412</v>
+        <v>1</v>
+      </c>
+      <c r="D117" s="42">
+        <v>2</v>
       </c>
       <c r="E117" s="12" t="s">
-        <v>404</v>
+        <v>487</v>
+      </c>
+      <c r="F117" s="16">
+        <v>2</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A118" s="12" t="s">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="B118" s="12" t="s">
-        <v>524</v>
-      </c>
-    </row>
-    <row r="119" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A119" s="17" t="s">
-        <v>68</v>
-      </c>
-      <c r="B119" s="17" t="s">
-        <v>524</v>
-      </c>
-      <c r="C119" s="23"/>
-      <c r="D119" s="17"/>
-      <c r="E119" s="17"/>
-      <c r="F119" s="20"/>
-      <c r="G119" s="18"/>
-    </row>
-    <row r="120" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A120" s="17" t="s">
-        <v>69</v>
-      </c>
-      <c r="B120" s="17" t="s">
-        <v>524</v>
-      </c>
-      <c r="C120" s="23"/>
-      <c r="D120" s="17"/>
-      <c r="E120" s="17"/>
-      <c r="F120" s="20"/>
-      <c r="G120" s="18"/>
-    </row>
-    <row r="121" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A121" s="17" t="s">
-        <v>71</v>
-      </c>
-      <c r="B121" s="17" t="s">
-        <v>524</v>
-      </c>
-      <c r="C121" s="23"/>
-      <c r="D121" s="17"/>
-      <c r="E121" s="17"/>
-      <c r="F121" s="20"/>
-      <c r="G121" s="18"/>
-    </row>
-    <row r="122" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A122" s="17" t="s">
-        <v>73</v>
-      </c>
-      <c r="B122" s="17" t="s">
-        <v>524</v>
-      </c>
-      <c r="C122" s="23"/>
-      <c r="D122" s="17"/>
-      <c r="E122" s="17"/>
-      <c r="F122" s="20"/>
-      <c r="G122" s="18"/>
-    </row>
-    <row r="123" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A123" s="17" t="s">
-        <v>634</v>
-      </c>
-      <c r="B123" s="17" t="s">
-        <v>524</v>
-      </c>
-      <c r="C123" s="23"/>
-      <c r="D123" s="17"/>
-      <c r="E123" s="17"/>
-      <c r="F123" s="20"/>
-      <c r="G123" s="18"/>
-    </row>
-    <row r="124" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A124" s="17" t="s">
-        <v>75</v>
-      </c>
-      <c r="B124" s="17" t="s">
-        <v>524</v>
-      </c>
-      <c r="C124" s="23"/>
-      <c r="D124" s="17"/>
-      <c r="E124" s="17"/>
-      <c r="F124" s="20"/>
-      <c r="G124" s="18"/>
+        <v>522</v>
+      </c>
+      <c r="C118" s="24" t="b">
+        <v>1</v>
+      </c>
+      <c r="D118" s="42">
+        <v>3</v>
+      </c>
+      <c r="E118" s="12" t="s">
+        <v>490</v>
+      </c>
+      <c r="F118" s="16">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A119" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="B119" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="C119" s="24" t="b">
+        <v>1</v>
+      </c>
+      <c r="D119" s="42">
+        <v>4</v>
+      </c>
+      <c r="E119" s="12" t="s">
+        <v>493</v>
+      </c>
+      <c r="F119" s="16">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A120" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="B120" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="C120" s="24" t="b">
+        <v>1</v>
+      </c>
+      <c r="D120" s="42">
+        <v>5</v>
+      </c>
+      <c r="E120" s="12" t="s">
+        <v>495</v>
+      </c>
+      <c r="F120" s="16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A121" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="B121" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="C121" s="24" t="b">
+        <v>1</v>
+      </c>
+      <c r="D121" s="42">
+        <v>6</v>
+      </c>
+      <c r="E121" s="12" t="s">
+        <v>498</v>
+      </c>
+      <c r="F121" s="16">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A122" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="B122" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="C122" s="24" t="b">
+        <v>1</v>
+      </c>
+      <c r="D122" s="42">
+        <v>7</v>
+      </c>
+      <c r="E122" s="12" t="s">
+        <v>501</v>
+      </c>
+      <c r="F122" s="16">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A123" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="B123" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="C123" s="24" t="b">
+        <v>1</v>
+      </c>
+      <c r="D123" s="42">
+        <v>8</v>
+      </c>
+      <c r="E123" s="12" t="s">
+        <v>503</v>
+      </c>
+      <c r="F123" s="16">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A124" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="B124" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="C124" s="24" t="b">
+        <v>1</v>
+      </c>
+      <c r="D124" s="42">
+        <v>9</v>
+      </c>
+      <c r="E124" s="12" t="s">
+        <v>404</v>
+      </c>
+      <c r="F124" s="16">
+        <v>9</v>
+      </c>
     </row>
     <row r="125" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A125" s="17" t="s">
-        <v>77</v>
+        <v>46</v>
       </c>
       <c r="B125" s="17" t="s">
-        <v>524</v>
-      </c>
-      <c r="C125" s="23"/>
-      <c r="D125" s="17"/>
-      <c r="E125" s="17"/>
-      <c r="F125" s="20"/>
+        <v>522</v>
+      </c>
+      <c r="C125" s="23" t="b">
+        <v>1</v>
+      </c>
+      <c r="D125" s="41">
+        <v>0</v>
+      </c>
+      <c r="E125" s="17" t="s">
+        <v>536</v>
+      </c>
+      <c r="F125" s="22">
+        <v>1</v>
+      </c>
       <c r="G125" s="18"/>
     </row>
-    <row r="126" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A126" s="17" t="s">
-        <v>79</v>
-      </c>
-      <c r="B126" s="17" t="s">
-        <v>524</v>
-      </c>
-      <c r="C126" s="23"/>
-      <c r="D126" s="17"/>
-      <c r="E126" s="17"/>
-      <c r="F126" s="20"/>
-      <c r="G126" s="18"/>
-    </row>
-    <row r="127" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A127" s="17" t="s">
-        <v>81</v>
-      </c>
-      <c r="B127" s="17" t="s">
-        <v>524</v>
-      </c>
-      <c r="C127" s="23"/>
-      <c r="D127" s="17"/>
-      <c r="E127" s="17"/>
-      <c r="F127" s="20"/>
-      <c r="G127" s="18"/>
-    </row>
-    <row r="128" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A128" s="17" t="s">
-        <v>83</v>
-      </c>
-      <c r="B128" s="17" t="s">
-        <v>522</v>
-      </c>
-      <c r="C128" s="23" t="b">
-        <v>0</v>
-      </c>
-      <c r="D128" s="17" t="s">
-        <v>410</v>
-      </c>
-      <c r="E128" s="17" t="s">
-        <v>456</v>
-      </c>
-      <c r="F128" s="20"/>
-      <c r="G128" s="18"/>
+    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A126" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="B126" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="C126" s="24" t="b">
+        <v>1</v>
+      </c>
+      <c r="D126" s="42">
+        <v>1</v>
+      </c>
+      <c r="E126" s="12" t="s">
+        <v>537</v>
+      </c>
+      <c r="F126" s="16">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A127" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="B127" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="C127" s="24" t="b">
+        <v>1</v>
+      </c>
+      <c r="D127" s="42">
+        <v>2</v>
+      </c>
+      <c r="E127" s="12" t="s">
+        <v>538</v>
+      </c>
+      <c r="F127" s="16">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A128" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="B128" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="C128" s="24" t="b">
+        <v>1</v>
+      </c>
+      <c r="D128" s="42">
+        <v>3</v>
+      </c>
+      <c r="E128" s="12" t="s">
+        <v>539</v>
+      </c>
+      <c r="F128" s="16">
+        <v>4</v>
+      </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A129" s="12" t="s">
-        <v>83</v>
+        <v>46</v>
       </c>
       <c r="B129" s="12" t="s">
         <v>522</v>
       </c>
       <c r="C129" s="24" t="b">
-        <v>0</v>
-      </c>
-      <c r="D129" s="12" t="s">
-        <v>458</v>
+        <v>1</v>
+      </c>
+      <c r="D129" s="42">
+        <v>4</v>
       </c>
       <c r="E129" s="12" t="s">
-        <v>457</v>
+        <v>540</v>
+      </c>
+      <c r="F129" s="16">
+        <v>5</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A130" s="12" t="s">
-        <v>83</v>
+        <v>46</v>
       </c>
       <c r="B130" s="12" t="s">
         <v>522</v>
       </c>
       <c r="C130" s="24" t="b">
-        <v>0</v>
-      </c>
-      <c r="D130" s="12" t="s">
-        <v>460</v>
+        <v>1</v>
+      </c>
+      <c r="D130" s="42">
+        <v>5</v>
       </c>
       <c r="E130" s="12" t="s">
-        <v>459</v>
+        <v>541</v>
+      </c>
+      <c r="F130" s="16">
+        <v>6</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A131" s="12" t="s">
-        <v>83</v>
+        <v>46</v>
       </c>
       <c r="B131" s="12" t="s">
         <v>522</v>
       </c>
       <c r="C131" s="24" t="b">
-        <v>0</v>
-      </c>
-      <c r="D131" s="12" t="s">
-        <v>462</v>
+        <v>1</v>
+      </c>
+      <c r="D131" s="42">
+        <v>6</v>
       </c>
       <c r="E131" s="12" t="s">
-        <v>461</v>
+        <v>542</v>
+      </c>
+      <c r="F131" s="16">
+        <v>7</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A132" s="12" t="s">
-        <v>83</v>
+        <v>46</v>
       </c>
       <c r="B132" s="12" t="s">
         <v>522</v>
       </c>
       <c r="C132" s="24" t="b">
-        <v>0</v>
-      </c>
-      <c r="D132" s="12" t="s">
-        <v>443</v>
+        <v>1</v>
+      </c>
+      <c r="D132" s="42">
+        <v>7</v>
       </c>
       <c r="E132" s="12" t="s">
-        <v>463</v>
+        <v>543</v>
+      </c>
+      <c r="F132" s="16">
+        <v>8</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A133" s="12" t="s">
-        <v>83</v>
+        <v>46</v>
       </c>
       <c r="B133" s="12" t="s">
         <v>522</v>
       </c>
       <c r="C133" s="24" t="b">
-        <v>0</v>
-      </c>
-      <c r="D133" s="12" t="s">
-        <v>465</v>
+        <v>1</v>
+      </c>
+      <c r="D133" s="42">
+        <v>8</v>
       </c>
       <c r="E133" s="12" t="s">
-        <v>464</v>
+        <v>544</v>
+      </c>
+      <c r="F133" s="16">
+        <v>9</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A134" s="12" t="s">
-        <v>83</v>
+        <v>46</v>
       </c>
       <c r="B134" s="12" t="s">
         <v>522</v>
       </c>
       <c r="C134" s="24" t="b">
-        <v>0</v>
-      </c>
-      <c r="D134" s="12" t="s">
-        <v>412</v>
+        <v>1</v>
+      </c>
+      <c r="D134" s="42">
+        <v>9</v>
       </c>
       <c r="E134" s="12" t="s">
         <v>404</v>
       </c>
-      <c r="G134" t="s">
-        <v>560</v>
+      <c r="F134" s="16">
+        <v>10</v>
       </c>
     </row>
     <row r="135" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A135" s="17" t="s">
-        <v>85</v>
+      <c r="A135" s="19" t="s">
+        <v>391</v>
       </c>
       <c r="B135" s="17" t="s">
-        <v>522</v>
-      </c>
-      <c r="C135" s="23" t="b">
-        <v>0</v>
-      </c>
-      <c r="D135" s="19" t="s">
-        <v>460</v>
-      </c>
-      <c r="E135" s="17" t="s">
-        <v>466</v>
-      </c>
+        <v>521</v>
+      </c>
+      <c r="C135" s="23"/>
+      <c r="D135" s="39"/>
+      <c r="E135" s="17"/>
       <c r="F135" s="20"/>
       <c r="G135" s="18"/>
     </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A136" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="B136" s="12" t="s">
-        <v>522</v>
-      </c>
-      <c r="C136" s="24" t="b">
-        <v>0</v>
-      </c>
-      <c r="D136" s="4" t="s">
-        <v>467</v>
-      </c>
-      <c r="E136" s="12" t="s">
-        <v>238</v>
-      </c>
+    <row r="136" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A136" s="19" t="s">
+        <v>713</v>
+      </c>
+      <c r="B136" s="17" t="s">
+        <v>521</v>
+      </c>
+      <c r="C136" s="23"/>
+      <c r="D136" s="39"/>
+      <c r="E136" s="17"/>
+      <c r="F136" s="20"/>
+      <c r="G136" s="18"/>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A137" s="12" t="s">
-        <v>85</v>
+      <c r="A137" s="4" t="s">
+        <v>713</v>
       </c>
       <c r="B137" s="12" t="s">
-        <v>522</v>
-      </c>
-      <c r="C137" s="24" t="b">
-        <v>0</v>
-      </c>
-      <c r="D137" s="4" t="s">
-        <v>465</v>
-      </c>
-      <c r="E137" s="12" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A138" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="B138" s="12" t="s">
-        <v>522</v>
-      </c>
-      <c r="C138" s="24" t="b">
-        <v>0</v>
-      </c>
-      <c r="D138" s="4" t="s">
-        <v>447</v>
-      </c>
-      <c r="E138" s="12" t="s">
-        <v>468</v>
-      </c>
+        <v>521</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A138" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="B138" s="17" t="s">
+        <v>522</v>
+      </c>
+      <c r="C138" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="D138" s="39" t="s">
+        <v>407</v>
+      </c>
+      <c r="E138" s="17" t="s">
+        <v>406</v>
+      </c>
+      <c r="F138" s="20"/>
+      <c r="G138" s="18"/>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A139" s="12" t="s">
-        <v>85</v>
+        <v>48</v>
       </c>
       <c r="B139" s="12" t="s">
         <v>522</v>
@@ -22413,16 +22800,16 @@
       <c r="C139" s="24" t="b">
         <v>0</v>
       </c>
-      <c r="D139" s="4" t="s">
-        <v>470</v>
+      <c r="D139" s="40" t="s">
+        <v>410</v>
       </c>
       <c r="E139" s="12" t="s">
-        <v>469</v>
+        <v>409</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A140" s="12" t="s">
-        <v>85</v>
+        <v>48</v>
       </c>
       <c r="B140" s="12" t="s">
         <v>522</v>
@@ -22430,52 +22817,52 @@
       <c r="C140" s="24" t="b">
         <v>0</v>
       </c>
-      <c r="D140" s="4" t="s">
-        <v>458</v>
+      <c r="D140" s="40" t="s">
+        <v>412</v>
       </c>
       <c r="E140" s="12" t="s">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A141" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="B141" s="12" t="s">
-        <v>522</v>
-      </c>
-      <c r="C141" s="24" t="b">
-        <v>0</v>
-      </c>
-      <c r="D141" s="4" t="s">
-        <v>412</v>
-      </c>
-      <c r="E141" s="12" t="s">
         <v>404</v>
       </c>
     </row>
-    <row r="142" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A142" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="B142" s="17" t="s">
-        <v>522</v>
-      </c>
-      <c r="C142" s="23" t="b">
-        <v>0</v>
-      </c>
-      <c r="D142" s="17" t="s">
+    <row r="141" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A141" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="B141" s="17" t="s">
+        <v>522</v>
+      </c>
+      <c r="C141" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="D141" s="39" t="s">
         <v>407</v>
       </c>
-      <c r="E142" s="17" t="s">
+      <c r="E141" s="17" t="s">
         <v>406</v>
       </c>
-      <c r="F142" s="20"/>
-      <c r="G142" s="18"/>
+      <c r="F141" s="20"/>
+      <c r="G141" s="18"/>
+    </row>
+    <row r="142" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A142" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="B142" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="C142" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="D142" s="40" t="s">
+        <v>410</v>
+      </c>
+      <c r="E142" s="12" t="s">
+        <v>409</v>
+      </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A143" s="12" t="s">
-        <v>87</v>
+        <v>50</v>
       </c>
       <c r="B143" s="12" t="s">
         <v>522</v>
@@ -22483,98 +22870,120 @@
       <c r="C143" s="24" t="b">
         <v>0</v>
       </c>
-      <c r="D143" s="12" t="s">
-        <v>410</v>
+      <c r="D143" s="40" t="s">
+        <v>412</v>
       </c>
       <c r="E143" s="12" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A144" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="B144" s="12" t="s">
-        <v>522</v>
-      </c>
-      <c r="C144" s="24" t="b">
-        <v>0</v>
-      </c>
-      <c r="D144" s="12" t="s">
-        <v>412</v>
-      </c>
-      <c r="E144" s="12" t="s">
         <v>404</v>
       </c>
     </row>
-    <row r="145" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A145" s="17" t="s">
-        <v>647</v>
-      </c>
-      <c r="B145" s="17" t="s">
-        <v>524</v>
-      </c>
-      <c r="C145" s="23"/>
-      <c r="D145" s="17"/>
-      <c r="E145" s="17"/>
-      <c r="F145" s="20"/>
-      <c r="G145" s="18"/>
-    </row>
-    <row r="146" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A146" s="17" t="s">
-        <v>648</v>
-      </c>
-      <c r="B146" s="17" t="s">
-        <v>524</v>
-      </c>
-      <c r="C146" s="23"/>
-      <c r="D146" s="17"/>
-      <c r="E146" s="17"/>
-      <c r="F146" s="20"/>
-      <c r="G146" s="18"/>
-    </row>
-    <row r="147" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A147" s="17" t="s">
-        <v>649</v>
-      </c>
-      <c r="B147" s="17" t="s">
-        <v>524</v>
-      </c>
-      <c r="C147" s="23"/>
-      <c r="D147" s="17"/>
-      <c r="E147" s="17"/>
-      <c r="F147" s="20"/>
-      <c r="G147" s="18"/>
-    </row>
-    <row r="148" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A148" s="17" t="s">
-        <v>650</v>
-      </c>
-      <c r="B148" s="17" t="s">
-        <v>524</v>
-      </c>
-      <c r="C148" s="23"/>
-      <c r="D148" s="17"/>
-      <c r="E148" s="17"/>
-      <c r="F148" s="20"/>
-      <c r="G148" s="18"/>
-    </row>
-    <row r="149" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A149" s="17" t="s">
-        <v>89</v>
-      </c>
-      <c r="B149" s="17" t="s">
-        <v>524</v>
-      </c>
-      <c r="C149" s="23"/>
-      <c r="D149" s="17"/>
-      <c r="E149" s="17"/>
-      <c r="F149" s="20"/>
-      <c r="G149" s="18"/>
+    <row r="144" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A144" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="B144" s="17" t="s">
+        <v>522</v>
+      </c>
+      <c r="C144" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="D144" s="41">
+        <v>0</v>
+      </c>
+      <c r="E144" s="17" t="s">
+        <v>545</v>
+      </c>
+      <c r="F144" s="20"/>
+      <c r="G144" s="18"/>
+    </row>
+    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A145" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="B145" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="C145" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="D145" s="42">
+        <v>1</v>
+      </c>
+      <c r="E145" s="12" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A146" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="B146" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="C146" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="D146" s="42">
+        <v>2</v>
+      </c>
+      <c r="E146" s="12" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A147" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="B147" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="C147" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="D147" s="42">
+        <v>3</v>
+      </c>
+      <c r="E147" s="12" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A148" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="B148" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="C148" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="D148" s="42">
+        <v>4</v>
+      </c>
+      <c r="E148" s="12" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A149" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="B149" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="C149" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="D149" s="42">
+        <v>5</v>
+      </c>
+      <c r="E149" s="12" t="s">
+        <v>550</v>
+      </c>
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A150" s="12" t="s">
-        <v>91</v>
+        <v>52</v>
       </c>
       <c r="B150" s="12" t="s">
         <v>522</v>
@@ -22582,33 +22991,35 @@
       <c r="C150" s="24" t="b">
         <v>0</v>
       </c>
-      <c r="D150" s="12">
-        <v>0</v>
+      <c r="D150" s="42">
+        <v>9</v>
       </c>
       <c r="E150" s="12" t="s">
-        <v>551</v>
-      </c>
-    </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A151" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="B151" s="12" t="s">
-        <v>522</v>
-      </c>
-      <c r="C151" s="24" t="b">
-        <v>0</v>
-      </c>
-      <c r="D151" s="12">
-        <v>1</v>
-      </c>
-      <c r="E151" s="12" t="s">
-        <v>561</v>
-      </c>
+        <v>411</v>
+      </c>
+    </row>
+    <row r="151" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A151" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="B151" s="17" t="s">
+        <v>522</v>
+      </c>
+      <c r="C151" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="D151" s="41" t="s">
+        <v>407</v>
+      </c>
+      <c r="E151" s="17" t="s">
+        <v>406</v>
+      </c>
+      <c r="F151" s="20"/>
+      <c r="G151" s="18"/>
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A152" s="12" t="s">
-        <v>91</v>
+        <v>54</v>
       </c>
       <c r="B152" s="12" t="s">
         <v>522</v>
@@ -22616,16 +23027,16 @@
       <c r="C152" s="24" t="b">
         <v>0</v>
       </c>
-      <c r="D152" s="12">
-        <v>2</v>
+      <c r="D152" s="42" t="s">
+        <v>410</v>
       </c>
       <c r="E152" s="12" t="s">
-        <v>562</v>
+        <v>409</v>
       </c>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A153" s="12" t="s">
-        <v>91</v>
+        <v>54</v>
       </c>
       <c r="B153" s="12" t="s">
         <v>522</v>
@@ -22633,33 +23044,35 @@
       <c r="C153" s="24" t="b">
         <v>0</v>
       </c>
-      <c r="D153" s="12">
-        <v>3</v>
+      <c r="D153" s="42" t="s">
+        <v>412</v>
       </c>
       <c r="E153" s="12" t="s">
-        <v>563</v>
-      </c>
-    </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A154" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="B154" s="12" t="s">
-        <v>522</v>
-      </c>
-      <c r="C154" s="24" t="b">
-        <v>0</v>
-      </c>
-      <c r="D154" s="12">
-        <v>4</v>
-      </c>
-      <c r="E154" s="12" t="s">
-        <v>564</v>
-      </c>
+        <v>404</v>
+      </c>
+    </row>
+    <row r="154" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A154" s="17" t="s">
+        <v>56</v>
+      </c>
+      <c r="B154" s="17" t="s">
+        <v>522</v>
+      </c>
+      <c r="C154" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="D154" s="41" t="s">
+        <v>407</v>
+      </c>
+      <c r="E154" s="17" t="s">
+        <v>406</v>
+      </c>
+      <c r="F154" s="20"/>
+      <c r="G154" s="18"/>
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A155" s="12" t="s">
-        <v>91</v>
+        <v>56</v>
       </c>
       <c r="B155" s="12" t="s">
         <v>522</v>
@@ -22667,16 +23080,16 @@
       <c r="C155" s="24" t="b">
         <v>0</v>
       </c>
-      <c r="D155" s="12">
-        <v>5</v>
+      <c r="D155" s="42" t="s">
+        <v>410</v>
       </c>
       <c r="E155" s="12" t="s">
-        <v>565</v>
+        <v>409</v>
       </c>
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A156" s="12" t="s">
-        <v>91</v>
+        <v>56</v>
       </c>
       <c r="B156" s="12" t="s">
         <v>522</v>
@@ -22684,33 +23097,35 @@
       <c r="C156" s="24" t="b">
         <v>0</v>
       </c>
-      <c r="D156" s="12">
-        <v>6</v>
+      <c r="D156" s="42" t="s">
+        <v>412</v>
       </c>
       <c r="E156" s="12" t="s">
-        <v>566</v>
-      </c>
-    </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A157" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="B157" s="12" t="s">
-        <v>522</v>
-      </c>
-      <c r="C157" s="24" t="b">
-        <v>0</v>
-      </c>
-      <c r="D157" s="12">
-        <v>7</v>
-      </c>
-      <c r="E157" s="12" t="s">
-        <v>567</v>
-      </c>
+        <v>404</v>
+      </c>
+    </row>
+    <row r="157" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A157" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="B157" s="17" t="s">
+        <v>522</v>
+      </c>
+      <c r="C157" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="D157" s="39" t="s">
+        <v>407</v>
+      </c>
+      <c r="E157" s="17" t="s">
+        <v>406</v>
+      </c>
+      <c r="F157" s="20"/>
+      <c r="G157" s="18"/>
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A158" s="12" t="s">
-        <v>91</v>
+        <v>58</v>
       </c>
       <c r="B158" s="12" t="s">
         <v>522</v>
@@ -22718,16 +23133,16 @@
       <c r="C158" s="24" t="b">
         <v>0</v>
       </c>
-      <c r="D158" s="12">
-        <v>8</v>
+      <c r="D158" s="40" t="s">
+        <v>410</v>
       </c>
       <c r="E158" s="12" t="s">
-        <v>568</v>
+        <v>409</v>
       </c>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A159" s="12" t="s">
-        <v>91</v>
+        <v>58</v>
       </c>
       <c r="B159" s="12" t="s">
         <v>522</v>
@@ -22735,8 +23150,8 @@
       <c r="C159" s="24" t="b">
         <v>0</v>
       </c>
-      <c r="D159" s="12">
-        <v>9</v>
+      <c r="D159" s="40" t="s">
+        <v>412</v>
       </c>
       <c r="E159" s="12" t="s">
         <v>404</v>
@@ -22744,43 +23159,33 @@
     </row>
     <row r="160" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A160" s="17" t="s">
-        <v>93</v>
+        <v>60</v>
       </c>
       <c r="B160" s="17" t="s">
-        <v>522</v>
-      </c>
-      <c r="C160" s="23" t="b">
-        <v>0</v>
-      </c>
-      <c r="D160" s="17">
-        <v>1</v>
-      </c>
-      <c r="E160" s="17" t="s">
-        <v>569</v>
-      </c>
+        <v>524</v>
+      </c>
+      <c r="C160" s="23"/>
+      <c r="D160" s="39"/>
+      <c r="E160" s="17"/>
       <c r="F160" s="20"/>
       <c r="G160" s="18"/>
     </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A161" s="12" t="s">
-        <v>93</v>
-      </c>
-      <c r="B161" s="12" t="s">
-        <v>522</v>
-      </c>
-      <c r="C161" s="24" t="b">
-        <v>0</v>
-      </c>
-      <c r="D161" s="12">
-        <v>2</v>
-      </c>
-      <c r="E161" s="12" t="s">
-        <v>570</v>
-      </c>
+    <row r="161" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A161" s="17" t="s">
+        <v>62</v>
+      </c>
+      <c r="B161" s="17" t="s">
+        <v>524</v>
+      </c>
+      <c r="C161" s="23"/>
+      <c r="D161" s="39"/>
+      <c r="E161" s="17"/>
+      <c r="F161" s="20"/>
+      <c r="G161" s="18"/>
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A162" s="12" t="s">
-        <v>93</v>
+        <v>64</v>
       </c>
       <c r="B162" s="12" t="s">
         <v>522</v>
@@ -22788,16 +23193,16 @@
       <c r="C162" s="24" t="b">
         <v>0</v>
       </c>
-      <c r="D162" s="12">
-        <v>3</v>
+      <c r="D162" s="42">
+        <v>0</v>
       </c>
       <c r="E162" s="12" t="s">
-        <v>571</v>
+        <v>551</v>
       </c>
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A163" s="12" t="s">
-        <v>93</v>
+        <v>64</v>
       </c>
       <c r="B163" s="12" t="s">
         <v>522</v>
@@ -22805,16 +23210,16 @@
       <c r="C163" s="24" t="b">
         <v>0</v>
       </c>
-      <c r="D163" s="12">
-        <v>4</v>
+      <c r="D163" s="42">
+        <v>1</v>
       </c>
       <c r="E163" s="12" t="s">
-        <v>572</v>
+        <v>552</v>
       </c>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A164" s="12" t="s">
-        <v>93</v>
+        <v>64</v>
       </c>
       <c r="B164" s="12" t="s">
         <v>522</v>
@@ -22822,16 +23227,16 @@
       <c r="C164" s="24" t="b">
         <v>0</v>
       </c>
-      <c r="D164" s="12">
-        <v>8</v>
+      <c r="D164" s="42">
+        <v>2</v>
       </c>
       <c r="E164" s="12" t="s">
-        <v>573</v>
+        <v>553</v>
       </c>
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A165" s="12" t="s">
-        <v>93</v>
+        <v>64</v>
       </c>
       <c r="B165" s="12" t="s">
         <v>522</v>
@@ -22839,35 +23244,33 @@
       <c r="C165" s="24" t="b">
         <v>0</v>
       </c>
-      <c r="D165" s="12">
-        <v>9</v>
+      <c r="D165" s="42">
+        <v>3</v>
       </c>
       <c r="E165" s="12" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="166" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A166" s="17" t="s">
-        <v>95</v>
-      </c>
-      <c r="B166" s="17" t="s">
-        <v>522</v>
-      </c>
-      <c r="C166" s="23" t="b">
-        <v>0</v>
-      </c>
-      <c r="D166" s="17" t="s">
-        <v>407</v>
-      </c>
-      <c r="E166" s="17" t="s">
-        <v>406</v>
-      </c>
-      <c r="F166" s="20"/>
-      <c r="G166" s="18"/>
+        <v>554</v>
+      </c>
+    </row>
+    <row r="166" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A166" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="B166" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="C166" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="D166" s="42">
+        <v>4</v>
+      </c>
+      <c r="E166" s="12" t="s">
+        <v>555</v>
+      </c>
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A167" s="12" t="s">
-        <v>95</v>
+        <v>64</v>
       </c>
       <c r="B167" s="12" t="s">
         <v>522</v>
@@ -22875,16 +23278,16 @@
       <c r="C167" s="24" t="b">
         <v>0</v>
       </c>
-      <c r="D167" s="12" t="s">
-        <v>410</v>
+      <c r="D167" s="42">
+        <v>5</v>
       </c>
       <c r="E167" s="12" t="s">
-        <v>409</v>
+        <v>556</v>
       </c>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A168" s="12" t="s">
-        <v>95</v>
+        <v>64</v>
       </c>
       <c r="B168" s="12" t="s">
         <v>522</v>
@@ -22892,35 +23295,33 @@
       <c r="C168" s="24" t="b">
         <v>0</v>
       </c>
-      <c r="D168" s="12" t="s">
-        <v>412</v>
+      <c r="D168" s="42">
+        <v>6</v>
       </c>
       <c r="E168" s="12" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="169" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A169" s="17" t="s">
-        <v>97</v>
-      </c>
-      <c r="B169" s="17" t="s">
-        <v>522</v>
-      </c>
-      <c r="C169" s="23" t="b">
-        <v>0</v>
-      </c>
-      <c r="D169" s="17" t="s">
-        <v>407</v>
-      </c>
-      <c r="E169" s="17" t="s">
-        <v>406</v>
-      </c>
-      <c r="F169" s="20"/>
-      <c r="G169" s="18"/>
+        <v>557</v>
+      </c>
+    </row>
+    <row r="169" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A169" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="B169" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="C169" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="D169" s="42">
+        <v>7</v>
+      </c>
+      <c r="E169" s="12" t="s">
+        <v>558</v>
+      </c>
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A170" s="12" t="s">
-        <v>97</v>
+        <v>64</v>
       </c>
       <c r="B170" s="12" t="s">
         <v>522</v>
@@ -22928,16 +23329,16 @@
       <c r="C170" s="24" t="b">
         <v>0</v>
       </c>
-      <c r="D170" s="12" t="s">
-        <v>410</v>
+      <c r="D170" s="42">
+        <v>8</v>
       </c>
       <c r="E170" s="12" t="s">
-        <v>409</v>
+        <v>559</v>
       </c>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A171" s="12" t="s">
-        <v>97</v>
+        <v>64</v>
       </c>
       <c r="B171" s="12" t="s">
         <v>522</v>
@@ -22945,16 +23346,16 @@
       <c r="C171" s="24" t="b">
         <v>0</v>
       </c>
-      <c r="D171" s="12" t="s">
-        <v>412</v>
+      <c r="D171" s="42">
+        <v>9</v>
       </c>
       <c r="E171" s="12" t="s">
-        <v>404</v>
+        <v>514</v>
       </c>
     </row>
     <row r="172" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A172" s="17" t="s">
-        <v>99</v>
+        <v>66</v>
       </c>
       <c r="B172" s="17" t="s">
         <v>522</v>
@@ -22962,7 +23363,7 @@
       <c r="C172" s="23" t="b">
         <v>0</v>
       </c>
-      <c r="D172" s="17" t="s">
+      <c r="D172" s="41" t="s">
         <v>407</v>
       </c>
       <c r="E172" s="17" t="s">
@@ -22973,7 +23374,7 @@
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A173" s="12" t="s">
-        <v>99</v>
+        <v>66</v>
       </c>
       <c r="B173" s="12" t="s">
         <v>522</v>
@@ -22981,7 +23382,7 @@
       <c r="C173" s="24" t="b">
         <v>0</v>
       </c>
-      <c r="D173" s="12" t="s">
+      <c r="D173" s="42" t="s">
         <v>410</v>
       </c>
       <c r="E173" s="12" t="s">
@@ -22990,7 +23391,7 @@
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A174" s="12" t="s">
-        <v>99</v>
+        <v>66</v>
       </c>
       <c r="B174" s="12" t="s">
         <v>522</v>
@@ -22998,211 +23399,160 @@
       <c r="C174" s="24" t="b">
         <v>0</v>
       </c>
-      <c r="D174" s="12" t="s">
+      <c r="D174" s="42" t="s">
         <v>412</v>
       </c>
       <c r="E174" s="12" t="s">
         <v>404</v>
       </c>
     </row>
-    <row r="175" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A175" s="17" t="s">
-        <v>101</v>
-      </c>
-      <c r="B175" s="17" t="s">
-        <v>522</v>
-      </c>
-      <c r="C175" s="23" t="b">
-        <v>0</v>
-      </c>
-      <c r="D175" s="17" t="s">
-        <v>407</v>
-      </c>
-      <c r="E175" s="17" t="s">
-        <v>406</v>
-      </c>
-      <c r="F175" s="20"/>
-      <c r="G175" s="18"/>
-    </row>
-    <row r="176" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A176" s="12" t="s">
-        <v>101</v>
-      </c>
-      <c r="B176" s="12" t="s">
-        <v>522</v>
-      </c>
-      <c r="C176" s="24" t="b">
-        <v>0</v>
-      </c>
-      <c r="D176" s="12" t="s">
-        <v>410</v>
-      </c>
-      <c r="E176" s="12" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="177" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A177" s="12" t="s">
-        <v>101</v>
-      </c>
-      <c r="B177" s="12" t="s">
-        <v>522</v>
-      </c>
-      <c r="C177" s="24" t="b">
-        <v>0</v>
-      </c>
-      <c r="D177" s="12" t="s">
-        <v>412</v>
-      </c>
-      <c r="E177" s="12" t="s">
-        <v>404</v>
-      </c>
+    <row r="175" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A175" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="B175" s="12" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="176" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A176" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="B176" s="17" t="s">
+        <v>524</v>
+      </c>
+      <c r="C176" s="23"/>
+      <c r="D176" s="39"/>
+      <c r="E176" s="17"/>
+      <c r="F176" s="20"/>
+      <c r="G176" s="18"/>
+    </row>
+    <row r="177" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A177" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="B177" s="17" t="s">
+        <v>524</v>
+      </c>
+      <c r="C177" s="23"/>
+      <c r="D177" s="39"/>
+      <c r="E177" s="17"/>
+      <c r="F177" s="20"/>
+      <c r="G177" s="18"/>
     </row>
     <row r="178" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A178" s="17" t="s">
-        <v>103</v>
+        <v>71</v>
       </c>
       <c r="B178" s="17" t="s">
-        <v>522</v>
-      </c>
-      <c r="C178" s="23" t="b">
-        <v>0</v>
-      </c>
-      <c r="D178" s="17" t="s">
-        <v>407</v>
-      </c>
-      <c r="E178" s="17" t="s">
-        <v>406</v>
-      </c>
+        <v>524</v>
+      </c>
+      <c r="C178" s="23"/>
+      <c r="D178" s="39"/>
+      <c r="E178" s="17"/>
       <c r="F178" s="20"/>
       <c r="G178" s="18"/>
     </row>
-    <row r="179" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A179" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="B179" s="12" t="s">
-        <v>522</v>
-      </c>
-      <c r="C179" s="24" t="b">
-        <v>0</v>
-      </c>
-      <c r="D179" s="12" t="s">
-        <v>410</v>
-      </c>
-      <c r="E179" s="12" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="180" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A180" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="B180" s="12" t="s">
-        <v>522</v>
-      </c>
-      <c r="C180" s="24" t="b">
-        <v>0</v>
-      </c>
-      <c r="D180" s="12" t="s">
-        <v>412</v>
-      </c>
-      <c r="E180" s="12" t="s">
-        <v>404</v>
-      </c>
+    <row r="179" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A179" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="B179" s="17" t="s">
+        <v>524</v>
+      </c>
+      <c r="C179" s="23"/>
+      <c r="D179" s="39"/>
+      <c r="E179" s="17"/>
+      <c r="F179" s="20"/>
+      <c r="G179" s="18"/>
+    </row>
+    <row r="180" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A180" s="17" t="s">
+        <v>634</v>
+      </c>
+      <c r="B180" s="17" t="s">
+        <v>524</v>
+      </c>
+      <c r="C180" s="23"/>
+      <c r="D180" s="39"/>
+      <c r="E180" s="17"/>
+      <c r="F180" s="20"/>
+      <c r="G180" s="18"/>
     </row>
     <row r="181" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A181" s="17" t="s">
-        <v>105</v>
+        <v>75</v>
       </c>
       <c r="B181" s="17" t="s">
-        <v>522</v>
-      </c>
-      <c r="C181" s="23" t="b">
-        <v>0</v>
-      </c>
-      <c r="D181" s="17" t="s">
-        <v>407</v>
-      </c>
-      <c r="E181" s="17" t="s">
-        <v>406</v>
-      </c>
+        <v>524</v>
+      </c>
+      <c r="C181" s="23"/>
+      <c r="D181" s="39"/>
+      <c r="E181" s="17"/>
       <c r="F181" s="20"/>
       <c r="G181" s="18"/>
     </row>
-    <row r="182" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A182" s="12" t="s">
-        <v>105</v>
-      </c>
-      <c r="B182" s="12" t="s">
-        <v>522</v>
-      </c>
-      <c r="C182" s="24" t="b">
-        <v>0</v>
-      </c>
-      <c r="D182" s="12" t="s">
-        <v>410</v>
-      </c>
-      <c r="E182" s="12" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="183" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A183" s="12" t="s">
-        <v>105</v>
-      </c>
-      <c r="B183" s="12" t="s">
-        <v>522</v>
-      </c>
-      <c r="C183" s="24" t="b">
-        <v>0</v>
-      </c>
-      <c r="D183" s="12" t="s">
-        <v>412</v>
-      </c>
-      <c r="E183" s="12" t="s">
-        <v>404</v>
-      </c>
+    <row r="182" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A182" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="B182" s="17" t="s">
+        <v>524</v>
+      </c>
+      <c r="C182" s="23"/>
+      <c r="D182" s="39"/>
+      <c r="E182" s="17"/>
+      <c r="F182" s="20"/>
+      <c r="G182" s="18"/>
+    </row>
+    <row r="183" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A183" s="17" t="s">
+        <v>79</v>
+      </c>
+      <c r="B183" s="17" t="s">
+        <v>524</v>
+      </c>
+      <c r="C183" s="23"/>
+      <c r="D183" s="39"/>
+      <c r="E183" s="17"/>
+      <c r="F183" s="20"/>
+      <c r="G183" s="18"/>
     </row>
     <row r="184" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A184" s="17" t="s">
-        <v>107</v>
+        <v>81</v>
       </c>
       <c r="B184" s="17" t="s">
-        <v>522</v>
-      </c>
-      <c r="C184" s="23" t="b">
-        <v>0</v>
-      </c>
-      <c r="D184" s="17" t="s">
-        <v>407</v>
-      </c>
-      <c r="E184" s="17" t="s">
-        <v>406</v>
-      </c>
+        <v>524</v>
+      </c>
+      <c r="C184" s="23"/>
+      <c r="D184" s="39"/>
+      <c r="E184" s="17"/>
       <c r="F184" s="20"/>
       <c r="G184" s="18"/>
     </row>
-    <row r="185" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A185" s="12" t="s">
-        <v>107</v>
-      </c>
-      <c r="B185" s="12" t="s">
-        <v>522</v>
-      </c>
-      <c r="C185" s="24" t="b">
-        <v>0</v>
-      </c>
-      <c r="D185" s="12" t="s">
+    <row r="185" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A185" s="17" t="s">
+        <v>83</v>
+      </c>
+      <c r="B185" s="17" t="s">
+        <v>522</v>
+      </c>
+      <c r="C185" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="D185" s="39" t="s">
         <v>410</v>
       </c>
-      <c r="E185" s="12" t="s">
-        <v>409</v>
-      </c>
+      <c r="E185" s="17" t="s">
+        <v>456</v>
+      </c>
+      <c r="F185" s="20"/>
+      <c r="G185" s="18"/>
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A186" s="12" t="s">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="B186" s="12" t="s">
         <v>522</v>
@@ -23210,35 +23560,33 @@
       <c r="C186" s="24" t="b">
         <v>0</v>
       </c>
-      <c r="D186" s="12" t="s">
-        <v>412</v>
+      <c r="D186" s="40" t="s">
+        <v>458</v>
       </c>
       <c r="E186" s="12" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="187" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A187" s="17" t="s">
-        <v>109</v>
-      </c>
-      <c r="B187" s="17" t="s">
-        <v>522</v>
-      </c>
-      <c r="C187" s="23" t="b">
-        <v>0</v>
-      </c>
-      <c r="D187" s="17" t="s">
-        <v>407</v>
-      </c>
-      <c r="E187" s="17" t="s">
-        <v>406</v>
-      </c>
-      <c r="F187" s="20"/>
-      <c r="G187" s="18"/>
+        <v>457</v>
+      </c>
+    </row>
+    <row r="187" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A187" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="B187" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="C187" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="D187" s="40" t="s">
+        <v>460</v>
+      </c>
+      <c r="E187" s="12" t="s">
+        <v>459</v>
+      </c>
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A188" s="12" t="s">
-        <v>109</v>
+        <v>83</v>
       </c>
       <c r="B188" s="12" t="s">
         <v>522</v>
@@ -23246,16 +23594,16 @@
       <c r="C188" s="24" t="b">
         <v>0</v>
       </c>
-      <c r="D188" s="12" t="s">
-        <v>410</v>
+      <c r="D188" s="40" t="s">
+        <v>462</v>
       </c>
       <c r="E188" s="12" t="s">
-        <v>409</v>
+        <v>461</v>
       </c>
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A189" s="12" t="s">
-        <v>109</v>
+        <v>83</v>
       </c>
       <c r="B189" s="12" t="s">
         <v>522</v>
@@ -23263,35 +23611,33 @@
       <c r="C189" s="24" t="b">
         <v>0</v>
       </c>
-      <c r="D189" s="12" t="s">
-        <v>412</v>
+      <c r="D189" s="40" t="s">
+        <v>443</v>
       </c>
       <c r="E189" s="12" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="190" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A190" s="17" t="s">
-        <v>111</v>
-      </c>
-      <c r="B190" s="17" t="s">
-        <v>522</v>
-      </c>
-      <c r="C190" s="23" t="b">
-        <v>0</v>
-      </c>
-      <c r="D190" s="17" t="s">
-        <v>407</v>
-      </c>
-      <c r="E190" s="17" t="s">
-        <v>406</v>
-      </c>
-      <c r="F190" s="20"/>
-      <c r="G190" s="18"/>
+        <v>463</v>
+      </c>
+    </row>
+    <row r="190" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A190" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="B190" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="C190" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="D190" s="40" t="s">
+        <v>465</v>
+      </c>
+      <c r="E190" s="12" t="s">
+        <v>464</v>
+      </c>
     </row>
     <row r="191" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A191" s="12" t="s">
-        <v>111</v>
+        <v>83</v>
       </c>
       <c r="B191" s="12" t="s">
         <v>522</v>
@@ -23299,52 +23645,55 @@
       <c r="C191" s="24" t="b">
         <v>0</v>
       </c>
-      <c r="D191" s="12" t="s">
-        <v>410</v>
+      <c r="D191" s="40" t="s">
+        <v>412</v>
       </c>
       <c r="E191" s="12" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="192" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A192" s="12" t="s">
-        <v>111</v>
-      </c>
-      <c r="B192" s="12" t="s">
-        <v>522</v>
-      </c>
-      <c r="C192" s="24" t="b">
-        <v>0</v>
-      </c>
-      <c r="D192" s="12" t="s">
-        <v>412</v>
-      </c>
-      <c r="E192" s="12" t="s">
         <v>404</v>
       </c>
-    </row>
-    <row r="193" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A193" s="17" t="s">
-        <v>113</v>
-      </c>
-      <c r="B193" s="17" t="s">
-        <v>522</v>
-      </c>
-      <c r="C193" s="23" t="b">
-        <v>0</v>
-      </c>
-      <c r="D193" s="17" t="s">
-        <v>407</v>
-      </c>
-      <c r="E193" s="17" t="s">
-        <v>406</v>
-      </c>
-      <c r="F193" s="20"/>
-      <c r="G193" s="18"/>
+      <c r="G191" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="192" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A192" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="B192" s="17" t="s">
+        <v>522</v>
+      </c>
+      <c r="C192" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="D192" s="41" t="s">
+        <v>460</v>
+      </c>
+      <c r="E192" s="17" t="s">
+        <v>466</v>
+      </c>
+      <c r="F192" s="20"/>
+      <c r="G192" s="18"/>
+    </row>
+    <row r="193" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A193" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="B193" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="C193" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="D193" s="42" t="s">
+        <v>467</v>
+      </c>
+      <c r="E193" s="12" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="194" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A194" s="12" t="s">
-        <v>113</v>
+        <v>85</v>
       </c>
       <c r="B194" s="12" t="s">
         <v>522</v>
@@ -23352,16 +23701,16 @@
       <c r="C194" s="24" t="b">
         <v>0</v>
       </c>
-      <c r="D194" s="12" t="s">
-        <v>410</v>
+      <c r="D194" s="42" t="s">
+        <v>465</v>
       </c>
       <c r="E194" s="12" t="s">
-        <v>409</v>
+        <v>473</v>
       </c>
     </row>
     <row r="195" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A195" s="12" t="s">
-        <v>113</v>
+        <v>85</v>
       </c>
       <c r="B195" s="12" t="s">
         <v>522</v>
@@ -23369,35 +23718,33 @@
       <c r="C195" s="24" t="b">
         <v>0</v>
       </c>
-      <c r="D195" s="12" t="s">
-        <v>412</v>
+      <c r="D195" s="42" t="s">
+        <v>447</v>
       </c>
       <c r="E195" s="12" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="196" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A196" s="17" t="s">
-        <v>115</v>
-      </c>
-      <c r="B196" s="17" t="s">
-        <v>522</v>
-      </c>
-      <c r="C196" s="23" t="b">
-        <v>0</v>
-      </c>
-      <c r="D196" s="17" t="s">
-        <v>407</v>
-      </c>
-      <c r="E196" s="17" t="s">
-        <v>406</v>
-      </c>
-      <c r="F196" s="20"/>
-      <c r="G196" s="18"/>
+        <v>468</v>
+      </c>
+    </row>
+    <row r="196" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A196" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="B196" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="C196" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="D196" s="42" t="s">
+        <v>470</v>
+      </c>
+      <c r="E196" s="12" t="s">
+        <v>469</v>
+      </c>
     </row>
     <row r="197" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A197" s="12" t="s">
-        <v>115</v>
+        <v>85</v>
       </c>
       <c r="B197" s="12" t="s">
         <v>522</v>
@@ -23405,16 +23752,16 @@
       <c r="C197" s="24" t="b">
         <v>0</v>
       </c>
-      <c r="D197" s="12" t="s">
-        <v>410</v>
+      <c r="D197" s="42" t="s">
+        <v>458</v>
       </c>
       <c r="E197" s="12" t="s">
-        <v>409</v>
+        <v>472</v>
       </c>
     </row>
     <row r="198" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A198" s="12" t="s">
-        <v>115</v>
+        <v>85</v>
       </c>
       <c r="B198" s="12" t="s">
         <v>522</v>
@@ -23422,7 +23769,7 @@
       <c r="C198" s="24" t="b">
         <v>0</v>
       </c>
-      <c r="D198" s="12" t="s">
+      <c r="D198" s="42" t="s">
         <v>412</v>
       </c>
       <c r="E198" s="12" t="s">
@@ -23431,7 +23778,7 @@
     </row>
     <row r="199" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A199" s="17" t="s">
-        <v>117</v>
+        <v>87</v>
       </c>
       <c r="B199" s="17" t="s">
         <v>522</v>
@@ -23439,7 +23786,7 @@
       <c r="C199" s="23" t="b">
         <v>0</v>
       </c>
-      <c r="D199" s="17" t="s">
+      <c r="D199" s="39" t="s">
         <v>407</v>
       </c>
       <c r="E199" s="17" t="s">
@@ -23450,7 +23797,7 @@
     </row>
     <row r="200" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A200" s="12" t="s">
-        <v>117</v>
+        <v>87</v>
       </c>
       <c r="B200" s="12" t="s">
         <v>522</v>
@@ -23458,7 +23805,7 @@
       <c r="C200" s="24" t="b">
         <v>0</v>
       </c>
-      <c r="D200" s="12" t="s">
+      <c r="D200" s="40" t="s">
         <v>410</v>
       </c>
       <c r="E200" s="12" t="s">
@@ -23467,7 +23814,7 @@
     </row>
     <row r="201" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A201" s="12" t="s">
-        <v>117</v>
+        <v>87</v>
       </c>
       <c r="B201" s="12" t="s">
         <v>522</v>
@@ -23475,7 +23822,7 @@
       <c r="C201" s="24" t="b">
         <v>0</v>
       </c>
-      <c r="D201" s="12" t="s">
+      <c r="D201" s="40" t="s">
         <v>412</v>
       </c>
       <c r="E201" s="12" t="s">
@@ -23484,96 +23831,72 @@
     </row>
     <row r="202" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A202" s="17" t="s">
-        <v>119</v>
+        <v>647</v>
       </c>
       <c r="B202" s="17" t="s">
-        <v>522</v>
-      </c>
-      <c r="C202" s="23" t="b">
-        <v>0</v>
-      </c>
-      <c r="D202" s="17" t="s">
-        <v>407</v>
-      </c>
-      <c r="E202" s="17" t="s">
-        <v>406</v>
-      </c>
+        <v>524</v>
+      </c>
+      <c r="C202" s="23"/>
+      <c r="D202" s="39"/>
+      <c r="E202" s="17"/>
       <c r="F202" s="20"/>
       <c r="G202" s="18"/>
     </row>
-    <row r="203" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A203" s="12" t="s">
-        <v>119</v>
-      </c>
-      <c r="B203" s="12" t="s">
-        <v>522</v>
-      </c>
-      <c r="C203" s="24" t="b">
-        <v>0</v>
-      </c>
-      <c r="D203" s="12" t="s">
-        <v>410</v>
-      </c>
-      <c r="E203" s="12" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="204" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A204" s="12" t="s">
-        <v>119</v>
-      </c>
-      <c r="B204" s="12" t="s">
-        <v>522</v>
-      </c>
-      <c r="C204" s="24" t="b">
-        <v>0</v>
-      </c>
-      <c r="D204" s="12" t="s">
-        <v>412</v>
-      </c>
-      <c r="E204" s="12" t="s">
-        <v>404</v>
-      </c>
+    <row r="203" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A203" s="17" t="s">
+        <v>648</v>
+      </c>
+      <c r="B203" s="17" t="s">
+        <v>524</v>
+      </c>
+      <c r="C203" s="23"/>
+      <c r="D203" s="39"/>
+      <c r="E203" s="17"/>
+      <c r="F203" s="20"/>
+      <c r="G203" s="18"/>
+    </row>
+    <row r="204" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A204" s="17" t="s">
+        <v>649</v>
+      </c>
+      <c r="B204" s="17" t="s">
+        <v>524</v>
+      </c>
+      <c r="C204" s="23"/>
+      <c r="D204" s="39"/>
+      <c r="E204" s="17"/>
+      <c r="F204" s="20"/>
+      <c r="G204" s="18"/>
     </row>
     <row r="205" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A205" s="17" t="s">
-        <v>121</v>
+        <v>650</v>
       </c>
       <c r="B205" s="17" t="s">
-        <v>522</v>
-      </c>
-      <c r="C205" s="23" t="b">
-        <v>0</v>
-      </c>
-      <c r="D205" s="17">
-        <v>10</v>
-      </c>
-      <c r="E205" s="17" t="s">
-        <v>574</v>
-      </c>
+        <v>524</v>
+      </c>
+      <c r="C205" s="23"/>
+      <c r="D205" s="39"/>
+      <c r="E205" s="17"/>
       <c r="F205" s="20"/>
       <c r="G205" s="18"/>
     </row>
-    <row r="206" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A206" s="12" t="s">
-        <v>121</v>
-      </c>
-      <c r="B206" s="12" t="s">
-        <v>522</v>
-      </c>
-      <c r="C206" s="24" t="b">
-        <v>0</v>
-      </c>
-      <c r="D206" s="12">
-        <v>11</v>
-      </c>
-      <c r="E206" s="12" t="s">
-        <v>575</v>
-      </c>
+    <row r="206" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A206" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="B206" s="17" t="s">
+        <v>524</v>
+      </c>
+      <c r="C206" s="23"/>
+      <c r="D206" s="39"/>
+      <c r="E206" s="17"/>
+      <c r="F206" s="20"/>
+      <c r="G206" s="18"/>
     </row>
     <row r="207" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A207" s="12" t="s">
-        <v>121</v>
+        <v>91</v>
       </c>
       <c r="B207" s="12" t="s">
         <v>522</v>
@@ -23581,16 +23904,16 @@
       <c r="C207" s="24" t="b">
         <v>0</v>
       </c>
-      <c r="D207" s="12">
-        <v>12</v>
+      <c r="D207" s="40">
+        <v>0</v>
       </c>
       <c r="E207" s="12" t="s">
-        <v>576</v>
+        <v>551</v>
       </c>
     </row>
     <row r="208" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A208" s="12" t="s">
-        <v>121</v>
+        <v>91</v>
       </c>
       <c r="B208" s="12" t="s">
         <v>522</v>
@@ -23598,16 +23921,16 @@
       <c r="C208" s="24" t="b">
         <v>0</v>
       </c>
-      <c r="D208" s="12">
-        <v>13</v>
+      <c r="D208" s="40">
+        <v>1</v>
       </c>
       <c r="E208" s="12" t="s">
-        <v>577</v>
-      </c>
-    </row>
-    <row r="209" spans="1:5" x14ac:dyDescent="0.25">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="209" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A209" s="12" t="s">
-        <v>121</v>
+        <v>91</v>
       </c>
       <c r="B209" s="12" t="s">
         <v>522</v>
@@ -23615,16 +23938,16 @@
       <c r="C209" s="24" t="b">
         <v>0</v>
       </c>
-      <c r="D209" s="12">
-        <v>14</v>
+      <c r="D209" s="40">
+        <v>2</v>
       </c>
       <c r="E209" s="12" t="s">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="210" spans="1:5" x14ac:dyDescent="0.25">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="210" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A210" s="12" t="s">
-        <v>121</v>
+        <v>91</v>
       </c>
       <c r="B210" s="12" t="s">
         <v>522</v>
@@ -23632,16 +23955,16 @@
       <c r="C210" s="24" t="b">
         <v>0</v>
       </c>
-      <c r="D210" s="12">
-        <v>20</v>
+      <c r="D210" s="40">
+        <v>3</v>
       </c>
       <c r="E210" s="12" t="s">
-        <v>579</v>
-      </c>
-    </row>
-    <row r="211" spans="1:5" x14ac:dyDescent="0.25">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="211" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A211" s="12" t="s">
-        <v>121</v>
+        <v>91</v>
       </c>
       <c r="B211" s="12" t="s">
         <v>522</v>
@@ -23649,16 +23972,16 @@
       <c r="C211" s="24" t="b">
         <v>0</v>
       </c>
-      <c r="D211" s="12">
-        <v>21</v>
+      <c r="D211" s="40">
+        <v>4</v>
       </c>
       <c r="E211" s="12" t="s">
-        <v>580</v>
-      </c>
-    </row>
-    <row r="212" spans="1:5" x14ac:dyDescent="0.25">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="212" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A212" s="12" t="s">
-        <v>121</v>
+        <v>91</v>
       </c>
       <c r="B212" s="12" t="s">
         <v>522</v>
@@ -23666,16 +23989,16 @@
       <c r="C212" s="24" t="b">
         <v>0</v>
       </c>
-      <c r="D212" s="12">
-        <v>22</v>
+      <c r="D212" s="40">
+        <v>5</v>
       </c>
       <c r="E212" s="12" t="s">
-        <v>581</v>
-      </c>
-    </row>
-    <row r="213" spans="1:5" x14ac:dyDescent="0.25">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="213" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A213" s="12" t="s">
-        <v>121</v>
+        <v>91</v>
       </c>
       <c r="B213" s="12" t="s">
         <v>522</v>
@@ -23683,16 +24006,16 @@
       <c r="C213" s="24" t="b">
         <v>0</v>
       </c>
-      <c r="D213" s="12">
-        <v>23</v>
+      <c r="D213" s="40">
+        <v>6</v>
       </c>
       <c r="E213" s="12" t="s">
-        <v>582</v>
-      </c>
-    </row>
-    <row r="214" spans="1:5" x14ac:dyDescent="0.25">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="214" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A214" s="12" t="s">
-        <v>121</v>
+        <v>91</v>
       </c>
       <c r="B214" s="12" t="s">
         <v>522</v>
@@ -23700,16 +24023,16 @@
       <c r="C214" s="24" t="b">
         <v>0</v>
       </c>
-      <c r="D214" s="12">
-        <v>24</v>
+      <c r="D214" s="40">
+        <v>7</v>
       </c>
       <c r="E214" s="12" t="s">
-        <v>583</v>
-      </c>
-    </row>
-    <row r="215" spans="1:5" x14ac:dyDescent="0.25">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="215" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A215" s="12" t="s">
-        <v>121</v>
+        <v>91</v>
       </c>
       <c r="B215" s="12" t="s">
         <v>522</v>
@@ -23717,16 +24040,16 @@
       <c r="C215" s="24" t="b">
         <v>0</v>
       </c>
-      <c r="D215" s="12">
-        <v>25</v>
+      <c r="D215" s="40">
+        <v>8</v>
       </c>
       <c r="E215" s="12" t="s">
-        <v>584</v>
-      </c>
-    </row>
-    <row r="216" spans="1:5" x14ac:dyDescent="0.25">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="216" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A216" s="12" t="s">
-        <v>121</v>
+        <v>91</v>
       </c>
       <c r="B216" s="12" t="s">
         <v>522</v>
@@ -23734,33 +24057,35 @@
       <c r="C216" s="24" t="b">
         <v>0</v>
       </c>
-      <c r="D216" s="12">
-        <v>26</v>
+      <c r="D216" s="40">
+        <v>9</v>
       </c>
       <c r="E216" s="12" t="s">
-        <v>585</v>
-      </c>
-    </row>
-    <row r="217" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A217" s="12" t="s">
-        <v>121</v>
-      </c>
-      <c r="B217" s="12" t="s">
-        <v>522</v>
-      </c>
-      <c r="C217" s="24" t="b">
-        <v>0</v>
-      </c>
-      <c r="D217" s="12">
-        <v>27</v>
-      </c>
-      <c r="E217" s="12" t="s">
-        <v>586</v>
-      </c>
-    </row>
-    <row r="218" spans="1:5" x14ac:dyDescent="0.25">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="217" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A217" s="17" t="s">
+        <v>93</v>
+      </c>
+      <c r="B217" s="17" t="s">
+        <v>522</v>
+      </c>
+      <c r="C217" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="D217" s="39">
+        <v>1</v>
+      </c>
+      <c r="E217" s="17" t="s">
+        <v>569</v>
+      </c>
+      <c r="F217" s="20"/>
+      <c r="G217" s="18"/>
+    </row>
+    <row r="218" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A218" s="12" t="s">
-        <v>121</v>
+        <v>93</v>
       </c>
       <c r="B218" s="12" t="s">
         <v>522</v>
@@ -23768,16 +24093,16 @@
       <c r="C218" s="24" t="b">
         <v>0</v>
       </c>
-      <c r="D218" s="12">
-        <v>28</v>
+      <c r="D218" s="40">
+        <v>2</v>
       </c>
       <c r="E218" s="12" t="s">
-        <v>587</v>
-      </c>
-    </row>
-    <row r="219" spans="1:5" x14ac:dyDescent="0.25">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="219" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A219" s="12" t="s">
-        <v>121</v>
+        <v>93</v>
       </c>
       <c r="B219" s="12" t="s">
         <v>522</v>
@@ -23785,16 +24110,16 @@
       <c r="C219" s="24" t="b">
         <v>0</v>
       </c>
-      <c r="D219" s="12">
-        <v>29</v>
+      <c r="D219" s="40">
+        <v>3</v>
       </c>
       <c r="E219" s="12" t="s">
-        <v>588</v>
-      </c>
-    </row>
-    <row r="220" spans="1:5" x14ac:dyDescent="0.25">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="220" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A220" s="12" t="s">
-        <v>121</v>
+        <v>93</v>
       </c>
       <c r="B220" s="12" t="s">
         <v>522</v>
@@ -23802,16 +24127,16 @@
       <c r="C220" s="24" t="b">
         <v>0</v>
       </c>
-      <c r="D220" s="12">
-        <v>30</v>
+      <c r="D220" s="40">
+        <v>4</v>
       </c>
       <c r="E220" s="12" t="s">
-        <v>589</v>
-      </c>
-    </row>
-    <row r="221" spans="1:5" x14ac:dyDescent="0.25">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="221" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A221" s="12" t="s">
-        <v>121</v>
+        <v>93</v>
       </c>
       <c r="B221" s="12" t="s">
         <v>522</v>
@@ -23819,16 +24144,16 @@
       <c r="C221" s="24" t="b">
         <v>0</v>
       </c>
-      <c r="D221" s="12">
-        <v>31</v>
+      <c r="D221" s="40">
+        <v>8</v>
       </c>
       <c r="E221" s="12" t="s">
-        <v>590</v>
-      </c>
-    </row>
-    <row r="222" spans="1:5" x14ac:dyDescent="0.25">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="222" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A222" s="12" t="s">
-        <v>121</v>
+        <v>93</v>
       </c>
       <c r="B222" s="12" t="s">
         <v>522</v>
@@ -23836,33 +24161,33 @@
       <c r="C222" s="24" t="b">
         <v>0</v>
       </c>
-      <c r="D222" s="12">
-        <v>32</v>
+      <c r="D222" s="40">
+        <v>9</v>
       </c>
       <c r="E222" s="12" t="s">
-        <v>591</v>
-      </c>
-    </row>
-    <row r="223" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A223" s="12" t="s">
-        <v>121</v>
-      </c>
-      <c r="B223" s="12" t="s">
-        <v>522</v>
-      </c>
-      <c r="C223" s="24" t="b">
-        <v>0</v>
-      </c>
-      <c r="D223" s="12">
-        <v>33</v>
-      </c>
-      <c r="E223" s="12" t="s">
-        <v>592</v>
-      </c>
-    </row>
-    <row r="224" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="223" spans="1:7" s="21" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A223" s="17" t="s">
+        <v>716</v>
+      </c>
+      <c r="B223" s="17" t="s">
+        <v>522</v>
+      </c>
+      <c r="C223" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="D223" s="39" t="s">
+        <v>717</v>
+      </c>
+      <c r="E223" s="17"/>
+      <c r="F223" s="20"/>
+      <c r="G223" s="18"/>
+    </row>
+    <row r="224" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A224" s="12" t="s">
-        <v>121</v>
+        <v>716</v>
       </c>
       <c r="B224" s="12" t="s">
         <v>522</v>
@@ -23870,16 +24195,16 @@
       <c r="C224" s="24" t="b">
         <v>0</v>
       </c>
-      <c r="D224" s="12">
-        <v>34</v>
+      <c r="D224" s="40" t="s">
+        <v>718</v>
       </c>
       <c r="E224" s="12" t="s">
-        <v>593</v>
+        <v>717</v>
       </c>
     </row>
     <row r="225" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A225" s="12" t="s">
-        <v>121</v>
+        <v>716</v>
       </c>
       <c r="B225" s="12" t="s">
         <v>522</v>
@@ -23887,16 +24212,16 @@
       <c r="C225" s="24" t="b">
         <v>0</v>
       </c>
-      <c r="D225" s="12">
-        <v>35</v>
+      <c r="D225" s="40" t="s">
+        <v>719</v>
       </c>
       <c r="E225" s="12" t="s">
-        <v>594</v>
+        <v>718</v>
       </c>
     </row>
     <row r="226" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A226" s="12" t="s">
-        <v>121</v>
+        <v>716</v>
       </c>
       <c r="B226" s="12" t="s">
         <v>522</v>
@@ -23904,16 +24229,16 @@
       <c r="C226" s="24" t="b">
         <v>0</v>
       </c>
-      <c r="D226" s="12">
-        <v>36</v>
+      <c r="D226" s="40" t="s">
+        <v>720</v>
       </c>
       <c r="E226" s="12" t="s">
-        <v>595</v>
-      </c>
-    </row>
-    <row r="227" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="227" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A227" s="12" t="s">
-        <v>121</v>
+        <v>716</v>
       </c>
       <c r="B227" s="12" t="s">
         <v>522</v>
@@ -23921,16 +24246,16 @@
       <c r="C227" s="24" t="b">
         <v>0</v>
       </c>
-      <c r="D227" s="12">
-        <v>37</v>
+      <c r="D227" s="40" t="s">
+        <v>721</v>
       </c>
       <c r="E227" s="12" t="s">
-        <v>596</v>
+        <v>720</v>
       </c>
     </row>
     <row r="228" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A228" s="12" t="s">
-        <v>121</v>
+        <v>716</v>
       </c>
       <c r="B228" s="12" t="s">
         <v>522</v>
@@ -23938,33 +24263,35 @@
       <c r="C228" s="24" t="b">
         <v>0</v>
       </c>
-      <c r="D228" s="12">
-        <v>38</v>
+      <c r="D228" s="40" t="s">
+        <v>730</v>
       </c>
       <c r="E228" s="12" t="s">
-        <v>597</v>
-      </c>
-    </row>
-    <row r="229" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A229" s="12" t="s">
-        <v>121</v>
-      </c>
-      <c r="B229" s="12" t="s">
-        <v>522</v>
-      </c>
-      <c r="C229" s="24" t="b">
-        <v>0</v>
-      </c>
-      <c r="D229" s="12">
-        <v>39</v>
-      </c>
-      <c r="E229" s="12" t="s">
-        <v>598</v>
-      </c>
+        <v>721</v>
+      </c>
+    </row>
+    <row r="229" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A229" s="17" t="s">
+        <v>95</v>
+      </c>
+      <c r="B229" s="17" t="s">
+        <v>522</v>
+      </c>
+      <c r="C229" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="D229" s="39" t="s">
+        <v>407</v>
+      </c>
+      <c r="E229" s="17" t="s">
+        <v>406</v>
+      </c>
+      <c r="F229" s="20"/>
+      <c r="G229" s="18"/>
     </row>
     <row r="230" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A230" s="12" t="s">
-        <v>121</v>
+        <v>95</v>
       </c>
       <c r="B230" s="12" t="s">
         <v>522</v>
@@ -23972,16 +24299,16 @@
       <c r="C230" s="24" t="b">
         <v>0</v>
       </c>
-      <c r="D230" s="12">
-        <v>40</v>
+      <c r="D230" s="40" t="s">
+        <v>410</v>
       </c>
       <c r="E230" s="12" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="231" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="231" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A231" s="12" t="s">
-        <v>121</v>
+        <v>95</v>
       </c>
       <c r="B231" s="12" t="s">
         <v>522</v>
@@ -23989,33 +24316,35 @@
       <c r="C231" s="24" t="b">
         <v>0</v>
       </c>
-      <c r="D231" s="12">
-        <v>41</v>
+      <c r="D231" s="40" t="s">
+        <v>412</v>
       </c>
       <c r="E231" s="12" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="232" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A232" s="12" t="s">
-        <v>121</v>
-      </c>
-      <c r="B232" s="12" t="s">
-        <v>522</v>
-      </c>
-      <c r="C232" s="24" t="b">
-        <v>0</v>
-      </c>
-      <c r="D232" s="12">
-        <v>42</v>
-      </c>
-      <c r="E232" s="12" t="s">
-        <v>601</v>
-      </c>
-    </row>
-    <row r="233" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="232" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A232" s="17" t="s">
+        <v>674</v>
+      </c>
+      <c r="B232" s="17" t="s">
+        <v>522</v>
+      </c>
+      <c r="C232" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="D232" s="39" t="s">
+        <v>407</v>
+      </c>
+      <c r="E232" s="17" t="s">
+        <v>406</v>
+      </c>
+      <c r="F232" s="20"/>
+      <c r="G232" s="18"/>
+    </row>
+    <row r="233" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A233" s="12" t="s">
-        <v>121</v>
+        <v>674</v>
       </c>
       <c r="B233" s="12" t="s">
         <v>522</v>
@@ -24023,33 +24352,35 @@
       <c r="C233" s="24" t="b">
         <v>0</v>
       </c>
-      <c r="D233" s="12">
-        <v>43</v>
+      <c r="D233" s="40" t="s">
+        <v>410</v>
       </c>
       <c r="E233" s="12" t="s">
-        <v>602</v>
-      </c>
-    </row>
-    <row r="234" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A234" s="12" t="s">
-        <v>121</v>
-      </c>
-      <c r="B234" s="12" t="s">
-        <v>522</v>
-      </c>
-      <c r="C234" s="24" t="b">
-        <v>0</v>
-      </c>
-      <c r="D234" s="12">
-        <v>44</v>
-      </c>
-      <c r="E234" s="12" t="s">
-        <v>603</v>
-      </c>
-    </row>
-    <row r="235" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="234" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A234" s="17" t="s">
+        <v>97</v>
+      </c>
+      <c r="B234" s="17" t="s">
+        <v>522</v>
+      </c>
+      <c r="C234" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="D234" s="39" t="s">
+        <v>407</v>
+      </c>
+      <c r="E234" s="17" t="s">
+        <v>406</v>
+      </c>
+      <c r="F234" s="20"/>
+      <c r="G234" s="18"/>
+    </row>
+    <row r="235" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A235" s="12" t="s">
-        <v>121</v>
+        <v>97</v>
       </c>
       <c r="B235" s="12" t="s">
         <v>522</v>
@@ -24057,16 +24388,16 @@
       <c r="C235" s="24" t="b">
         <v>0</v>
       </c>
-      <c r="D235" s="12">
-        <v>50</v>
+      <c r="D235" s="40" t="s">
+        <v>410</v>
       </c>
       <c r="E235" s="12" t="s">
-        <v>604</v>
+        <v>409</v>
       </c>
     </row>
     <row r="236" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A236" s="12" t="s">
-        <v>121</v>
+        <v>97</v>
       </c>
       <c r="B236" s="12" t="s">
         <v>522</v>
@@ -24074,401 +24405,487 @@
       <c r="C236" s="24" t="b">
         <v>0</v>
       </c>
-      <c r="D236" s="12">
-        <v>99</v>
+      <c r="D236" s="40" t="s">
+        <v>412</v>
       </c>
       <c r="E236" s="12" t="s">
         <v>404</v>
       </c>
     </row>
     <row r="237" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A237" s="19" t="s">
-        <v>123</v>
-      </c>
-      <c r="B237" s="19" t="s">
+      <c r="A237" s="17" t="s">
+        <v>99</v>
+      </c>
+      <c r="B237" s="17" t="s">
         <v>522</v>
       </c>
       <c r="C237" s="23" t="b">
         <v>0</v>
       </c>
-      <c r="D237" s="19" t="s">
+      <c r="D237" s="39" t="s">
         <v>407</v>
       </c>
-      <c r="E237" s="19" t="s">
+      <c r="E237" s="17" t="s">
         <v>406</v>
       </c>
       <c r="F237" s="20"/>
       <c r="G237" s="18"/>
     </row>
     <row r="238" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A238" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="B238" s="4" t="s">
+      <c r="A238" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="B238" s="12" t="s">
         <v>522</v>
       </c>
       <c r="C238" s="24" t="b">
         <v>0</v>
       </c>
-      <c r="D238" s="4" t="s">
+      <c r="D238" s="40" t="s">
         <v>410</v>
       </c>
-      <c r="E238" s="4" t="s">
+      <c r="E238" s="12" t="s">
         <v>409</v>
       </c>
     </row>
     <row r="239" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A239" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="B239" s="4" t="s">
+      <c r="A239" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="B239" s="12" t="s">
         <v>522</v>
       </c>
       <c r="C239" s="24" t="b">
         <v>0</v>
       </c>
-      <c r="D239" s="4" t="s">
+      <c r="D239" s="40" t="s">
         <v>412</v>
       </c>
-      <c r="E239" s="4" t="s">
+      <c r="E239" s="12" t="s">
         <v>404</v>
       </c>
     </row>
     <row r="240" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A240" s="19" t="s">
-        <v>125</v>
-      </c>
-      <c r="B240" s="19" t="s">
+      <c r="A240" s="17" t="s">
+        <v>101</v>
+      </c>
+      <c r="B240" s="17" t="s">
         <v>522</v>
       </c>
       <c r="C240" s="23" t="b">
         <v>0</v>
       </c>
-      <c r="D240" s="19" t="s">
+      <c r="D240" s="39" t="s">
         <v>407</v>
       </c>
-      <c r="E240" s="19" t="s">
+      <c r="E240" s="17" t="s">
         <v>406</v>
       </c>
       <c r="F240" s="20"/>
       <c r="G240" s="18"/>
     </row>
     <row r="241" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A241" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="B241" s="4" t="s">
+      <c r="A241" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="B241" s="12" t="s">
         <v>522</v>
       </c>
       <c r="C241" s="24" t="b">
         <v>0</v>
       </c>
-      <c r="D241" s="4" t="s">
+      <c r="D241" s="40" t="s">
         <v>410</v>
       </c>
-      <c r="E241" s="4" t="s">
+      <c r="E241" s="12" t="s">
         <v>409</v>
       </c>
     </row>
     <row r="242" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A242" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="B242" s="4" t="s">
+      <c r="A242" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="B242" s="12" t="s">
         <v>522</v>
       </c>
       <c r="C242" s="24" t="b">
         <v>0</v>
       </c>
-      <c r="D242" s="4" t="s">
+      <c r="D242" s="40" t="s">
         <v>412</v>
       </c>
-      <c r="E242" s="4" t="s">
+      <c r="E242" s="12" t="s">
         <v>404</v>
       </c>
     </row>
     <row r="243" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A243" s="19" t="s">
-        <v>127</v>
-      </c>
-      <c r="B243" s="19" t="s">
+      <c r="A243" s="17" t="s">
+        <v>673</v>
+      </c>
+      <c r="B243" s="17" t="s">
         <v>524</v>
       </c>
       <c r="C243" s="23"/>
-      <c r="D243" s="17"/>
+      <c r="D243" s="39"/>
       <c r="E243" s="17"/>
       <c r="F243" s="20"/>
       <c r="G243" s="18"/>
     </row>
     <row r="244" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A244" s="19" t="s">
-        <v>149</v>
-      </c>
-      <c r="B244" s="19" t="s">
-        <v>524</v>
-      </c>
-      <c r="C244" s="23"/>
-      <c r="D244" s="17"/>
-      <c r="E244" s="17"/>
+      <c r="A244" s="17" t="s">
+        <v>714</v>
+      </c>
+      <c r="B244" s="17" t="s">
+        <v>522</v>
+      </c>
+      <c r="C244" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="D244" s="39" t="s">
+        <v>511</v>
+      </c>
+      <c r="E244" s="39" t="s">
+        <v>511</v>
+      </c>
       <c r="F244" s="20"/>
       <c r="G244" s="18"/>
     </row>
-    <row r="245" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A245" s="19" t="s">
-        <v>153</v>
-      </c>
-      <c r="B245" s="19" t="s">
-        <v>524</v>
-      </c>
-      <c r="C245" s="23"/>
-      <c r="D245" s="17"/>
-      <c r="E245" s="17"/>
-      <c r="F245" s="20"/>
-      <c r="G245" s="18"/>
+    <row r="245" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A245" s="12" t="s">
+        <v>714</v>
+      </c>
+      <c r="B245" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="C245" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="D245" s="40" t="s">
+        <v>715</v>
+      </c>
+      <c r="E245" s="40" t="s">
+        <v>715</v>
+      </c>
     </row>
     <row r="246" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A246" s="19" t="s">
-        <v>155</v>
-      </c>
-      <c r="B246" s="19" t="s">
-        <v>524</v>
-      </c>
-      <c r="C246" s="23"/>
-      <c r="D246" s="17"/>
-      <c r="E246" s="17"/>
+      <c r="A246" s="17" t="s">
+        <v>722</v>
+      </c>
+      <c r="B246" s="17" t="s">
+        <v>522</v>
+      </c>
+      <c r="C246" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="D246" s="43" t="s">
+        <v>723</v>
+      </c>
+      <c r="E246" s="43" t="s">
+        <v>723</v>
+      </c>
       <c r="F246" s="20"/>
       <c r="G246" s="18"/>
     </row>
-    <row r="247" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A247" s="19" t="s">
-        <v>157</v>
-      </c>
-      <c r="B247" s="19" t="s">
-        <v>524</v>
-      </c>
-      <c r="C247" s="23"/>
-      <c r="D247" s="17"/>
-      <c r="E247" s="17"/>
-      <c r="F247" s="20"/>
-      <c r="G247" s="18"/>
-    </row>
-    <row r="248" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A248" s="19" t="s">
-        <v>159</v>
-      </c>
-      <c r="B248" s="19" t="s">
-        <v>524</v>
-      </c>
-      <c r="C248" s="23"/>
-      <c r="D248" s="17"/>
-      <c r="E248" s="17"/>
-      <c r="F248" s="20"/>
-      <c r="G248" s="18"/>
-    </row>
-    <row r="249" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A249" s="19" t="s">
-        <v>161</v>
-      </c>
-      <c r="B249" s="19" t="s">
-        <v>524</v>
-      </c>
-      <c r="C249" s="23"/>
-      <c r="D249" s="17"/>
-      <c r="E249" s="17"/>
-      <c r="F249" s="20"/>
-      <c r="G249" s="18"/>
-    </row>
-    <row r="250" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A250" s="19" t="s">
-        <v>163</v>
-      </c>
-      <c r="B250" s="19" t="s">
-        <v>524</v>
-      </c>
-      <c r="C250" s="23"/>
-      <c r="D250" s="17"/>
-      <c r="E250" s="17"/>
-      <c r="F250" s="20"/>
-      <c r="G250" s="18"/>
-    </row>
-    <row r="251" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A251" s="19" t="s">
-        <v>165</v>
-      </c>
-      <c r="B251" s="19" t="s">
-        <v>524</v>
-      </c>
-      <c r="C251" s="23"/>
-      <c r="D251" s="17"/>
-      <c r="E251" s="17"/>
-      <c r="F251" s="20"/>
-      <c r="G251" s="18"/>
-    </row>
-    <row r="252" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A252" s="19" t="s">
-        <v>129</v>
-      </c>
-      <c r="B252" s="19" t="s">
-        <v>524</v>
-      </c>
-      <c r="C252" s="23"/>
-      <c r="D252" s="17"/>
-      <c r="E252" s="17"/>
-      <c r="F252" s="20"/>
-      <c r="G252" s="18"/>
+    <row r="247" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A247" s="12" t="s">
+        <v>722</v>
+      </c>
+      <c r="B247" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="C247" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="D247" s="40" t="s">
+        <v>724</v>
+      </c>
+      <c r="E247" s="40" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="248" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A248" s="12" t="s">
+        <v>722</v>
+      </c>
+      <c r="B248" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="C248" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="D248" s="40" t="s">
+        <v>725</v>
+      </c>
+      <c r="E248" s="40" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="249" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A249" s="12" t="s">
+        <v>722</v>
+      </c>
+      <c r="B249" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="C249" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="D249" s="40" t="s">
+        <v>726</v>
+      </c>
+      <c r="E249" s="40" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="250" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A250" s="12" t="s">
+        <v>722</v>
+      </c>
+      <c r="B250" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="C250" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="D250" s="40" t="s">
+        <v>727</v>
+      </c>
+      <c r="E250" s="40" t="s">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="251" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A251" s="12" t="s">
+        <v>722</v>
+      </c>
+      <c r="B251" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="C251" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="D251" s="40" t="s">
+        <v>728</v>
+      </c>
+      <c r="E251" s="40" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="252" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A252" s="12" t="s">
+        <v>722</v>
+      </c>
+      <c r="B252" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="C252" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="D252" s="40" t="s">
+        <v>729</v>
+      </c>
+      <c r="E252" s="40" t="s">
+        <v>729</v>
+      </c>
     </row>
     <row r="253" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A253" s="19" t="s">
-        <v>131</v>
-      </c>
-      <c r="B253" s="19" t="s">
-        <v>524</v>
-      </c>
-      <c r="C253" s="23"/>
-      <c r="D253" s="17"/>
-      <c r="E253" s="17"/>
+      <c r="A253" s="17" t="s">
+        <v>103</v>
+      </c>
+      <c r="B253" s="17" t="s">
+        <v>522</v>
+      </c>
+      <c r="C253" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="D253" s="39" t="s">
+        <v>407</v>
+      </c>
+      <c r="E253" s="17" t="s">
+        <v>406</v>
+      </c>
       <c r="F253" s="20"/>
       <c r="G253" s="18"/>
     </row>
-    <row r="254" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A254" s="19" t="s">
-        <v>133</v>
-      </c>
-      <c r="B254" s="19" t="s">
-        <v>524</v>
-      </c>
-      <c r="C254" s="23"/>
-      <c r="D254" s="17"/>
-      <c r="E254" s="17"/>
-      <c r="F254" s="20"/>
-      <c r="G254" s="18"/>
-    </row>
-    <row r="255" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A255" s="19" t="s">
-        <v>135</v>
-      </c>
-      <c r="B255" s="19" t="s">
-        <v>524</v>
-      </c>
-      <c r="C255" s="23"/>
-      <c r="D255" s="17"/>
-      <c r="E255" s="17"/>
-      <c r="F255" s="20"/>
-      <c r="G255" s="18"/>
+    <row r="254" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A254" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="B254" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="C254" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="D254" s="40" t="s">
+        <v>410</v>
+      </c>
+      <c r="E254" s="12" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="255" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A255" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="B255" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="C255" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="D255" s="40" t="s">
+        <v>412</v>
+      </c>
+      <c r="E255" s="12" t="s">
+        <v>404</v>
+      </c>
     </row>
     <row r="256" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A256" s="19" t="s">
-        <v>137</v>
-      </c>
-      <c r="B256" s="19" t="s">
-        <v>524</v>
-      </c>
-      <c r="C256" s="23"/>
-      <c r="D256" s="17"/>
-      <c r="E256" s="17"/>
+      <c r="A256" s="17" t="s">
+        <v>105</v>
+      </c>
+      <c r="B256" s="17" t="s">
+        <v>522</v>
+      </c>
+      <c r="C256" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="D256" s="39" t="s">
+        <v>407</v>
+      </c>
+      <c r="E256" s="17" t="s">
+        <v>406</v>
+      </c>
       <c r="F256" s="20"/>
       <c r="G256" s="18"/>
     </row>
-    <row r="257" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A257" s="19" t="s">
-        <v>139</v>
-      </c>
-      <c r="B257" s="19" t="s">
-        <v>524</v>
-      </c>
-      <c r="C257" s="23"/>
-      <c r="D257" s="17"/>
-      <c r="E257" s="17"/>
-      <c r="F257" s="20"/>
-      <c r="G257" s="18"/>
-    </row>
-    <row r="258" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A258" s="19" t="s">
-        <v>141</v>
-      </c>
-      <c r="B258" s="19" t="s">
-        <v>524</v>
-      </c>
-      <c r="C258" s="23"/>
-      <c r="D258" s="17"/>
-      <c r="E258" s="17"/>
-      <c r="F258" s="20"/>
-      <c r="G258" s="18"/>
+    <row r="257" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A257" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="B257" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="C257" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="D257" s="40" t="s">
+        <v>410</v>
+      </c>
+      <c r="E257" s="12" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="258" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A258" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="B258" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="C258" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="D258" s="40" t="s">
+        <v>412</v>
+      </c>
+      <c r="E258" s="12" t="s">
+        <v>404</v>
+      </c>
     </row>
     <row r="259" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A259" s="19" t="s">
-        <v>143</v>
-      </c>
-      <c r="B259" s="19" t="s">
-        <v>524</v>
-      </c>
-      <c r="C259" s="23"/>
-      <c r="D259" s="17"/>
-      <c r="E259" s="17"/>
+      <c r="A259" s="17" t="s">
+        <v>107</v>
+      </c>
+      <c r="B259" s="17" t="s">
+        <v>522</v>
+      </c>
+      <c r="C259" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="D259" s="39" t="s">
+        <v>407</v>
+      </c>
+      <c r="E259" s="17" t="s">
+        <v>406</v>
+      </c>
       <c r="F259" s="20"/>
       <c r="G259" s="18"/>
     </row>
-    <row r="260" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A260" s="19" t="s">
-        <v>145</v>
-      </c>
-      <c r="B260" s="19" t="s">
-        <v>524</v>
-      </c>
-      <c r="C260" s="23"/>
-      <c r="D260" s="17"/>
-      <c r="E260" s="17"/>
-      <c r="F260" s="20"/>
-      <c r="G260" s="18"/>
-    </row>
-    <row r="261" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A261" s="19" t="s">
-        <v>147</v>
-      </c>
-      <c r="B261" s="19" t="s">
-        <v>524</v>
-      </c>
-      <c r="C261" s="23"/>
-      <c r="D261" s="17"/>
-      <c r="E261" s="17"/>
-      <c r="F261" s="20"/>
-      <c r="G261" s="18"/>
+    <row r="260" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A260" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="B260" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="C260" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="D260" s="40" t="s">
+        <v>410</v>
+      </c>
+      <c r="E260" s="12" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="261" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A261" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="B261" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="C261" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="D261" s="40" t="s">
+        <v>412</v>
+      </c>
+      <c r="E261" s="12" t="s">
+        <v>404</v>
+      </c>
     </row>
     <row r="262" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A262" s="19" t="s">
-        <v>151</v>
-      </c>
-      <c r="B262" s="19" t="s">
-        <v>524</v>
-      </c>
-      <c r="C262" s="23"/>
-      <c r="D262" s="17"/>
-      <c r="E262" s="17"/>
+      <c r="A262" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="B262" s="17" t="s">
+        <v>522</v>
+      </c>
+      <c r="C262" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="D262" s="39" t="s">
+        <v>407</v>
+      </c>
+      <c r="E262" s="17" t="s">
+        <v>406</v>
+      </c>
       <c r="F262" s="20"/>
       <c r="G262" s="18"/>
     </row>
-    <row r="263" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A263" s="17" t="s">
-        <v>167</v>
-      </c>
-      <c r="B263" s="17" t="s">
-        <v>522</v>
-      </c>
-      <c r="C263" s="23" t="b">
-        <v>0</v>
-      </c>
-      <c r="D263" s="19" t="s">
-        <v>407</v>
-      </c>
-      <c r="E263" s="19" t="s">
-        <v>406</v>
-      </c>
-      <c r="F263" s="20"/>
-      <c r="G263" s="18"/>
+    <row r="263" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A263" s="12" t="s">
+        <v>109</v>
+      </c>
+      <c r="B263" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="C263" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="D263" s="40" t="s">
+        <v>410</v>
+      </c>
+      <c r="E263" s="12" t="s">
+        <v>409</v>
+      </c>
     </row>
     <row r="264" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A264" s="12" t="s">
-        <v>167</v>
+        <v>109</v>
       </c>
       <c r="B264" s="12" t="s">
         <v>522</v>
@@ -24476,147 +24893,177 @@
       <c r="C264" s="24" t="b">
         <v>0</v>
       </c>
-      <c r="D264" s="4" t="s">
+      <c r="D264" s="40" t="s">
+        <v>412</v>
+      </c>
+      <c r="E264" s="12" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="265" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A265" s="17" t="s">
+        <v>111</v>
+      </c>
+      <c r="B265" s="17" t="s">
+        <v>522</v>
+      </c>
+      <c r="C265" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="D265" s="39" t="s">
+        <v>407</v>
+      </c>
+      <c r="E265" s="17" t="s">
+        <v>406</v>
+      </c>
+      <c r="F265" s="20"/>
+      <c r="G265" s="18"/>
+    </row>
+    <row r="266" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A266" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="B266" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="C266" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="D266" s="40" t="s">
         <v>410</v>
       </c>
-      <c r="E264" s="4" t="s">
+      <c r="E266" s="12" t="s">
         <v>409</v>
       </c>
     </row>
-    <row r="265" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A265" s="12" t="s">
-        <v>167</v>
-      </c>
-      <c r="B265" s="12" t="s">
-        <v>522</v>
-      </c>
-      <c r="C265" s="24" t="b">
-        <v>0</v>
-      </c>
-      <c r="D265" s="4" t="s">
+    <row r="267" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A267" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="B267" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="C267" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="D267" s="40" t="s">
         <v>412</v>
       </c>
-      <c r="E265" s="4" t="s">
+      <c r="E267" s="12" t="s">
         <v>404</v>
       </c>
     </row>
-    <row r="266" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A266" s="19" t="s">
-        <v>168</v>
-      </c>
-      <c r="B266" s="19" t="s">
-        <v>524</v>
-      </c>
-      <c r="C266" s="23"/>
-      <c r="D266" s="17"/>
-      <c r="E266" s="17"/>
-      <c r="F266" s="20"/>
-      <c r="G266" s="18"/>
-    </row>
-    <row r="267" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A267" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="B267" s="19" t="s">
-        <v>524</v>
-      </c>
-      <c r="C267" s="23"/>
-      <c r="D267" s="17"/>
-      <c r="E267" s="17"/>
-      <c r="F267" s="20"/>
-      <c r="G267" s="18"/>
-    </row>
     <row r="268" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A268" s="19" t="s">
-        <v>170</v>
-      </c>
-      <c r="B268" s="19" t="s">
-        <v>524</v>
-      </c>
-      <c r="C268" s="23"/>
-      <c r="D268" s="17"/>
-      <c r="E268" s="17"/>
+      <c r="A268" s="17" t="s">
+        <v>675</v>
+      </c>
+      <c r="B268" s="17" t="s">
+        <v>522</v>
+      </c>
+      <c r="C268" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="D268" s="39" t="s">
+        <v>407</v>
+      </c>
+      <c r="E268" s="17" t="s">
+        <v>406</v>
+      </c>
       <c r="F268" s="20"/>
       <c r="G268" s="18"/>
     </row>
-    <row r="269" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A269" s="19" t="s">
-        <v>172</v>
-      </c>
-      <c r="B269" s="19" t="s">
-        <v>524</v>
-      </c>
-      <c r="C269" s="23"/>
-      <c r="D269" s="17"/>
-      <c r="E269" s="17"/>
-      <c r="F269" s="20"/>
-      <c r="G269" s="18"/>
+    <row r="269" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A269" s="12" t="s">
+        <v>675</v>
+      </c>
+      <c r="B269" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="C269" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="D269" s="40" t="s">
+        <v>410</v>
+      </c>
+      <c r="E269" s="12" t="s">
+        <v>409</v>
+      </c>
     </row>
     <row r="270" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A270" s="19" t="s">
-        <v>174</v>
-      </c>
-      <c r="B270" s="19" t="s">
-        <v>524</v>
-      </c>
-      <c r="C270" s="23"/>
-      <c r="D270" s="17"/>
-      <c r="E270" s="17"/>
+      <c r="A270" s="17" t="s">
+        <v>113</v>
+      </c>
+      <c r="B270" s="17" t="s">
+        <v>522</v>
+      </c>
+      <c r="C270" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="D270" s="39" t="s">
+        <v>407</v>
+      </c>
+      <c r="E270" s="17" t="s">
+        <v>406</v>
+      </c>
       <c r="F270" s="20"/>
       <c r="G270" s="18"/>
     </row>
-    <row r="271" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A271" s="19" t="s">
-        <v>176</v>
-      </c>
-      <c r="B271" s="19" t="s">
-        <v>521</v>
-      </c>
-      <c r="C271" s="23"/>
-      <c r="D271" s="17"/>
-      <c r="E271" s="17"/>
-      <c r="F271" s="20"/>
-      <c r="G271" s="18"/>
-    </row>
-    <row r="272" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A272" s="17" t="s">
-        <v>178</v>
-      </c>
-      <c r="B272" s="17" t="s">
-        <v>522</v>
-      </c>
-      <c r="C272" s="23" t="b">
-        <v>0</v>
-      </c>
-      <c r="D272" s="19" t="s">
+    <row r="271" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A271" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="B271" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="C271" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="D271" s="40" t="s">
+        <v>410</v>
+      </c>
+      <c r="E271" s="12" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="272" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A272" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="B272" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="C272" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="D272" s="40" t="s">
+        <v>412</v>
+      </c>
+      <c r="E272" s="12" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="273" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A273" s="17" t="s">
+        <v>115</v>
+      </c>
+      <c r="B273" s="17" t="s">
+        <v>522</v>
+      </c>
+      <c r="C273" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="D273" s="39" t="s">
         <v>407</v>
       </c>
-      <c r="E272" s="19" t="s">
-        <v>401</v>
-      </c>
-      <c r="F272" s="20"/>
-      <c r="G272" s="18"/>
-    </row>
-    <row r="273" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A273" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="B273" s="12" t="s">
-        <v>522</v>
-      </c>
-      <c r="C273" s="24" t="b">
-        <v>0</v>
-      </c>
-      <c r="D273" s="4" t="s">
-        <v>467</v>
-      </c>
-      <c r="E273" s="4" t="s">
-        <v>474</v>
-      </c>
+      <c r="E273" s="17" t="s">
+        <v>406</v>
+      </c>
+      <c r="F273" s="20"/>
+      <c r="G273" s="18"/>
     </row>
     <row r="274" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A274" s="12" t="s">
-        <v>178</v>
+        <v>115</v>
       </c>
       <c r="B274" s="12" t="s">
         <v>522</v>
@@ -24624,16 +25071,16 @@
       <c r="C274" s="24" t="b">
         <v>0</v>
       </c>
-      <c r="D274" s="4" t="s">
-        <v>470</v>
-      </c>
-      <c r="E274" s="4" t="s">
-        <v>605</v>
+      <c r="D274" s="40" t="s">
+        <v>410</v>
+      </c>
+      <c r="E274" s="12" t="s">
+        <v>409</v>
       </c>
     </row>
     <row r="275" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A275" s="12" t="s">
-        <v>178</v>
+        <v>115</v>
       </c>
       <c r="B275" s="12" t="s">
         <v>522</v>
@@ -24641,33 +25088,35 @@
       <c r="C275" s="24" t="b">
         <v>0</v>
       </c>
-      <c r="D275" s="4" t="s">
-        <v>447</v>
-      </c>
-      <c r="E275" s="4" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="276" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A276" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="B276" s="12" t="s">
-        <v>522</v>
-      </c>
-      <c r="C276" s="24" t="b">
-        <v>0</v>
-      </c>
-      <c r="D276" s="4" t="s">
-        <v>462</v>
-      </c>
-      <c r="E276" s="4" t="s">
-        <v>476</v>
-      </c>
+      <c r="D275" s="40" t="s">
+        <v>412</v>
+      </c>
+      <c r="E275" s="12" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="276" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A276" s="17" t="s">
+        <v>117</v>
+      </c>
+      <c r="B276" s="17" t="s">
+        <v>522</v>
+      </c>
+      <c r="C276" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="D276" s="39" t="s">
+        <v>407</v>
+      </c>
+      <c r="E276" s="17" t="s">
+        <v>406</v>
+      </c>
+      <c r="F276" s="20"/>
+      <c r="G276" s="18"/>
     </row>
     <row r="277" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A277" s="12" t="s">
-        <v>178</v>
+        <v>117</v>
       </c>
       <c r="B277" s="12" t="s">
         <v>522</v>
@@ -24675,16 +25124,16 @@
       <c r="C277" s="24" t="b">
         <v>0</v>
       </c>
-      <c r="D277" s="4" t="s">
+      <c r="D277" s="40" t="s">
         <v>410</v>
       </c>
-      <c r="E277" s="4" t="s">
-        <v>477</v>
+      <c r="E277" s="12" t="s">
+        <v>409</v>
       </c>
     </row>
     <row r="278" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A278" s="12" t="s">
-        <v>178</v>
+        <v>117</v>
       </c>
       <c r="B278" s="12" t="s">
         <v>522</v>
@@ -24692,274 +25141,1491 @@
       <c r="C278" s="24" t="b">
         <v>0</v>
       </c>
-      <c r="D278" s="4" t="s">
+      <c r="D278" s="40" t="s">
         <v>412</v>
       </c>
-      <c r="E278" s="4" t="s">
+      <c r="E278" s="12" t="s">
         <v>404</v>
       </c>
     </row>
     <row r="279" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A279" s="17" t="s">
-        <v>180</v>
+        <v>119</v>
       </c>
       <c r="B279" s="17" t="s">
-        <v>524</v>
-      </c>
-      <c r="C279" s="23"/>
-      <c r="D279" s="17"/>
-      <c r="E279" s="17"/>
+        <v>522</v>
+      </c>
+      <c r="C279" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="D279" s="39" t="s">
+        <v>407</v>
+      </c>
+      <c r="E279" s="17" t="s">
+        <v>406</v>
+      </c>
       <c r="F279" s="20"/>
       <c r="G279" s="18"/>
     </row>
-    <row r="280" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A280" s="17" t="s">
+    <row r="280" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A280" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="B280" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="C280" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="D280" s="40" t="s">
+        <v>410</v>
+      </c>
+      <c r="E280" s="12" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="281" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A281" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="B281" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="C281" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="D281" s="40" t="s">
+        <v>412</v>
+      </c>
+      <c r="E281" s="12" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="282" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A282" s="17" t="s">
+        <v>121</v>
+      </c>
+      <c r="B282" s="17" t="s">
+        <v>522</v>
+      </c>
+      <c r="C282" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="D282" s="39">
+        <v>10</v>
+      </c>
+      <c r="E282" s="17" t="s">
+        <v>574</v>
+      </c>
+      <c r="F282" s="20"/>
+      <c r="G282" s="18"/>
+    </row>
+    <row r="283" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A283" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="B283" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="C283" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="D283" s="40">
+        <v>11</v>
+      </c>
+      <c r="E283" s="12" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="284" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A284" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="B284" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="C284" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="D284" s="40">
+        <v>12</v>
+      </c>
+      <c r="E284" s="12" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="285" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A285" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="B285" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="C285" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="D285" s="40">
+        <v>13</v>
+      </c>
+      <c r="E285" s="12" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="286" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A286" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="B286" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="C286" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="D286" s="40">
+        <v>14</v>
+      </c>
+      <c r="E286" s="12" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="287" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A287" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="B287" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="C287" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="D287" s="40">
+        <v>20</v>
+      </c>
+      <c r="E287" s="12" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="288" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A288" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="B288" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="C288" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="D288" s="40">
+        <v>21</v>
+      </c>
+      <c r="E288" s="12" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="289" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A289" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="B289" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="C289" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="D289" s="40">
+        <v>22</v>
+      </c>
+      <c r="E289" s="12" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="290" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A290" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="B290" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="C290" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="D290" s="40">
+        <v>23</v>
+      </c>
+      <c r="E290" s="12" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="291" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A291" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="B291" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="C291" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="D291" s="40">
+        <v>24</v>
+      </c>
+      <c r="E291" s="12" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="292" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A292" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="B292" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="C292" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="D292" s="40">
+        <v>25</v>
+      </c>
+      <c r="E292" s="12" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="293" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A293" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="B293" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="C293" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="D293" s="40">
+        <v>26</v>
+      </c>
+      <c r="E293" s="12" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="294" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A294" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="B294" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="C294" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="D294" s="40">
+        <v>27</v>
+      </c>
+      <c r="E294" s="12" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="295" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A295" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="B295" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="C295" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="D295" s="40">
+        <v>28</v>
+      </c>
+      <c r="E295" s="12" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="296" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A296" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="B296" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="C296" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="D296" s="40">
+        <v>29</v>
+      </c>
+      <c r="E296" s="12" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="297" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A297" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="B297" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="C297" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="D297" s="40">
+        <v>30</v>
+      </c>
+      <c r="E297" s="12" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="298" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A298" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="B298" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="C298" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="D298" s="40">
+        <v>31</v>
+      </c>
+      <c r="E298" s="12" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="299" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A299" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="B299" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="C299" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="D299" s="40">
+        <v>32</v>
+      </c>
+      <c r="E299" s="12" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="300" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A300" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="B300" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="C300" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="D300" s="40">
+        <v>33</v>
+      </c>
+      <c r="E300" s="12" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="301" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A301" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="B301" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="C301" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="D301" s="40">
+        <v>34</v>
+      </c>
+      <c r="E301" s="12" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="302" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A302" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="B302" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="C302" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="D302" s="40">
+        <v>35</v>
+      </c>
+      <c r="E302" s="12" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="303" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A303" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="B303" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="C303" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="D303" s="40">
+        <v>36</v>
+      </c>
+      <c r="E303" s="12" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="304" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A304" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="B304" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="C304" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="D304" s="40">
+        <v>37</v>
+      </c>
+      <c r="E304" s="12" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="305" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A305" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="B305" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="C305" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="D305" s="40">
+        <v>38</v>
+      </c>
+      <c r="E305" s="12" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="306" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A306" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="B306" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="C306" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="D306" s="40">
+        <v>39</v>
+      </c>
+      <c r="E306" s="12" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="307" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A307" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="B307" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="C307" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="D307" s="40">
+        <v>40</v>
+      </c>
+      <c r="E307" s="12" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="308" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A308" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="B308" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="C308" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="D308" s="40">
+        <v>41</v>
+      </c>
+      <c r="E308" s="12" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="309" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A309" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="B309" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="C309" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="D309" s="40">
+        <v>42</v>
+      </c>
+      <c r="E309" s="12" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="310" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A310" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="B310" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="C310" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="D310" s="40">
+        <v>43</v>
+      </c>
+      <c r="E310" s="12" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="311" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A311" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="B311" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="C311" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="D311" s="40">
+        <v>44</v>
+      </c>
+      <c r="E311" s="12" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="312" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A312" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="B312" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="C312" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="D312" s="40">
+        <v>50</v>
+      </c>
+      <c r="E312" s="12" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="313" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A313" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="B313" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="C313" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="D313" s="40">
+        <v>99</v>
+      </c>
+      <c r="E313" s="12" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="314" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A314" s="19" t="s">
+        <v>123</v>
+      </c>
+      <c r="B314" s="19" t="s">
+        <v>522</v>
+      </c>
+      <c r="C314" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="D314" s="41" t="s">
+        <v>407</v>
+      </c>
+      <c r="E314" s="19" t="s">
+        <v>406</v>
+      </c>
+      <c r="F314" s="20"/>
+      <c r="G314" s="18"/>
+    </row>
+    <row r="315" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A315" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="B315" s="4" t="s">
+        <v>522</v>
+      </c>
+      <c r="C315" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="D315" s="42" t="s">
+        <v>410</v>
+      </c>
+      <c r="E315" s="4" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="316" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A316" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="B316" s="4" t="s">
+        <v>522</v>
+      </c>
+      <c r="C316" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="D316" s="42" t="s">
+        <v>412</v>
+      </c>
+      <c r="E316" s="4" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="317" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A317" s="19" t="s">
+        <v>125</v>
+      </c>
+      <c r="B317" s="19" t="s">
+        <v>522</v>
+      </c>
+      <c r="C317" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="D317" s="41" t="s">
+        <v>407</v>
+      </c>
+      <c r="E317" s="19" t="s">
+        <v>406</v>
+      </c>
+      <c r="F317" s="20"/>
+      <c r="G317" s="18"/>
+    </row>
+    <row r="318" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A318" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="B318" s="4" t="s">
+        <v>522</v>
+      </c>
+      <c r="C318" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="D318" s="42" t="s">
+        <v>410</v>
+      </c>
+      <c r="E318" s="4" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="319" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A319" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="B319" s="4" t="s">
+        <v>522</v>
+      </c>
+      <c r="C319" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="D319" s="42" t="s">
+        <v>412</v>
+      </c>
+      <c r="E319" s="4" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="320" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A320" s="19" t="s">
+        <v>127</v>
+      </c>
+      <c r="B320" s="19" t="s">
+        <v>524</v>
+      </c>
+      <c r="C320" s="23"/>
+      <c r="D320" s="39"/>
+      <c r="E320" s="17"/>
+      <c r="F320" s="20"/>
+      <c r="G320" s="18"/>
+    </row>
+    <row r="321" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A321" s="19" t="s">
+        <v>149</v>
+      </c>
+      <c r="B321" s="19" t="s">
+        <v>524</v>
+      </c>
+      <c r="C321" s="23"/>
+      <c r="D321" s="39"/>
+      <c r="E321" s="17"/>
+      <c r="F321" s="20"/>
+      <c r="G321" s="18"/>
+    </row>
+    <row r="322" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A322" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="B322" s="19" t="s">
+        <v>524</v>
+      </c>
+      <c r="C322" s="23"/>
+      <c r="D322" s="39"/>
+      <c r="E322" s="17"/>
+      <c r="F322" s="20"/>
+      <c r="G322" s="18"/>
+    </row>
+    <row r="323" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A323" s="19" t="s">
+        <v>155</v>
+      </c>
+      <c r="B323" s="19" t="s">
+        <v>524</v>
+      </c>
+      <c r="C323" s="23"/>
+      <c r="D323" s="39"/>
+      <c r="E323" s="17"/>
+      <c r="F323" s="20"/>
+      <c r="G323" s="18"/>
+    </row>
+    <row r="324" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A324" s="19" t="s">
+        <v>157</v>
+      </c>
+      <c r="B324" s="19" t="s">
+        <v>524</v>
+      </c>
+      <c r="C324" s="23"/>
+      <c r="D324" s="39"/>
+      <c r="E324" s="17"/>
+      <c r="F324" s="20"/>
+      <c r="G324" s="18"/>
+    </row>
+    <row r="325" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A325" s="19" t="s">
+        <v>159</v>
+      </c>
+      <c r="B325" s="19" t="s">
+        <v>524</v>
+      </c>
+      <c r="C325" s="23"/>
+      <c r="D325" s="39"/>
+      <c r="E325" s="17"/>
+      <c r="F325" s="20"/>
+      <c r="G325" s="18"/>
+    </row>
+    <row r="326" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A326" s="19" t="s">
+        <v>161</v>
+      </c>
+      <c r="B326" s="19" t="s">
+        <v>524</v>
+      </c>
+      <c r="C326" s="23"/>
+      <c r="D326" s="39"/>
+      <c r="E326" s="17"/>
+      <c r="F326" s="20"/>
+      <c r="G326" s="18"/>
+    </row>
+    <row r="327" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A327" s="19" t="s">
+        <v>163</v>
+      </c>
+      <c r="B327" s="19" t="s">
+        <v>524</v>
+      </c>
+      <c r="C327" s="23"/>
+      <c r="D327" s="39"/>
+      <c r="E327" s="17"/>
+      <c r="F327" s="20"/>
+      <c r="G327" s="18"/>
+    </row>
+    <row r="328" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A328" s="19" t="s">
+        <v>165</v>
+      </c>
+      <c r="B328" s="19" t="s">
+        <v>524</v>
+      </c>
+      <c r="C328" s="23"/>
+      <c r="D328" s="39"/>
+      <c r="E328" s="17"/>
+      <c r="F328" s="20"/>
+      <c r="G328" s="18"/>
+    </row>
+    <row r="329" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A329" s="19" t="s">
+        <v>129</v>
+      </c>
+      <c r="B329" s="19" t="s">
+        <v>524</v>
+      </c>
+      <c r="C329" s="23"/>
+      <c r="D329" s="39"/>
+      <c r="E329" s="17"/>
+      <c r="F329" s="20"/>
+      <c r="G329" s="18"/>
+    </row>
+    <row r="330" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A330" s="19" t="s">
+        <v>131</v>
+      </c>
+      <c r="B330" s="19" t="s">
+        <v>524</v>
+      </c>
+      <c r="C330" s="23"/>
+      <c r="D330" s="39"/>
+      <c r="E330" s="17"/>
+      <c r="F330" s="20"/>
+      <c r="G330" s="18"/>
+    </row>
+    <row r="331" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A331" s="19" t="s">
+        <v>133</v>
+      </c>
+      <c r="B331" s="19" t="s">
+        <v>524</v>
+      </c>
+      <c r="C331" s="23"/>
+      <c r="D331" s="39"/>
+      <c r="E331" s="17"/>
+      <c r="F331" s="20"/>
+      <c r="G331" s="18"/>
+    </row>
+    <row r="332" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A332" s="19" t="s">
+        <v>135</v>
+      </c>
+      <c r="B332" s="19" t="s">
+        <v>524</v>
+      </c>
+      <c r="C332" s="23"/>
+      <c r="D332" s="39"/>
+      <c r="E332" s="17"/>
+      <c r="F332" s="20"/>
+      <c r="G332" s="18"/>
+    </row>
+    <row r="333" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A333" s="19" t="s">
+        <v>137</v>
+      </c>
+      <c r="B333" s="19" t="s">
+        <v>524</v>
+      </c>
+      <c r="C333" s="23"/>
+      <c r="D333" s="39"/>
+      <c r="E333" s="17"/>
+      <c r="F333" s="20"/>
+      <c r="G333" s="18"/>
+    </row>
+    <row r="334" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A334" s="19" t="s">
+        <v>139</v>
+      </c>
+      <c r="B334" s="19" t="s">
+        <v>524</v>
+      </c>
+      <c r="C334" s="23"/>
+      <c r="D334" s="39"/>
+      <c r="E334" s="17"/>
+      <c r="F334" s="20"/>
+      <c r="G334" s="18"/>
+    </row>
+    <row r="335" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A335" s="19" t="s">
+        <v>141</v>
+      </c>
+      <c r="B335" s="19" t="s">
+        <v>524</v>
+      </c>
+      <c r="C335" s="23"/>
+      <c r="D335" s="39"/>
+      <c r="E335" s="17"/>
+      <c r="F335" s="20"/>
+      <c r="G335" s="18"/>
+    </row>
+    <row r="336" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A336" s="19" t="s">
+        <v>143</v>
+      </c>
+      <c r="B336" s="19" t="s">
+        <v>524</v>
+      </c>
+      <c r="C336" s="23"/>
+      <c r="D336" s="39"/>
+      <c r="E336" s="17"/>
+      <c r="F336" s="20"/>
+      <c r="G336" s="18"/>
+    </row>
+    <row r="337" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A337" s="19" t="s">
+        <v>145</v>
+      </c>
+      <c r="B337" s="19" t="s">
+        <v>524</v>
+      </c>
+      <c r="C337" s="23"/>
+      <c r="D337" s="39"/>
+      <c r="E337" s="17"/>
+      <c r="F337" s="20"/>
+      <c r="G337" s="18"/>
+    </row>
+    <row r="338" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A338" s="19" t="s">
+        <v>147</v>
+      </c>
+      <c r="B338" s="19" t="s">
+        <v>524</v>
+      </c>
+      <c r="C338" s="23"/>
+      <c r="D338" s="39"/>
+      <c r="E338" s="17"/>
+      <c r="F338" s="20"/>
+      <c r="G338" s="18"/>
+    </row>
+    <row r="339" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A339" s="19" t="s">
+        <v>151</v>
+      </c>
+      <c r="B339" s="19" t="s">
+        <v>524</v>
+      </c>
+      <c r="C339" s="23"/>
+      <c r="D339" s="39"/>
+      <c r="E339" s="17"/>
+      <c r="F339" s="20"/>
+      <c r="G339" s="18"/>
+    </row>
+    <row r="340" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A340" s="17" t="s">
+        <v>167</v>
+      </c>
+      <c r="B340" s="17" t="s">
+        <v>522</v>
+      </c>
+      <c r="C340" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="D340" s="41" t="s">
+        <v>407</v>
+      </c>
+      <c r="E340" s="19" t="s">
+        <v>406</v>
+      </c>
+      <c r="F340" s="20"/>
+      <c r="G340" s="18"/>
+    </row>
+    <row r="341" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A341" s="12" t="s">
+        <v>167</v>
+      </c>
+      <c r="B341" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="C341" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="D341" s="42" t="s">
+        <v>410</v>
+      </c>
+      <c r="E341" s="4" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="342" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A342" s="12" t="s">
+        <v>167</v>
+      </c>
+      <c r="B342" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="C342" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="D342" s="42" t="s">
+        <v>412</v>
+      </c>
+      <c r="E342" s="4" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="343" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A343" s="19" t="s">
+        <v>168</v>
+      </c>
+      <c r="B343" s="19" t="s">
+        <v>524</v>
+      </c>
+      <c r="C343" s="23"/>
+      <c r="D343" s="39"/>
+      <c r="E343" s="17"/>
+      <c r="F343" s="20"/>
+      <c r="G343" s="18"/>
+    </row>
+    <row r="344" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A344" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="B344" s="19" t="s">
+        <v>524</v>
+      </c>
+      <c r="C344" s="23"/>
+      <c r="D344" s="39"/>
+      <c r="E344" s="17"/>
+      <c r="F344" s="20"/>
+      <c r="G344" s="18"/>
+    </row>
+    <row r="345" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A345" s="19" t="s">
+        <v>170</v>
+      </c>
+      <c r="B345" s="19" t="s">
+        <v>524</v>
+      </c>
+      <c r="C345" s="23"/>
+      <c r="D345" s="39"/>
+      <c r="E345" s="17"/>
+      <c r="F345" s="20"/>
+      <c r="G345" s="18"/>
+    </row>
+    <row r="346" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A346" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="B346" s="19" t="s">
+        <v>524</v>
+      </c>
+      <c r="C346" s="23"/>
+      <c r="D346" s="39"/>
+      <c r="E346" s="17"/>
+      <c r="F346" s="20"/>
+      <c r="G346" s="18"/>
+    </row>
+    <row r="347" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A347" s="19" t="s">
+        <v>174</v>
+      </c>
+      <c r="B347" s="19" t="s">
+        <v>524</v>
+      </c>
+      <c r="C347" s="23"/>
+      <c r="D347" s="39"/>
+      <c r="E347" s="17"/>
+      <c r="F347" s="20"/>
+      <c r="G347" s="18"/>
+    </row>
+    <row r="348" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A348" s="19" t="s">
+        <v>176</v>
+      </c>
+      <c r="B348" s="19" t="s">
+        <v>521</v>
+      </c>
+      <c r="C348" s="23"/>
+      <c r="D348" s="39"/>
+      <c r="E348" s="17"/>
+      <c r="F348" s="20"/>
+      <c r="G348" s="18"/>
+    </row>
+    <row r="349" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A349" s="17" t="s">
+        <v>178</v>
+      </c>
+      <c r="B349" s="17" t="s">
+        <v>522</v>
+      </c>
+      <c r="C349" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="D349" s="41" t="s">
+        <v>407</v>
+      </c>
+      <c r="E349" s="19" t="s">
+        <v>401</v>
+      </c>
+      <c r="F349" s="20"/>
+      <c r="G349" s="18"/>
+    </row>
+    <row r="350" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A350" s="12" t="s">
+        <v>178</v>
+      </c>
+      <c r="B350" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="C350" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="D350" s="42" t="s">
+        <v>467</v>
+      </c>
+      <c r="E350" s="4" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="351" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A351" s="12" t="s">
+        <v>178</v>
+      </c>
+      <c r="B351" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="C351" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="D351" s="42" t="s">
+        <v>470</v>
+      </c>
+      <c r="E351" s="4" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="352" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A352" s="12" t="s">
+        <v>178</v>
+      </c>
+      <c r="B352" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="C352" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="D352" s="42" t="s">
+        <v>447</v>
+      </c>
+      <c r="E352" s="4" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="353" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A353" s="12" t="s">
+        <v>178</v>
+      </c>
+      <c r="B353" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="C353" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="D353" s="42" t="s">
+        <v>462</v>
+      </c>
+      <c r="E353" s="4" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="354" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A354" s="12" t="s">
+        <v>178</v>
+      </c>
+      <c r="B354" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="C354" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="D354" s="42" t="s">
+        <v>410</v>
+      </c>
+      <c r="E354" s="4" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="355" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A355" s="12" t="s">
+        <v>178</v>
+      </c>
+      <c r="B355" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="C355" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="D355" s="42" t="s">
+        <v>412</v>
+      </c>
+      <c r="E355" s="4" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="356" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A356" s="17" t="s">
+        <v>180</v>
+      </c>
+      <c r="B356" s="17" t="s">
+        <v>524</v>
+      </c>
+      <c r="C356" s="23"/>
+      <c r="D356" s="39"/>
+      <c r="E356" s="17"/>
+      <c r="F356" s="20"/>
+      <c r="G356" s="18"/>
+    </row>
+    <row r="357" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A357" s="17" t="s">
         <v>182</v>
       </c>
-      <c r="B280" s="17" t="s">
+      <c r="B357" s="17" t="s">
         <v>524</v>
       </c>
-      <c r="C280" s="23"/>
-      <c r="D280" s="17"/>
-      <c r="E280" s="17"/>
-      <c r="F280" s="20"/>
-      <c r="G280" s="18"/>
-    </row>
-    <row r="281" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A281" s="19" t="s">
+      <c r="C357" s="23"/>
+      <c r="D357" s="39"/>
+      <c r="E357" s="17"/>
+      <c r="F357" s="20"/>
+      <c r="G357" s="18"/>
+    </row>
+    <row r="358" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A358" s="19" t="s">
         <v>183</v>
       </c>
-      <c r="B281" s="19" t="s">
-        <v>522</v>
-      </c>
-      <c r="C281" s="23" t="b">
-        <v>0</v>
-      </c>
-      <c r="D281" s="19" t="s">
+      <c r="B358" s="19" t="s">
+        <v>522</v>
+      </c>
+      <c r="C358" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="D358" s="41" t="s">
         <v>467</v>
       </c>
-      <c r="E281" s="19" t="s">
+      <c r="E358" s="19" t="s">
         <v>606</v>
       </c>
-      <c r="F281" s="20"/>
-      <c r="G281" s="18"/>
-    </row>
-    <row r="282" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A282" s="4" t="s">
+      <c r="F358" s="20"/>
+      <c r="G358" s="18"/>
+    </row>
+    <row r="359" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A359" s="4" t="s">
         <v>183</v>
       </c>
-      <c r="B282" s="4" t="s">
-        <v>522</v>
-      </c>
-      <c r="C282" s="24" t="b">
-        <v>0</v>
-      </c>
-      <c r="D282" s="4" t="s">
+      <c r="B359" s="4" t="s">
+        <v>522</v>
+      </c>
+      <c r="C359" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="D359" s="42" t="s">
         <v>519</v>
       </c>
-      <c r="E282" s="4" t="s">
+      <c r="E359" s="4" t="s">
         <v>607</v>
       </c>
     </row>
-    <row r="283" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A283" s="4" t="s">
+    <row r="360" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A360" s="4" t="s">
         <v>183</v>
       </c>
-      <c r="B283" s="4" t="s">
-        <v>522</v>
-      </c>
-      <c r="C283" s="24" t="b">
-        <v>0</v>
-      </c>
-      <c r="D283" s="4" t="s">
+      <c r="B360" s="4" t="s">
+        <v>522</v>
+      </c>
+      <c r="C360" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="D360" s="42" t="s">
         <v>412</v>
       </c>
-      <c r="E283" s="4" t="s">
+      <c r="E360" s="4" t="s">
         <v>463</v>
       </c>
     </row>
-    <row r="284" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A284" s="4" t="s">
+    <row r="361" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A361" s="4" t="s">
         <v>183</v>
       </c>
-      <c r="B284" s="4" t="s">
-        <v>522</v>
-      </c>
-      <c r="C284" s="24" t="b">
-        <v>0</v>
-      </c>
-      <c r="D284" s="4" t="s">
+      <c r="B361" s="4" t="s">
+        <v>522</v>
+      </c>
+      <c r="C361" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="D361" s="42" t="s">
         <v>512</v>
       </c>
-      <c r="E284" s="4" t="s">
+      <c r="E361" s="4" t="s">
         <v>439</v>
       </c>
-      <c r="G284" t="s">
+      <c r="G361" t="s">
         <v>560</v>
       </c>
     </row>
-    <row r="285" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A285" s="19" t="s">
+    <row r="362" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A362" s="19" t="s">
         <v>651</v>
       </c>
-      <c r="B285" s="19" t="s">
+      <c r="B362" s="19" t="s">
         <v>524</v>
       </c>
-      <c r="C285" s="23"/>
-      <c r="D285" s="19"/>
-      <c r="E285" s="19"/>
-      <c r="F285" s="20"/>
-    </row>
-    <row r="286" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A286" s="19" t="s">
+      <c r="C362" s="23"/>
+      <c r="D362" s="41"/>
+      <c r="E362" s="19"/>
+      <c r="F362" s="20"/>
+    </row>
+    <row r="363" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A363" s="19" t="s">
         <v>527</v>
       </c>
-      <c r="B286" s="19" t="s">
+      <c r="B363" s="19" t="s">
         <v>524</v>
       </c>
-      <c r="C286" s="23"/>
-      <c r="D286" s="17"/>
-      <c r="E286" s="17"/>
-      <c r="F286" s="20"/>
-      <c r="G286" s="18"/>
-    </row>
-    <row r="287" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A287" s="19" t="s">
+      <c r="C363" s="23"/>
+      <c r="D363" s="39"/>
+      <c r="E363" s="17"/>
+      <c r="F363" s="20"/>
+      <c r="G363" s="18"/>
+    </row>
+    <row r="364" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A364" s="19" t="s">
         <v>185</v>
       </c>
-      <c r="B287" s="19" t="s">
+      <c r="B364" s="19" t="s">
         <v>524</v>
       </c>
-      <c r="C287" s="23"/>
-      <c r="D287" s="17"/>
-      <c r="E287" s="17"/>
-      <c r="F287" s="20"/>
-      <c r="G287" s="18"/>
-    </row>
-    <row r="288" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A288" s="19" t="s">
+      <c r="C364" s="23"/>
+      <c r="D364" s="39"/>
+      <c r="E364" s="17"/>
+      <c r="F364" s="20"/>
+      <c r="G364" s="18"/>
+    </row>
+    <row r="365" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A365" s="19" t="s">
         <v>186</v>
       </c>
-      <c r="B288" s="19" t="s">
+      <c r="B365" s="19" t="s">
         <v>528</v>
       </c>
-      <c r="C288" s="23"/>
-      <c r="D288" s="17"/>
-      <c r="E288" s="17"/>
-      <c r="F288" s="20"/>
-      <c r="G288" s="18"/>
-    </row>
-    <row r="289" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A289" s="19" t="s">
+      <c r="C365" s="23"/>
+      <c r="D365" s="39"/>
+      <c r="E365" s="17"/>
+      <c r="F365" s="20"/>
+      <c r="G365" s="18"/>
+    </row>
+    <row r="366" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A366" s="19" t="s">
         <v>191</v>
       </c>
-      <c r="B289" s="19" t="s">
+      <c r="B366" s="19" t="s">
         <v>528</v>
       </c>
-      <c r="C289" s="23"/>
-      <c r="D289" s="17"/>
-      <c r="E289" s="17"/>
-      <c r="F289" s="20"/>
-      <c r="G289" s="18"/>
-    </row>
-    <row r="290" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A290" s="17" t="s">
+      <c r="C366" s="23"/>
+      <c r="D366" s="39"/>
+      <c r="E366" s="17"/>
+      <c r="F366" s="20"/>
+      <c r="G366" s="18"/>
+    </row>
+    <row r="367" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A367" s="17" t="s">
         <v>197</v>
       </c>
-      <c r="B290" s="17" t="s">
-        <v>522</v>
-      </c>
-      <c r="C290" s="23" t="b">
-        <v>0</v>
-      </c>
-      <c r="D290" s="19" t="s">
+      <c r="B367" s="17" t="s">
+        <v>522</v>
+      </c>
+      <c r="C367" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="D367" s="41" t="s">
         <v>407</v>
       </c>
-      <c r="E290" s="19" t="s">
+      <c r="E367" s="19" t="s">
         <v>406</v>
       </c>
-      <c r="F290" s="20"/>
-      <c r="G290" s="18"/>
-    </row>
-    <row r="291" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A291" s="12" t="s">
+      <c r="F367" s="20"/>
+      <c r="G367" s="18"/>
+    </row>
+    <row r="368" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A368" s="12" t="s">
         <v>197</v>
       </c>
-      <c r="B291" s="12" t="s">
-        <v>522</v>
-      </c>
-      <c r="C291" s="24" t="b">
-        <v>0</v>
-      </c>
-      <c r="D291" s="4" t="s">
+      <c r="B368" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="C368" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="D368" s="42" t="s">
         <v>410</v>
       </c>
-      <c r="E291" s="4" t="s">
+      <c r="E368" s="4" t="s">
         <v>409</v>
       </c>
     </row>
-    <row r="292" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A292" s="12" t="s">
+    <row r="369" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A369" s="12" t="s">
         <v>197</v>
       </c>
-      <c r="B292" s="12" t="s">
-        <v>522</v>
-      </c>
-      <c r="C292" s="24" t="b">
-        <v>0</v>
-      </c>
-      <c r="D292" s="4" t="s">
+      <c r="B369" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="C369" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="D369" s="42" t="s">
         <v>465</v>
       </c>
-      <c r="E292" s="4" t="s">
+      <c r="E369" s="4" t="s">
         <v>478</v>
       </c>
     </row>
-    <row r="293" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A293" s="12" t="s">
+    <row r="370" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A370" s="12" t="s">
         <v>197</v>
       </c>
-      <c r="B293" s="12" t="s">
-        <v>522</v>
-      </c>
-      <c r="C293" s="24" t="b">
-        <v>0</v>
-      </c>
-      <c r="D293" s="4" t="s">
+      <c r="B370" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="C370" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="D370" s="42" t="s">
         <v>412</v>
       </c>
-      <c r="E293" s="4" t="s">
+      <c r="E370" s="4" t="s">
         <v>404</v>
       </c>
     </row>
-    <row r="294" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A294" s="19" t="s">
+    <row r="371" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A371" s="19" t="s">
         <v>199</v>
       </c>
-      <c r="B294" s="19" t="s">
+      <c r="B371" s="19" t="s">
         <v>524</v>
       </c>
-      <c r="C294" s="23"/>
-      <c r="D294" s="17"/>
-      <c r="E294" s="17"/>
-      <c r="F294" s="20"/>
-      <c r="G294" s="18"/>
-    </row>
-    <row r="295" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A295" s="19" t="s">
+      <c r="C371" s="23"/>
+      <c r="D371" s="39"/>
+      <c r="E371" s="17"/>
+      <c r="F371" s="20"/>
+      <c r="G371" s="18"/>
+    </row>
+    <row r="372" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A372" s="19" t="s">
         <v>529</v>
       </c>
-      <c r="B295" s="19" t="s">
+      <c r="B372" s="19" t="s">
         <v>524</v>
       </c>
-      <c r="C295" s="23"/>
-      <c r="D295" s="17"/>
-      <c r="E295" s="17"/>
-      <c r="F295" s="20"/>
-      <c r="G295" s="18"/>
+      <c r="C372" s="23"/>
+      <c r="D372" s="39"/>
+      <c r="E372" s="17"/>
+      <c r="F372" s="20"/>
+      <c r="G372" s="18"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G295" xr:uid="{51D60DD1-DC0B-4658-A996-7DC0B41964ED}"/>
+  <autoFilter ref="A1:G372" xr:uid="{51D60DD1-DC0B-4658-A996-7DC0B41964ED}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Resources/Admin/Crosswalks and Schemas.xlsx
+++ b/Resources/Admin/Crosswalks and Schemas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SHDTJB\Documents\LocalSave\Code\R\GitHub\WA-DOH-CHS-Death-Files-ETL\Resources\Admin\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DA9971D-67F4-49C8-965B-6ED0067B6BFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAB0C845-FD16-4D9A-B0AF-26352C9E6F0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5692" uniqueCount="731">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5693" uniqueCount="731">
   <si>
     <t>to_name</t>
   </si>
@@ -20284,6 +20284,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51D60DD1-DC0B-4658-A996-7DC0B41964ED}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:H372"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -20319,7 +20320,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" s="21" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" s="17" t="s">
         <v>4</v>
       </c>
@@ -20332,7 +20333,7 @@
       <c r="F2" s="20"/>
       <c r="G2" s="18"/>
     </row>
-    <row r="3" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" s="21" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" s="17" t="s">
         <v>676</v>
       </c>
@@ -20353,7 +20354,7 @@
       </c>
       <c r="G3" s="18"/>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
         <v>676</v>
       </c>
@@ -20373,7 +20374,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
         <v>676</v>
       </c>
@@ -20393,7 +20394,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" s="12" t="s">
         <v>676</v>
       </c>
@@ -20413,7 +20414,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
         <v>676</v>
       </c>
@@ -20433,7 +20434,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
         <v>676</v>
       </c>
@@ -20453,7 +20454,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" s="21" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
         <v>682</v>
       </c>
@@ -20474,7 +20475,7 @@
       </c>
       <c r="G9" s="18"/>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="12" t="s">
         <v>682</v>
       </c>
@@ -20494,7 +20495,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
         <v>682</v>
       </c>
@@ -20514,7 +20515,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="12" t="s">
         <v>682</v>
       </c>
@@ -20534,7 +20535,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
         <v>682</v>
       </c>
@@ -20554,7 +20555,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
         <v>682</v>
       </c>
@@ -20574,7 +20575,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="12" t="s">
         <v>682</v>
       </c>
@@ -20594,7 +20595,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" s="12" t="s">
         <v>682</v>
       </c>
@@ -20614,7 +20615,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="12" t="s">
         <v>682</v>
       </c>
@@ -20634,7 +20635,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="12" t="s">
         <v>682</v>
       </c>
@@ -20654,7 +20655,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
         <v>682</v>
       </c>
@@ -20674,7 +20675,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="20" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" s="21" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="17" t="s">
         <v>692</v>
       </c>
@@ -20695,7 +20696,7 @@
       </c>
       <c r="G20" s="18"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" s="12" t="s">
         <v>692</v>
       </c>
@@ -20715,7 +20716,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" s="12" t="s">
         <v>692</v>
       </c>
@@ -20735,7 +20736,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="12" t="s">
         <v>692</v>
       </c>
@@ -20755,7 +20756,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="12" t="s">
         <v>692</v>
       </c>
@@ -20775,7 +20776,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="12" t="s">
         <v>692</v>
       </c>
@@ -20795,7 +20796,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="12" t="s">
         <v>692</v>
       </c>
@@ -20815,7 +20816,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="12" t="s">
         <v>692</v>
       </c>
@@ -20835,7 +20836,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="12" t="s">
         <v>692</v>
       </c>
@@ -20855,7 +20856,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="12" t="s">
         <v>692</v>
       </c>
@@ -20875,7 +20876,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="12" t="s">
         <v>692</v>
       </c>
@@ -20895,7 +20896,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="12" t="s">
         <v>692</v>
       </c>
@@ -20915,7 +20916,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="12" t="s">
         <v>692</v>
       </c>
@@ -20935,7 +20936,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="12" t="s">
         <v>692</v>
       </c>
@@ -20955,7 +20956,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" s="12" t="s">
         <v>692</v>
       </c>
@@ -20975,7 +20976,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="12" t="s">
         <v>692</v>
       </c>
@@ -20995,7 +20996,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" s="12" t="s">
         <v>692</v>
       </c>
@@ -21015,7 +21016,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" s="12" t="s">
         <v>692</v>
       </c>
@@ -21035,7 +21036,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" s="12" t="s">
         <v>692</v>
       </c>
@@ -21055,7 +21056,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="12" t="s">
         <v>692</v>
       </c>
@@ -21075,7 +21076,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="40" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" s="21" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" s="17" t="s">
         <v>710</v>
       </c>
@@ -21096,7 +21097,7 @@
       </c>
       <c r="G40" s="18"/>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" s="12" t="s">
         <v>710</v>
       </c>
@@ -21116,7 +21117,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" s="12" t="s">
         <v>710</v>
       </c>
@@ -21136,7 +21137,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" s="12" t="s">
         <v>710</v>
       </c>
@@ -21156,7 +21157,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" s="12" t="s">
         <v>710</v>
       </c>
@@ -21176,7 +21177,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" s="12" t="s">
         <v>710</v>
       </c>
@@ -21196,7 +21197,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" s="12" t="s">
         <v>710</v>
       </c>
@@ -21216,7 +21217,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" s="12" t="s">
         <v>710</v>
       </c>
@@ -21236,7 +21237,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" s="12" t="s">
         <v>710</v>
       </c>
@@ -21256,7 +21257,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" s="12" t="s">
         <v>710</v>
       </c>
@@ -21276,7 +21277,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" s="12" t="s">
         <v>710</v>
       </c>
@@ -21296,7 +21297,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" s="12" t="s">
         <v>710</v>
       </c>
@@ -21316,7 +21317,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" s="12" t="s">
         <v>710</v>
       </c>
@@ -21336,7 +21337,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" s="12" t="s">
         <v>710</v>
       </c>
@@ -21356,7 +21357,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" s="12" t="s">
         <v>710</v>
       </c>
@@ -21376,7 +21377,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" s="12" t="s">
         <v>710</v>
       </c>
@@ -21396,7 +21397,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" s="12" t="s">
         <v>710</v>
       </c>
@@ -21416,7 +21417,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" s="12" t="s">
         <v>710</v>
       </c>
@@ -21436,7 +21437,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="58" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:7" s="21" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" s="17" t="s">
         <v>6</v>
       </c>
@@ -21455,7 +21456,7 @@
       <c r="F58" s="20"/>
       <c r="G58" s="18"/>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" s="12" t="s">
         <v>6</v>
       </c>
@@ -21472,7 +21473,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" s="12" t="s">
         <v>6</v>
       </c>
@@ -21489,7 +21490,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" s="12" t="s">
         <v>6</v>
       </c>
@@ -21506,7 +21507,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" s="12" t="s">
         <v>6</v>
       </c>
@@ -21523,7 +21524,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" s="12" t="s">
         <v>6</v>
       </c>
@@ -21540,7 +21541,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="64" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:7" s="21" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" s="17" t="s">
         <v>7</v>
       </c>
@@ -21553,7 +21554,7 @@
       <c r="F64" s="20"/>
       <c r="G64" s="18"/>
     </row>
-    <row r="65" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:7" s="21" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" s="17" t="s">
         <v>523</v>
       </c>
@@ -21566,7 +21567,7 @@
       <c r="F65" s="20"/>
       <c r="G65" s="18"/>
     </row>
-    <row r="66" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:7" s="21" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" s="17" t="s">
         <v>9</v>
       </c>
@@ -21585,7 +21586,7 @@
       <c r="F66" s="20"/>
       <c r="G66" s="18"/>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" s="12" t="s">
         <v>9</v>
       </c>
@@ -21602,7 +21603,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" s="12" t="s">
         <v>9</v>
       </c>
@@ -21619,7 +21620,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="69" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:7" s="21" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" s="17" t="s">
         <v>10</v>
       </c>
@@ -21638,7 +21639,7 @@
       <c r="F69" s="20"/>
       <c r="G69" s="18"/>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" s="12" t="s">
         <v>10</v>
       </c>
@@ -21655,7 +21656,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71" s="12" t="s">
         <v>10</v>
       </c>
@@ -21672,7 +21673,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="72" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:7" s="21" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" s="17" t="s">
         <v>12</v>
       </c>
@@ -21689,7 +21690,7 @@
       <c r="F72" s="20"/>
       <c r="G72" s="18"/>
     </row>
-    <row r="73" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:7" s="21" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" s="17" t="s">
         <v>14</v>
       </c>
@@ -21706,7 +21707,7 @@
       <c r="F73" s="20"/>
       <c r="G73" s="18"/>
     </row>
-    <row r="74" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:7" s="21" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" s="19" t="s">
         <v>16</v>
       </c>
@@ -21725,7 +21726,7 @@
       <c r="F74" s="20"/>
       <c r="G74" s="18"/>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" s="4" t="s">
         <v>16</v>
       </c>
@@ -21742,7 +21743,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
         <v>16</v>
       </c>
@@ -21759,7 +21760,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" s="4" t="s">
         <v>16</v>
       </c>
@@ -21776,7 +21777,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
         <v>16</v>
       </c>
@@ -21793,7 +21794,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" s="4" t="s">
         <v>16</v>
       </c>
@@ -21810,7 +21811,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
         <v>16</v>
       </c>
@@ -21827,7 +21828,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81" s="4" t="s">
         <v>16</v>
       </c>
@@ -21844,7 +21845,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
         <v>16</v>
       </c>
@@ -21861,7 +21862,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="83" spans="1:8" s="19" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:8" s="19" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83" s="34" t="s">
         <v>629</v>
       </c>
@@ -21874,7 +21875,7 @@
       <c r="F83" s="35"/>
       <c r="G83" s="17"/>
     </row>
-    <row r="84" spans="1:8" s="21" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:8" s="21" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" s="34" t="s">
         <v>630</v>
       </c>
@@ -21887,7 +21888,7 @@
       <c r="F84" s="20"/>
       <c r="G84" s="18"/>
     </row>
-    <row r="85" spans="1:8" s="21" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:8" s="21" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85" s="34" t="s">
         <v>631</v>
       </c>
@@ -21900,7 +21901,7 @@
       <c r="F85" s="20"/>
       <c r="G85" s="18"/>
     </row>
-    <row r="86" spans="1:8" s="21" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:8" s="21" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" s="34" t="s">
         <v>632</v>
       </c>
@@ -21913,7 +21914,7 @@
       <c r="F86" s="20"/>
       <c r="G86" s="18"/>
     </row>
-    <row r="87" spans="1:8" s="21" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:8" s="21" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87" s="34" t="s">
         <v>633</v>
       </c>
@@ -21926,7 +21927,7 @@
       <c r="F87" s="20"/>
       <c r="G87" s="18"/>
     </row>
-    <row r="88" spans="1:8" s="21" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:8" s="21" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88" s="17" t="s">
         <v>525</v>
       </c>
@@ -21940,7 +21941,7 @@
       <c r="G88" s="18"/>
       <c r="H88" s="18"/>
     </row>
-    <row r="89" spans="1:8" s="21" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:8" s="21" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89" s="17" t="s">
         <v>18</v>
       </c>
@@ -21953,7 +21954,7 @@
       <c r="F89" s="20"/>
       <c r="G89" s="18"/>
     </row>
-    <row r="90" spans="1:8" s="21" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:8" s="21" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90" s="17" t="s">
         <v>20</v>
       </c>
@@ -21966,7 +21967,7 @@
       <c r="F90" s="20"/>
       <c r="G90" s="18"/>
     </row>
-    <row r="91" spans="1:8" s="21" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:8" s="21" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" s="17" t="s">
         <v>22</v>
       </c>
@@ -21985,7 +21986,7 @@
       <c r="F91" s="20"/>
       <c r="G91" s="18"/>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" s="12" t="s">
         <v>22</v>
       </c>
@@ -22002,7 +22003,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93" s="12" t="s">
         <v>22</v>
       </c>
@@ -22019,7 +22020,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" s="12" t="s">
         <v>22</v>
       </c>
@@ -22036,7 +22037,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95" s="12" t="s">
         <v>22</v>
       </c>
@@ -22053,7 +22054,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96" s="12" t="s">
         <v>22</v>
       </c>
@@ -22070,7 +22071,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97" s="12" t="s">
         <v>22</v>
       </c>
@@ -22087,7 +22088,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="98" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:7" s="21" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98" s="17" t="s">
         <v>24</v>
       </c>
@@ -22100,7 +22101,7 @@
       <c r="F98" s="20"/>
       <c r="G98" s="18"/>
     </row>
-    <row r="99" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:7" s="21" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99" s="17" t="s">
         <v>26</v>
       </c>
@@ -22113,7 +22114,7 @@
       <c r="F99" s="20"/>
       <c r="G99" s="18"/>
     </row>
-    <row r="100" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:7" s="21" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100" s="17" t="s">
         <v>27</v>
       </c>
@@ -22126,7 +22127,7 @@
       <c r="F100" s="20"/>
       <c r="G100" s="18"/>
     </row>
-    <row r="101" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:7" s="21" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101" s="17" t="s">
         <v>28</v>
       </c>
@@ -22139,7 +22140,7 @@
       <c r="F101" s="20"/>
       <c r="G101" s="18"/>
     </row>
-    <row r="102" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:7" s="21" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102" s="17" t="s">
         <v>30</v>
       </c>
@@ -22152,7 +22153,7 @@
       <c r="F102" s="20"/>
       <c r="G102" s="18"/>
     </row>
-    <row r="103" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:7" s="21" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103" s="17" t="s">
         <v>32</v>
       </c>
@@ -22165,7 +22166,7 @@
       <c r="F103" s="20"/>
       <c r="G103" s="18"/>
     </row>
-    <row r="104" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:7" s="21" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104" s="17" t="s">
         <v>34</v>
       </c>
@@ -22178,7 +22179,7 @@
       <c r="F104" s="20"/>
       <c r="G104" s="18"/>
     </row>
-    <row r="105" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:7" s="21" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105" s="17" t="s">
         <v>36</v>
       </c>
@@ -22191,7 +22192,7 @@
       <c r="F105" s="20"/>
       <c r="G105" s="18"/>
     </row>
-    <row r="106" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:7" s="21" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A106" s="17" t="s">
         <v>38</v>
       </c>
@@ -22204,7 +22205,7 @@
       <c r="F106" s="20"/>
       <c r="G106" s="18"/>
     </row>
-    <row r="107" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:7" s="21" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107" s="17" t="s">
         <v>40</v>
       </c>
@@ -22223,7 +22224,7 @@
       <c r="F107" s="20"/>
       <c r="G107" s="18"/>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A108" s="12" t="s">
         <v>40</v>
       </c>
@@ -22240,7 +22241,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109" s="12" t="s">
         <v>40</v>
       </c>
@@ -22257,7 +22258,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110" s="12" t="s">
         <v>40</v>
       </c>
@@ -22274,7 +22275,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A111" s="12" t="s">
         <v>40</v>
       </c>
@@ -22291,7 +22292,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112" s="12" t="s">
         <v>40</v>
       </c>
@@ -22308,7 +22309,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A113" s="12" t="s">
         <v>40</v>
       </c>
@@ -22325,7 +22326,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114" s="12" t="s">
         <v>40</v>
       </c>
@@ -22342,7 +22343,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="115" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:7" s="21" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A115" s="17" t="s">
         <v>42</v>
       </c>
@@ -22355,7 +22356,7 @@
       <c r="F115" s="20"/>
       <c r="G115" s="18"/>
     </row>
-    <row r="116" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:7" s="21" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A116" s="17" t="s">
         <v>44</v>
       </c>
@@ -22376,7 +22377,7 @@
       </c>
       <c r="G116" s="18"/>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117" s="12" t="s">
         <v>44</v>
       </c>
@@ -22396,7 +22397,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A118" s="12" t="s">
         <v>44</v>
       </c>
@@ -22416,7 +22417,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A119" s="12" t="s">
         <v>44</v>
       </c>
@@ -22436,7 +22437,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120" s="12" t="s">
         <v>44</v>
       </c>
@@ -22456,7 +22457,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121" s="12" t="s">
         <v>44</v>
       </c>
@@ -22476,7 +22477,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122" s="12" t="s">
         <v>44</v>
       </c>
@@ -22496,7 +22497,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A123" s="12" t="s">
         <v>44</v>
       </c>
@@ -22516,7 +22517,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A124" s="12" t="s">
         <v>44</v>
       </c>
@@ -22536,7 +22537,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="125" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:7" s="21" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A125" s="17" t="s">
         <v>46</v>
       </c>
@@ -22557,7 +22558,7 @@
       </c>
       <c r="G125" s="18"/>
     </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A126" s="12" t="s">
         <v>46</v>
       </c>
@@ -22577,7 +22578,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A127" s="12" t="s">
         <v>46</v>
       </c>
@@ -22597,7 +22598,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A128" s="12" t="s">
         <v>46</v>
       </c>
@@ -22617,7 +22618,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A129" s="12" t="s">
         <v>46</v>
       </c>
@@ -22637,7 +22638,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A130" s="12" t="s">
         <v>46</v>
       </c>
@@ -22657,7 +22658,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A131" s="12" t="s">
         <v>46</v>
       </c>
@@ -22677,7 +22678,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A132" s="12" t="s">
         <v>46</v>
       </c>
@@ -22697,7 +22698,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A133" s="12" t="s">
         <v>46</v>
       </c>
@@ -22717,7 +22718,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A134" s="12" t="s">
         <v>46</v>
       </c>
@@ -22737,7 +22738,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="135" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:7" s="21" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A135" s="19" t="s">
         <v>391</v>
       </c>
@@ -22750,7 +22751,7 @@
       <c r="F135" s="20"/>
       <c r="G135" s="18"/>
     </row>
-    <row r="136" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:7" s="21" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A136" s="19" t="s">
         <v>713</v>
       </c>
@@ -22763,7 +22764,7 @@
       <c r="F136" s="20"/>
       <c r="G136" s="18"/>
     </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A137" s="4" t="s">
         <v>713</v>
       </c>
@@ -22771,7 +22772,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="138" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:7" s="21" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A138" s="17" t="s">
         <v>48</v>
       </c>
@@ -22790,7 +22791,7 @@
       <c r="F138" s="20"/>
       <c r="G138" s="18"/>
     </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A139" s="12" t="s">
         <v>48</v>
       </c>
@@ -22807,7 +22808,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A140" s="12" t="s">
         <v>48</v>
       </c>
@@ -22824,7 +22825,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="141" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:7" s="21" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A141" s="17" t="s">
         <v>50</v>
       </c>
@@ -22843,7 +22844,7 @@
       <c r="F141" s="20"/>
       <c r="G141" s="18"/>
     </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A142" s="12" t="s">
         <v>50</v>
       </c>
@@ -22860,7 +22861,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A143" s="12" t="s">
         <v>50</v>
       </c>
@@ -22877,7 +22878,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="144" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:7" s="21" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A144" s="17" t="s">
         <v>52</v>
       </c>
@@ -22896,7 +22897,7 @@
       <c r="F144" s="20"/>
       <c r="G144" s="18"/>
     </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A145" s="12" t="s">
         <v>52</v>
       </c>
@@ -22913,7 +22914,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A146" s="12" t="s">
         <v>52</v>
       </c>
@@ -22930,7 +22931,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A147" s="12" t="s">
         <v>52</v>
       </c>
@@ -22947,7 +22948,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A148" s="12" t="s">
         <v>52</v>
       </c>
@@ -22964,7 +22965,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A149" s="12" t="s">
         <v>52</v>
       </c>
@@ -22981,7 +22982,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A150" s="12" t="s">
         <v>52</v>
       </c>
@@ -22998,7 +22999,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="151" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:7" s="21" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A151" s="17" t="s">
         <v>54</v>
       </c>
@@ -23017,7 +23018,7 @@
       <c r="F151" s="20"/>
       <c r="G151" s="18"/>
     </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A152" s="12" t="s">
         <v>54</v>
       </c>
@@ -23034,7 +23035,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A153" s="12" t="s">
         <v>54</v>
       </c>
@@ -23051,7 +23052,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="154" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:7" s="21" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A154" s="17" t="s">
         <v>56</v>
       </c>
@@ -23070,7 +23071,7 @@
       <c r="F154" s="20"/>
       <c r="G154" s="18"/>
     </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A155" s="12" t="s">
         <v>56</v>
       </c>
@@ -23087,7 +23088,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A156" s="12" t="s">
         <v>56</v>
       </c>
@@ -23104,7 +23105,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="157" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:7" s="21" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A157" s="17" t="s">
         <v>58</v>
       </c>
@@ -23123,7 +23124,7 @@
       <c r="F157" s="20"/>
       <c r="G157" s="18"/>
     </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A158" s="12" t="s">
         <v>58</v>
       </c>
@@ -23140,7 +23141,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A159" s="12" t="s">
         <v>58</v>
       </c>
@@ -23157,7 +23158,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="160" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:7" s="21" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A160" s="17" t="s">
         <v>60</v>
       </c>
@@ -23170,7 +23171,7 @@
       <c r="F160" s="20"/>
       <c r="G160" s="18"/>
     </row>
-    <row r="161" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:7" s="21" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A161" s="17" t="s">
         <v>62</v>
       </c>
@@ -23183,7 +23184,7 @@
       <c r="F161" s="20"/>
       <c r="G161" s="18"/>
     </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A162" s="12" t="s">
         <v>64</v>
       </c>
@@ -23200,7 +23201,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A163" s="12" t="s">
         <v>64</v>
       </c>
@@ -23217,7 +23218,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A164" s="12" t="s">
         <v>64</v>
       </c>
@@ -23234,7 +23235,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A165" s="12" t="s">
         <v>64</v>
       </c>
@@ -23251,7 +23252,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A166" s="12" t="s">
         <v>64</v>
       </c>
@@ -23268,7 +23269,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A167" s="12" t="s">
         <v>64</v>
       </c>
@@ -23285,7 +23286,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A168" s="12" t="s">
         <v>64</v>
       </c>
@@ -23302,7 +23303,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A169" s="12" t="s">
         <v>64</v>
       </c>
@@ -23319,7 +23320,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A170" s="12" t="s">
         <v>64</v>
       </c>
@@ -23336,7 +23337,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A171" s="12" t="s">
         <v>64</v>
       </c>
@@ -23353,7 +23354,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="172" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:7" s="21" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A172" s="17" t="s">
         <v>66</v>
       </c>
@@ -23372,7 +23373,7 @@
       <c r="F172" s="20"/>
       <c r="G172" s="18"/>
     </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A173" s="12" t="s">
         <v>66</v>
       </c>
@@ -23389,7 +23390,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A174" s="12" t="s">
         <v>66</v>
       </c>
@@ -23406,7 +23407,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A175" s="12" t="s">
         <v>67</v>
       </c>
@@ -23414,7 +23415,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="176" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:7" s="21" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A176" s="17" t="s">
         <v>68</v>
       </c>
@@ -23427,7 +23428,7 @@
       <c r="F176" s="20"/>
       <c r="G176" s="18"/>
     </row>
-    <row r="177" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:7" s="21" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A177" s="17" t="s">
         <v>69</v>
       </c>
@@ -23440,7 +23441,7 @@
       <c r="F177" s="20"/>
       <c r="G177" s="18"/>
     </row>
-    <row r="178" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:7" s="21" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A178" s="17" t="s">
         <v>71</v>
       </c>
@@ -23453,7 +23454,7 @@
       <c r="F178" s="20"/>
       <c r="G178" s="18"/>
     </row>
-    <row r="179" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:7" s="21" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A179" s="17" t="s">
         <v>73</v>
       </c>
@@ -23466,7 +23467,7 @@
       <c r="F179" s="20"/>
       <c r="G179" s="18"/>
     </row>
-    <row r="180" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:7" s="21" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A180" s="17" t="s">
         <v>634</v>
       </c>
@@ -23479,7 +23480,7 @@
       <c r="F180" s="20"/>
       <c r="G180" s="18"/>
     </row>
-    <row r="181" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:7" s="21" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A181" s="17" t="s">
         <v>75</v>
       </c>
@@ -23492,7 +23493,7 @@
       <c r="F181" s="20"/>
       <c r="G181" s="18"/>
     </row>
-    <row r="182" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:7" s="21" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A182" s="17" t="s">
         <v>77</v>
       </c>
@@ -23505,7 +23506,7 @@
       <c r="F182" s="20"/>
       <c r="G182" s="18"/>
     </row>
-    <row r="183" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:7" s="21" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A183" s="17" t="s">
         <v>79</v>
       </c>
@@ -23518,7 +23519,7 @@
       <c r="F183" s="20"/>
       <c r="G183" s="18"/>
     </row>
-    <row r="184" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:7" s="21" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A184" s="17" t="s">
         <v>81</v>
       </c>
@@ -23531,7 +23532,7 @@
       <c r="F184" s="20"/>
       <c r="G184" s="18"/>
     </row>
-    <row r="185" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:7" s="21" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A185" s="17" t="s">
         <v>83</v>
       </c>
@@ -23550,7 +23551,7 @@
       <c r="F185" s="20"/>
       <c r="G185" s="18"/>
     </row>
-    <row r="186" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A186" s="12" t="s">
         <v>83</v>
       </c>
@@ -23567,7 +23568,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="187" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A187" s="12" t="s">
         <v>83</v>
       </c>
@@ -23584,7 +23585,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="188" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A188" s="12" t="s">
         <v>83</v>
       </c>
@@ -23601,7 +23602,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="189" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A189" s="12" t="s">
         <v>83</v>
       </c>
@@ -23618,7 +23619,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="190" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A190" s="12" t="s">
         <v>83</v>
       </c>
@@ -23635,7 +23636,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="191" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A191" s="12" t="s">
         <v>83</v>
       </c>
@@ -23655,7 +23656,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="192" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:7" s="21" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A192" s="17" t="s">
         <v>85</v>
       </c>
@@ -23674,7 +23675,7 @@
       <c r="F192" s="20"/>
       <c r="G192" s="18"/>
     </row>
-    <row r="193" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A193" s="12" t="s">
         <v>85</v>
       </c>
@@ -23691,7 +23692,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="194" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A194" s="12" t="s">
         <v>85</v>
       </c>
@@ -23708,7 +23709,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="195" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A195" s="12" t="s">
         <v>85</v>
       </c>
@@ -23725,7 +23726,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="196" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A196" s="12" t="s">
         <v>85</v>
       </c>
@@ -23742,7 +23743,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="197" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A197" s="12" t="s">
         <v>85</v>
       </c>
@@ -23759,7 +23760,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="198" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A198" s="12" t="s">
         <v>85</v>
       </c>
@@ -23776,7 +23777,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="199" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:7" s="21" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A199" s="17" t="s">
         <v>87</v>
       </c>
@@ -23795,7 +23796,7 @@
       <c r="F199" s="20"/>
       <c r="G199" s="18"/>
     </row>
-    <row r="200" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A200" s="12" t="s">
         <v>87</v>
       </c>
@@ -23812,7 +23813,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="201" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A201" s="12" t="s">
         <v>87</v>
       </c>
@@ -23829,7 +23830,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="202" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:7" s="21" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A202" s="17" t="s">
         <v>647</v>
       </c>
@@ -23842,7 +23843,7 @@
       <c r="F202" s="20"/>
       <c r="G202" s="18"/>
     </row>
-    <row r="203" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:7" s="21" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A203" s="17" t="s">
         <v>648</v>
       </c>
@@ -23855,7 +23856,7 @@
       <c r="F203" s="20"/>
       <c r="G203" s="18"/>
     </row>
-    <row r="204" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:7" s="21" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A204" s="17" t="s">
         <v>649</v>
       </c>
@@ -23868,7 +23869,7 @@
       <c r="F204" s="20"/>
       <c r="G204" s="18"/>
     </row>
-    <row r="205" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:7" s="21" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A205" s="17" t="s">
         <v>650</v>
       </c>
@@ -23881,7 +23882,7 @@
       <c r="F205" s="20"/>
       <c r="G205" s="18"/>
     </row>
-    <row r="206" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:7" s="21" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A206" s="17" t="s">
         <v>89</v>
       </c>
@@ -23894,7 +23895,7 @@
       <c r="F206" s="20"/>
       <c r="G206" s="18"/>
     </row>
-    <row r="207" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A207" s="12" t="s">
         <v>91</v>
       </c>
@@ -23911,7 +23912,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="208" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A208" s="12" t="s">
         <v>91</v>
       </c>
@@ -23928,7 +23929,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="209" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A209" s="12" t="s">
         <v>91</v>
       </c>
@@ -23945,7 +23946,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="210" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A210" s="12" t="s">
         <v>91</v>
       </c>
@@ -23962,7 +23963,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="211" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A211" s="12" t="s">
         <v>91</v>
       </c>
@@ -23979,7 +23980,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="212" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A212" s="12" t="s">
         <v>91</v>
       </c>
@@ -23996,7 +23997,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="213" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A213" s="12" t="s">
         <v>91</v>
       </c>
@@ -24013,7 +24014,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="214" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A214" s="12" t="s">
         <v>91</v>
       </c>
@@ -24030,7 +24031,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="215" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A215" s="12" t="s">
         <v>91</v>
       </c>
@@ -24047,7 +24048,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="216" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A216" s="12" t="s">
         <v>91</v>
       </c>
@@ -24064,7 +24065,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="217" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:7" s="21" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A217" s="17" t="s">
         <v>93</v>
       </c>
@@ -24083,7 +24084,7 @@
       <c r="F217" s="20"/>
       <c r="G217" s="18"/>
     </row>
-    <row r="218" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A218" s="12" t="s">
         <v>93</v>
       </c>
@@ -24100,7 +24101,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="219" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A219" s="12" t="s">
         <v>93</v>
       </c>
@@ -24117,7 +24118,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="220" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A220" s="12" t="s">
         <v>93</v>
       </c>
@@ -24134,7 +24135,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="221" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A221" s="12" t="s">
         <v>93</v>
       </c>
@@ -24151,7 +24152,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="222" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A222" s="12" t="s">
         <v>93</v>
       </c>
@@ -24181,7 +24182,9 @@
       <c r="D223" s="39" t="s">
         <v>717</v>
       </c>
-      <c r="E223" s="17"/>
+      <c r="E223" s="39" t="s">
+        <v>717</v>
+      </c>
       <c r="F223" s="20"/>
       <c r="G223" s="18"/>
     </row>
@@ -24198,8 +24201,8 @@
       <c r="D224" s="40" t="s">
         <v>718</v>
       </c>
-      <c r="E224" s="12" t="s">
-        <v>717</v>
+      <c r="E224" s="40" t="s">
+        <v>718</v>
       </c>
     </row>
     <row r="225" spans="1:7" x14ac:dyDescent="0.25">
@@ -24215,8 +24218,8 @@
       <c r="D225" s="40" t="s">
         <v>719</v>
       </c>
-      <c r="E225" s="12" t="s">
-        <v>718</v>
+      <c r="E225" s="40" t="s">
+        <v>719</v>
       </c>
     </row>
     <row r="226" spans="1:7" x14ac:dyDescent="0.25">
@@ -24232,8 +24235,8 @@
       <c r="D226" s="40" t="s">
         <v>720</v>
       </c>
-      <c r="E226" s="12" t="s">
-        <v>719</v>
+      <c r="E226" s="40" t="s">
+        <v>720</v>
       </c>
     </row>
     <row r="227" spans="1:7" ht="45" x14ac:dyDescent="0.25">
@@ -24249,8 +24252,8 @@
       <c r="D227" s="40" t="s">
         <v>721</v>
       </c>
-      <c r="E227" s="12" t="s">
-        <v>720</v>
+      <c r="E227" s="40" t="s">
+        <v>721</v>
       </c>
     </row>
     <row r="228" spans="1:7" x14ac:dyDescent="0.25">
@@ -24266,11 +24269,11 @@
       <c r="D228" s="40" t="s">
         <v>730</v>
       </c>
-      <c r="E228" s="12" t="s">
-        <v>721</v>
-      </c>
-    </row>
-    <row r="229" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E228" s="40" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="229" spans="1:7" s="21" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A229" s="17" t="s">
         <v>95</v>
       </c>
@@ -24289,7 +24292,7 @@
       <c r="F229" s="20"/>
       <c r="G229" s="18"/>
     </row>
-    <row r="230" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A230" s="12" t="s">
         <v>95</v>
       </c>
@@ -24306,7 +24309,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="231" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A231" s="12" t="s">
         <v>95</v>
       </c>
@@ -24323,7 +24326,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="232" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:7" s="21" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A232" s="17" t="s">
         <v>674</v>
       </c>
@@ -24342,7 +24345,7 @@
       <c r="F232" s="20"/>
       <c r="G232" s="18"/>
     </row>
-    <row r="233" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A233" s="12" t="s">
         <v>674</v>
       </c>
@@ -24359,7 +24362,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="234" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:7" s="21" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A234" s="17" t="s">
         <v>97</v>
       </c>
@@ -24378,7 +24381,7 @@
       <c r="F234" s="20"/>
       <c r="G234" s="18"/>
     </row>
-    <row r="235" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A235" s="12" t="s">
         <v>97</v>
       </c>
@@ -24395,7 +24398,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="236" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A236" s="12" t="s">
         <v>97</v>
       </c>
@@ -24412,7 +24415,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="237" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:7" s="21" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A237" s="17" t="s">
         <v>99</v>
       </c>
@@ -24431,7 +24434,7 @@
       <c r="F237" s="20"/>
       <c r="G237" s="18"/>
     </row>
-    <row r="238" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A238" s="12" t="s">
         <v>99</v>
       </c>
@@ -24448,7 +24451,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="239" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A239" s="12" t="s">
         <v>99</v>
       </c>
@@ -24465,7 +24468,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="240" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:7" s="21" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A240" s="17" t="s">
         <v>101</v>
       </c>
@@ -24484,7 +24487,7 @@
       <c r="F240" s="20"/>
       <c r="G240" s="18"/>
     </row>
-    <row r="241" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A241" s="12" t="s">
         <v>101</v>
       </c>
@@ -24501,7 +24504,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="242" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A242" s="12" t="s">
         <v>101</v>
       </c>
@@ -24518,7 +24521,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="243" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:7" s="21" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A243" s="17" t="s">
         <v>673</v>
       </c>
@@ -24531,7 +24534,7 @@
       <c r="F243" s="20"/>
       <c r="G243" s="18"/>
     </row>
-    <row r="244" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:7" s="21" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A244" s="17" t="s">
         <v>714</v>
       </c>
@@ -24550,7 +24553,7 @@
       <c r="F244" s="20"/>
       <c r="G244" s="18"/>
     </row>
-    <row r="245" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A245" s="12" t="s">
         <v>714</v>
       </c>
@@ -24567,7 +24570,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="246" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:7" s="21" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A246" s="17" t="s">
         <v>722</v>
       </c>
@@ -24586,7 +24589,7 @@
       <c r="F246" s="20"/>
       <c r="G246" s="18"/>
     </row>
-    <row r="247" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A247" s="12" t="s">
         <v>722</v>
       </c>
@@ -24603,7 +24606,7 @@
         <v>724</v>
       </c>
     </row>
-    <row r="248" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A248" s="12" t="s">
         <v>722</v>
       </c>
@@ -24620,7 +24623,7 @@
         <v>725</v>
       </c>
     </row>
-    <row r="249" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A249" s="12" t="s">
         <v>722</v>
       </c>
@@ -24637,7 +24640,7 @@
         <v>726</v>
       </c>
     </row>
-    <row r="250" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A250" s="12" t="s">
         <v>722</v>
       </c>
@@ -24654,7 +24657,7 @@
         <v>727</v>
       </c>
     </row>
-    <row r="251" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:7" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A251" s="12" t="s">
         <v>722</v>
       </c>
@@ -24671,7 +24674,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="252" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A252" s="12" t="s">
         <v>722</v>
       </c>
@@ -24688,7 +24691,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="253" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:7" s="21" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A253" s="17" t="s">
         <v>103</v>
       </c>
@@ -24707,7 +24710,7 @@
       <c r="F253" s="20"/>
       <c r="G253" s="18"/>
     </row>
-    <row r="254" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A254" s="12" t="s">
         <v>103</v>
       </c>
@@ -24724,7 +24727,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="255" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A255" s="12" t="s">
         <v>103</v>
       </c>
@@ -24741,7 +24744,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="256" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:7" s="21" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A256" s="17" t="s">
         <v>105</v>
       </c>
@@ -24760,7 +24763,7 @@
       <c r="F256" s="20"/>
       <c r="G256" s="18"/>
     </row>
-    <row r="257" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A257" s="12" t="s">
         <v>105</v>
       </c>
@@ -24777,7 +24780,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="258" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A258" s="12" t="s">
         <v>105</v>
       </c>
@@ -24794,7 +24797,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="259" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:7" s="21" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A259" s="17" t="s">
         <v>107</v>
       </c>
@@ -24813,7 +24816,7 @@
       <c r="F259" s="20"/>
       <c r="G259" s="18"/>
     </row>
-    <row r="260" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A260" s="12" t="s">
         <v>107</v>
       </c>
@@ -24830,7 +24833,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="261" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A261" s="12" t="s">
         <v>107</v>
       </c>
@@ -24847,7 +24850,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="262" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:7" s="21" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A262" s="17" t="s">
         <v>109</v>
       </c>
@@ -24866,7 +24869,7 @@
       <c r="F262" s="20"/>
       <c r="G262" s="18"/>
     </row>
-    <row r="263" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A263" s="12" t="s">
         <v>109</v>
       </c>
@@ -24883,7 +24886,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="264" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A264" s="12" t="s">
         <v>109</v>
       </c>
@@ -24900,7 +24903,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="265" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:7" s="21" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A265" s="17" t="s">
         <v>111</v>
       </c>
@@ -24919,7 +24922,7 @@
       <c r="F265" s="20"/>
       <c r="G265" s="18"/>
     </row>
-    <row r="266" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A266" s="12" t="s">
         <v>111</v>
       </c>
@@ -24936,7 +24939,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="267" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A267" s="12" t="s">
         <v>111</v>
       </c>
@@ -24953,7 +24956,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="268" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:7" s="21" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A268" s="17" t="s">
         <v>675</v>
       </c>
@@ -24972,7 +24975,7 @@
       <c r="F268" s="20"/>
       <c r="G268" s="18"/>
     </row>
-    <row r="269" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A269" s="12" t="s">
         <v>675</v>
       </c>
@@ -24989,7 +24992,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="270" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:7" s="21" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A270" s="17" t="s">
         <v>113</v>
       </c>
@@ -25008,7 +25011,7 @@
       <c r="F270" s="20"/>
       <c r="G270" s="18"/>
     </row>
-    <row r="271" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A271" s="12" t="s">
         <v>113</v>
       </c>
@@ -25025,7 +25028,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="272" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A272" s="12" t="s">
         <v>113</v>
       </c>
@@ -25042,7 +25045,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="273" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:7" s="21" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A273" s="17" t="s">
         <v>115</v>
       </c>
@@ -25061,7 +25064,7 @@
       <c r="F273" s="20"/>
       <c r="G273" s="18"/>
     </row>
-    <row r="274" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A274" s="12" t="s">
         <v>115</v>
       </c>
@@ -25078,7 +25081,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="275" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A275" s="12" t="s">
         <v>115</v>
       </c>
@@ -25095,7 +25098,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="276" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:7" s="21" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A276" s="17" t="s">
         <v>117</v>
       </c>
@@ -25114,7 +25117,7 @@
       <c r="F276" s="20"/>
       <c r="G276" s="18"/>
     </row>
-    <row r="277" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A277" s="12" t="s">
         <v>117</v>
       </c>
@@ -25131,7 +25134,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="278" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A278" s="12" t="s">
         <v>117</v>
       </c>
@@ -25148,7 +25151,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="279" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:7" s="21" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A279" s="17" t="s">
         <v>119</v>
       </c>
@@ -25167,7 +25170,7 @@
       <c r="F279" s="20"/>
       <c r="G279" s="18"/>
     </row>
-    <row r="280" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A280" s="12" t="s">
         <v>119</v>
       </c>
@@ -25184,7 +25187,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="281" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A281" s="12" t="s">
         <v>119</v>
       </c>
@@ -25201,7 +25204,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="282" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:7" s="21" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A282" s="17" t="s">
         <v>121</v>
       </c>
@@ -25220,7 +25223,7 @@
       <c r="F282" s="20"/>
       <c r="G282" s="18"/>
     </row>
-    <row r="283" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A283" s="12" t="s">
         <v>121</v>
       </c>
@@ -25237,7 +25240,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="284" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A284" s="12" t="s">
         <v>121</v>
       </c>
@@ -25254,7 +25257,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="285" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A285" s="12" t="s">
         <v>121</v>
       </c>
@@ -25271,7 +25274,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="286" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A286" s="12" t="s">
         <v>121</v>
       </c>
@@ -25288,7 +25291,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="287" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A287" s="12" t="s">
         <v>121</v>
       </c>
@@ -25305,7 +25308,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="288" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A288" s="12" t="s">
         <v>121</v>
       </c>
@@ -25322,7 +25325,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="289" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A289" s="12" t="s">
         <v>121</v>
       </c>
@@ -25339,7 +25342,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="290" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A290" s="12" t="s">
         <v>121</v>
       </c>
@@ -25356,7 +25359,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="291" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A291" s="12" t="s">
         <v>121</v>
       </c>
@@ -25373,7 +25376,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="292" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A292" s="12" t="s">
         <v>121</v>
       </c>
@@ -25390,7 +25393,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="293" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A293" s="12" t="s">
         <v>121</v>
       </c>
@@ -25407,7 +25410,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="294" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A294" s="12" t="s">
         <v>121</v>
       </c>
@@ -25424,7 +25427,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="295" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A295" s="12" t="s">
         <v>121</v>
       </c>
@@ -25441,7 +25444,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="296" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A296" s="12" t="s">
         <v>121</v>
       </c>
@@ -25458,7 +25461,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="297" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A297" s="12" t="s">
         <v>121</v>
       </c>
@@ -25475,7 +25478,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="298" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A298" s="12" t="s">
         <v>121</v>
       </c>
@@ -25492,7 +25495,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="299" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A299" s="12" t="s">
         <v>121</v>
       </c>
@@ -25509,7 +25512,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="300" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A300" s="12" t="s">
         <v>121</v>
       </c>
@@ -25526,7 +25529,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="301" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:5" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A301" s="12" t="s">
         <v>121</v>
       </c>
@@ -25543,7 +25546,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="302" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A302" s="12" t="s">
         <v>121</v>
       </c>
@@ -25560,7 +25563,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="303" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A303" s="12" t="s">
         <v>121</v>
       </c>
@@ -25577,7 +25580,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="304" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:5" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A304" s="12" t="s">
         <v>121</v>
       </c>
@@ -25594,7 +25597,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="305" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A305" s="12" t="s">
         <v>121</v>
       </c>
@@ -25611,7 +25614,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="306" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:7" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A306" s="12" t="s">
         <v>121</v>
       </c>
@@ -25628,7 +25631,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="307" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A307" s="12" t="s">
         <v>121</v>
       </c>
@@ -25645,7 +25648,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="308" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:7" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A308" s="12" t="s">
         <v>121</v>
       </c>
@@ -25662,7 +25665,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="309" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A309" s="12" t="s">
         <v>121</v>
       </c>
@@ -25679,7 +25682,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="310" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:7" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A310" s="12" t="s">
         <v>121</v>
       </c>
@@ -25696,7 +25699,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="311" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:7" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A311" s="12" t="s">
         <v>121</v>
       </c>
@@ -25713,7 +25716,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="312" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:7" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A312" s="12" t="s">
         <v>121</v>
       </c>
@@ -25730,7 +25733,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="313" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A313" s="12" t="s">
         <v>121</v>
       </c>
@@ -25747,7 +25750,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="314" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:7" s="21" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A314" s="19" t="s">
         <v>123</v>
       </c>
@@ -25766,7 +25769,7 @@
       <c r="F314" s="20"/>
       <c r="G314" s="18"/>
     </row>
-    <row r="315" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A315" s="4" t="s">
         <v>123</v>
       </c>
@@ -25783,7 +25786,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="316" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A316" s="4" t="s">
         <v>123</v>
       </c>
@@ -25800,7 +25803,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="317" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:7" s="21" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A317" s="19" t="s">
         <v>125</v>
       </c>
@@ -25819,7 +25822,7 @@
       <c r="F317" s="20"/>
       <c r="G317" s="18"/>
     </row>
-    <row r="318" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A318" s="4" t="s">
         <v>125</v>
       </c>
@@ -25836,7 +25839,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="319" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A319" s="4" t="s">
         <v>125</v>
       </c>
@@ -25853,7 +25856,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="320" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:7" s="21" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A320" s="19" t="s">
         <v>127</v>
       </c>
@@ -25866,7 +25869,7 @@
       <c r="F320" s="20"/>
       <c r="G320" s="18"/>
     </row>
-    <row r="321" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:7" s="21" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A321" s="19" t="s">
         <v>149</v>
       </c>
@@ -25879,7 +25882,7 @@
       <c r="F321" s="20"/>
       <c r="G321" s="18"/>
     </row>
-    <row r="322" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:7" s="21" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A322" s="19" t="s">
         <v>153</v>
       </c>
@@ -25892,7 +25895,7 @@
       <c r="F322" s="20"/>
       <c r="G322" s="18"/>
     </row>
-    <row r="323" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:7" s="21" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A323" s="19" t="s">
         <v>155</v>
       </c>
@@ -25905,7 +25908,7 @@
       <c r="F323" s="20"/>
       <c r="G323" s="18"/>
     </row>
-    <row r="324" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:7" s="21" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A324" s="19" t="s">
         <v>157</v>
       </c>
@@ -25918,7 +25921,7 @@
       <c r="F324" s="20"/>
       <c r="G324" s="18"/>
     </row>
-    <row r="325" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:7" s="21" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A325" s="19" t="s">
         <v>159</v>
       </c>
@@ -25931,7 +25934,7 @@
       <c r="F325" s="20"/>
       <c r="G325" s="18"/>
     </row>
-    <row r="326" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:7" s="21" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A326" s="19" t="s">
         <v>161</v>
       </c>
@@ -25944,7 +25947,7 @@
       <c r="F326" s="20"/>
       <c r="G326" s="18"/>
     </row>
-    <row r="327" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:7" s="21" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A327" s="19" t="s">
         <v>163</v>
       </c>
@@ -25957,7 +25960,7 @@
       <c r="F327" s="20"/>
       <c r="G327" s="18"/>
     </row>
-    <row r="328" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:7" s="21" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A328" s="19" t="s">
         <v>165</v>
       </c>
@@ -25970,7 +25973,7 @@
       <c r="F328" s="20"/>
       <c r="G328" s="18"/>
     </row>
-    <row r="329" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:7" s="21" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A329" s="19" t="s">
         <v>129</v>
       </c>
@@ -25983,7 +25986,7 @@
       <c r="F329" s="20"/>
       <c r="G329" s="18"/>
     </row>
-    <row r="330" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:7" s="21" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A330" s="19" t="s">
         <v>131</v>
       </c>
@@ -25996,7 +25999,7 @@
       <c r="F330" s="20"/>
       <c r="G330" s="18"/>
     </row>
-    <row r="331" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:7" s="21" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A331" s="19" t="s">
         <v>133</v>
       </c>
@@ -26009,7 +26012,7 @@
       <c r="F331" s="20"/>
       <c r="G331" s="18"/>
     </row>
-    <row r="332" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:7" s="21" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A332" s="19" t="s">
         <v>135</v>
       </c>
@@ -26022,7 +26025,7 @@
       <c r="F332" s="20"/>
       <c r="G332" s="18"/>
     </row>
-    <row r="333" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:7" s="21" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A333" s="19" t="s">
         <v>137</v>
       </c>
@@ -26035,7 +26038,7 @@
       <c r="F333" s="20"/>
       <c r="G333" s="18"/>
     </row>
-    <row r="334" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:7" s="21" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A334" s="19" t="s">
         <v>139</v>
       </c>
@@ -26048,7 +26051,7 @@
       <c r="F334" s="20"/>
       <c r="G334" s="18"/>
     </row>
-    <row r="335" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:7" s="21" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A335" s="19" t="s">
         <v>141</v>
       </c>
@@ -26061,7 +26064,7 @@
       <c r="F335" s="20"/>
       <c r="G335" s="18"/>
     </row>
-    <row r="336" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:7" s="21" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A336" s="19" t="s">
         <v>143</v>
       </c>
@@ -26074,7 +26077,7 @@
       <c r="F336" s="20"/>
       <c r="G336" s="18"/>
     </row>
-    <row r="337" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:7" s="21" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A337" s="19" t="s">
         <v>145</v>
       </c>
@@ -26087,7 +26090,7 @@
       <c r="F337" s="20"/>
       <c r="G337" s="18"/>
     </row>
-    <row r="338" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:7" s="21" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A338" s="19" t="s">
         <v>147</v>
       </c>
@@ -26100,7 +26103,7 @@
       <c r="F338" s="20"/>
       <c r="G338" s="18"/>
     </row>
-    <row r="339" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:7" s="21" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A339" s="19" t="s">
         <v>151</v>
       </c>
@@ -26113,7 +26116,7 @@
       <c r="F339" s="20"/>
       <c r="G339" s="18"/>
     </row>
-    <row r="340" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:7" s="21" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A340" s="17" t="s">
         <v>167</v>
       </c>
@@ -26132,7 +26135,7 @@
       <c r="F340" s="20"/>
       <c r="G340" s="18"/>
     </row>
-    <row r="341" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A341" s="12" t="s">
         <v>167</v>
       </c>
@@ -26149,7 +26152,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="342" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A342" s="12" t="s">
         <v>167</v>
       </c>
@@ -26166,7 +26169,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="343" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:7" s="21" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A343" s="19" t="s">
         <v>168</v>
       </c>
@@ -26179,7 +26182,7 @@
       <c r="F343" s="20"/>
       <c r="G343" s="18"/>
     </row>
-    <row r="344" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:7" s="21" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A344" s="19" t="s">
         <v>169</v>
       </c>
@@ -26192,7 +26195,7 @@
       <c r="F344" s="20"/>
       <c r="G344" s="18"/>
     </row>
-    <row r="345" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:7" s="21" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A345" s="19" t="s">
         <v>170</v>
       </c>
@@ -26205,7 +26208,7 @@
       <c r="F345" s="20"/>
       <c r="G345" s="18"/>
     </row>
-    <row r="346" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:7" s="21" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A346" s="19" t="s">
         <v>172</v>
       </c>
@@ -26218,7 +26221,7 @@
       <c r="F346" s="20"/>
       <c r="G346" s="18"/>
     </row>
-    <row r="347" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:7" s="21" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A347" s="19" t="s">
         <v>174</v>
       </c>
@@ -26231,7 +26234,7 @@
       <c r="F347" s="20"/>
       <c r="G347" s="18"/>
     </row>
-    <row r="348" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:7" s="21" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A348" s="19" t="s">
         <v>176</v>
       </c>
@@ -26244,7 +26247,7 @@
       <c r="F348" s="20"/>
       <c r="G348" s="18"/>
     </row>
-    <row r="349" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:7" s="21" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A349" s="17" t="s">
         <v>178</v>
       </c>
@@ -26263,7 +26266,7 @@
       <c r="F349" s="20"/>
       <c r="G349" s="18"/>
     </row>
-    <row r="350" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A350" s="12" t="s">
         <v>178</v>
       </c>
@@ -26280,7 +26283,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="351" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A351" s="12" t="s">
         <v>178</v>
       </c>
@@ -26297,7 +26300,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="352" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A352" s="12" t="s">
         <v>178</v>
       </c>
@@ -26314,7 +26317,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="353" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A353" s="12" t="s">
         <v>178</v>
       </c>
@@ -26331,7 +26334,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="354" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A354" s="12" t="s">
         <v>178</v>
       </c>
@@ -26348,7 +26351,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="355" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A355" s="12" t="s">
         <v>178</v>
       </c>
@@ -26365,7 +26368,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="356" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:7" s="21" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A356" s="17" t="s">
         <v>180</v>
       </c>
@@ -26378,7 +26381,7 @@
       <c r="F356" s="20"/>
       <c r="G356" s="18"/>
     </row>
-    <row r="357" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:7" s="21" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A357" s="17" t="s">
         <v>182</v>
       </c>
@@ -26391,7 +26394,7 @@
       <c r="F357" s="20"/>
       <c r="G357" s="18"/>
     </row>
-    <row r="358" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:7" s="21" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A358" s="19" t="s">
         <v>183</v>
       </c>
@@ -26410,7 +26413,7 @@
       <c r="F358" s="20"/>
       <c r="G358" s="18"/>
     </row>
-    <row r="359" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A359" s="4" t="s">
         <v>183</v>
       </c>
@@ -26427,7 +26430,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="360" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A360" s="4" t="s">
         <v>183</v>
       </c>
@@ -26444,7 +26447,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="361" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A361" s="4" t="s">
         <v>183</v>
       </c>
@@ -26464,7 +26467,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="362" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:7" s="21" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A362" s="19" t="s">
         <v>651</v>
       </c>
@@ -26476,7 +26479,7 @@
       <c r="E362" s="19"/>
       <c r="F362" s="20"/>
     </row>
-    <row r="363" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:7" s="21" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A363" s="19" t="s">
         <v>527</v>
       </c>
@@ -26489,7 +26492,7 @@
       <c r="F363" s="20"/>
       <c r="G363" s="18"/>
     </row>
-    <row r="364" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:7" s="21" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A364" s="19" t="s">
         <v>185</v>
       </c>
@@ -26502,7 +26505,7 @@
       <c r="F364" s="20"/>
       <c r="G364" s="18"/>
     </row>
-    <row r="365" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:7" s="21" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A365" s="19" t="s">
         <v>186</v>
       </c>
@@ -26515,7 +26518,7 @@
       <c r="F365" s="20"/>
       <c r="G365" s="18"/>
     </row>
-    <row r="366" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:7" s="21" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A366" s="19" t="s">
         <v>191</v>
       </c>
@@ -26528,7 +26531,7 @@
       <c r="F366" s="20"/>
       <c r="G366" s="18"/>
     </row>
-    <row r="367" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:7" s="21" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A367" s="17" t="s">
         <v>197</v>
       </c>
@@ -26547,7 +26550,7 @@
       <c r="F367" s="20"/>
       <c r="G367" s="18"/>
     </row>
-    <row r="368" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A368" s="12" t="s">
         <v>197</v>
       </c>
@@ -26564,7 +26567,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="369" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A369" s="12" t="s">
         <v>197</v>
       </c>
@@ -26581,7 +26584,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="370" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A370" s="12" t="s">
         <v>197</v>
       </c>
@@ -26598,7 +26601,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="371" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:7" s="21" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A371" s="19" t="s">
         <v>199</v>
       </c>
@@ -26611,7 +26614,7 @@
       <c r="F371" s="20"/>
       <c r="G371" s="18"/>
     </row>
-    <row r="372" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:7" s="21" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A372" s="19" t="s">
         <v>529</v>
       </c>
@@ -26625,7 +26628,13 @@
       <c r="G372" s="18"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G372" xr:uid="{51D60DD1-DC0B-4658-A996-7DC0B41964ED}"/>
+  <autoFilter ref="A1:G372" xr:uid="{51D60DD1-DC0B-4658-A996-7DC0B41964ED}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="race6"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Resources/Admin/Crosswalks and Schemas.xlsx
+++ b/Resources/Admin/Crosswalks and Schemas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SHDTJB\Documents\LocalSave\Code\R\GitHub\WA-DOH-CHS-Death-Files-ETL\Resources\Admin\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D12E1222-4991-411D-B0B8-815FD9C28A09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BB99517-3EED-42C1-8B9D-B840984D62DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-20520" yWindow="-16365" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
     <sheet name="harmonized_data_schema" sheetId="7" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">harmonized_data_schema!$H$1:$H$372</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">harmonized_data_schema!$A$1:$I$372</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">recode_variables_statistical!$A$1:$H$432</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6430" uniqueCount="850">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6437" uniqueCount="851">
   <si>
     <t>to_name</t>
   </si>
@@ -3499,9 +3499,6 @@
     <t>Date the harmonized data set was processed and created</t>
   </si>
   <si>
-    <t xml:space="preserve">Cause of Death </t>
-  </si>
-  <si>
     <t>Death City FIPS Code
 Added starting with 2022 data</t>
   </si>
@@ -3609,6 +3606,12 @@
   </si>
   <si>
     <t>Generated</t>
+  </si>
+  <si>
+    <t>underlying_cod_code &amp; all record_axis_code_[1-20] concatenated together</t>
+  </si>
+  <si>
+    <t>A concatenated tag indicating source_system and file_year</t>
   </si>
 </sst>
 </file>
@@ -3726,7 +3729,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3848,13 +3851,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -20690,6 +20687,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51D60DD1-DC0B-4658-A996-7DC0B41964ED}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:I372"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -20727,13 +20725,13 @@
         <v>731</v>
       </c>
       <c r="H1" s="43" t="s">
-        <v>845</v>
-      </c>
-      <c r="I1" s="44" t="s">
+        <v>844</v>
+      </c>
+      <c r="I1" s="43" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:9" s="20" customFormat="1" ht="75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" s="20" customFormat="1" ht="75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" s="16" t="s">
         <v>4</v>
       </c>
@@ -20748,10 +20746,10 @@
         <v>732</v>
       </c>
       <c r="H2" s="16" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" s="20" customFormat="1" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" s="16" t="s">
         <v>676</v>
       </c>
@@ -20770,12 +20768,14 @@
       <c r="F3" s="19">
         <v>1</v>
       </c>
-      <c r="G3" s="16"/>
+      <c r="G3" s="16" t="s">
+        <v>815</v>
+      </c>
       <c r="H3" s="16" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
         <v>676</v>
       </c>
@@ -20798,10 +20798,10 @@
         <v>815</v>
       </c>
       <c r="H4" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
         <v>676</v>
       </c>
@@ -20824,10 +20824,10 @@
         <v>815</v>
       </c>
       <c r="H5" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>676</v>
       </c>
@@ -20850,10 +20850,10 @@
         <v>815</v>
       </c>
       <c r="H6" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>676</v>
       </c>
@@ -20876,10 +20876,10 @@
         <v>815</v>
       </c>
       <c r="H7" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
         <v>676</v>
       </c>
@@ -20902,10 +20902,10 @@
         <v>815</v>
       </c>
       <c r="H8" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" s="20" customFormat="1" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="16" t="s">
         <v>682</v>
       </c>
@@ -20928,10 +20928,10 @@
         <v>816</v>
       </c>
       <c r="H9" s="16" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
         <v>682</v>
       </c>
@@ -20954,10 +20954,10 @@
         <v>816</v>
       </c>
       <c r="H10" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
         <v>682</v>
       </c>
@@ -20980,10 +20980,10 @@
         <v>816</v>
       </c>
       <c r="H11" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
         <v>682</v>
       </c>
@@ -21006,10 +21006,10 @@
         <v>816</v>
       </c>
       <c r="H12" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>682</v>
       </c>
@@ -21032,10 +21032,10 @@
         <v>816</v>
       </c>
       <c r="H13" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
         <v>682</v>
       </c>
@@ -21058,10 +21058,10 @@
         <v>816</v>
       </c>
       <c r="H14" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
         <v>682</v>
       </c>
@@ -21084,10 +21084,10 @@
         <v>816</v>
       </c>
       <c r="H15" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
         <v>682</v>
       </c>
@@ -21110,10 +21110,10 @@
         <v>816</v>
       </c>
       <c r="H16" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
         <v>682</v>
       </c>
@@ -21136,10 +21136,10 @@
         <v>816</v>
       </c>
       <c r="H17" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
         <v>682</v>
       </c>
@@ -21162,10 +21162,10 @@
         <v>816</v>
       </c>
       <c r="H18" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
         <v>682</v>
       </c>
@@ -21188,10 +21188,10 @@
         <v>816</v>
       </c>
       <c r="H19" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="16" t="s">
         <v>692</v>
       </c>
@@ -21214,10 +21214,10 @@
         <v>817</v>
       </c>
       <c r="H20" s="16" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
         <v>692</v>
       </c>
@@ -21240,10 +21240,10 @@
         <v>817</v>
       </c>
       <c r="H21" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
         <v>692</v>
       </c>
@@ -21266,10 +21266,10 @@
         <v>817</v>
       </c>
       <c r="H22" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="11" t="s">
         <v>692</v>
       </c>
@@ -21292,10 +21292,10 @@
         <v>817</v>
       </c>
       <c r="H23" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
         <v>692</v>
       </c>
@@ -21318,10 +21318,10 @@
         <v>817</v>
       </c>
       <c r="H24" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
         <v>692</v>
       </c>
@@ -21344,10 +21344,10 @@
         <v>817</v>
       </c>
       <c r="H25" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="11" t="s">
         <v>692</v>
       </c>
@@ -21370,10 +21370,10 @@
         <v>817</v>
       </c>
       <c r="H26" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
         <v>692</v>
       </c>
@@ -21396,10 +21396,10 @@
         <v>817</v>
       </c>
       <c r="H27" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="11" t="s">
         <v>692</v>
       </c>
@@ -21422,10 +21422,10 @@
         <v>817</v>
       </c>
       <c r="H28" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
         <v>692</v>
       </c>
@@ -21448,10 +21448,10 @@
         <v>817</v>
       </c>
       <c r="H29" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="11" t="s">
         <v>692</v>
       </c>
@@ -21474,10 +21474,10 @@
         <v>817</v>
       </c>
       <c r="H30" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="11" t="s">
         <v>692</v>
       </c>
@@ -21500,10 +21500,10 @@
         <v>817</v>
       </c>
       <c r="H31" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="11" t="s">
         <v>692</v>
       </c>
@@ -21526,10 +21526,10 @@
         <v>817</v>
       </c>
       <c r="H32" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="11" t="s">
         <v>692</v>
       </c>
@@ -21552,10 +21552,10 @@
         <v>817</v>
       </c>
       <c r="H33" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" s="11" t="s">
         <v>692</v>
       </c>
@@ -21578,10 +21578,10 @@
         <v>817</v>
       </c>
       <c r="H34" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="11" t="s">
         <v>692</v>
       </c>
@@ -21604,10 +21604,10 @@
         <v>817</v>
       </c>
       <c r="H35" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" s="11" t="s">
         <v>692</v>
       </c>
@@ -21630,10 +21630,10 @@
         <v>817</v>
       </c>
       <c r="H36" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" s="11" t="s">
         <v>692</v>
       </c>
@@ -21656,10 +21656,10 @@
         <v>817</v>
       </c>
       <c r="H37" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" s="11" t="s">
         <v>692</v>
       </c>
@@ -21682,10 +21682,10 @@
         <v>817</v>
       </c>
       <c r="H38" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="11" t="s">
         <v>692</v>
       </c>
@@ -21708,10 +21708,10 @@
         <v>817</v>
       </c>
       <c r="H39" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" s="16" t="s">
         <v>710</v>
       </c>
@@ -21734,10 +21734,10 @@
         <v>818</v>
       </c>
       <c r="H40" s="16" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" s="11" t="s">
         <v>710</v>
       </c>
@@ -21760,10 +21760,10 @@
         <v>818</v>
       </c>
       <c r="H41" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" s="11" t="s">
         <v>710</v>
       </c>
@@ -21786,10 +21786,10 @@
         <v>818</v>
       </c>
       <c r="H42" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" s="11" t="s">
         <v>710</v>
       </c>
@@ -21812,10 +21812,10 @@
         <v>818</v>
       </c>
       <c r="H43" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" s="11" t="s">
         <v>710</v>
       </c>
@@ -21838,10 +21838,10 @@
         <v>818</v>
       </c>
       <c r="H44" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" s="11" t="s">
         <v>710</v>
       </c>
@@ -21864,10 +21864,10 @@
         <v>818</v>
       </c>
       <c r="H45" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" s="11" t="s">
         <v>710</v>
       </c>
@@ -21890,10 +21890,10 @@
         <v>818</v>
       </c>
       <c r="H46" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" s="11" t="s">
         <v>710</v>
       </c>
@@ -21916,10 +21916,10 @@
         <v>818</v>
       </c>
       <c r="H47" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" s="11" t="s">
         <v>710</v>
       </c>
@@ -21942,10 +21942,10 @@
         <v>818</v>
       </c>
       <c r="H48" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" s="11" t="s">
         <v>710</v>
       </c>
@@ -21968,10 +21968,10 @@
         <v>818</v>
       </c>
       <c r="H49" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" s="11" t="s">
         <v>710</v>
       </c>
@@ -21994,10 +21994,10 @@
         <v>818</v>
       </c>
       <c r="H50" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" s="11" t="s">
         <v>710</v>
       </c>
@@ -22020,10 +22020,10 @@
         <v>818</v>
       </c>
       <c r="H51" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" s="11" t="s">
         <v>710</v>
       </c>
@@ -22046,10 +22046,10 @@
         <v>818</v>
       </c>
       <c r="H52" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" s="11" t="s">
         <v>710</v>
       </c>
@@ -22072,10 +22072,10 @@
         <v>818</v>
       </c>
       <c r="H53" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" s="11" t="s">
         <v>710</v>
       </c>
@@ -22098,10 +22098,10 @@
         <v>818</v>
       </c>
       <c r="H54" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" s="11" t="s">
         <v>710</v>
       </c>
@@ -22124,10 +22124,10 @@
         <v>818</v>
       </c>
       <c r="H55" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" s="11" t="s">
         <v>710</v>
       </c>
@@ -22150,10 +22150,10 @@
         <v>818</v>
       </c>
       <c r="H56" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" s="11" t="s">
         <v>710</v>
       </c>
@@ -22176,10 +22176,10 @@
         <v>818</v>
       </c>
       <c r="H57" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8" s="20" customFormat="1" ht="75" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" s="20" customFormat="1" ht="75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" s="16" t="s">
         <v>6</v>
       </c>
@@ -22200,10 +22200,10 @@
         <v>733</v>
       </c>
       <c r="H58" s="16" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8" ht="75" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" ht="75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" s="11" t="s">
         <v>6</v>
       </c>
@@ -22223,10 +22223,10 @@
         <v>733</v>
       </c>
       <c r="H59" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8" ht="75" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" ht="75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" s="11" t="s">
         <v>6</v>
       </c>
@@ -22246,10 +22246,10 @@
         <v>733</v>
       </c>
       <c r="H60" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8" ht="75" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" ht="75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" s="11" t="s">
         <v>6</v>
       </c>
@@ -22269,10 +22269,10 @@
         <v>733</v>
       </c>
       <c r="H61" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8" ht="75" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" ht="75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" s="11" t="s">
         <v>6</v>
       </c>
@@ -22292,10 +22292,10 @@
         <v>733</v>
       </c>
       <c r="H62" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="63" spans="1:8" ht="75" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" ht="75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" s="11" t="s">
         <v>6</v>
       </c>
@@ -22315,10 +22315,10 @@
         <v>733</v>
       </c>
       <c r="H63" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="64" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" s="16" t="s">
         <v>7</v>
       </c>
@@ -22333,10 +22333,10 @@
         <v>734</v>
       </c>
       <c r="H64" s="16" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="65" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" s="16" t="s">
         <v>523</v>
       </c>
@@ -22347,12 +22347,14 @@
       <c r="D65" s="38"/>
       <c r="E65" s="16"/>
       <c r="F65" s="19"/>
-      <c r="G65" s="16"/>
+      <c r="G65" s="16" t="s">
+        <v>849</v>
+      </c>
       <c r="H65" s="16" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
+        <v>848</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" s="16" t="s">
         <v>9</v>
       </c>
@@ -22373,10 +22375,10 @@
         <v>735</v>
       </c>
       <c r="H66" s="16" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" s="11" t="s">
         <v>9</v>
       </c>
@@ -22396,10 +22398,10 @@
         <v>735</v>
       </c>
       <c r="H67" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" s="11" t="s">
         <v>9</v>
       </c>
@@ -22419,10 +22421,10 @@
         <v>735</v>
       </c>
       <c r="H68" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="69" spans="1:8" s="20" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" s="20" customFormat="1" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" s="16" t="s">
         <v>10</v>
       </c>
@@ -22443,10 +22445,10 @@
         <v>736</v>
       </c>
       <c r="H69" s="16" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="70" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" s="11" t="s">
         <v>10</v>
       </c>
@@ -22466,10 +22468,10 @@
         <v>736</v>
       </c>
       <c r="H70" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="71" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71" s="11" t="s">
         <v>10</v>
       </c>
@@ -22489,10 +22491,10 @@
         <v>736</v>
       </c>
       <c r="H71" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="72" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" s="16" t="s">
         <v>12</v>
       </c>
@@ -22511,10 +22513,10 @@
         <v>737</v>
       </c>
       <c r="H72" s="16" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="73" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" s="16" t="s">
         <v>14</v>
       </c>
@@ -22533,10 +22535,10 @@
         <v>738</v>
       </c>
       <c r="H73" s="16" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="74" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" s="18" t="s">
         <v>16</v>
       </c>
@@ -22557,10 +22559,10 @@
         <v>739</v>
       </c>
       <c r="H74" s="16" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" s="4" t="s">
         <v>16</v>
       </c>
@@ -22580,10 +22582,10 @@
         <v>739</v>
       </c>
       <c r="H75" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
         <v>16</v>
       </c>
@@ -22603,10 +22605,10 @@
         <v>739</v>
       </c>
       <c r="H76" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" s="4" t="s">
         <v>16</v>
       </c>
@@ -22626,10 +22628,10 @@
         <v>739</v>
       </c>
       <c r="H77" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
         <v>16</v>
       </c>
@@ -22648,11 +22650,11 @@
       <c r="G78" s="11" t="s">
         <v>739</v>
       </c>
-      <c r="H78" s="47" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H78" s="45" t="s">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" s="4" t="s">
         <v>16</v>
       </c>
@@ -22671,11 +22673,11 @@
       <c r="G79" s="11" t="s">
         <v>739</v>
       </c>
-      <c r="H79" s="47" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H79" s="45" t="s">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
         <v>16</v>
       </c>
@@ -22695,10 +22697,10 @@
         <v>739</v>
       </c>
       <c r="H80" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81" s="4" t="s">
         <v>16</v>
       </c>
@@ -22718,10 +22720,10 @@
         <v>739</v>
       </c>
       <c r="H81" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
         <v>16</v>
       </c>
@@ -22741,7 +22743,7 @@
         <v>739</v>
       </c>
       <c r="H82" s="11" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
     </row>
     <row r="83" spans="1:9" s="18" customFormat="1" x14ac:dyDescent="0.25">
@@ -22756,13 +22758,13 @@
       <c r="E83" s="16"/>
       <c r="F83" s="34"/>
       <c r="G83" s="16" t="s">
-        <v>820</v>
+        <v>641</v>
       </c>
       <c r="H83" s="16" t="s">
-        <v>847</v>
-      </c>
-    </row>
-    <row r="84" spans="1:9" s="20" customFormat="1" x14ac:dyDescent="0.25">
+        <v>846</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" s="33" t="s">
         <v>630</v>
       </c>
@@ -22773,12 +22775,14 @@
       <c r="D84" s="40"/>
       <c r="E84" s="16"/>
       <c r="F84" s="19"/>
-      <c r="G84" s="16"/>
+      <c r="G84" s="16" t="s">
+        <v>642</v>
+      </c>
       <c r="H84" s="16" t="s">
-        <v>847</v>
-      </c>
-    </row>
-    <row r="85" spans="1:9" s="20" customFormat="1" x14ac:dyDescent="0.25">
+        <v>846</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85" s="33" t="s">
         <v>631</v>
       </c>
@@ -22789,12 +22793,14 @@
       <c r="D85" s="40"/>
       <c r="E85" s="16"/>
       <c r="F85" s="19"/>
-      <c r="G85" s="16"/>
+      <c r="G85" s="16" t="s">
+        <v>643</v>
+      </c>
       <c r="H85" s="16" t="s">
-        <v>847</v>
-      </c>
-    </row>
-    <row r="86" spans="1:9" s="20" customFormat="1" x14ac:dyDescent="0.25">
+        <v>846</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" s="33" t="s">
         <v>632</v>
       </c>
@@ -22805,12 +22811,14 @@
       <c r="D86" s="40"/>
       <c r="E86" s="16"/>
       <c r="F86" s="19"/>
-      <c r="G86" s="16"/>
+      <c r="G86" s="16" t="s">
+        <v>644</v>
+      </c>
       <c r="H86" s="16" t="s">
-        <v>847</v>
-      </c>
-    </row>
-    <row r="87" spans="1:9" s="20" customFormat="1" x14ac:dyDescent="0.25">
+        <v>846</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87" s="33" t="s">
         <v>633</v>
       </c>
@@ -22821,12 +22829,14 @@
       <c r="D87" s="40"/>
       <c r="E87" s="16"/>
       <c r="F87" s="19"/>
-      <c r="G87" s="16"/>
+      <c r="G87" s="16" t="s">
+        <v>645</v>
+      </c>
       <c r="H87" s="16" t="s">
-        <v>847</v>
-      </c>
-    </row>
-    <row r="88" spans="1:9" s="20" customFormat="1" x14ac:dyDescent="0.25">
+        <v>846</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88" s="16" t="s">
         <v>525</v>
       </c>
@@ -22841,11 +22851,11 @@
         <v>819</v>
       </c>
       <c r="H88" s="16" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="I88" s="17"/>
     </row>
-    <row r="89" spans="1:9" s="20" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:9" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89" s="16" t="s">
         <v>18</v>
       </c>
@@ -22860,10 +22870,10 @@
         <v>287</v>
       </c>
       <c r="H89" s="16" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="90" spans="1:9" s="20" customFormat="1" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90" s="16" t="s">
         <v>20</v>
       </c>
@@ -22878,10 +22888,10 @@
         <v>288</v>
       </c>
       <c r="H90" s="16" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="91" spans="1:9" s="20" customFormat="1" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" s="16" t="s">
         <v>22</v>
       </c>
@@ -22902,10 +22912,10 @@
         <v>289</v>
       </c>
       <c r="H91" s="16" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" s="11" t="s">
         <v>22</v>
       </c>
@@ -22925,10 +22935,10 @@
         <v>289</v>
       </c>
       <c r="H92" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93" s="11" t="s">
         <v>22</v>
       </c>
@@ -22948,10 +22958,10 @@
         <v>289</v>
       </c>
       <c r="H93" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" s="11" t="s">
         <v>22</v>
       </c>
@@ -22971,10 +22981,10 @@
         <v>289</v>
       </c>
       <c r="H94" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95" s="11" t="s">
         <v>22</v>
       </c>
@@ -22994,10 +23004,10 @@
         <v>289</v>
       </c>
       <c r="H95" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96" s="11" t="s">
         <v>22</v>
       </c>
@@ -23017,10 +23027,10 @@
         <v>289</v>
       </c>
       <c r="H96" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97" s="11" t="s">
         <v>22</v>
       </c>
@@ -23040,10 +23050,10 @@
         <v>289</v>
       </c>
       <c r="H97" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="98" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98" s="16" t="s">
         <v>24</v>
       </c>
@@ -23058,10 +23068,10 @@
         <v>740</v>
       </c>
       <c r="H98" s="16" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="99" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99" s="16" t="s">
         <v>26</v>
       </c>
@@ -23076,10 +23086,10 @@
         <v>741</v>
       </c>
       <c r="H99" s="16" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="100" spans="1:8" s="20" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" s="20" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100" s="16" t="s">
         <v>27</v>
       </c>
@@ -23091,13 +23101,13 @@
       <c r="E100" s="16"/>
       <c r="F100" s="19"/>
       <c r="G100" s="16" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="H100" s="16" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="101" spans="1:8" s="20" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" s="20" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101" s="16" t="s">
         <v>28</v>
       </c>
@@ -23109,13 +23119,13 @@
       <c r="E101" s="16"/>
       <c r="F101" s="19"/>
       <c r="G101" s="16" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="H101" s="16" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="102" spans="1:8" s="20" customFormat="1" ht="180" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" s="20" customFormat="1" ht="180" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102" s="16" t="s">
         <v>30</v>
       </c>
@@ -23127,13 +23137,13 @@
       <c r="E102" s="16"/>
       <c r="F102" s="19"/>
       <c r="G102" s="16" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="H102" s="16" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="103" spans="1:8" s="20" customFormat="1" ht="180" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" s="20" customFormat="1" ht="180" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103" s="16" t="s">
         <v>32</v>
       </c>
@@ -23145,13 +23155,13 @@
       <c r="E103" s="16"/>
       <c r="F103" s="19"/>
       <c r="G103" s="16" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="H103" s="16" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="104" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104" s="16" t="s">
         <v>34</v>
       </c>
@@ -23166,10 +23176,10 @@
         <v>742</v>
       </c>
       <c r="H104" s="16" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="105" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105" s="16" t="s">
         <v>36</v>
       </c>
@@ -23184,10 +23194,10 @@
         <v>743</v>
       </c>
       <c r="H105" s="16" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="106" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A106" s="16" t="s">
         <v>38</v>
       </c>
@@ -23202,10 +23212,10 @@
         <v>744</v>
       </c>
       <c r="H106" s="16" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="107" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107" s="16" t="s">
         <v>40</v>
       </c>
@@ -23226,10 +23236,10 @@
         <v>745</v>
       </c>
       <c r="H107" s="16" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A108" s="11" t="s">
         <v>40</v>
       </c>
@@ -23249,10 +23259,10 @@
         <v>745</v>
       </c>
       <c r="H108" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109" s="11" t="s">
         <v>40</v>
       </c>
@@ -23272,10 +23282,10 @@
         <v>745</v>
       </c>
       <c r="H109" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110" s="11" t="s">
         <v>40</v>
       </c>
@@ -23295,10 +23305,10 @@
         <v>745</v>
       </c>
       <c r="H110" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A111" s="11" t="s">
         <v>40</v>
       </c>
@@ -23318,10 +23328,10 @@
         <v>745</v>
       </c>
       <c r="H111" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112" s="11" t="s">
         <v>40</v>
       </c>
@@ -23341,10 +23351,10 @@
         <v>745</v>
       </c>
       <c r="H112" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A113" s="11" t="s">
         <v>40</v>
       </c>
@@ -23364,10 +23374,10 @@
         <v>745</v>
       </c>
       <c r="H113" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114" s="11" t="s">
         <v>40</v>
       </c>
@@ -23387,10 +23397,10 @@
         <v>745</v>
       </c>
       <c r="H114" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="115" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A115" s="16" t="s">
         <v>42</v>
       </c>
@@ -23405,10 +23415,10 @@
         <v>298</v>
       </c>
       <c r="H115" s="16" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="116" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A116" s="16" t="s">
         <v>44</v>
       </c>
@@ -23431,10 +23441,10 @@
         <v>746</v>
       </c>
       <c r="H116" s="16" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117" s="11" t="s">
         <v>44</v>
       </c>
@@ -23457,10 +23467,10 @@
         <v>746</v>
       </c>
       <c r="H117" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A118" s="11" t="s">
         <v>44</v>
       </c>
@@ -23483,10 +23493,10 @@
         <v>746</v>
       </c>
       <c r="H118" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A119" s="11" t="s">
         <v>44</v>
       </c>
@@ -23509,10 +23519,10 @@
         <v>746</v>
       </c>
       <c r="H119" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120" s="11" t="s">
         <v>44</v>
       </c>
@@ -23535,10 +23545,10 @@
         <v>746</v>
       </c>
       <c r="H120" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121" s="11" t="s">
         <v>44</v>
       </c>
@@ -23561,10 +23571,10 @@
         <v>746</v>
       </c>
       <c r="H121" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122" s="11" t="s">
         <v>44</v>
       </c>
@@ -23587,10 +23597,10 @@
         <v>746</v>
       </c>
       <c r="H122" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A123" s="11" t="s">
         <v>44</v>
       </c>
@@ -23613,10 +23623,10 @@
         <v>746</v>
       </c>
       <c r="H123" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A124" s="11" t="s">
         <v>44</v>
       </c>
@@ -23639,10 +23649,10 @@
         <v>746</v>
       </c>
       <c r="H124" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="125" spans="1:8" s="20" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8" s="20" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="16" t="s">
         <v>46</v>
       </c>
@@ -23665,10 +23675,10 @@
         <v>747</v>
       </c>
       <c r="H125" s="16" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A126" s="11" t="s">
         <v>46</v>
       </c>
@@ -23691,10 +23701,10 @@
         <v>747</v>
       </c>
       <c r="H126" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A127" s="11" t="s">
         <v>46</v>
       </c>
@@ -23717,10 +23727,10 @@
         <v>747</v>
       </c>
       <c r="H127" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A128" s="11" t="s">
         <v>46</v>
       </c>
@@ -23743,10 +23753,10 @@
         <v>747</v>
       </c>
       <c r="H128" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A129" s="11" t="s">
         <v>46</v>
       </c>
@@ -23769,10 +23779,10 @@
         <v>747</v>
       </c>
       <c r="H129" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A130" s="11" t="s">
         <v>46</v>
       </c>
@@ -23795,10 +23805,10 @@
         <v>747</v>
       </c>
       <c r="H130" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A131" s="11" t="s">
         <v>46</v>
       </c>
@@ -23821,10 +23831,10 @@
         <v>747</v>
       </c>
       <c r="H131" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A132" s="11" t="s">
         <v>46</v>
       </c>
@@ -23847,10 +23857,10 @@
         <v>747</v>
       </c>
       <c r="H132" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="133" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A133" s="11" t="s">
         <v>46</v>
       </c>
@@ -23873,10 +23883,10 @@
         <v>747</v>
       </c>
       <c r="H133" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A134" s="11" t="s">
         <v>46</v>
       </c>
@@ -23899,10 +23909,10 @@
         <v>747</v>
       </c>
       <c r="H134" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="135" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A135" s="18" t="s">
         <v>391</v>
       </c>
@@ -23914,13 +23924,13 @@
       <c r="E135" s="16"/>
       <c r="F135" s="19"/>
       <c r="G135" s="16" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="H135" s="16" t="s">
-        <v>849</v>
-      </c>
-    </row>
-    <row r="136" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
+        <v>848</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A136" s="18" t="s">
         <v>713</v>
       </c>
@@ -23932,13 +23942,13 @@
       <c r="E136" s="16"/>
       <c r="F136" s="19"/>
       <c r="G136" s="16" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="H136" s="16" t="s">
-        <v>849</v>
-      </c>
-    </row>
-    <row r="137" spans="1:8" x14ac:dyDescent="0.25">
+        <v>848</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A137" s="4" t="s">
         <v>713</v>
       </c>
@@ -23946,13 +23956,13 @@
         <v>521</v>
       </c>
       <c r="G137" s="11" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="H137" s="11" t="s">
-        <v>849</v>
-      </c>
-    </row>
-    <row r="138" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
+        <v>848</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A138" s="16" t="s">
         <v>48</v>
       </c>
@@ -23973,10 +23983,10 @@
         <v>748</v>
       </c>
       <c r="H138" s="16" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="139" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="139" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A139" s="11" t="s">
         <v>48</v>
       </c>
@@ -23996,10 +24006,10 @@
         <v>748</v>
       </c>
       <c r="H139" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="140" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="140" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A140" s="11" t="s">
         <v>48</v>
       </c>
@@ -24019,10 +24029,10 @@
         <v>748</v>
       </c>
       <c r="H140" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="141" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="141" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A141" s="16" t="s">
         <v>50</v>
       </c>
@@ -24043,10 +24053,10 @@
         <v>749</v>
       </c>
       <c r="H141" s="16" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="142" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="142" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A142" s="11" t="s">
         <v>50</v>
       </c>
@@ -24066,10 +24076,10 @@
         <v>749</v>
       </c>
       <c r="H142" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="143" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="143" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A143" s="11" t="s">
         <v>50</v>
       </c>
@@ -24089,10 +24099,10 @@
         <v>749</v>
       </c>
       <c r="H143" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="144" spans="1:8" s="20" customFormat="1" ht="75" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="144" spans="1:8" s="20" customFormat="1" ht="75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A144" s="16" t="s">
         <v>52</v>
       </c>
@@ -24113,10 +24123,10 @@
         <v>750</v>
       </c>
       <c r="H144" s="16" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="145" spans="1:8" ht="75" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="145" spans="1:8" ht="75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A145" s="11" t="s">
         <v>52</v>
       </c>
@@ -24136,10 +24146,10 @@
         <v>750</v>
       </c>
       <c r="H145" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="146" spans="1:8" ht="75" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="146" spans="1:8" ht="75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A146" s="11" t="s">
         <v>52</v>
       </c>
@@ -24159,10 +24169,10 @@
         <v>750</v>
       </c>
       <c r="H146" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="147" spans="1:8" ht="75" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="147" spans="1:8" ht="75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A147" s="11" t="s">
         <v>52</v>
       </c>
@@ -24182,10 +24192,10 @@
         <v>750</v>
       </c>
       <c r="H147" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="148" spans="1:8" ht="75" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="148" spans="1:8" ht="75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A148" s="11" t="s">
         <v>52</v>
       </c>
@@ -24205,10 +24215,10 @@
         <v>750</v>
       </c>
       <c r="H148" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="149" spans="1:8" ht="75" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="149" spans="1:8" ht="75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A149" s="11" t="s">
         <v>52</v>
       </c>
@@ -24228,10 +24238,10 @@
         <v>750</v>
       </c>
       <c r="H149" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="150" spans="1:8" ht="75" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="150" spans="1:8" ht="75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A150" s="11" t="s">
         <v>52</v>
       </c>
@@ -24251,10 +24261,10 @@
         <v>750</v>
       </c>
       <c r="H150" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="151" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="151" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A151" s="16" t="s">
         <v>54</v>
       </c>
@@ -24275,10 +24285,10 @@
         <v>751</v>
       </c>
       <c r="H151" s="16" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="152" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="152" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A152" s="11" t="s">
         <v>54</v>
       </c>
@@ -24298,10 +24308,10 @@
         <v>751</v>
       </c>
       <c r="H152" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="153" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="153" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A153" s="11" t="s">
         <v>54</v>
       </c>
@@ -24321,10 +24331,10 @@
         <v>751</v>
       </c>
       <c r="H153" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="154" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="154" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A154" s="16" t="s">
         <v>56</v>
       </c>
@@ -24345,10 +24355,10 @@
         <v>752</v>
       </c>
       <c r="H154" s="16" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="155" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="155" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A155" s="11" t="s">
         <v>56</v>
       </c>
@@ -24368,10 +24378,10 @@
         <v>752</v>
       </c>
       <c r="H155" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="156" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="156" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A156" s="11" t="s">
         <v>56</v>
       </c>
@@ -24391,10 +24401,10 @@
         <v>752</v>
       </c>
       <c r="H156" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="157" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="157" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A157" s="16" t="s">
         <v>58</v>
       </c>
@@ -24415,10 +24425,10 @@
         <v>753</v>
       </c>
       <c r="H157" s="16" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="158" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="158" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A158" s="11" t="s">
         <v>58</v>
       </c>
@@ -24438,10 +24448,10 @@
         <v>753</v>
       </c>
       <c r="H158" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="159" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="159" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A159" s="11" t="s">
         <v>58</v>
       </c>
@@ -24461,10 +24471,10 @@
         <v>753</v>
       </c>
       <c r="H159" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="160" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="160" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A160" s="16" t="s">
         <v>60</v>
       </c>
@@ -24479,10 +24489,10 @@
         <v>754</v>
       </c>
       <c r="H160" s="16" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="161" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="161" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A161" s="16" t="s">
         <v>62</v>
       </c>
@@ -24497,10 +24507,10 @@
         <v>308</v>
       </c>
       <c r="H161" s="16" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="162" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="162" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A162" s="16" t="s">
         <v>64</v>
       </c>
@@ -24521,10 +24531,10 @@
         <v>755</v>
       </c>
       <c r="H162" s="16" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="163" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="163" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A163" s="11" t="s">
         <v>64</v>
       </c>
@@ -24544,10 +24554,10 @@
         <v>755</v>
       </c>
       <c r="H163" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="164" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="164" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A164" s="11" t="s">
         <v>64</v>
       </c>
@@ -24567,10 +24577,10 @@
         <v>755</v>
       </c>
       <c r="H164" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="165" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="165" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A165" s="11" t="s">
         <v>64</v>
       </c>
@@ -24590,10 +24600,10 @@
         <v>755</v>
       </c>
       <c r="H165" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="166" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="166" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A166" s="11" t="s">
         <v>64</v>
       </c>
@@ -24613,10 +24623,10 @@
         <v>755</v>
       </c>
       <c r="H166" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="167" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="167" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A167" s="11" t="s">
         <v>64</v>
       </c>
@@ -24636,10 +24646,10 @@
         <v>755</v>
       </c>
       <c r="H167" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="168" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="168" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A168" s="11" t="s">
         <v>64</v>
       </c>
@@ -24659,10 +24669,10 @@
         <v>755</v>
       </c>
       <c r="H168" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="169" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="169" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A169" s="11" t="s">
         <v>64</v>
       </c>
@@ -24682,10 +24692,10 @@
         <v>755</v>
       </c>
       <c r="H169" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="170" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="170" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A170" s="11" t="s">
         <v>64</v>
       </c>
@@ -24705,10 +24715,10 @@
         <v>755</v>
       </c>
       <c r="H170" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="171" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="171" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A171" s="11" t="s">
         <v>64</v>
       </c>
@@ -24728,10 +24738,10 @@
         <v>755</v>
       </c>
       <c r="H171" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="172" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="172" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A172" s="16" t="s">
         <v>66</v>
       </c>
@@ -24752,10 +24762,10 @@
         <v>310</v>
       </c>
       <c r="H172" s="16" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="173" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="173" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A173" s="11" t="s">
         <v>66</v>
       </c>
@@ -24775,10 +24785,10 @@
         <v>310</v>
       </c>
       <c r="H173" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="174" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="174" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A174" s="11" t="s">
         <v>66</v>
       </c>
@@ -24798,10 +24808,10 @@
         <v>310</v>
       </c>
       <c r="H174" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="175" spans="1:8" s="20" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="175" spans="1:8" s="20" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A175" s="16" t="s">
         <v>67</v>
       </c>
@@ -24813,13 +24823,13 @@
       <c r="E175" s="16"/>
       <c r="F175" s="19"/>
       <c r="G175" s="16" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="H175" s="16" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="176" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="176" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A176" s="16" t="s">
         <v>68</v>
       </c>
@@ -24831,13 +24841,13 @@
       <c r="E176" s="16"/>
       <c r="F176" s="19"/>
       <c r="G176" s="16" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="H176" s="16" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="177" spans="1:9" s="20" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="177" spans="1:9" s="20" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A177" s="16" t="s">
         <v>69</v>
       </c>
@@ -24849,13 +24859,13 @@
       <c r="E177" s="16"/>
       <c r="F177" s="19"/>
       <c r="G177" s="16" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="H177" s="16" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="178" spans="1:9" s="20" customFormat="1" ht="180" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="178" spans="1:9" s="20" customFormat="1" ht="180" hidden="1" x14ac:dyDescent="0.25">
       <c r="A178" s="16" t="s">
         <v>71</v>
       </c>
@@ -24867,13 +24877,13 @@
       <c r="E178" s="16"/>
       <c r="F178" s="19"/>
       <c r="G178" s="16" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="H178" s="16" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="179" spans="1:9" s="20" customFormat="1" ht="180" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="179" spans="1:9" s="20" customFormat="1" ht="180" hidden="1" x14ac:dyDescent="0.25">
       <c r="A179" s="16" t="s">
         <v>73</v>
       </c>
@@ -24885,13 +24895,13 @@
       <c r="E179" s="16"/>
       <c r="F179" s="19"/>
       <c r="G179" s="16" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="H179" s="16" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="180" spans="1:9" s="20" customFormat="1" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="180" spans="1:9" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A180" s="16" t="s">
         <v>634</v>
       </c>
@@ -24903,13 +24913,13 @@
       <c r="E180" s="16"/>
       <c r="F180" s="19"/>
       <c r="G180" s="16" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="H180" s="16" t="s">
-        <v>847</v>
-      </c>
-    </row>
-    <row r="181" spans="1:9" s="20" customFormat="1" x14ac:dyDescent="0.25">
+        <v>846</v>
+      </c>
+    </row>
+    <row r="181" spans="1:9" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A181" s="16" t="s">
         <v>75</v>
       </c>
@@ -24924,10 +24934,10 @@
         <v>756</v>
       </c>
       <c r="H181" s="16" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="182" spans="1:9" s="20" customFormat="1" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="182" spans="1:9" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A182" s="16" t="s">
         <v>77</v>
       </c>
@@ -24942,10 +24952,10 @@
         <v>757</v>
       </c>
       <c r="H182" s="16" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="183" spans="1:9" s="20" customFormat="1" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="183" spans="1:9" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A183" s="16" t="s">
         <v>79</v>
       </c>
@@ -24960,10 +24970,10 @@
         <v>758</v>
       </c>
       <c r="H183" s="16" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="184" spans="1:9" s="20" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="184" spans="1:9" s="20" customFormat="1" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A184" s="16" t="s">
         <v>81</v>
       </c>
@@ -24978,10 +24988,10 @@
         <v>759</v>
       </c>
       <c r="H184" s="16" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="185" spans="1:9" s="20" customFormat="1" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="185" spans="1:9" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A185" s="16" t="s">
         <v>83</v>
       </c>
@@ -25002,10 +25012,10 @@
         <v>760</v>
       </c>
       <c r="H185" s="16" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="186" spans="1:9" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="186" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A186" s="11" t="s">
         <v>83</v>
       </c>
@@ -25025,10 +25035,10 @@
         <v>760</v>
       </c>
       <c r="H186" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="187" spans="1:9" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="187" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A187" s="11" t="s">
         <v>83</v>
       </c>
@@ -25048,10 +25058,10 @@
         <v>760</v>
       </c>
       <c r="H187" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="188" spans="1:9" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="188" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A188" s="11" t="s">
         <v>83</v>
       </c>
@@ -25071,10 +25081,10 @@
         <v>760</v>
       </c>
       <c r="H188" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="189" spans="1:9" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="189" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A189" s="11" t="s">
         <v>83</v>
       </c>
@@ -25094,10 +25104,10 @@
         <v>760</v>
       </c>
       <c r="H189" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="190" spans="1:9" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="190" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A190" s="11" t="s">
         <v>83</v>
       </c>
@@ -25117,10 +25127,10 @@
         <v>760</v>
       </c>
       <c r="H190" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="191" spans="1:9" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="191" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A191" s="11" t="s">
         <v>83</v>
       </c>
@@ -25140,13 +25150,13 @@
         <v>760</v>
       </c>
       <c r="H191" s="11" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="I191" t="s">
         <v>560</v>
       </c>
     </row>
-    <row r="192" spans="1:9" s="20" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:9" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A192" s="16" t="s">
         <v>85</v>
       </c>
@@ -25167,10 +25177,10 @@
         <v>319</v>
       </c>
       <c r="H192" s="16" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="193" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="193" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A193" s="11" t="s">
         <v>85</v>
       </c>
@@ -25190,10 +25200,10 @@
         <v>319</v>
       </c>
       <c r="H193" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="194" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="194" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A194" s="11" t="s">
         <v>85</v>
       </c>
@@ -25213,10 +25223,10 @@
         <v>319</v>
       </c>
       <c r="H194" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="195" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="195" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A195" s="11" t="s">
         <v>85</v>
       </c>
@@ -25236,10 +25246,10 @@
         <v>319</v>
       </c>
       <c r="H195" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="196" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="196" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A196" s="11" t="s">
         <v>85</v>
       </c>
@@ -25259,10 +25269,10 @@
         <v>319</v>
       </c>
       <c r="H196" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="197" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="197" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A197" s="11" t="s">
         <v>85</v>
       </c>
@@ -25282,10 +25292,10 @@
         <v>319</v>
       </c>
       <c r="H197" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="198" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="198" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A198" s="11" t="s">
         <v>85</v>
       </c>
@@ -25305,10 +25315,10 @@
         <v>319</v>
       </c>
       <c r="H198" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="199" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="199" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A199" s="16" t="s">
         <v>87</v>
       </c>
@@ -25329,10 +25339,10 @@
         <v>761</v>
       </c>
       <c r="H199" s="16" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="200" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="200" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A200" s="11" t="s">
         <v>87</v>
       </c>
@@ -25352,10 +25362,10 @@
         <v>761</v>
       </c>
       <c r="H200" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="201" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="201" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A201" s="11" t="s">
         <v>87</v>
       </c>
@@ -25375,10 +25385,10 @@
         <v>761</v>
       </c>
       <c r="H201" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="202" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="202" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A202" s="16" t="s">
         <v>647</v>
       </c>
@@ -25390,13 +25400,13 @@
       <c r="E202" s="16"/>
       <c r="F202" s="19"/>
       <c r="G202" s="16" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="H202" s="16" t="s">
-        <v>848</v>
-      </c>
-    </row>
-    <row r="203" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
+        <v>847</v>
+      </c>
+    </row>
+    <row r="203" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A203" s="16" t="s">
         <v>648</v>
       </c>
@@ -25408,13 +25418,13 @@
       <c r="E203" s="16"/>
       <c r="F203" s="19"/>
       <c r="G203" s="16" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="H203" s="16" t="s">
-        <v>848</v>
-      </c>
-    </row>
-    <row r="204" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
+        <v>847</v>
+      </c>
+    </row>
+    <row r="204" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A204" s="16" t="s">
         <v>649</v>
       </c>
@@ -25426,13 +25436,13 @@
       <c r="E204" s="16"/>
       <c r="F204" s="19"/>
       <c r="G204" s="16" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="H204" s="16" t="s">
-        <v>848</v>
-      </c>
-    </row>
-    <row r="205" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
+        <v>847</v>
+      </c>
+    </row>
+    <row r="205" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A205" s="16" t="s">
         <v>650</v>
       </c>
@@ -25444,13 +25454,13 @@
       <c r="E205" s="16"/>
       <c r="F205" s="19"/>
       <c r="G205" s="16" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="H205" s="16" t="s">
-        <v>848</v>
-      </c>
-    </row>
-    <row r="206" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
+        <v>847</v>
+      </c>
+    </row>
+    <row r="206" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A206" s="16" t="s">
         <v>89</v>
       </c>
@@ -25465,10 +25475,10 @@
         <v>762</v>
       </c>
       <c r="H206" s="16" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="207" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="207" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A207" s="16" t="s">
         <v>91</v>
       </c>
@@ -25489,10 +25499,10 @@
         <v>763</v>
       </c>
       <c r="H207" s="16" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="208" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="208" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A208" s="11" t="s">
         <v>91</v>
       </c>
@@ -25512,10 +25522,10 @@
         <v>763</v>
       </c>
       <c r="H208" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="209" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="209" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A209" s="11" t="s">
         <v>91</v>
       </c>
@@ -25535,10 +25545,10 @@
         <v>763</v>
       </c>
       <c r="H209" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="210" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="210" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A210" s="11" t="s">
         <v>91</v>
       </c>
@@ -25558,10 +25568,10 @@
         <v>763</v>
       </c>
       <c r="H210" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="211" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="211" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A211" s="11" t="s">
         <v>91</v>
       </c>
@@ -25581,10 +25591,10 @@
         <v>763</v>
       </c>
       <c r="H211" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="212" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="212" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A212" s="11" t="s">
         <v>91</v>
       </c>
@@ -25604,10 +25614,10 @@
         <v>763</v>
       </c>
       <c r="H212" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="213" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="213" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A213" s="11" t="s">
         <v>91</v>
       </c>
@@ -25627,10 +25637,10 @@
         <v>763</v>
       </c>
       <c r="H213" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="214" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="214" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A214" s="11" t="s">
         <v>91</v>
       </c>
@@ -25650,10 +25660,10 @@
         <v>763</v>
       </c>
       <c r="H214" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="215" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="215" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A215" s="11" t="s">
         <v>91</v>
       </c>
@@ -25673,10 +25683,10 @@
         <v>763</v>
       </c>
       <c r="H215" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="216" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="216" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A216" s="11" t="s">
         <v>91</v>
       </c>
@@ -25696,10 +25706,10 @@
         <v>763</v>
       </c>
       <c r="H216" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="217" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="217" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A217" s="16" t="s">
         <v>93</v>
       </c>
@@ -25720,10 +25730,10 @@
         <v>764</v>
       </c>
       <c r="H217" s="16" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="218" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="218" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A218" s="11" t="s">
         <v>93</v>
       </c>
@@ -25743,10 +25753,10 @@
         <v>764</v>
       </c>
       <c r="H218" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="219" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="219" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A219" s="11" t="s">
         <v>93</v>
       </c>
@@ -25766,10 +25776,10 @@
         <v>764</v>
       </c>
       <c r="H219" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="220" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="220" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A220" s="11" t="s">
         <v>93</v>
       </c>
@@ -25789,10 +25799,10 @@
         <v>764</v>
       </c>
       <c r="H220" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="221" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="221" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A221" s="11" t="s">
         <v>93</v>
       </c>
@@ -25812,10 +25822,10 @@
         <v>764</v>
       </c>
       <c r="H221" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="222" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="222" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A222" s="11" t="s">
         <v>93</v>
       </c>
@@ -25835,10 +25845,10 @@
         <v>764</v>
       </c>
       <c r="H222" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="223" spans="1:8" s="20" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="223" spans="1:8" s="20" customFormat="1" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A223" s="16" t="s">
         <v>716</v>
       </c>
@@ -25856,13 +25866,13 @@
       </c>
       <c r="F223" s="19"/>
       <c r="G223" s="16" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="H223" s="16" t="s">
-        <v>849</v>
-      </c>
-    </row>
-    <row r="224" spans="1:8" x14ac:dyDescent="0.25">
+        <v>848</v>
+      </c>
+    </row>
+    <row r="224" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A224" s="11" t="s">
         <v>716</v>
       </c>
@@ -25879,13 +25889,13 @@
         <v>718</v>
       </c>
       <c r="G224" s="11" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="H224" s="11" t="s">
-        <v>849</v>
-      </c>
-    </row>
-    <row r="225" spans="1:8" x14ac:dyDescent="0.25">
+        <v>848</v>
+      </c>
+    </row>
+    <row r="225" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A225" s="11" t="s">
         <v>716</v>
       </c>
@@ -25902,13 +25912,13 @@
         <v>719</v>
       </c>
       <c r="G225" s="11" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="H225" s="11" t="s">
-        <v>849</v>
-      </c>
-    </row>
-    <row r="226" spans="1:8" x14ac:dyDescent="0.25">
+        <v>848</v>
+      </c>
+    </row>
+    <row r="226" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A226" s="11" t="s">
         <v>716</v>
       </c>
@@ -25925,13 +25935,13 @@
         <v>720</v>
       </c>
       <c r="G226" s="11" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="H226" s="11" t="s">
-        <v>849</v>
-      </c>
-    </row>
-    <row r="227" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+        <v>848</v>
+      </c>
+    </row>
+    <row r="227" spans="1:8" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A227" s="11" t="s">
         <v>716</v>
       </c>
@@ -25948,13 +25958,13 @@
         <v>721</v>
       </c>
       <c r="G227" s="11" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="H227" s="11" t="s">
-        <v>849</v>
-      </c>
-    </row>
-    <row r="228" spans="1:8" x14ac:dyDescent="0.25">
+        <v>848</v>
+      </c>
+    </row>
+    <row r="228" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A228" s="11" t="s">
         <v>716</v>
       </c>
@@ -25971,13 +25981,13 @@
         <v>730</v>
       </c>
       <c r="G228" s="11" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="H228" s="11" t="s">
-        <v>849</v>
-      </c>
-    </row>
-    <row r="229" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
+        <v>848</v>
+      </c>
+    </row>
+    <row r="229" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A229" s="16" t="s">
         <v>95</v>
       </c>
@@ -25998,10 +26008,10 @@
         <v>765</v>
       </c>
       <c r="H229" s="16" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="230" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="230" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A230" s="11" t="s">
         <v>95</v>
       </c>
@@ -26021,10 +26031,10 @@
         <v>765</v>
       </c>
       <c r="H230" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="231" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="231" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A231" s="11" t="s">
         <v>95</v>
       </c>
@@ -26044,10 +26054,10 @@
         <v>765</v>
       </c>
       <c r="H231" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="232" spans="1:8" s="20" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="232" spans="1:8" s="20" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A232" s="16" t="s">
         <v>674</v>
       </c>
@@ -26065,13 +26075,13 @@
       </c>
       <c r="F232" s="19"/>
       <c r="G232" s="16" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="H232" s="16" t="s">
-        <v>849</v>
-      </c>
-    </row>
-    <row r="233" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+        <v>848</v>
+      </c>
+    </row>
+    <row r="233" spans="1:8" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A233" s="11" t="s">
         <v>674</v>
       </c>
@@ -26088,13 +26098,13 @@
         <v>409</v>
       </c>
       <c r="G233" s="11" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="H233" s="11" t="s">
-        <v>849</v>
-      </c>
-    </row>
-    <row r="234" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
+        <v>848</v>
+      </c>
+    </row>
+    <row r="234" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A234" s="16" t="s">
         <v>97</v>
       </c>
@@ -26115,10 +26125,10 @@
         <v>766</v>
       </c>
       <c r="H234" s="16" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="235" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="235" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A235" s="11" t="s">
         <v>97</v>
       </c>
@@ -26138,10 +26148,10 @@
         <v>766</v>
       </c>
       <c r="H235" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="236" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="236" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A236" s="11" t="s">
         <v>97</v>
       </c>
@@ -26161,10 +26171,10 @@
         <v>766</v>
       </c>
       <c r="H236" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="237" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="237" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A237" s="16" t="s">
         <v>99</v>
       </c>
@@ -26185,10 +26195,10 @@
         <v>767</v>
       </c>
       <c r="H237" s="16" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="238" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="238" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A238" s="11" t="s">
         <v>99</v>
       </c>
@@ -26208,10 +26218,10 @@
         <v>767</v>
       </c>
       <c r="H238" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="239" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="239" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A239" s="11" t="s">
         <v>99</v>
       </c>
@@ -26231,10 +26241,10 @@
         <v>767</v>
       </c>
       <c r="H239" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="240" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="240" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A240" s="16" t="s">
         <v>101</v>
       </c>
@@ -26255,10 +26265,10 @@
         <v>768</v>
       </c>
       <c r="H240" s="16" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="241" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="241" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A241" s="11" t="s">
         <v>101</v>
       </c>
@@ -26278,10 +26288,10 @@
         <v>768</v>
       </c>
       <c r="H241" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="242" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="242" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A242" s="11" t="s">
         <v>101</v>
       </c>
@@ -26301,10 +26311,10 @@
         <v>768</v>
       </c>
       <c r="H242" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="243" spans="1:8" s="20" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="243" spans="1:8" s="20" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A243" s="16" t="s">
         <v>673</v>
       </c>
@@ -26316,13 +26326,13 @@
       <c r="E243" s="16"/>
       <c r="F243" s="19"/>
       <c r="G243" s="16" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="H243" s="16" t="s">
-        <v>849</v>
-      </c>
-    </row>
-    <row r="244" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
+        <v>848</v>
+      </c>
+    </row>
+    <row r="244" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A244" s="16" t="s">
         <v>714</v>
       </c>
@@ -26340,13 +26350,13 @@
       </c>
       <c r="F244" s="19"/>
       <c r="G244" s="16" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="H244" s="16" t="s">
-        <v>849</v>
-      </c>
-    </row>
-    <row r="245" spans="1:8" x14ac:dyDescent="0.25">
+        <v>848</v>
+      </c>
+    </row>
+    <row r="245" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A245" s="11" t="s">
         <v>714</v>
       </c>
@@ -26362,14 +26372,14 @@
       <c r="E245" s="39" t="s">
         <v>715</v>
       </c>
-      <c r="G245" s="45" t="s">
-        <v>839</v>
-      </c>
-      <c r="H245" s="45" t="s">
-        <v>849</v>
-      </c>
-    </row>
-    <row r="246" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="G245" s="11" t="s">
+        <v>838</v>
+      </c>
+      <c r="H245" s="11" t="s">
+        <v>848</v>
+      </c>
+    </row>
+    <row r="246" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A246" s="16" t="s">
         <v>722</v>
       </c>
@@ -26382,18 +26392,18 @@
       <c r="D246" s="42" t="s">
         <v>723</v>
       </c>
-      <c r="E246" s="46" t="s">
+      <c r="E246" s="44" t="s">
         <v>723</v>
       </c>
       <c r="F246" s="19"/>
       <c r="G246" s="16" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="H246" s="16" t="s">
-        <v>849</v>
-      </c>
-    </row>
-    <row r="247" spans="1:8" x14ac:dyDescent="0.25">
+        <v>848</v>
+      </c>
+    </row>
+    <row r="247" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A247" s="11" t="s">
         <v>722</v>
       </c>
@@ -26410,13 +26420,13 @@
         <v>724</v>
       </c>
       <c r="G247" s="11" t="s">
-        <v>840</v>
-      </c>
-      <c r="H247" s="45" t="s">
-        <v>849</v>
-      </c>
-    </row>
-    <row r="248" spans="1:8" x14ac:dyDescent="0.25">
+        <v>839</v>
+      </c>
+      <c r="H247" s="11" t="s">
+        <v>848</v>
+      </c>
+    </row>
+    <row r="248" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A248" s="11" t="s">
         <v>722</v>
       </c>
@@ -26433,13 +26443,13 @@
         <v>725</v>
       </c>
       <c r="G248" s="11" t="s">
-        <v>840</v>
-      </c>
-      <c r="H248" s="45" t="s">
-        <v>849</v>
-      </c>
-    </row>
-    <row r="249" spans="1:8" x14ac:dyDescent="0.25">
+        <v>839</v>
+      </c>
+      <c r="H248" s="11" t="s">
+        <v>848</v>
+      </c>
+    </row>
+    <row r="249" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A249" s="11" t="s">
         <v>722</v>
       </c>
@@ -26456,13 +26466,13 @@
         <v>726</v>
       </c>
       <c r="G249" s="11" t="s">
-        <v>840</v>
-      </c>
-      <c r="H249" s="45" t="s">
-        <v>849</v>
-      </c>
-    </row>
-    <row r="250" spans="1:8" x14ac:dyDescent="0.25">
+        <v>839</v>
+      </c>
+      <c r="H249" s="11" t="s">
+        <v>848</v>
+      </c>
+    </row>
+    <row r="250" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A250" s="11" t="s">
         <v>722</v>
       </c>
@@ -26479,13 +26489,13 @@
         <v>727</v>
       </c>
       <c r="G250" s="11" t="s">
-        <v>840</v>
-      </c>
-      <c r="H250" s="45" t="s">
-        <v>849</v>
-      </c>
-    </row>
-    <row r="251" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+        <v>839</v>
+      </c>
+      <c r="H250" s="11" t="s">
+        <v>848</v>
+      </c>
+    </row>
+    <row r="251" spans="1:8" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A251" s="11" t="s">
         <v>722</v>
       </c>
@@ -26502,13 +26512,13 @@
         <v>728</v>
       </c>
       <c r="G251" s="11" t="s">
-        <v>840</v>
-      </c>
-      <c r="H251" s="45" t="s">
-        <v>849</v>
-      </c>
-    </row>
-    <row r="252" spans="1:8" x14ac:dyDescent="0.25">
+        <v>839</v>
+      </c>
+      <c r="H251" s="11" t="s">
+        <v>848</v>
+      </c>
+    </row>
+    <row r="252" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A252" s="11" t="s">
         <v>722</v>
       </c>
@@ -26525,13 +26535,13 @@
         <v>729</v>
       </c>
       <c r="G252" s="11" t="s">
-        <v>840</v>
-      </c>
-      <c r="H252" s="45" t="s">
-        <v>849</v>
-      </c>
-    </row>
-    <row r="253" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
+        <v>839</v>
+      </c>
+      <c r="H252" s="11" t="s">
+        <v>848</v>
+      </c>
+    </row>
+    <row r="253" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A253" s="16" t="s">
         <v>103</v>
       </c>
@@ -26552,10 +26562,10 @@
         <v>769</v>
       </c>
       <c r="H253" s="16" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="254" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="254" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A254" s="11" t="s">
         <v>103</v>
       </c>
@@ -26575,10 +26585,10 @@
         <v>769</v>
       </c>
       <c r="H254" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="255" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="255" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A255" s="11" t="s">
         <v>103</v>
       </c>
@@ -26598,10 +26608,10 @@
         <v>769</v>
       </c>
       <c r="H255" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="256" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="256" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A256" s="16" t="s">
         <v>105</v>
       </c>
@@ -26622,10 +26632,10 @@
         <v>770</v>
       </c>
       <c r="H256" s="16" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="257" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="257" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A257" s="11" t="s">
         <v>105</v>
       </c>
@@ -26645,10 +26655,10 @@
         <v>770</v>
       </c>
       <c r="H257" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="258" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="258" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A258" s="11" t="s">
         <v>105</v>
       </c>
@@ -26668,10 +26678,10 @@
         <v>770</v>
       </c>
       <c r="H258" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="259" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="259" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A259" s="16" t="s">
         <v>107</v>
       </c>
@@ -26692,10 +26702,10 @@
         <v>771</v>
       </c>
       <c r="H259" s="16" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="260" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="260" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A260" s="11" t="s">
         <v>107</v>
       </c>
@@ -26715,10 +26725,10 @@
         <v>771</v>
       </c>
       <c r="H260" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="261" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="261" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A261" s="11" t="s">
         <v>107</v>
       </c>
@@ -26738,10 +26748,10 @@
         <v>771</v>
       </c>
       <c r="H261" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="262" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="262" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A262" s="16" t="s">
         <v>109</v>
       </c>
@@ -26762,10 +26772,10 @@
         <v>772</v>
       </c>
       <c r="H262" s="16" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="263" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="263" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A263" s="11" t="s">
         <v>109</v>
       </c>
@@ -26785,10 +26795,10 @@
         <v>772</v>
       </c>
       <c r="H263" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="264" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="264" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A264" s="11" t="s">
         <v>109</v>
       </c>
@@ -26808,10 +26818,10 @@
         <v>772</v>
       </c>
       <c r="H264" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="265" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="265" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A265" s="16" t="s">
         <v>111</v>
       </c>
@@ -26832,10 +26842,10 @@
         <v>773</v>
       </c>
       <c r="H265" s="16" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="266" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="266" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A266" s="11" t="s">
         <v>111</v>
       </c>
@@ -26855,10 +26865,10 @@
         <v>773</v>
       </c>
       <c r="H266" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="267" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="267" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A267" s="11" t="s">
         <v>111</v>
       </c>
@@ -26878,10 +26888,10 @@
         <v>773</v>
       </c>
       <c r="H267" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="268" spans="1:8" s="20" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="268" spans="1:8" s="20" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A268" s="16" t="s">
         <v>675</v>
       </c>
@@ -26899,13 +26909,13 @@
       </c>
       <c r="F268" s="19"/>
       <c r="G268" s="16" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="H268" s="16" t="s">
-        <v>849</v>
-      </c>
-    </row>
-    <row r="269" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+        <v>848</v>
+      </c>
+    </row>
+    <row r="269" spans="1:8" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A269" s="11" t="s">
         <v>675</v>
       </c>
@@ -26922,13 +26932,13 @@
         <v>409</v>
       </c>
       <c r="G269" s="11" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="H269" s="11" t="s">
-        <v>849</v>
-      </c>
-    </row>
-    <row r="270" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
+        <v>848</v>
+      </c>
+    </row>
+    <row r="270" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A270" s="16" t="s">
         <v>113</v>
       </c>
@@ -26949,10 +26959,10 @@
         <v>774</v>
       </c>
       <c r="H270" s="16" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="271" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="271" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A271" s="11" t="s">
         <v>113</v>
       </c>
@@ -26972,10 +26982,10 @@
         <v>774</v>
       </c>
       <c r="H271" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="272" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="272" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A272" s="11" t="s">
         <v>113</v>
       </c>
@@ -26995,10 +27005,10 @@
         <v>774</v>
       </c>
       <c r="H272" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="273" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="273" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A273" s="16" t="s">
         <v>115</v>
       </c>
@@ -27019,10 +27029,10 @@
         <v>775</v>
       </c>
       <c r="H273" s="16" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="274" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="274" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A274" s="11" t="s">
         <v>115</v>
       </c>
@@ -27042,10 +27052,10 @@
         <v>775</v>
       </c>
       <c r="H274" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="275" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="275" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A275" s="11" t="s">
         <v>115</v>
       </c>
@@ -27065,10 +27075,10 @@
         <v>775</v>
       </c>
       <c r="H275" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="276" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="276" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A276" s="16" t="s">
         <v>117</v>
       </c>
@@ -27089,10 +27099,10 @@
         <v>776</v>
       </c>
       <c r="H276" s="16" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="277" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="277" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A277" s="11" t="s">
         <v>117</v>
       </c>
@@ -27112,10 +27122,10 @@
         <v>776</v>
       </c>
       <c r="H277" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="278" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="278" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A278" s="11" t="s">
         <v>117</v>
       </c>
@@ -27135,10 +27145,10 @@
         <v>776</v>
       </c>
       <c r="H278" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="279" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="279" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A279" s="16" t="s">
         <v>119</v>
       </c>
@@ -27159,10 +27169,10 @@
         <v>777</v>
       </c>
       <c r="H279" s="16" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="280" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="280" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A280" s="11" t="s">
         <v>119</v>
       </c>
@@ -27182,10 +27192,10 @@
         <v>777</v>
       </c>
       <c r="H280" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="281" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="281" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A281" s="11" t="s">
         <v>119</v>
       </c>
@@ -27205,10 +27215,10 @@
         <v>777</v>
       </c>
       <c r="H281" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="282" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="282" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A282" s="16" t="s">
         <v>121</v>
       </c>
@@ -27229,10 +27239,10 @@
         <v>778</v>
       </c>
       <c r="H282" s="16" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="283" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="283" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A283" s="11" t="s">
         <v>121</v>
       </c>
@@ -27252,10 +27262,10 @@
         <v>778</v>
       </c>
       <c r="H283" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="284" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="284" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A284" s="11" t="s">
         <v>121</v>
       </c>
@@ -27275,10 +27285,10 @@
         <v>778</v>
       </c>
       <c r="H284" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="285" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="285" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A285" s="11" t="s">
         <v>121</v>
       </c>
@@ -27298,10 +27308,10 @@
         <v>778</v>
       </c>
       <c r="H285" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="286" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="286" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A286" s="11" t="s">
         <v>121</v>
       </c>
@@ -27321,10 +27331,10 @@
         <v>778</v>
       </c>
       <c r="H286" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="287" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="287" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A287" s="11" t="s">
         <v>121</v>
       </c>
@@ -27344,10 +27354,10 @@
         <v>778</v>
       </c>
       <c r="H287" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="288" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="288" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A288" s="11" t="s">
         <v>121</v>
       </c>
@@ -27367,10 +27377,10 @@
         <v>778</v>
       </c>
       <c r="H288" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="289" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="289" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A289" s="11" t="s">
         <v>121</v>
       </c>
@@ -27390,10 +27400,10 @@
         <v>778</v>
       </c>
       <c r="H289" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="290" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="290" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A290" s="11" t="s">
         <v>121</v>
       </c>
@@ -27413,10 +27423,10 @@
         <v>778</v>
       </c>
       <c r="H290" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="291" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="291" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A291" s="11" t="s">
         <v>121</v>
       </c>
@@ -27436,10 +27446,10 @@
         <v>778</v>
       </c>
       <c r="H291" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="292" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="292" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A292" s="11" t="s">
         <v>121</v>
       </c>
@@ -27459,10 +27469,10 @@
         <v>778</v>
       </c>
       <c r="H292" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="293" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="293" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A293" s="11" t="s">
         <v>121</v>
       </c>
@@ -27482,10 +27492,10 @@
         <v>778</v>
       </c>
       <c r="H293" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="294" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="294" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A294" s="11" t="s">
         <v>121</v>
       </c>
@@ -27505,10 +27515,10 @@
         <v>778</v>
       </c>
       <c r="H294" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="295" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="295" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A295" s="11" t="s">
         <v>121</v>
       </c>
@@ -27528,10 +27538,10 @@
         <v>778</v>
       </c>
       <c r="H295" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="296" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="296" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A296" s="11" t="s">
         <v>121</v>
       </c>
@@ -27551,10 +27561,10 @@
         <v>778</v>
       </c>
       <c r="H296" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="297" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="297" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A297" s="11" t="s">
         <v>121</v>
       </c>
@@ -27574,10 +27584,10 @@
         <v>778</v>
       </c>
       <c r="H297" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="298" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="298" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A298" s="11" t="s">
         <v>121</v>
       </c>
@@ -27597,10 +27607,10 @@
         <v>778</v>
       </c>
       <c r="H298" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="299" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="299" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A299" s="11" t="s">
         <v>121</v>
       </c>
@@ -27620,10 +27630,10 @@
         <v>778</v>
       </c>
       <c r="H299" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="300" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="300" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A300" s="11" t="s">
         <v>121</v>
       </c>
@@ -27643,10 +27653,10 @@
         <v>778</v>
       </c>
       <c r="H300" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="301" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="301" spans="1:8" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A301" s="11" t="s">
         <v>121</v>
       </c>
@@ -27666,10 +27676,10 @@
         <v>778</v>
       </c>
       <c r="H301" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="302" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="302" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A302" s="11" t="s">
         <v>121</v>
       </c>
@@ -27689,10 +27699,10 @@
         <v>778</v>
       </c>
       <c r="H302" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="303" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="303" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A303" s="11" t="s">
         <v>121</v>
       </c>
@@ -27712,10 +27722,10 @@
         <v>778</v>
       </c>
       <c r="H303" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="304" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="304" spans="1:8" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A304" s="11" t="s">
         <v>121</v>
       </c>
@@ -27735,10 +27745,10 @@
         <v>778</v>
       </c>
       <c r="H304" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="305" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="305" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A305" s="11" t="s">
         <v>121</v>
       </c>
@@ -27758,10 +27768,10 @@
         <v>778</v>
       </c>
       <c r="H305" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="306" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="306" spans="1:8" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A306" s="11" t="s">
         <v>121</v>
       </c>
@@ -27781,10 +27791,10 @@
         <v>778</v>
       </c>
       <c r="H306" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="307" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="307" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A307" s="11" t="s">
         <v>121</v>
       </c>
@@ -27804,10 +27814,10 @@
         <v>778</v>
       </c>
       <c r="H307" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="308" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="308" spans="1:8" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A308" s="11" t="s">
         <v>121</v>
       </c>
@@ -27827,10 +27837,10 @@
         <v>778</v>
       </c>
       <c r="H308" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="309" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="309" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A309" s="11" t="s">
         <v>121</v>
       </c>
@@ -27850,10 +27860,10 @@
         <v>778</v>
       </c>
       <c r="H309" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="310" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="310" spans="1:8" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A310" s="11" t="s">
         <v>121</v>
       </c>
@@ -27873,10 +27883,10 @@
         <v>778</v>
       </c>
       <c r="H310" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="311" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="311" spans="1:8" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A311" s="11" t="s">
         <v>121</v>
       </c>
@@ -27896,10 +27906,10 @@
         <v>778</v>
       </c>
       <c r="H311" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="312" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="312" spans="1:8" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A312" s="11" t="s">
         <v>121</v>
       </c>
@@ -27919,10 +27929,10 @@
         <v>778</v>
       </c>
       <c r="H312" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="313" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="313" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A313" s="11" t="s">
         <v>121</v>
       </c>
@@ -27942,10 +27952,10 @@
         <v>778</v>
       </c>
       <c r="H313" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="314" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="314" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A314" s="18" t="s">
         <v>123</v>
       </c>
@@ -27966,10 +27976,10 @@
         <v>779</v>
       </c>
       <c r="H314" s="16" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="315" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="315" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A315" s="4" t="s">
         <v>123</v>
       </c>
@@ -27989,10 +27999,10 @@
         <v>779</v>
       </c>
       <c r="H315" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="316" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="316" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A316" s="4" t="s">
         <v>123</v>
       </c>
@@ -28012,10 +28022,10 @@
         <v>779</v>
       </c>
       <c r="H316" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="317" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="317" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A317" s="18" t="s">
         <v>125</v>
       </c>
@@ -28036,10 +28046,10 @@
         <v>780</v>
       </c>
       <c r="H317" s="16" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="318" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="318" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A318" s="4" t="s">
         <v>125</v>
       </c>
@@ -28059,10 +28069,10 @@
         <v>780</v>
       </c>
       <c r="H318" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="319" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="319" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A319" s="4" t="s">
         <v>125</v>
       </c>
@@ -28082,10 +28092,10 @@
         <v>780</v>
       </c>
       <c r="H319" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="320" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="320" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A320" s="18" t="s">
         <v>127</v>
       </c>
@@ -28100,10 +28110,10 @@
         <v>781</v>
       </c>
       <c r="H320" s="16" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="321" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="321" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A321" s="18" t="s">
         <v>149</v>
       </c>
@@ -28118,10 +28128,10 @@
         <v>782</v>
       </c>
       <c r="H321" s="16" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="322" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="322" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A322" s="18" t="s">
         <v>153</v>
       </c>
@@ -28136,10 +28146,10 @@
         <v>783</v>
       </c>
       <c r="H322" s="16" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="323" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="323" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A323" s="18" t="s">
         <v>155</v>
       </c>
@@ -28154,10 +28164,10 @@
         <v>784</v>
       </c>
       <c r="H323" s="16" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="324" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="324" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A324" s="18" t="s">
         <v>157</v>
       </c>
@@ -28172,10 +28182,10 @@
         <v>785</v>
       </c>
       <c r="H324" s="16" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="325" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="325" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A325" s="18" t="s">
         <v>159</v>
       </c>
@@ -28190,10 +28200,10 @@
         <v>786</v>
       </c>
       <c r="H325" s="16" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="326" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="326" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A326" s="18" t="s">
         <v>161</v>
       </c>
@@ -28208,10 +28218,10 @@
         <v>787</v>
       </c>
       <c r="H326" s="16" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="327" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="327" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A327" s="18" t="s">
         <v>163</v>
       </c>
@@ -28226,10 +28236,10 @@
         <v>788</v>
       </c>
       <c r="H327" s="16" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="328" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="328" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A328" s="18" t="s">
         <v>165</v>
       </c>
@@ -28244,10 +28254,10 @@
         <v>789</v>
       </c>
       <c r="H328" s="16" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="329" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="329" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A329" s="18" t="s">
         <v>129</v>
       </c>
@@ -28262,10 +28272,10 @@
         <v>790</v>
       </c>
       <c r="H329" s="16" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="330" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="330" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A330" s="18" t="s">
         <v>131</v>
       </c>
@@ -28280,10 +28290,10 @@
         <v>791</v>
       </c>
       <c r="H330" s="16" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="331" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="331" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A331" s="18" t="s">
         <v>133</v>
       </c>
@@ -28298,10 +28308,10 @@
         <v>792</v>
       </c>
       <c r="H331" s="16" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="332" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="332" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A332" s="18" t="s">
         <v>135</v>
       </c>
@@ -28316,10 +28326,10 @@
         <v>793</v>
       </c>
       <c r="H332" s="16" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="333" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="333" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A333" s="18" t="s">
         <v>137</v>
       </c>
@@ -28334,10 +28344,10 @@
         <v>794</v>
       </c>
       <c r="H333" s="16" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="334" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="334" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A334" s="18" t="s">
         <v>139</v>
       </c>
@@ -28352,10 +28362,10 @@
         <v>795</v>
       </c>
       <c r="H334" s="16" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="335" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="335" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A335" s="18" t="s">
         <v>141</v>
       </c>
@@ -28370,10 +28380,10 @@
         <v>796</v>
       </c>
       <c r="H335" s="16" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="336" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="336" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A336" s="18" t="s">
         <v>143</v>
       </c>
@@ -28388,10 +28398,10 @@
         <v>797</v>
       </c>
       <c r="H336" s="16" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="337" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="337" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A337" s="18" t="s">
         <v>145</v>
       </c>
@@ -28406,10 +28416,10 @@
         <v>798</v>
       </c>
       <c r="H337" s="16" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="338" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="338" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A338" s="18" t="s">
         <v>147</v>
       </c>
@@ -28424,10 +28434,10 @@
         <v>799</v>
       </c>
       <c r="H338" s="16" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="339" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="339" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A339" s="18" t="s">
         <v>151</v>
       </c>
@@ -28442,10 +28452,10 @@
         <v>800</v>
       </c>
       <c r="H339" s="16" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="340" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="340" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A340" s="16" t="s">
         <v>167</v>
       </c>
@@ -28466,10 +28476,10 @@
         <v>801</v>
       </c>
       <c r="H340" s="16" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="341" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="341" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A341" s="11" t="s">
         <v>167</v>
       </c>
@@ -28489,10 +28499,10 @@
         <v>801</v>
       </c>
       <c r="H341" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="342" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="342" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A342" s="11" t="s">
         <v>167</v>
       </c>
@@ -28512,10 +28522,10 @@
         <v>801</v>
       </c>
       <c r="H342" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="343" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="343" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A343" s="18" t="s">
         <v>168</v>
       </c>
@@ -28530,10 +28540,10 @@
         <v>802</v>
       </c>
       <c r="H343" s="16" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="344" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="344" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A344" s="18" t="s">
         <v>169</v>
       </c>
@@ -28548,10 +28558,10 @@
         <v>803</v>
       </c>
       <c r="H344" s="16" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="345" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="345" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A345" s="18" t="s">
         <v>170</v>
       </c>
@@ -28566,10 +28576,10 @@
         <v>804</v>
       </c>
       <c r="H345" s="16" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="346" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="346" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A346" s="18" t="s">
         <v>172</v>
       </c>
@@ -28584,10 +28594,10 @@
         <v>364</v>
       </c>
       <c r="H346" s="16" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="347" spans="1:8" s="20" customFormat="1" ht="165" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="347" spans="1:8" s="20" customFormat="1" ht="165" hidden="1" x14ac:dyDescent="0.25">
       <c r="A347" s="18" t="s">
         <v>174</v>
       </c>
@@ -28602,10 +28612,10 @@
         <v>805</v>
       </c>
       <c r="H347" s="16" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="348" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="348" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A348" s="18" t="s">
         <v>176</v>
       </c>
@@ -28620,10 +28630,10 @@
         <v>806</v>
       </c>
       <c r="H348" s="16" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="349" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="349" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A349" s="16" t="s">
         <v>178</v>
       </c>
@@ -28644,10 +28654,10 @@
         <v>807</v>
       </c>
       <c r="H349" s="16" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="350" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="350" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A350" s="11" t="s">
         <v>178</v>
       </c>
@@ -28667,10 +28677,10 @@
         <v>807</v>
       </c>
       <c r="H350" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="351" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="351" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A351" s="11" t="s">
         <v>178</v>
       </c>
@@ -28690,10 +28700,10 @@
         <v>807</v>
       </c>
       <c r="H351" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="352" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="352" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A352" s="11" t="s">
         <v>178</v>
       </c>
@@ -28713,10 +28723,10 @@
         <v>807</v>
       </c>
       <c r="H352" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="353" spans="1:9" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="353" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A353" s="11" t="s">
         <v>178</v>
       </c>
@@ -28736,10 +28746,10 @@
         <v>807</v>
       </c>
       <c r="H353" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="354" spans="1:9" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="354" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A354" s="11" t="s">
         <v>178</v>
       </c>
@@ -28759,10 +28769,10 @@
         <v>807</v>
       </c>
       <c r="H354" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="355" spans="1:9" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="355" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A355" s="11" t="s">
         <v>178</v>
       </c>
@@ -28782,10 +28792,10 @@
         <v>807</v>
       </c>
       <c r="H355" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="356" spans="1:9" s="20" customFormat="1" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="356" spans="1:9" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A356" s="16" t="s">
         <v>180</v>
       </c>
@@ -28800,10 +28810,10 @@
         <v>808</v>
       </c>
       <c r="H356" s="16" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="357" spans="1:9" s="20" customFormat="1" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="357" spans="1:9" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A357" s="16" t="s">
         <v>182</v>
       </c>
@@ -28818,10 +28828,10 @@
         <v>809</v>
       </c>
       <c r="H357" s="16" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="358" spans="1:9" s="20" customFormat="1" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="358" spans="1:9" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A358" s="18" t="s">
         <v>183</v>
       </c>
@@ -28842,10 +28852,10 @@
         <v>266</v>
       </c>
       <c r="H358" s="16" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="359" spans="1:9" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="359" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A359" s="4" t="s">
         <v>183</v>
       </c>
@@ -28865,10 +28875,10 @@
         <v>266</v>
       </c>
       <c r="H359" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="360" spans="1:9" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="360" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A360" s="4" t="s">
         <v>183</v>
       </c>
@@ -28888,10 +28898,10 @@
         <v>266</v>
       </c>
       <c r="H360" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="361" spans="1:9" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="361" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A361" s="4" t="s">
         <v>183</v>
       </c>
@@ -28911,13 +28921,13 @@
         <v>266</v>
       </c>
       <c r="H361" s="11" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="I361" s="25" t="s">
         <v>560</v>
       </c>
     </row>
-    <row r="362" spans="1:9" s="20" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:9" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A362" s="18" t="s">
         <v>651</v>
       </c>
@@ -28929,13 +28939,13 @@
       <c r="E362" s="18"/>
       <c r="F362" s="19"/>
       <c r="G362" s="18" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="H362" s="18" t="s">
-        <v>848</v>
-      </c>
-    </row>
-    <row r="363" spans="1:9" s="20" customFormat="1" x14ac:dyDescent="0.25">
+        <v>847</v>
+      </c>
+    </row>
+    <row r="363" spans="1:9" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A363" s="18" t="s">
         <v>527</v>
       </c>
@@ -28947,13 +28957,13 @@
       <c r="E363" s="16"/>
       <c r="F363" s="19"/>
       <c r="G363" s="16" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="H363" s="16" t="s">
-        <v>849</v>
-      </c>
-    </row>
-    <row r="364" spans="1:9" s="20" customFormat="1" x14ac:dyDescent="0.25">
+        <v>848</v>
+      </c>
+    </row>
+    <row r="364" spans="1:9" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A364" s="18" t="s">
         <v>185</v>
       </c>
@@ -28968,10 +28978,10 @@
         <v>810</v>
       </c>
       <c r="H364" s="16" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="365" spans="1:9" s="20" customFormat="1" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="365" spans="1:9" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A365" s="18" t="s">
         <v>186</v>
       </c>
@@ -28986,10 +28996,10 @@
         <v>812</v>
       </c>
       <c r="H365" s="16" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="366" spans="1:9" s="20" customFormat="1" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="366" spans="1:9" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A366" s="18" t="s">
         <v>191</v>
       </c>
@@ -29004,10 +29014,10 @@
         <v>811</v>
       </c>
       <c r="H366" s="16" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="367" spans="1:9" s="20" customFormat="1" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="367" spans="1:9" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A367" s="16" t="s">
         <v>197</v>
       </c>
@@ -29028,10 +29038,10 @@
         <v>813</v>
       </c>
       <c r="H367" s="16" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="368" spans="1:9" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="368" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A368" s="11" t="s">
         <v>197</v>
       </c>
@@ -29051,10 +29061,10 @@
         <v>813</v>
       </c>
       <c r="H368" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="369" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="369" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A369" s="11" t="s">
         <v>197</v>
       </c>
@@ -29074,10 +29084,10 @@
         <v>813</v>
       </c>
       <c r="H369" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="370" spans="1:8" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="370" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A370" s="11" t="s">
         <v>197</v>
       </c>
@@ -29097,10 +29107,10 @@
         <v>813</v>
       </c>
       <c r="H370" s="11" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="371" spans="1:8" s="20" customFormat="1" ht="315" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="371" spans="1:8" s="20" customFormat="1" ht="315" hidden="1" x14ac:dyDescent="0.25">
       <c r="A371" s="18" t="s">
         <v>199</v>
       </c>
@@ -29115,10 +29125,10 @@
         <v>814</v>
       </c>
       <c r="H371" s="16" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="372" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="372" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A372" s="18" t="s">
         <v>529</v>
       </c>
@@ -29129,13 +29139,21 @@
       <c r="D372" s="38"/>
       <c r="E372" s="16"/>
       <c r="F372" s="19"/>
-      <c r="G372" s="16"/>
+      <c r="G372" s="16" t="s">
+        <v>850</v>
+      </c>
       <c r="H372" s="16" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="H1:H372" xr:uid="{51D60DD1-DC0B-4658-A996-7DC0B41964ED}"/>
+  <autoFilter ref="A1:I372" xr:uid="{51D60DD1-DC0B-4658-A996-7DC0B41964ED}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="cod_text_1"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Resources/Admin/Crosswalks and Schemas.xlsx
+++ b/Resources/Admin/Crosswalks and Schemas.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SHDTJB\Documents\LocalSave\Code\R\GitHub\WA-DOH-CHS-Death-Files-ETL\Resources\Admin\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BB99517-3EED-42C1-8B9D-B840984D62DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DB3E5AF-0EAF-4F6C-B31D-BEB116B34CF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20520" yWindow="-16365" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8280" yWindow="-16320" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="3" r:id="rId1"/>
@@ -20687,7 +20687,6 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51D60DD1-DC0B-4658-A996-7DC0B41964ED}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:I372"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -20731,7 +20730,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:9" s="20" customFormat="1" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" s="20" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A2" s="16" t="s">
         <v>4</v>
       </c>
@@ -20749,7 +20748,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="3" spans="1:9" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="16" t="s">
         <v>676</v>
       </c>
@@ -20775,7 +20774,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="4" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
         <v>676</v>
       </c>
@@ -20801,7 +20800,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="5" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
         <v>676</v>
       </c>
@@ -20827,7 +20826,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="6" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>676</v>
       </c>
@@ -20853,7 +20852,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="7" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>676</v>
       </c>
@@ -20879,7 +20878,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="8" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
         <v>676</v>
       </c>
@@ -20905,7 +20904,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="9" spans="1:9" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="16" t="s">
         <v>682</v>
       </c>
@@ -20931,7 +20930,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="10" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
         <v>682</v>
       </c>
@@ -20957,7 +20956,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="11" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
         <v>682</v>
       </c>
@@ -20983,7 +20982,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="12" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
         <v>682</v>
       </c>
@@ -21009,7 +21008,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="13" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>682</v>
       </c>
@@ -21035,7 +21034,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="14" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
         <v>682</v>
       </c>
@@ -21061,7 +21060,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="15" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
         <v>682</v>
       </c>
@@ -21087,7 +21086,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="16" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
         <v>682</v>
       </c>
@@ -21113,7 +21112,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="17" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
         <v>682</v>
       </c>
@@ -21139,7 +21138,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="18" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
         <v>682</v>
       </c>
@@ -21165,7 +21164,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="19" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
         <v>682</v>
       </c>
@@ -21191,7 +21190,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="20" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="16" t="s">
         <v>692</v>
       </c>
@@ -21217,7 +21216,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="21" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
         <v>692</v>
       </c>
@@ -21243,7 +21242,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="22" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
         <v>692</v>
       </c>
@@ -21269,7 +21268,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="23" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="11" t="s">
         <v>692</v>
       </c>
@@ -21295,7 +21294,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="24" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
         <v>692</v>
       </c>
@@ -21321,7 +21320,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="25" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
         <v>692</v>
       </c>
@@ -21347,7 +21346,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="26" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="11" t="s">
         <v>692</v>
       </c>
@@ -21373,7 +21372,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="27" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
         <v>692</v>
       </c>
@@ -21399,7 +21398,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="28" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="11" t="s">
         <v>692</v>
       </c>
@@ -21425,7 +21424,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="29" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
         <v>692</v>
       </c>
@@ -21451,7 +21450,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="11" t="s">
         <v>692</v>
       </c>
@@ -21477,7 +21476,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="31" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="11" t="s">
         <v>692</v>
       </c>
@@ -21503,7 +21502,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="32" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="11" t="s">
         <v>692</v>
       </c>
@@ -21529,7 +21528,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="33" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="11" t="s">
         <v>692</v>
       </c>
@@ -21555,7 +21554,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="34" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="11" t="s">
         <v>692</v>
       </c>
@@ -21581,7 +21580,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="35" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="11" t="s">
         <v>692</v>
       </c>
@@ -21607,7 +21606,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="36" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="11" t="s">
         <v>692</v>
       </c>
@@ -21633,7 +21632,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="37" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" s="11" t="s">
         <v>692</v>
       </c>
@@ -21659,7 +21658,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="38" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="11" t="s">
         <v>692</v>
       </c>
@@ -21685,7 +21684,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="39" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="11" t="s">
         <v>692</v>
       </c>
@@ -21711,7 +21710,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="40" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="16" t="s">
         <v>710</v>
       </c>
@@ -21737,7 +21736,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="41" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="11" t="s">
         <v>710</v>
       </c>
@@ -21763,7 +21762,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="42" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="11" t="s">
         <v>710</v>
       </c>
@@ -21789,7 +21788,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="43" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="11" t="s">
         <v>710</v>
       </c>
@@ -21815,7 +21814,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="44" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="11" t="s">
         <v>710</v>
       </c>
@@ -21841,7 +21840,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="45" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" s="11" t="s">
         <v>710</v>
       </c>
@@ -21867,7 +21866,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="46" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" s="11" t="s">
         <v>710</v>
       </c>
@@ -21893,7 +21892,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="47" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" s="11" t="s">
         <v>710</v>
       </c>
@@ -21919,7 +21918,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="48" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" s="11" t="s">
         <v>710</v>
       </c>
@@ -21945,7 +21944,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="49" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" s="11" t="s">
         <v>710</v>
       </c>
@@ -21971,7 +21970,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="50" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" s="11" t="s">
         <v>710</v>
       </c>
@@ -21997,7 +21996,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="51" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" s="11" t="s">
         <v>710</v>
       </c>
@@ -22023,7 +22022,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="52" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" s="11" t="s">
         <v>710</v>
       </c>
@@ -22049,7 +22048,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="53" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" s="11" t="s">
         <v>710</v>
       </c>
@@ -22075,7 +22074,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="54" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" s="11" t="s">
         <v>710</v>
       </c>
@@ -22101,7 +22100,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="55" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" s="11" t="s">
         <v>710</v>
       </c>
@@ -22127,7 +22126,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="56" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" s="11" t="s">
         <v>710</v>
       </c>
@@ -22153,7 +22152,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="57" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" s="11" t="s">
         <v>710</v>
       </c>
@@ -22179,7 +22178,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="58" spans="1:8" s="20" customFormat="1" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:8" s="20" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A58" s="16" t="s">
         <v>6</v>
       </c>
@@ -22203,7 +22202,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="59" spans="1:8" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A59" s="11" t="s">
         <v>6</v>
       </c>
@@ -22226,7 +22225,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="60" spans="1:8" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A60" s="11" t="s">
         <v>6</v>
       </c>
@@ -22249,7 +22248,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="61" spans="1:8" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A61" s="11" t="s">
         <v>6</v>
       </c>
@@ -22272,7 +22271,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="62" spans="1:8" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A62" s="11" t="s">
         <v>6</v>
       </c>
@@ -22295,7 +22294,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="63" spans="1:8" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A63" s="11" t="s">
         <v>6</v>
       </c>
@@ -22318,7 +22317,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="64" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A64" s="16" t="s">
         <v>7</v>
       </c>
@@ -22336,7 +22335,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="65" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A65" s="16" t="s">
         <v>523</v>
       </c>
@@ -22354,7 +22353,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="66" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A66" s="16" t="s">
         <v>9</v>
       </c>
@@ -22378,7 +22377,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="67" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" s="11" t="s">
         <v>9</v>
       </c>
@@ -22401,7 +22400,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="68" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" s="11" t="s">
         <v>9</v>
       </c>
@@ -22424,7 +22423,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="69" spans="1:8" s="20" customFormat="1" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:8" s="20" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A69" s="16" t="s">
         <v>10</v>
       </c>
@@ -22448,7 +22447,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="70" spans="1:8" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A70" s="11" t="s">
         <v>10</v>
       </c>
@@ -22471,7 +22470,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="71" spans="1:8" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A71" s="11" t="s">
         <v>10</v>
       </c>
@@ -22494,7 +22493,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="72" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A72" s="16" t="s">
         <v>12</v>
       </c>
@@ -22516,7 +22515,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="73" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A73" s="16" t="s">
         <v>14</v>
       </c>
@@ -22538,7 +22537,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="74" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A74" s="18" t="s">
         <v>16</v>
       </c>
@@ -22562,7 +22561,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="75" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" s="4" t="s">
         <v>16</v>
       </c>
@@ -22585,7 +22584,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="76" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
         <v>16</v>
       </c>
@@ -22608,7 +22607,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="77" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" s="4" t="s">
         <v>16</v>
       </c>
@@ -22631,7 +22630,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="78" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
         <v>16</v>
       </c>
@@ -22654,7 +22653,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="79" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" s="4" t="s">
         <v>16</v>
       </c>
@@ -22677,7 +22676,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="80" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
         <v>16</v>
       </c>
@@ -22700,7 +22699,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="81" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81" s="4" t="s">
         <v>16</v>
       </c>
@@ -22723,7 +22722,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="82" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
         <v>16</v>
       </c>
@@ -22764,7 +22763,7 @@
         <v>846</v>
       </c>
     </row>
-    <row r="84" spans="1:9" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:9" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A84" s="33" t="s">
         <v>630</v>
       </c>
@@ -22782,7 +22781,7 @@
         <v>846</v>
       </c>
     </row>
-    <row r="85" spans="1:9" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:9" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A85" s="33" t="s">
         <v>631</v>
       </c>
@@ -22800,7 +22799,7 @@
         <v>846</v>
       </c>
     </row>
-    <row r="86" spans="1:9" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:9" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A86" s="33" t="s">
         <v>632</v>
       </c>
@@ -22818,7 +22817,7 @@
         <v>846</v>
       </c>
     </row>
-    <row r="87" spans="1:9" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:9" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A87" s="33" t="s">
         <v>633</v>
       </c>
@@ -22836,7 +22835,7 @@
         <v>846</v>
       </c>
     </row>
-    <row r="88" spans="1:9" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:9" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A88" s="16" t="s">
         <v>525</v>
       </c>
@@ -22855,7 +22854,7 @@
       </c>
       <c r="I88" s="17"/>
     </row>
-    <row r="89" spans="1:9" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:9" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A89" s="16" t="s">
         <v>18</v>
       </c>
@@ -22873,7 +22872,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="90" spans="1:9" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:9" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A90" s="16" t="s">
         <v>20</v>
       </c>
@@ -22891,7 +22890,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="91" spans="1:9" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:9" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A91" s="16" t="s">
         <v>22</v>
       </c>
@@ -22915,7 +22914,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="92" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A92" s="11" t="s">
         <v>22</v>
       </c>
@@ -22938,7 +22937,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="93" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A93" s="11" t="s">
         <v>22</v>
       </c>
@@ -22961,7 +22960,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="94" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A94" s="11" t="s">
         <v>22</v>
       </c>
@@ -22984,7 +22983,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="95" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A95" s="11" t="s">
         <v>22</v>
       </c>
@@ -23007,7 +23006,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="96" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A96" s="11" t="s">
         <v>22</v>
       </c>
@@ -23030,7 +23029,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="97" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97" s="11" t="s">
         <v>22</v>
       </c>
@@ -23053,7 +23052,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="98" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A98" s="16" t="s">
         <v>24</v>
       </c>
@@ -23071,7 +23070,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="99" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A99" s="16" t="s">
         <v>26</v>
       </c>
@@ -23089,7 +23088,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="100" spans="1:8" s="20" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:8" s="20" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A100" s="16" t="s">
         <v>27</v>
       </c>
@@ -23107,7 +23106,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="101" spans="1:8" s="20" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:8" s="20" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A101" s="16" t="s">
         <v>28</v>
       </c>
@@ -23125,7 +23124,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="102" spans="1:8" s="20" customFormat="1" ht="180" hidden="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:8" s="20" customFormat="1" ht="180" x14ac:dyDescent="0.25">
       <c r="A102" s="16" t="s">
         <v>30</v>
       </c>
@@ -23143,7 +23142,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="103" spans="1:8" s="20" customFormat="1" ht="180" hidden="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:8" s="20" customFormat="1" ht="180" x14ac:dyDescent="0.25">
       <c r="A103" s="16" t="s">
         <v>32</v>
       </c>
@@ -23161,7 +23160,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="104" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A104" s="16" t="s">
         <v>34</v>
       </c>
@@ -23179,7 +23178,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="105" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A105" s="16" t="s">
         <v>36</v>
       </c>
@@ -23197,7 +23196,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="106" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A106" s="16" t="s">
         <v>38</v>
       </c>
@@ -23215,7 +23214,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="107" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A107" s="16" t="s">
         <v>40</v>
       </c>
@@ -23239,7 +23238,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="108" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A108" s="11" t="s">
         <v>40</v>
       </c>
@@ -23262,7 +23261,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="109" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A109" s="11" t="s">
         <v>40</v>
       </c>
@@ -23285,7 +23284,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="110" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A110" s="11" t="s">
         <v>40</v>
       </c>
@@ -23308,7 +23307,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="111" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A111" s="11" t="s">
         <v>40</v>
       </c>
@@ -23331,7 +23330,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="112" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A112" s="11" t="s">
         <v>40</v>
       </c>
@@ -23354,7 +23353,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="113" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A113" s="11" t="s">
         <v>40</v>
       </c>
@@ -23377,7 +23376,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="114" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A114" s="11" t="s">
         <v>40</v>
       </c>
@@ -23400,7 +23399,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="115" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A115" s="16" t="s">
         <v>42</v>
       </c>
@@ -23418,7 +23417,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="116" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A116" s="16" t="s">
         <v>44</v>
       </c>
@@ -23444,7 +23443,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="117" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A117" s="11" t="s">
         <v>44</v>
       </c>
@@ -23470,7 +23469,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="118" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A118" s="11" t="s">
         <v>44</v>
       </c>
@@ -23496,7 +23495,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="119" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A119" s="11" t="s">
         <v>44</v>
       </c>
@@ -23522,7 +23521,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="120" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A120" s="11" t="s">
         <v>44</v>
       </c>
@@ -23548,7 +23547,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="121" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A121" s="11" t="s">
         <v>44</v>
       </c>
@@ -23574,7 +23573,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="122" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A122" s="11" t="s">
         <v>44</v>
       </c>
@@ -23600,7 +23599,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="123" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A123" s="11" t="s">
         <v>44</v>
       </c>
@@ -23626,7 +23625,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="124" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A124" s="11" t="s">
         <v>44</v>
       </c>
@@ -23652,7 +23651,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="125" spans="1:8" s="20" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:8" s="20" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="16" t="s">
         <v>46</v>
       </c>
@@ -23678,7 +23677,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="126" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A126" s="11" t="s">
         <v>46</v>
       </c>
@@ -23704,7 +23703,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="127" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A127" s="11" t="s">
         <v>46</v>
       </c>
@@ -23730,7 +23729,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="128" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A128" s="11" t="s">
         <v>46</v>
       </c>
@@ -23756,7 +23755,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="129" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A129" s="11" t="s">
         <v>46</v>
       </c>
@@ -23782,7 +23781,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="130" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A130" s="11" t="s">
         <v>46</v>
       </c>
@@ -23808,7 +23807,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="131" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A131" s="11" t="s">
         <v>46</v>
       </c>
@@ -23834,7 +23833,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="132" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A132" s="11" t="s">
         <v>46</v>
       </c>
@@ -23860,7 +23859,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="133" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A133" s="11" t="s">
         <v>46</v>
       </c>
@@ -23886,7 +23885,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="134" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A134" s="11" t="s">
         <v>46</v>
       </c>
@@ -23912,7 +23911,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="135" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A135" s="18" t="s">
         <v>391</v>
       </c>
@@ -23930,7 +23929,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="136" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A136" s="18" t="s">
         <v>713</v>
       </c>
@@ -23948,7 +23947,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="137" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A137" s="4" t="s">
         <v>713</v>
       </c>
@@ -23962,7 +23961,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="138" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A138" s="16" t="s">
         <v>48</v>
       </c>
@@ -23986,7 +23985,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="139" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A139" s="11" t="s">
         <v>48</v>
       </c>
@@ -24009,7 +24008,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="140" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A140" s="11" t="s">
         <v>48</v>
       </c>
@@ -24032,7 +24031,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="141" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A141" s="16" t="s">
         <v>50</v>
       </c>
@@ -24056,7 +24055,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="142" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A142" s="11" t="s">
         <v>50</v>
       </c>
@@ -24079,7 +24078,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="143" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A143" s="11" t="s">
         <v>50</v>
       </c>
@@ -24102,7 +24101,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="144" spans="1:8" s="20" customFormat="1" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:8" s="20" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A144" s="16" t="s">
         <v>52</v>
       </c>
@@ -24126,7 +24125,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="145" spans="1:8" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A145" s="11" t="s">
         <v>52</v>
       </c>
@@ -24149,7 +24148,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="146" spans="1:8" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A146" s="11" t="s">
         <v>52</v>
       </c>
@@ -24172,7 +24171,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="147" spans="1:8" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A147" s="11" t="s">
         <v>52</v>
       </c>
@@ -24195,7 +24194,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="148" spans="1:8" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A148" s="11" t="s">
         <v>52</v>
       </c>
@@ -24218,7 +24217,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="149" spans="1:8" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A149" s="11" t="s">
         <v>52</v>
       </c>
@@ -24241,7 +24240,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="150" spans="1:8" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A150" s="11" t="s">
         <v>52</v>
       </c>
@@ -24264,7 +24263,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="151" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A151" s="16" t="s">
         <v>54</v>
       </c>
@@ -24288,7 +24287,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="152" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A152" s="11" t="s">
         <v>54</v>
       </c>
@@ -24311,7 +24310,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="153" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A153" s="11" t="s">
         <v>54</v>
       </c>
@@ -24334,7 +24333,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="154" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A154" s="16" t="s">
         <v>56</v>
       </c>
@@ -24358,7 +24357,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="155" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A155" s="11" t="s">
         <v>56</v>
       </c>
@@ -24381,7 +24380,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="156" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A156" s="11" t="s">
         <v>56</v>
       </c>
@@ -24404,7 +24403,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="157" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A157" s="16" t="s">
         <v>58</v>
       </c>
@@ -24428,7 +24427,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="158" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A158" s="11" t="s">
         <v>58</v>
       </c>
@@ -24451,7 +24450,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="159" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A159" s="11" t="s">
         <v>58</v>
       </c>
@@ -24474,7 +24473,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="160" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A160" s="16" t="s">
         <v>60</v>
       </c>
@@ -24492,7 +24491,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="161" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A161" s="16" t="s">
         <v>62</v>
       </c>
@@ -24510,7 +24509,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="162" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A162" s="16" t="s">
         <v>64</v>
       </c>
@@ -24534,7 +24533,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="163" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A163" s="11" t="s">
         <v>64</v>
       </c>
@@ -24557,7 +24556,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="164" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A164" s="11" t="s">
         <v>64</v>
       </c>
@@ -24580,7 +24579,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="165" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A165" s="11" t="s">
         <v>64</v>
       </c>
@@ -24603,7 +24602,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="166" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A166" s="11" t="s">
         <v>64</v>
       </c>
@@ -24626,7 +24625,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="167" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A167" s="11" t="s">
         <v>64</v>
       </c>
@@ -24649,7 +24648,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="168" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A168" s="11" t="s">
         <v>64</v>
       </c>
@@ -24672,7 +24671,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="169" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A169" s="11" t="s">
         <v>64</v>
       </c>
@@ -24695,7 +24694,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="170" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A170" s="11" t="s">
         <v>64</v>
       </c>
@@ -24718,7 +24717,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="171" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A171" s="11" t="s">
         <v>64</v>
       </c>
@@ -24741,7 +24740,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="172" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A172" s="16" t="s">
         <v>66</v>
       </c>
@@ -24765,7 +24764,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="173" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A173" s="11" t="s">
         <v>66</v>
       </c>
@@ -24788,7 +24787,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="174" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A174" s="11" t="s">
         <v>66</v>
       </c>
@@ -24811,7 +24810,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="175" spans="1:8" s="20" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:8" s="20" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A175" s="16" t="s">
         <v>67</v>
       </c>
@@ -24829,7 +24828,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="176" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A176" s="16" t="s">
         <v>68</v>
       </c>
@@ -24847,7 +24846,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="177" spans="1:9" s="20" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:9" s="20" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A177" s="16" t="s">
         <v>69</v>
       </c>
@@ -24865,7 +24864,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="178" spans="1:9" s="20" customFormat="1" ht="180" hidden="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:9" s="20" customFormat="1" ht="180" x14ac:dyDescent="0.25">
       <c r="A178" s="16" t="s">
         <v>71</v>
       </c>
@@ -24883,7 +24882,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="179" spans="1:9" s="20" customFormat="1" ht="180" hidden="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:9" s="20" customFormat="1" ht="180" x14ac:dyDescent="0.25">
       <c r="A179" s="16" t="s">
         <v>73</v>
       </c>
@@ -24901,7 +24900,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="180" spans="1:9" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:9" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A180" s="16" t="s">
         <v>634</v>
       </c>
@@ -24919,7 +24918,7 @@
         <v>846</v>
       </c>
     </row>
-    <row r="181" spans="1:9" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:9" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A181" s="16" t="s">
         <v>75</v>
       </c>
@@ -24937,7 +24936,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="182" spans="1:9" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:9" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A182" s="16" t="s">
         <v>77</v>
       </c>
@@ -24955,7 +24954,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="183" spans="1:9" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:9" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A183" s="16" t="s">
         <v>79</v>
       </c>
@@ -24973,7 +24972,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="184" spans="1:9" s="20" customFormat="1" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:9" s="20" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A184" s="16" t="s">
         <v>81</v>
       </c>
@@ -24991,7 +24990,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="185" spans="1:9" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:9" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A185" s="16" t="s">
         <v>83</v>
       </c>
@@ -25015,7 +25014,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="186" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A186" s="11" t="s">
         <v>83</v>
       </c>
@@ -25038,7 +25037,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="187" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A187" s="11" t="s">
         <v>83</v>
       </c>
@@ -25061,7 +25060,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="188" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A188" s="11" t="s">
         <v>83</v>
       </c>
@@ -25084,7 +25083,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="189" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A189" s="11" t="s">
         <v>83</v>
       </c>
@@ -25107,7 +25106,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="190" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A190" s="11" t="s">
         <v>83</v>
       </c>
@@ -25130,7 +25129,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="191" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A191" s="11" t="s">
         <v>83</v>
       </c>
@@ -25156,7 +25155,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="192" spans="1:9" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:9" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A192" s="16" t="s">
         <v>85</v>
       </c>
@@ -25180,7 +25179,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="193" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A193" s="11" t="s">
         <v>85</v>
       </c>
@@ -25203,7 +25202,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="194" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A194" s="11" t="s">
         <v>85</v>
       </c>
@@ -25226,7 +25225,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="195" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A195" s="11" t="s">
         <v>85</v>
       </c>
@@ -25249,7 +25248,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="196" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A196" s="11" t="s">
         <v>85</v>
       </c>
@@ -25272,7 +25271,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="197" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A197" s="11" t="s">
         <v>85</v>
       </c>
@@ -25295,7 +25294,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="198" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A198" s="11" t="s">
         <v>85</v>
       </c>
@@ -25318,7 +25317,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="199" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A199" s="16" t="s">
         <v>87</v>
       </c>
@@ -25342,7 +25341,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="200" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A200" s="11" t="s">
         <v>87</v>
       </c>
@@ -25365,7 +25364,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="201" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A201" s="11" t="s">
         <v>87</v>
       </c>
@@ -25388,7 +25387,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="202" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A202" s="16" t="s">
         <v>647</v>
       </c>
@@ -25406,7 +25405,7 @@
         <v>847</v>
       </c>
     </row>
-    <row r="203" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A203" s="16" t="s">
         <v>648</v>
       </c>
@@ -25424,7 +25423,7 @@
         <v>847</v>
       </c>
     </row>
-    <row r="204" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A204" s="16" t="s">
         <v>649</v>
       </c>
@@ -25442,7 +25441,7 @@
         <v>847</v>
       </c>
     </row>
-    <row r="205" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A205" s="16" t="s">
         <v>650</v>
       </c>
@@ -25460,7 +25459,7 @@
         <v>847</v>
       </c>
     </row>
-    <row r="206" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A206" s="16" t="s">
         <v>89</v>
       </c>
@@ -25478,7 +25477,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="207" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A207" s="16" t="s">
         <v>91</v>
       </c>
@@ -25502,7 +25501,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="208" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A208" s="11" t="s">
         <v>91</v>
       </c>
@@ -25525,7 +25524,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="209" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A209" s="11" t="s">
         <v>91</v>
       </c>
@@ -25548,7 +25547,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="210" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A210" s="11" t="s">
         <v>91</v>
       </c>
@@ -25571,7 +25570,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="211" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A211" s="11" t="s">
         <v>91</v>
       </c>
@@ -25594,7 +25593,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="212" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A212" s="11" t="s">
         <v>91</v>
       </c>
@@ -25617,7 +25616,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="213" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A213" s="11" t="s">
         <v>91</v>
       </c>
@@ -25640,7 +25639,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="214" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A214" s="11" t="s">
         <v>91</v>
       </c>
@@ -25663,7 +25662,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="215" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A215" s="11" t="s">
         <v>91</v>
       </c>
@@ -25686,7 +25685,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="216" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A216" s="11" t="s">
         <v>91</v>
       </c>
@@ -25709,7 +25708,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="217" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A217" s="16" t="s">
         <v>93</v>
       </c>
@@ -25733,7 +25732,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="218" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A218" s="11" t="s">
         <v>93</v>
       </c>
@@ -25756,7 +25755,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="219" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A219" s="11" t="s">
         <v>93</v>
       </c>
@@ -25779,7 +25778,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="220" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A220" s="11" t="s">
         <v>93</v>
       </c>
@@ -25802,7 +25801,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="221" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A221" s="11" t="s">
         <v>93</v>
       </c>
@@ -25825,7 +25824,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="222" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A222" s="11" t="s">
         <v>93</v>
       </c>
@@ -25848,7 +25847,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="223" spans="1:8" s="20" customFormat="1" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:8" s="20" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A223" s="16" t="s">
         <v>716</v>
       </c>
@@ -25872,7 +25871,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="224" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A224" s="11" t="s">
         <v>716</v>
       </c>
@@ -25895,7 +25894,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="225" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A225" s="11" t="s">
         <v>716</v>
       </c>
@@ -25918,7 +25917,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="226" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A226" s="11" t="s">
         <v>716</v>
       </c>
@@ -25941,7 +25940,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="227" spans="1:8" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A227" s="11" t="s">
         <v>716</v>
       </c>
@@ -25964,7 +25963,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="228" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A228" s="11" t="s">
         <v>716</v>
       </c>
@@ -25987,7 +25986,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="229" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A229" s="16" t="s">
         <v>95</v>
       </c>
@@ -26011,7 +26010,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="230" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A230" s="11" t="s">
         <v>95</v>
       </c>
@@ -26034,7 +26033,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="231" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A231" s="11" t="s">
         <v>95</v>
       </c>
@@ -26057,7 +26056,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="232" spans="1:8" s="20" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:8" s="20" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A232" s="16" t="s">
         <v>674</v>
       </c>
@@ -26081,7 +26080,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="233" spans="1:8" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A233" s="11" t="s">
         <v>674</v>
       </c>
@@ -26104,7 +26103,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="234" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A234" s="16" t="s">
         <v>97</v>
       </c>
@@ -26128,7 +26127,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="235" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A235" s="11" t="s">
         <v>97</v>
       </c>
@@ -26151,7 +26150,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="236" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A236" s="11" t="s">
         <v>97</v>
       </c>
@@ -26174,7 +26173,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="237" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A237" s="16" t="s">
         <v>99</v>
       </c>
@@ -26198,7 +26197,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="238" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A238" s="11" t="s">
         <v>99</v>
       </c>
@@ -26221,7 +26220,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="239" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A239" s="11" t="s">
         <v>99</v>
       </c>
@@ -26244,7 +26243,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="240" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A240" s="16" t="s">
         <v>101</v>
       </c>
@@ -26268,7 +26267,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="241" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A241" s="11" t="s">
         <v>101</v>
       </c>
@@ -26291,7 +26290,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="242" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A242" s="11" t="s">
         <v>101</v>
       </c>
@@ -26314,7 +26313,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="243" spans="1:8" s="20" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:8" s="20" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A243" s="16" t="s">
         <v>673</v>
       </c>
@@ -26332,7 +26331,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="244" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A244" s="16" t="s">
         <v>714</v>
       </c>
@@ -26356,7 +26355,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="245" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A245" s="11" t="s">
         <v>714</v>
       </c>
@@ -26379,7 +26378,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="246" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A246" s="16" t="s">
         <v>722</v>
       </c>
@@ -26403,7 +26402,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="247" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A247" s="11" t="s">
         <v>722</v>
       </c>
@@ -26426,7 +26425,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="248" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A248" s="11" t="s">
         <v>722</v>
       </c>
@@ -26449,7 +26448,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="249" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A249" s="11" t="s">
         <v>722</v>
       </c>
@@ -26472,7 +26471,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="250" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A250" s="11" t="s">
         <v>722</v>
       </c>
@@ -26495,7 +26494,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="251" spans="1:8" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A251" s="11" t="s">
         <v>722</v>
       </c>
@@ -26518,7 +26517,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="252" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A252" s="11" t="s">
         <v>722</v>
       </c>
@@ -26541,7 +26540,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="253" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A253" s="16" t="s">
         <v>103</v>
       </c>
@@ -26565,7 +26564,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="254" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A254" s="11" t="s">
         <v>103</v>
       </c>
@@ -26588,7 +26587,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="255" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A255" s="11" t="s">
         <v>103</v>
       </c>
@@ -26611,7 +26610,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="256" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A256" s="16" t="s">
         <v>105</v>
       </c>
@@ -26635,7 +26634,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="257" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A257" s="11" t="s">
         <v>105</v>
       </c>
@@ -26658,7 +26657,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="258" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A258" s="11" t="s">
         <v>105</v>
       </c>
@@ -26681,7 +26680,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="259" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A259" s="16" t="s">
         <v>107</v>
       </c>
@@ -26705,7 +26704,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="260" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A260" s="11" t="s">
         <v>107</v>
       </c>
@@ -26728,7 +26727,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="261" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A261" s="11" t="s">
         <v>107</v>
       </c>
@@ -26751,7 +26750,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="262" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A262" s="16" t="s">
         <v>109</v>
       </c>
@@ -26775,7 +26774,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="263" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A263" s="11" t="s">
         <v>109</v>
       </c>
@@ -26798,7 +26797,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="264" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A264" s="11" t="s">
         <v>109</v>
       </c>
@@ -26821,7 +26820,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="265" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A265" s="16" t="s">
         <v>111</v>
       </c>
@@ -26845,7 +26844,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="266" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A266" s="11" t="s">
         <v>111</v>
       </c>
@@ -26868,7 +26867,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="267" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A267" s="11" t="s">
         <v>111</v>
       </c>
@@ -26891,7 +26890,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="268" spans="1:8" s="20" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:8" s="20" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A268" s="16" t="s">
         <v>675</v>
       </c>
@@ -26915,7 +26914,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="269" spans="1:8" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A269" s="11" t="s">
         <v>675</v>
       </c>
@@ -26938,7 +26937,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="270" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A270" s="16" t="s">
         <v>113</v>
       </c>
@@ -26962,7 +26961,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="271" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A271" s="11" t="s">
         <v>113</v>
       </c>
@@ -26985,7 +26984,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="272" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A272" s="11" t="s">
         <v>113</v>
       </c>
@@ -27008,7 +27007,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="273" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A273" s="16" t="s">
         <v>115</v>
       </c>
@@ -27032,7 +27031,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="274" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A274" s="11" t="s">
         <v>115</v>
       </c>
@@ -27055,7 +27054,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="275" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A275" s="11" t="s">
         <v>115</v>
       </c>
@@ -27078,7 +27077,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="276" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A276" s="16" t="s">
         <v>117</v>
       </c>
@@ -27102,7 +27101,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="277" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A277" s="11" t="s">
         <v>117</v>
       </c>
@@ -27125,7 +27124,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="278" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A278" s="11" t="s">
         <v>117</v>
       </c>
@@ -27148,7 +27147,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="279" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A279" s="16" t="s">
         <v>119</v>
       </c>
@@ -27172,7 +27171,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="280" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A280" s="11" t="s">
         <v>119</v>
       </c>
@@ -27195,7 +27194,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="281" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A281" s="11" t="s">
         <v>119</v>
       </c>
@@ -27218,7 +27217,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="282" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A282" s="16" t="s">
         <v>121</v>
       </c>
@@ -27242,7 +27241,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="283" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A283" s="11" t="s">
         <v>121</v>
       </c>
@@ -27265,7 +27264,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="284" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A284" s="11" t="s">
         <v>121</v>
       </c>
@@ -27288,7 +27287,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="285" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A285" s="11" t="s">
         <v>121</v>
       </c>
@@ -27311,7 +27310,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="286" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A286" s="11" t="s">
         <v>121</v>
       </c>
@@ -27334,7 +27333,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="287" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A287" s="11" t="s">
         <v>121</v>
       </c>
@@ -27357,7 +27356,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="288" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A288" s="11" t="s">
         <v>121</v>
       </c>
@@ -27380,7 +27379,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="289" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A289" s="11" t="s">
         <v>121</v>
       </c>
@@ -27403,7 +27402,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="290" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A290" s="11" t="s">
         <v>121</v>
       </c>
@@ -27426,7 +27425,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="291" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A291" s="11" t="s">
         <v>121</v>
       </c>
@@ -27449,7 +27448,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="292" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A292" s="11" t="s">
         <v>121</v>
       </c>
@@ -27472,7 +27471,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="293" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A293" s="11" t="s">
         <v>121</v>
       </c>
@@ -27495,7 +27494,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="294" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A294" s="11" t="s">
         <v>121</v>
       </c>
@@ -27518,7 +27517,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="295" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A295" s="11" t="s">
         <v>121</v>
       </c>
@@ -27541,7 +27540,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="296" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A296" s="11" t="s">
         <v>121</v>
       </c>
@@ -27564,7 +27563,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="297" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A297" s="11" t="s">
         <v>121</v>
       </c>
@@ -27587,7 +27586,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="298" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A298" s="11" t="s">
         <v>121</v>
       </c>
@@ -27610,7 +27609,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="299" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A299" s="11" t="s">
         <v>121</v>
       </c>
@@ -27633,7 +27632,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="300" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A300" s="11" t="s">
         <v>121</v>
       </c>
@@ -27656,7 +27655,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="301" spans="1:8" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A301" s="11" t="s">
         <v>121</v>
       </c>
@@ -27679,7 +27678,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="302" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A302" s="11" t="s">
         <v>121</v>
       </c>
@@ -27702,7 +27701,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="303" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A303" s="11" t="s">
         <v>121</v>
       </c>
@@ -27725,7 +27724,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="304" spans="1:8" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A304" s="11" t="s">
         <v>121</v>
       </c>
@@ -27748,7 +27747,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="305" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A305" s="11" t="s">
         <v>121</v>
       </c>
@@ -27771,7 +27770,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="306" spans="1:8" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A306" s="11" t="s">
         <v>121</v>
       </c>
@@ -27794,7 +27793,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="307" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A307" s="11" t="s">
         <v>121</v>
       </c>
@@ -27817,7 +27816,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="308" spans="1:8" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A308" s="11" t="s">
         <v>121</v>
       </c>
@@ -27840,7 +27839,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="309" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A309" s="11" t="s">
         <v>121</v>
       </c>
@@ -27863,7 +27862,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="310" spans="1:8" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A310" s="11" t="s">
         <v>121</v>
       </c>
@@ -27886,7 +27885,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="311" spans="1:8" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A311" s="11" t="s">
         <v>121</v>
       </c>
@@ -27909,7 +27908,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="312" spans="1:8" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A312" s="11" t="s">
         <v>121</v>
       </c>
@@ -27932,7 +27931,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="313" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A313" s="11" t="s">
         <v>121</v>
       </c>
@@ -27955,7 +27954,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="314" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A314" s="18" t="s">
         <v>123</v>
       </c>
@@ -27979,7 +27978,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="315" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A315" s="4" t="s">
         <v>123</v>
       </c>
@@ -28002,7 +28001,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="316" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A316" s="4" t="s">
         <v>123</v>
       </c>
@@ -28025,7 +28024,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="317" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A317" s="18" t="s">
         <v>125</v>
       </c>
@@ -28049,7 +28048,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="318" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A318" s="4" t="s">
         <v>125</v>
       </c>
@@ -28072,7 +28071,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="319" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A319" s="4" t="s">
         <v>125</v>
       </c>
@@ -28095,7 +28094,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="320" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A320" s="18" t="s">
         <v>127</v>
       </c>
@@ -28113,7 +28112,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="321" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A321" s="18" t="s">
         <v>149</v>
       </c>
@@ -28131,7 +28130,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="322" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A322" s="18" t="s">
         <v>153</v>
       </c>
@@ -28149,7 +28148,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="323" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A323" s="18" t="s">
         <v>155</v>
       </c>
@@ -28167,7 +28166,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="324" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A324" s="18" t="s">
         <v>157</v>
       </c>
@@ -28185,7 +28184,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="325" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A325" s="18" t="s">
         <v>159</v>
       </c>
@@ -28203,7 +28202,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="326" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A326" s="18" t="s">
         <v>161</v>
       </c>
@@ -28221,7 +28220,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="327" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A327" s="18" t="s">
         <v>163</v>
       </c>
@@ -28239,7 +28238,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="328" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A328" s="18" t="s">
         <v>165</v>
       </c>
@@ -28257,7 +28256,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="329" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A329" s="18" t="s">
         <v>129</v>
       </c>
@@ -28275,7 +28274,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="330" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A330" s="18" t="s">
         <v>131</v>
       </c>
@@ -28293,7 +28292,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="331" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A331" s="18" t="s">
         <v>133</v>
       </c>
@@ -28311,7 +28310,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="332" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A332" s="18" t="s">
         <v>135</v>
       </c>
@@ -28329,7 +28328,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="333" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A333" s="18" t="s">
         <v>137</v>
       </c>
@@ -28347,7 +28346,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="334" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A334" s="18" t="s">
         <v>139</v>
       </c>
@@ -28365,7 +28364,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="335" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A335" s="18" t="s">
         <v>141</v>
       </c>
@@ -28383,7 +28382,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="336" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A336" s="18" t="s">
         <v>143</v>
       </c>
@@ -28401,7 +28400,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="337" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A337" s="18" t="s">
         <v>145</v>
       </c>
@@ -28419,7 +28418,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="338" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A338" s="18" t="s">
         <v>147</v>
       </c>
@@ -28437,7 +28436,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="339" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A339" s="18" t="s">
         <v>151</v>
       </c>
@@ -28455,7 +28454,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="340" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A340" s="16" t="s">
         <v>167</v>
       </c>
@@ -28479,7 +28478,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="341" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A341" s="11" t="s">
         <v>167</v>
       </c>
@@ -28502,7 +28501,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="342" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A342" s="11" t="s">
         <v>167</v>
       </c>
@@ -28525,7 +28524,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="343" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A343" s="18" t="s">
         <v>168</v>
       </c>
@@ -28543,7 +28542,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="344" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A344" s="18" t="s">
         <v>169</v>
       </c>
@@ -28561,7 +28560,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="345" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A345" s="18" t="s">
         <v>170</v>
       </c>
@@ -28579,7 +28578,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="346" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A346" s="18" t="s">
         <v>172</v>
       </c>
@@ -28597,7 +28596,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="347" spans="1:8" s="20" customFormat="1" ht="165" hidden="1" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:8" s="20" customFormat="1" ht="165" x14ac:dyDescent="0.25">
       <c r="A347" s="18" t="s">
         <v>174</v>
       </c>
@@ -28615,7 +28614,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="348" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A348" s="18" t="s">
         <v>176</v>
       </c>
@@ -28633,7 +28632,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="349" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A349" s="16" t="s">
         <v>178</v>
       </c>
@@ -28657,7 +28656,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="350" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A350" s="11" t="s">
         <v>178</v>
       </c>
@@ -28680,7 +28679,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="351" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A351" s="11" t="s">
         <v>178</v>
       </c>
@@ -28703,7 +28702,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="352" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A352" s="11" t="s">
         <v>178</v>
       </c>
@@ -28726,7 +28725,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="353" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A353" s="11" t="s">
         <v>178</v>
       </c>
@@ -28749,7 +28748,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="354" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A354" s="11" t="s">
         <v>178</v>
       </c>
@@ -28772,7 +28771,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="355" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A355" s="11" t="s">
         <v>178</v>
       </c>
@@ -28795,7 +28794,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="356" spans="1:9" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:9" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A356" s="16" t="s">
         <v>180</v>
       </c>
@@ -28813,7 +28812,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="357" spans="1:9" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:9" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A357" s="16" t="s">
         <v>182</v>
       </c>
@@ -28831,7 +28830,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="358" spans="1:9" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:9" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A358" s="18" t="s">
         <v>183</v>
       </c>
@@ -28855,7 +28854,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="359" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A359" s="4" t="s">
         <v>183</v>
       </c>
@@ -28878,7 +28877,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="360" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A360" s="4" t="s">
         <v>183</v>
       </c>
@@ -28901,7 +28900,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="361" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A361" s="4" t="s">
         <v>183</v>
       </c>
@@ -28927,7 +28926,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="362" spans="1:9" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:9" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A362" s="18" t="s">
         <v>651</v>
       </c>
@@ -28945,7 +28944,7 @@
         <v>847</v>
       </c>
     </row>
-    <row r="363" spans="1:9" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:9" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A363" s="18" t="s">
         <v>527</v>
       </c>
@@ -28963,7 +28962,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="364" spans="1:9" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:9" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A364" s="18" t="s">
         <v>185</v>
       </c>
@@ -28981,7 +28980,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="365" spans="1:9" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:9" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A365" s="18" t="s">
         <v>186</v>
       </c>
@@ -28999,7 +28998,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="366" spans="1:9" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:9" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A366" s="18" t="s">
         <v>191</v>
       </c>
@@ -29017,7 +29016,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="367" spans="1:9" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:9" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A367" s="16" t="s">
         <v>197</v>
       </c>
@@ -29041,7 +29040,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="368" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A368" s="11" t="s">
         <v>197</v>
       </c>
@@ -29064,7 +29063,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="369" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A369" s="11" t="s">
         <v>197</v>
       </c>
@@ -29087,7 +29086,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="370" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A370" s="11" t="s">
         <v>197</v>
       </c>
@@ -29110,7 +29109,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="371" spans="1:8" s="20" customFormat="1" ht="315" hidden="1" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:8" s="20" customFormat="1" ht="315" x14ac:dyDescent="0.25">
       <c r="A371" s="18" t="s">
         <v>199</v>
       </c>
@@ -29128,7 +29127,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="372" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A372" s="18" t="s">
         <v>529</v>
       </c>
@@ -29147,13 +29146,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I372" xr:uid="{51D60DD1-DC0B-4658-A996-7DC0B41964ED}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="cod_text_1"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:I372" xr:uid="{51D60DD1-DC0B-4658-A996-7DC0B41964ED}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Resources/Admin/Crosswalks and Schemas.xlsx
+++ b/Resources/Admin/Crosswalks and Schemas.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SHDTJB\Documents\LocalSave\Code\R\GitHub\WA-DOH-CHS-Death-Files-ETL\Resources\Admin\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BB99517-3EED-42C1-8B9D-B840984D62DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39ED779F-B821-4E50-BD76-8FF408AC5888}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20520" yWindow="-16365" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8280" yWindow="-16320" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="3" r:id="rId1"/>
@@ -20687,7 +20687,6 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51D60DD1-DC0B-4658-A996-7DC0B41964ED}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:I372"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -20731,7 +20730,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:9" s="20" customFormat="1" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" s="20" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A2" s="16" t="s">
         <v>4</v>
       </c>
@@ -20749,7 +20748,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="3" spans="1:9" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="16" t="s">
         <v>676</v>
       </c>
@@ -20775,7 +20774,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="4" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
         <v>676</v>
       </c>
@@ -20801,7 +20800,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="5" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
         <v>676</v>
       </c>
@@ -20827,7 +20826,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="6" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>676</v>
       </c>
@@ -20853,7 +20852,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="7" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>676</v>
       </c>
@@ -20879,7 +20878,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="8" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
         <v>676</v>
       </c>
@@ -20905,7 +20904,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="9" spans="1:9" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="16" t="s">
         <v>682</v>
       </c>
@@ -20931,7 +20930,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="10" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
         <v>682</v>
       </c>
@@ -20957,7 +20956,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="11" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
         <v>682</v>
       </c>
@@ -20983,7 +20982,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="12" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
         <v>682</v>
       </c>
@@ -21009,7 +21008,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="13" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>682</v>
       </c>
@@ -21035,7 +21034,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="14" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
         <v>682</v>
       </c>
@@ -21061,7 +21060,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="15" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
         <v>682</v>
       </c>
@@ -21087,7 +21086,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="16" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
         <v>682</v>
       </c>
@@ -21113,7 +21112,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="17" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
         <v>682</v>
       </c>
@@ -21139,7 +21138,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="18" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
         <v>682</v>
       </c>
@@ -21165,7 +21164,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="19" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
         <v>682</v>
       </c>
@@ -21191,7 +21190,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="20" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="16" t="s">
         <v>692</v>
       </c>
@@ -21217,7 +21216,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="21" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
         <v>692</v>
       </c>
@@ -21243,7 +21242,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="22" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
         <v>692</v>
       </c>
@@ -21269,7 +21268,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="23" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="11" t="s">
         <v>692</v>
       </c>
@@ -21295,7 +21294,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="24" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
         <v>692</v>
       </c>
@@ -21321,7 +21320,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="25" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
         <v>692</v>
       </c>
@@ -21347,7 +21346,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="26" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="11" t="s">
         <v>692</v>
       </c>
@@ -21373,7 +21372,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="27" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
         <v>692</v>
       </c>
@@ -21399,7 +21398,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="28" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="11" t="s">
         <v>692</v>
       </c>
@@ -21425,7 +21424,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="29" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
         <v>692</v>
       </c>
@@ -21451,7 +21450,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="11" t="s">
         <v>692</v>
       </c>
@@ -21477,7 +21476,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="31" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="11" t="s">
         <v>692</v>
       </c>
@@ -21503,7 +21502,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="32" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="11" t="s">
         <v>692</v>
       </c>
@@ -21529,7 +21528,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="33" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="11" t="s">
         <v>692</v>
       </c>
@@ -21555,7 +21554,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="34" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="11" t="s">
         <v>692</v>
       </c>
@@ -21581,7 +21580,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="35" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="11" t="s">
         <v>692</v>
       </c>
@@ -21607,7 +21606,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="36" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="11" t="s">
         <v>692</v>
       </c>
@@ -21633,7 +21632,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="37" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" s="11" t="s">
         <v>692</v>
       </c>
@@ -21659,7 +21658,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="38" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="11" t="s">
         <v>692</v>
       </c>
@@ -21685,7 +21684,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="39" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="11" t="s">
         <v>692</v>
       </c>
@@ -21711,7 +21710,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="40" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="16" t="s">
         <v>710</v>
       </c>
@@ -21737,7 +21736,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="41" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="11" t="s">
         <v>710</v>
       </c>
@@ -21763,7 +21762,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="42" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="11" t="s">
         <v>710</v>
       </c>
@@ -21789,7 +21788,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="43" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="11" t="s">
         <v>710</v>
       </c>
@@ -21815,7 +21814,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="44" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="11" t="s">
         <v>710</v>
       </c>
@@ -21841,7 +21840,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="45" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" s="11" t="s">
         <v>710</v>
       </c>
@@ -21867,7 +21866,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="46" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" s="11" t="s">
         <v>710</v>
       </c>
@@ -21893,7 +21892,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="47" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" s="11" t="s">
         <v>710</v>
       </c>
@@ -21919,7 +21918,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="48" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" s="11" t="s">
         <v>710</v>
       </c>
@@ -21945,7 +21944,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="49" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" s="11" t="s">
         <v>710</v>
       </c>
@@ -21971,7 +21970,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="50" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" s="11" t="s">
         <v>710</v>
       </c>
@@ -21997,7 +21996,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="51" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" s="11" t="s">
         <v>710</v>
       </c>
@@ -22023,7 +22022,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="52" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" s="11" t="s">
         <v>710</v>
       </c>
@@ -22049,7 +22048,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="53" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" s="11" t="s">
         <v>710</v>
       </c>
@@ -22075,7 +22074,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="54" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" s="11" t="s">
         <v>710</v>
       </c>
@@ -22101,7 +22100,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="55" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" s="11" t="s">
         <v>710</v>
       </c>
@@ -22127,7 +22126,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="56" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" s="11" t="s">
         <v>710</v>
       </c>
@@ -22153,7 +22152,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="57" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" s="11" t="s">
         <v>710</v>
       </c>
@@ -22179,7 +22178,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="58" spans="1:8" s="20" customFormat="1" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:8" s="20" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A58" s="16" t="s">
         <v>6</v>
       </c>
@@ -22203,7 +22202,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="59" spans="1:8" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A59" s="11" t="s">
         <v>6</v>
       </c>
@@ -22226,7 +22225,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="60" spans="1:8" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A60" s="11" t="s">
         <v>6</v>
       </c>
@@ -22249,7 +22248,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="61" spans="1:8" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A61" s="11" t="s">
         <v>6</v>
       </c>
@@ -22272,7 +22271,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="62" spans="1:8" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A62" s="11" t="s">
         <v>6</v>
       </c>
@@ -22295,7 +22294,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="63" spans="1:8" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A63" s="11" t="s">
         <v>6</v>
       </c>
@@ -22318,7 +22317,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="64" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A64" s="16" t="s">
         <v>7</v>
       </c>
@@ -22336,7 +22335,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="65" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A65" s="16" t="s">
         <v>523</v>
       </c>
@@ -22354,7 +22353,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="66" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A66" s="16" t="s">
         <v>9</v>
       </c>
@@ -22378,7 +22377,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="67" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" s="11" t="s">
         <v>9</v>
       </c>
@@ -22401,7 +22400,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="68" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" s="11" t="s">
         <v>9</v>
       </c>
@@ -22424,7 +22423,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="69" spans="1:8" s="20" customFormat="1" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:8" s="20" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A69" s="16" t="s">
         <v>10</v>
       </c>
@@ -22448,7 +22447,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="70" spans="1:8" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A70" s="11" t="s">
         <v>10</v>
       </c>
@@ -22471,7 +22470,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="71" spans="1:8" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A71" s="11" t="s">
         <v>10</v>
       </c>
@@ -22494,7 +22493,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="72" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A72" s="16" t="s">
         <v>12</v>
       </c>
@@ -22516,7 +22515,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="73" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A73" s="16" t="s">
         <v>14</v>
       </c>
@@ -22538,7 +22537,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="74" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A74" s="18" t="s">
         <v>16</v>
       </c>
@@ -22562,7 +22561,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="75" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" s="4" t="s">
         <v>16</v>
       </c>
@@ -22585,7 +22584,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="76" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
         <v>16</v>
       </c>
@@ -22608,7 +22607,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="77" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" s="4" t="s">
         <v>16</v>
       </c>
@@ -22631,7 +22630,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="78" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
         <v>16</v>
       </c>
@@ -22654,7 +22653,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="79" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" s="4" t="s">
         <v>16</v>
       </c>
@@ -22677,7 +22676,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="80" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
         <v>16</v>
       </c>
@@ -22700,7 +22699,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="81" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81" s="4" t="s">
         <v>16</v>
       </c>
@@ -22723,7 +22722,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="82" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
         <v>16</v>
       </c>
@@ -22764,7 +22763,7 @@
         <v>846</v>
       </c>
     </row>
-    <row r="84" spans="1:9" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:9" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A84" s="33" t="s">
         <v>630</v>
       </c>
@@ -22782,7 +22781,7 @@
         <v>846</v>
       </c>
     </row>
-    <row r="85" spans="1:9" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:9" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A85" s="33" t="s">
         <v>631</v>
       </c>
@@ -22800,7 +22799,7 @@
         <v>846</v>
       </c>
     </row>
-    <row r="86" spans="1:9" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:9" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A86" s="33" t="s">
         <v>632</v>
       </c>
@@ -22818,7 +22817,7 @@
         <v>846</v>
       </c>
     </row>
-    <row r="87" spans="1:9" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:9" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A87" s="33" t="s">
         <v>633</v>
       </c>
@@ -22836,7 +22835,7 @@
         <v>846</v>
       </c>
     </row>
-    <row r="88" spans="1:9" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:9" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A88" s="16" t="s">
         <v>525</v>
       </c>
@@ -22855,7 +22854,7 @@
       </c>
       <c r="I88" s="17"/>
     </row>
-    <row r="89" spans="1:9" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:9" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A89" s="16" t="s">
         <v>18</v>
       </c>
@@ -22873,7 +22872,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="90" spans="1:9" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:9" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A90" s="16" t="s">
         <v>20</v>
       </c>
@@ -22891,7 +22890,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="91" spans="1:9" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:9" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A91" s="16" t="s">
         <v>22</v>
       </c>
@@ -22915,7 +22914,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="92" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A92" s="11" t="s">
         <v>22</v>
       </c>
@@ -22938,7 +22937,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="93" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A93" s="11" t="s">
         <v>22</v>
       </c>
@@ -22961,7 +22960,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="94" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A94" s="11" t="s">
         <v>22</v>
       </c>
@@ -22984,7 +22983,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="95" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A95" s="11" t="s">
         <v>22</v>
       </c>
@@ -23007,7 +23006,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="96" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A96" s="11" t="s">
         <v>22</v>
       </c>
@@ -23030,7 +23029,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="97" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97" s="11" t="s">
         <v>22</v>
       </c>
@@ -23053,7 +23052,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="98" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A98" s="16" t="s">
         <v>24</v>
       </c>
@@ -23071,7 +23070,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="99" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A99" s="16" t="s">
         <v>26</v>
       </c>
@@ -23089,7 +23088,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="100" spans="1:8" s="20" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:8" s="20" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A100" s="16" t="s">
         <v>27</v>
       </c>
@@ -23107,7 +23106,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="101" spans="1:8" s="20" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:8" s="20" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A101" s="16" t="s">
         <v>28</v>
       </c>
@@ -23125,7 +23124,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="102" spans="1:8" s="20" customFormat="1" ht="180" hidden="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:8" s="20" customFormat="1" ht="180" x14ac:dyDescent="0.25">
       <c r="A102" s="16" t="s">
         <v>30</v>
       </c>
@@ -23143,7 +23142,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="103" spans="1:8" s="20" customFormat="1" ht="180" hidden="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:8" s="20" customFormat="1" ht="180" x14ac:dyDescent="0.25">
       <c r="A103" s="16" t="s">
         <v>32</v>
       </c>
@@ -23161,7 +23160,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="104" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A104" s="16" t="s">
         <v>34</v>
       </c>
@@ -23179,7 +23178,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="105" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A105" s="16" t="s">
         <v>36</v>
       </c>
@@ -23197,7 +23196,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="106" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A106" s="16" t="s">
         <v>38</v>
       </c>
@@ -23215,7 +23214,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="107" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A107" s="16" t="s">
         <v>40</v>
       </c>
@@ -23239,7 +23238,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="108" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A108" s="11" t="s">
         <v>40</v>
       </c>
@@ -23262,7 +23261,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="109" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A109" s="11" t="s">
         <v>40</v>
       </c>
@@ -23285,7 +23284,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="110" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A110" s="11" t="s">
         <v>40</v>
       </c>
@@ -23308,7 +23307,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="111" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A111" s="11" t="s">
         <v>40</v>
       </c>
@@ -23331,7 +23330,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="112" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A112" s="11" t="s">
         <v>40</v>
       </c>
@@ -23354,7 +23353,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="113" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A113" s="11" t="s">
         <v>40</v>
       </c>
@@ -23377,7 +23376,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="114" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A114" s="11" t="s">
         <v>40</v>
       </c>
@@ -23400,7 +23399,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="115" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A115" s="16" t="s">
         <v>42</v>
       </c>
@@ -23418,7 +23417,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="116" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A116" s="16" t="s">
         <v>44</v>
       </c>
@@ -23444,7 +23443,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="117" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A117" s="11" t="s">
         <v>44</v>
       </c>
@@ -23470,7 +23469,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="118" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A118" s="11" t="s">
         <v>44</v>
       </c>
@@ -23496,7 +23495,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="119" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A119" s="11" t="s">
         <v>44</v>
       </c>
@@ -23522,7 +23521,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="120" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A120" s="11" t="s">
         <v>44</v>
       </c>
@@ -23548,7 +23547,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="121" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A121" s="11" t="s">
         <v>44</v>
       </c>
@@ -23574,7 +23573,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="122" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A122" s="11" t="s">
         <v>44</v>
       </c>
@@ -23600,7 +23599,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="123" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A123" s="11" t="s">
         <v>44</v>
       </c>
@@ -23626,7 +23625,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="124" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A124" s="11" t="s">
         <v>44</v>
       </c>
@@ -23652,7 +23651,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="125" spans="1:8" s="20" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:8" s="20" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="16" t="s">
         <v>46</v>
       </c>
@@ -23678,7 +23677,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="126" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A126" s="11" t="s">
         <v>46</v>
       </c>
@@ -23704,7 +23703,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="127" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A127" s="11" t="s">
         <v>46</v>
       </c>
@@ -23730,7 +23729,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="128" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A128" s="11" t="s">
         <v>46</v>
       </c>
@@ -23756,7 +23755,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="129" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A129" s="11" t="s">
         <v>46</v>
       </c>
@@ -23782,7 +23781,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="130" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A130" s="11" t="s">
         <v>46</v>
       </c>
@@ -23808,7 +23807,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="131" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A131" s="11" t="s">
         <v>46</v>
       </c>
@@ -23834,7 +23833,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="132" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A132" s="11" t="s">
         <v>46</v>
       </c>
@@ -23860,7 +23859,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="133" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A133" s="11" t="s">
         <v>46</v>
       </c>
@@ -23886,7 +23885,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="134" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A134" s="11" t="s">
         <v>46</v>
       </c>
@@ -23912,7 +23911,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="135" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A135" s="18" t="s">
         <v>391</v>
       </c>
@@ -23930,7 +23929,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="136" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A136" s="18" t="s">
         <v>713</v>
       </c>
@@ -23948,7 +23947,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="137" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A137" s="4" t="s">
         <v>713</v>
       </c>
@@ -23962,7 +23961,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="138" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A138" s="16" t="s">
         <v>48</v>
       </c>
@@ -23986,7 +23985,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="139" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A139" s="11" t="s">
         <v>48</v>
       </c>
@@ -24009,7 +24008,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="140" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A140" s="11" t="s">
         <v>48</v>
       </c>
@@ -24032,7 +24031,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="141" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A141" s="16" t="s">
         <v>50</v>
       </c>
@@ -24056,7 +24055,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="142" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A142" s="11" t="s">
         <v>50</v>
       </c>
@@ -24079,7 +24078,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="143" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A143" s="11" t="s">
         <v>50</v>
       </c>
@@ -24102,7 +24101,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="144" spans="1:8" s="20" customFormat="1" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:8" s="20" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A144" s="16" t="s">
         <v>52</v>
       </c>
@@ -24126,7 +24125,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="145" spans="1:8" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A145" s="11" t="s">
         <v>52</v>
       </c>
@@ -24149,7 +24148,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="146" spans="1:8" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A146" s="11" t="s">
         <v>52</v>
       </c>
@@ -24172,7 +24171,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="147" spans="1:8" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A147" s="11" t="s">
         <v>52</v>
       </c>
@@ -24195,7 +24194,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="148" spans="1:8" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A148" s="11" t="s">
         <v>52</v>
       </c>
@@ -24218,7 +24217,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="149" spans="1:8" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A149" s="11" t="s">
         <v>52</v>
       </c>
@@ -24241,7 +24240,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="150" spans="1:8" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A150" s="11" t="s">
         <v>52</v>
       </c>
@@ -24264,7 +24263,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="151" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A151" s="16" t="s">
         <v>54</v>
       </c>
@@ -24288,7 +24287,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="152" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A152" s="11" t="s">
         <v>54</v>
       </c>
@@ -24311,7 +24310,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="153" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A153" s="11" t="s">
         <v>54</v>
       </c>
@@ -24334,7 +24333,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="154" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A154" s="16" t="s">
         <v>56</v>
       </c>
@@ -24358,7 +24357,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="155" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A155" s="11" t="s">
         <v>56</v>
       </c>
@@ -24381,7 +24380,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="156" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A156" s="11" t="s">
         <v>56</v>
       </c>
@@ -24404,7 +24403,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="157" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A157" s="16" t="s">
         <v>58</v>
       </c>
@@ -24428,7 +24427,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="158" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A158" s="11" t="s">
         <v>58</v>
       </c>
@@ -24451,7 +24450,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="159" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A159" s="11" t="s">
         <v>58</v>
       </c>
@@ -24474,7 +24473,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="160" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A160" s="16" t="s">
         <v>60</v>
       </c>
@@ -24492,7 +24491,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="161" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A161" s="16" t="s">
         <v>62</v>
       </c>
@@ -24510,7 +24509,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="162" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A162" s="16" t="s">
         <v>64</v>
       </c>
@@ -24534,7 +24533,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="163" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A163" s="11" t="s">
         <v>64</v>
       </c>
@@ -24557,7 +24556,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="164" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A164" s="11" t="s">
         <v>64</v>
       </c>
@@ -24580,7 +24579,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="165" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A165" s="11" t="s">
         <v>64</v>
       </c>
@@ -24603,7 +24602,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="166" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A166" s="11" t="s">
         <v>64</v>
       </c>
@@ -24626,7 +24625,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="167" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A167" s="11" t="s">
         <v>64</v>
       </c>
@@ -24649,7 +24648,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="168" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A168" s="11" t="s">
         <v>64</v>
       </c>
@@ -24672,7 +24671,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="169" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A169" s="11" t="s">
         <v>64</v>
       </c>
@@ -24695,7 +24694,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="170" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A170" s="11" t="s">
         <v>64</v>
       </c>
@@ -24718,7 +24717,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="171" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A171" s="11" t="s">
         <v>64</v>
       </c>
@@ -24741,7 +24740,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="172" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A172" s="16" t="s">
         <v>66</v>
       </c>
@@ -24765,7 +24764,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="173" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A173" s="11" t="s">
         <v>66</v>
       </c>
@@ -24788,7 +24787,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="174" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A174" s="11" t="s">
         <v>66</v>
       </c>
@@ -24811,7 +24810,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="175" spans="1:8" s="20" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:8" s="20" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A175" s="16" t="s">
         <v>67</v>
       </c>
@@ -24829,7 +24828,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="176" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A176" s="16" t="s">
         <v>68</v>
       </c>
@@ -24847,7 +24846,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="177" spans="1:9" s="20" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:9" s="20" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A177" s="16" t="s">
         <v>69</v>
       </c>
@@ -24865,7 +24864,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="178" spans="1:9" s="20" customFormat="1" ht="180" hidden="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:9" s="20" customFormat="1" ht="180" x14ac:dyDescent="0.25">
       <c r="A178" s="16" t="s">
         <v>71</v>
       </c>
@@ -24883,7 +24882,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="179" spans="1:9" s="20" customFormat="1" ht="180" hidden="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:9" s="20" customFormat="1" ht="180" x14ac:dyDescent="0.25">
       <c r="A179" s="16" t="s">
         <v>73</v>
       </c>
@@ -24901,7 +24900,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="180" spans="1:9" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:9" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A180" s="16" t="s">
         <v>634</v>
       </c>
@@ -24919,7 +24918,7 @@
         <v>846</v>
       </c>
     </row>
-    <row r="181" spans="1:9" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:9" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A181" s="16" t="s">
         <v>75</v>
       </c>
@@ -24937,7 +24936,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="182" spans="1:9" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:9" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A182" s="16" t="s">
         <v>77</v>
       </c>
@@ -24955,7 +24954,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="183" spans="1:9" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:9" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A183" s="16" t="s">
         <v>79</v>
       </c>
@@ -24973,7 +24972,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="184" spans="1:9" s="20" customFormat="1" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:9" s="20" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A184" s="16" t="s">
         <v>81</v>
       </c>
@@ -24991,7 +24990,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="185" spans="1:9" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:9" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A185" s="16" t="s">
         <v>83</v>
       </c>
@@ -25015,7 +25014,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="186" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A186" s="11" t="s">
         <v>83</v>
       </c>
@@ -25038,7 +25037,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="187" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A187" s="11" t="s">
         <v>83</v>
       </c>
@@ -25061,7 +25060,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="188" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A188" s="11" t="s">
         <v>83</v>
       </c>
@@ -25084,7 +25083,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="189" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A189" s="11" t="s">
         <v>83</v>
       </c>
@@ -25107,7 +25106,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="190" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A190" s="11" t="s">
         <v>83</v>
       </c>
@@ -25130,7 +25129,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="191" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A191" s="11" t="s">
         <v>83</v>
       </c>
@@ -25156,7 +25155,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="192" spans="1:9" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:9" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A192" s="16" t="s">
         <v>85</v>
       </c>
@@ -25180,7 +25179,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="193" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A193" s="11" t="s">
         <v>85</v>
       </c>
@@ -25203,7 +25202,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="194" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A194" s="11" t="s">
         <v>85</v>
       </c>
@@ -25226,7 +25225,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="195" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A195" s="11" t="s">
         <v>85</v>
       </c>
@@ -25249,7 +25248,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="196" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A196" s="11" t="s">
         <v>85</v>
       </c>
@@ -25272,7 +25271,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="197" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A197" s="11" t="s">
         <v>85</v>
       </c>
@@ -25295,7 +25294,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="198" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A198" s="11" t="s">
         <v>85</v>
       </c>
@@ -25318,7 +25317,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="199" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A199" s="16" t="s">
         <v>87</v>
       </c>
@@ -25342,7 +25341,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="200" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A200" s="11" t="s">
         <v>87</v>
       </c>
@@ -25365,7 +25364,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="201" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A201" s="11" t="s">
         <v>87</v>
       </c>
@@ -25388,7 +25387,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="202" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A202" s="16" t="s">
         <v>647</v>
       </c>
@@ -25406,7 +25405,7 @@
         <v>847</v>
       </c>
     </row>
-    <row r="203" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A203" s="16" t="s">
         <v>648</v>
       </c>
@@ -25424,7 +25423,7 @@
         <v>847</v>
       </c>
     </row>
-    <row r="204" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A204" s="16" t="s">
         <v>649</v>
       </c>
@@ -25442,7 +25441,7 @@
         <v>847</v>
       </c>
     </row>
-    <row r="205" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A205" s="16" t="s">
         <v>650</v>
       </c>
@@ -25460,7 +25459,7 @@
         <v>847</v>
       </c>
     </row>
-    <row r="206" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A206" s="16" t="s">
         <v>89</v>
       </c>
@@ -25478,7 +25477,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="207" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A207" s="16" t="s">
         <v>91</v>
       </c>
@@ -25502,7 +25501,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="208" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A208" s="11" t="s">
         <v>91</v>
       </c>
@@ -25525,7 +25524,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="209" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A209" s="11" t="s">
         <v>91</v>
       </c>
@@ -25548,7 +25547,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="210" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A210" s="11" t="s">
         <v>91</v>
       </c>
@@ -25571,7 +25570,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="211" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A211" s="11" t="s">
         <v>91</v>
       </c>
@@ -25594,7 +25593,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="212" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A212" s="11" t="s">
         <v>91</v>
       </c>
@@ -25617,7 +25616,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="213" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A213" s="11" t="s">
         <v>91</v>
       </c>
@@ -25640,7 +25639,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="214" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A214" s="11" t="s">
         <v>91</v>
       </c>
@@ -25663,7 +25662,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="215" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A215" s="11" t="s">
         <v>91</v>
       </c>
@@ -25686,7 +25685,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="216" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A216" s="11" t="s">
         <v>91</v>
       </c>
@@ -25709,7 +25708,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="217" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A217" s="16" t="s">
         <v>93</v>
       </c>
@@ -25733,7 +25732,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="218" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A218" s="11" t="s">
         <v>93</v>
       </c>
@@ -25756,7 +25755,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="219" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A219" s="11" t="s">
         <v>93</v>
       </c>
@@ -25779,7 +25778,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="220" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A220" s="11" t="s">
         <v>93</v>
       </c>
@@ -25802,7 +25801,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="221" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A221" s="11" t="s">
         <v>93</v>
       </c>
@@ -25825,7 +25824,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="222" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A222" s="11" t="s">
         <v>93</v>
       </c>
@@ -25848,7 +25847,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="223" spans="1:8" s="20" customFormat="1" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:8" s="20" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A223" s="16" t="s">
         <v>716</v>
       </c>
@@ -25872,7 +25871,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="224" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A224" s="11" t="s">
         <v>716</v>
       </c>
@@ -25895,7 +25894,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="225" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A225" s="11" t="s">
         <v>716</v>
       </c>
@@ -25918,7 +25917,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="226" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A226" s="11" t="s">
         <v>716</v>
       </c>
@@ -25941,7 +25940,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="227" spans="1:8" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A227" s="11" t="s">
         <v>716</v>
       </c>
@@ -25964,7 +25963,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="228" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A228" s="11" t="s">
         <v>716</v>
       </c>
@@ -25987,7 +25986,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="229" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A229" s="16" t="s">
         <v>95</v>
       </c>
@@ -26011,7 +26010,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="230" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A230" s="11" t="s">
         <v>95</v>
       </c>
@@ -26034,7 +26033,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="231" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A231" s="11" t="s">
         <v>95</v>
       </c>
@@ -26057,7 +26056,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="232" spans="1:8" s="20" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:8" s="20" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A232" s="16" t="s">
         <v>674</v>
       </c>
@@ -26081,7 +26080,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="233" spans="1:8" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A233" s="11" t="s">
         <v>674</v>
       </c>
@@ -26104,7 +26103,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="234" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A234" s="16" t="s">
         <v>97</v>
       </c>
@@ -26128,7 +26127,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="235" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A235" s="11" t="s">
         <v>97</v>
       </c>
@@ -26151,7 +26150,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="236" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A236" s="11" t="s">
         <v>97</v>
       </c>
@@ -26174,7 +26173,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="237" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A237" s="16" t="s">
         <v>99</v>
       </c>
@@ -26198,7 +26197,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="238" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A238" s="11" t="s">
         <v>99</v>
       </c>
@@ -26221,7 +26220,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="239" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A239" s="11" t="s">
         <v>99</v>
       </c>
@@ -26244,7 +26243,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="240" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A240" s="16" t="s">
         <v>101</v>
       </c>
@@ -26268,7 +26267,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="241" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A241" s="11" t="s">
         <v>101</v>
       </c>
@@ -26291,7 +26290,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="242" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A242" s="11" t="s">
         <v>101</v>
       </c>
@@ -26314,7 +26313,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="243" spans="1:8" s="20" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:8" s="20" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A243" s="16" t="s">
         <v>673</v>
       </c>
@@ -26332,7 +26331,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="244" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A244" s="16" t="s">
         <v>714</v>
       </c>
@@ -26356,7 +26355,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="245" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A245" s="11" t="s">
         <v>714</v>
       </c>
@@ -26379,7 +26378,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="246" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A246" s="16" t="s">
         <v>722</v>
       </c>
@@ -26403,7 +26402,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="247" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A247" s="11" t="s">
         <v>722</v>
       </c>
@@ -26426,7 +26425,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="248" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A248" s="11" t="s">
         <v>722</v>
       </c>
@@ -26449,7 +26448,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="249" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A249" s="11" t="s">
         <v>722</v>
       </c>
@@ -26472,7 +26471,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="250" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A250" s="11" t="s">
         <v>722</v>
       </c>
@@ -26495,7 +26494,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="251" spans="1:8" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A251" s="11" t="s">
         <v>722</v>
       </c>
@@ -26518,7 +26517,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="252" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A252" s="11" t="s">
         <v>722</v>
       </c>
@@ -26541,7 +26540,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="253" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A253" s="16" t="s">
         <v>103</v>
       </c>
@@ -26565,7 +26564,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="254" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A254" s="11" t="s">
         <v>103</v>
       </c>
@@ -26588,7 +26587,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="255" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A255" s="11" t="s">
         <v>103</v>
       </c>
@@ -26611,7 +26610,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="256" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A256" s="16" t="s">
         <v>105</v>
       </c>
@@ -26635,7 +26634,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="257" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A257" s="11" t="s">
         <v>105</v>
       </c>
@@ -26658,7 +26657,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="258" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A258" s="11" t="s">
         <v>105</v>
       </c>
@@ -26681,7 +26680,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="259" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A259" s="16" t="s">
         <v>107</v>
       </c>
@@ -26705,7 +26704,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="260" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A260" s="11" t="s">
         <v>107</v>
       </c>
@@ -26728,7 +26727,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="261" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A261" s="11" t="s">
         <v>107</v>
       </c>
@@ -26751,7 +26750,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="262" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A262" s="16" t="s">
         <v>109</v>
       </c>
@@ -26775,7 +26774,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="263" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A263" s="11" t="s">
         <v>109</v>
       </c>
@@ -26798,7 +26797,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="264" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A264" s="11" t="s">
         <v>109</v>
       </c>
@@ -26821,7 +26820,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="265" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A265" s="16" t="s">
         <v>111</v>
       </c>
@@ -26845,7 +26844,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="266" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A266" s="11" t="s">
         <v>111</v>
       </c>
@@ -26868,7 +26867,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="267" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A267" s="11" t="s">
         <v>111</v>
       </c>
@@ -26891,7 +26890,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="268" spans="1:8" s="20" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:8" s="20" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A268" s="16" t="s">
         <v>675</v>
       </c>
@@ -26915,7 +26914,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="269" spans="1:8" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A269" s="11" t="s">
         <v>675</v>
       </c>
@@ -26938,7 +26937,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="270" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A270" s="16" t="s">
         <v>113</v>
       </c>
@@ -26962,7 +26961,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="271" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A271" s="11" t="s">
         <v>113</v>
       </c>
@@ -26985,7 +26984,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="272" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A272" s="11" t="s">
         <v>113</v>
       </c>
@@ -27008,7 +27007,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="273" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A273" s="16" t="s">
         <v>115</v>
       </c>
@@ -27032,7 +27031,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="274" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A274" s="11" t="s">
         <v>115</v>
       </c>
@@ -27055,7 +27054,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="275" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A275" s="11" t="s">
         <v>115</v>
       </c>
@@ -27078,7 +27077,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="276" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A276" s="16" t="s">
         <v>117</v>
       </c>
@@ -27102,7 +27101,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="277" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A277" s="11" t="s">
         <v>117</v>
       </c>
@@ -27125,7 +27124,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="278" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A278" s="11" t="s">
         <v>117</v>
       </c>
@@ -27148,7 +27147,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="279" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A279" s="16" t="s">
         <v>119</v>
       </c>
@@ -27172,7 +27171,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="280" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A280" s="11" t="s">
         <v>119</v>
       </c>
@@ -27195,7 +27194,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="281" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A281" s="11" t="s">
         <v>119</v>
       </c>
@@ -27218,7 +27217,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="282" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A282" s="16" t="s">
         <v>121</v>
       </c>
@@ -27242,7 +27241,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="283" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A283" s="11" t="s">
         <v>121</v>
       </c>
@@ -27265,7 +27264,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="284" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A284" s="11" t="s">
         <v>121</v>
       </c>
@@ -27288,7 +27287,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="285" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A285" s="11" t="s">
         <v>121</v>
       </c>
@@ -27311,7 +27310,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="286" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A286" s="11" t="s">
         <v>121</v>
       </c>
@@ -27334,7 +27333,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="287" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A287" s="11" t="s">
         <v>121</v>
       </c>
@@ -27357,7 +27356,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="288" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A288" s="11" t="s">
         <v>121</v>
       </c>
@@ -27380,7 +27379,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="289" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A289" s="11" t="s">
         <v>121</v>
       </c>
@@ -27403,7 +27402,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="290" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A290" s="11" t="s">
         <v>121</v>
       </c>
@@ -27426,7 +27425,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="291" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A291" s="11" t="s">
         <v>121</v>
       </c>
@@ -27449,7 +27448,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="292" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A292" s="11" t="s">
         <v>121</v>
       </c>
@@ -27472,7 +27471,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="293" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A293" s="11" t="s">
         <v>121</v>
       </c>
@@ -27495,7 +27494,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="294" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A294" s="11" t="s">
         <v>121</v>
       </c>
@@ -27518,7 +27517,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="295" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A295" s="11" t="s">
         <v>121</v>
       </c>
@@ -27541,7 +27540,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="296" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A296" s="11" t="s">
         <v>121</v>
       </c>
@@ -27564,7 +27563,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="297" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A297" s="11" t="s">
         <v>121</v>
       </c>
@@ -27587,7 +27586,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="298" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A298" s="11" t="s">
         <v>121</v>
       </c>
@@ -27610,7 +27609,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="299" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A299" s="11" t="s">
         <v>121</v>
       </c>
@@ -27633,7 +27632,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="300" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A300" s="11" t="s">
         <v>121</v>
       </c>
@@ -27656,7 +27655,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="301" spans="1:8" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A301" s="11" t="s">
         <v>121</v>
       </c>
@@ -27679,7 +27678,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="302" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A302" s="11" t="s">
         <v>121</v>
       </c>
@@ -27702,7 +27701,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="303" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A303" s="11" t="s">
         <v>121</v>
       </c>
@@ -27725,7 +27724,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="304" spans="1:8" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A304" s="11" t="s">
         <v>121</v>
       </c>
@@ -27748,7 +27747,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="305" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A305" s="11" t="s">
         <v>121</v>
       </c>
@@ -27771,7 +27770,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="306" spans="1:8" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A306" s="11" t="s">
         <v>121</v>
       </c>
@@ -27794,7 +27793,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="307" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A307" s="11" t="s">
         <v>121</v>
       </c>
@@ -27817,7 +27816,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="308" spans="1:8" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A308" s="11" t="s">
         <v>121</v>
       </c>
@@ -27840,7 +27839,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="309" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A309" s="11" t="s">
         <v>121</v>
       </c>
@@ -27863,7 +27862,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="310" spans="1:8" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A310" s="11" t="s">
         <v>121</v>
       </c>
@@ -27886,7 +27885,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="311" spans="1:8" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A311" s="11" t="s">
         <v>121</v>
       </c>
@@ -27909,7 +27908,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="312" spans="1:8" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A312" s="11" t="s">
         <v>121</v>
       </c>
@@ -27932,7 +27931,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="313" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A313" s="11" t="s">
         <v>121</v>
       </c>
@@ -27955,7 +27954,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="314" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A314" s="18" t="s">
         <v>123</v>
       </c>
@@ -27979,7 +27978,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="315" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A315" s="4" t="s">
         <v>123</v>
       </c>
@@ -28002,7 +28001,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="316" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A316" s="4" t="s">
         <v>123</v>
       </c>
@@ -28025,7 +28024,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="317" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A317" s="18" t="s">
         <v>125</v>
       </c>
@@ -28049,7 +28048,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="318" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A318" s="4" t="s">
         <v>125</v>
       </c>
@@ -28072,7 +28071,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="319" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A319" s="4" t="s">
         <v>125</v>
       </c>
@@ -28095,7 +28094,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="320" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A320" s="18" t="s">
         <v>127</v>
       </c>
@@ -28113,7 +28112,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="321" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A321" s="18" t="s">
         <v>149</v>
       </c>
@@ -28131,7 +28130,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="322" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A322" s="18" t="s">
         <v>153</v>
       </c>
@@ -28149,7 +28148,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="323" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A323" s="18" t="s">
         <v>155</v>
       </c>
@@ -28167,7 +28166,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="324" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A324" s="18" t="s">
         <v>157</v>
       </c>
@@ -28185,7 +28184,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="325" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A325" s="18" t="s">
         <v>159</v>
       </c>
@@ -28203,7 +28202,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="326" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A326" s="18" t="s">
         <v>161</v>
       </c>
@@ -28221,7 +28220,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="327" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A327" s="18" t="s">
         <v>163</v>
       </c>
@@ -28239,7 +28238,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="328" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A328" s="18" t="s">
         <v>165</v>
       </c>
@@ -28257,7 +28256,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="329" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A329" s="18" t="s">
         <v>129</v>
       </c>
@@ -28275,7 +28274,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="330" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A330" s="18" t="s">
         <v>131</v>
       </c>
@@ -28293,7 +28292,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="331" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A331" s="18" t="s">
         <v>133</v>
       </c>
@@ -28311,7 +28310,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="332" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A332" s="18" t="s">
         <v>135</v>
       </c>
@@ -28329,7 +28328,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="333" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A333" s="18" t="s">
         <v>137</v>
       </c>
@@ -28347,7 +28346,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="334" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A334" s="18" t="s">
         <v>139</v>
       </c>
@@ -28365,7 +28364,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="335" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A335" s="18" t="s">
         <v>141</v>
       </c>
@@ -28383,7 +28382,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="336" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A336" s="18" t="s">
         <v>143</v>
       </c>
@@ -28401,7 +28400,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="337" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A337" s="18" t="s">
         <v>145</v>
       </c>
@@ -28419,7 +28418,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="338" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A338" s="18" t="s">
         <v>147</v>
       </c>
@@ -28437,7 +28436,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="339" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A339" s="18" t="s">
         <v>151</v>
       </c>
@@ -28455,7 +28454,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="340" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A340" s="16" t="s">
         <v>167</v>
       </c>
@@ -28479,7 +28478,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="341" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A341" s="11" t="s">
         <v>167</v>
       </c>
@@ -28502,7 +28501,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="342" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A342" s="11" t="s">
         <v>167</v>
       </c>
@@ -28525,7 +28524,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="343" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A343" s="18" t="s">
         <v>168</v>
       </c>
@@ -28543,7 +28542,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="344" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A344" s="18" t="s">
         <v>169</v>
       </c>
@@ -28561,7 +28560,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="345" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A345" s="18" t="s">
         <v>170</v>
       </c>
@@ -28579,7 +28578,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="346" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A346" s="18" t="s">
         <v>172</v>
       </c>
@@ -28597,7 +28596,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="347" spans="1:8" s="20" customFormat="1" ht="165" hidden="1" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:8" s="20" customFormat="1" ht="165" x14ac:dyDescent="0.25">
       <c r="A347" s="18" t="s">
         <v>174</v>
       </c>
@@ -28615,7 +28614,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="348" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A348" s="18" t="s">
         <v>176</v>
       </c>
@@ -28633,7 +28632,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="349" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A349" s="16" t="s">
         <v>178</v>
       </c>
@@ -28657,7 +28656,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="350" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A350" s="11" t="s">
         <v>178</v>
       </c>
@@ -28680,7 +28679,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="351" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A351" s="11" t="s">
         <v>178</v>
       </c>
@@ -28703,7 +28702,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="352" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A352" s="11" t="s">
         <v>178</v>
       </c>
@@ -28726,7 +28725,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="353" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A353" s="11" t="s">
         <v>178</v>
       </c>
@@ -28749,7 +28748,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="354" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A354" s="11" t="s">
         <v>178</v>
       </c>
@@ -28772,7 +28771,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="355" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A355" s="11" t="s">
         <v>178</v>
       </c>
@@ -28795,7 +28794,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="356" spans="1:9" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:9" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A356" s="16" t="s">
         <v>180</v>
       </c>
@@ -28813,7 +28812,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="357" spans="1:9" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:9" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A357" s="16" t="s">
         <v>182</v>
       </c>
@@ -28831,7 +28830,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="358" spans="1:9" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:9" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A358" s="18" t="s">
         <v>183</v>
       </c>
@@ -28855,7 +28854,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="359" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A359" s="4" t="s">
         <v>183</v>
       </c>
@@ -28878,7 +28877,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="360" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A360" s="4" t="s">
         <v>183</v>
       </c>
@@ -28901,7 +28900,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="361" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A361" s="4" t="s">
         <v>183</v>
       </c>
@@ -28927,7 +28926,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="362" spans="1:9" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:9" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A362" s="18" t="s">
         <v>651</v>
       </c>
@@ -28945,7 +28944,7 @@
         <v>847</v>
       </c>
     </row>
-    <row r="363" spans="1:9" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:9" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A363" s="18" t="s">
         <v>527</v>
       </c>
@@ -28963,7 +28962,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="364" spans="1:9" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:9" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A364" s="18" t="s">
         <v>185</v>
       </c>
@@ -28981,7 +28980,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="365" spans="1:9" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:9" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A365" s="18" t="s">
         <v>186</v>
       </c>
@@ -28999,7 +28998,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="366" spans="1:9" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:9" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A366" s="18" t="s">
         <v>191</v>
       </c>
@@ -29017,7 +29016,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="367" spans="1:9" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:9" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A367" s="16" t="s">
         <v>197</v>
       </c>
@@ -29041,7 +29040,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="368" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A368" s="11" t="s">
         <v>197</v>
       </c>
@@ -29064,7 +29063,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="369" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A369" s="11" t="s">
         <v>197</v>
       </c>
@@ -29087,7 +29086,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="370" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A370" s="11" t="s">
         <v>197</v>
       </c>
@@ -29110,7 +29109,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="371" spans="1:8" s="20" customFormat="1" ht="315" hidden="1" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:8" s="20" customFormat="1" ht="315" x14ac:dyDescent="0.25">
       <c r="A371" s="18" t="s">
         <v>199</v>
       </c>
@@ -29128,7 +29127,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="372" spans="1:8" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A372" s="18" t="s">
         <v>529</v>
       </c>
@@ -29147,13 +29146,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I372" xr:uid="{51D60DD1-DC0B-4658-A996-7DC0B41964ED}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="cod_text_1"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:I372" xr:uid="{51D60DD1-DC0B-4658-A996-7DC0B41964ED}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>